--- a/Templates/Tables/BlockInfo/BlockInfoTable.xlsx
+++ b/Templates/Tables/BlockInfo/BlockInfoTable.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>Name</t>
   </si>
@@ -23,6 +23,15 @@
   </si>
   <si>
     <t>NextBlockKinds</t>
+  </si>
+  <si>
+    <t>SizeX</t>
+  </si>
+  <si>
+    <t>SizeY</t>
+  </si>
+  <si>
+    <t>SizeZ</t>
   </si>
   <si>
     <t>Description</t>
@@ -79,12 +88,15 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -303,7 +315,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="7" width="14.43"/>
+    <col customWidth="1" min="1" max="10" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -319,12 +331,18 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -339,26 +357,35 @@
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1">
         <v>0.0</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="1">
         <v>-1.0</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>6</v>
+      <c r="E2" s="4">
+        <v>0.0</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
+      <c r="F2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -373,6 +400,9 @@
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1"/>
@@ -397,6 +427,9 @@
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1"/>
@@ -421,6 +454,9 @@
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
+      <c r="X4" s="1"/>
+      <c r="Y4" s="1"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1"/>
@@ -445,6 +481,9 @@
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
+      <c r="Y5" s="1"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1"/>
@@ -469,6 +508,9 @@
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1"/>
@@ -493,6 +535,9 @@
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="1"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1"/>
@@ -517,6 +562,9 @@
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
+      <c r="X8" s="1"/>
+      <c r="Y8" s="1"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="1"/>
@@ -541,6 +589,9 @@
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="1"/>
@@ -565,6 +616,9 @@
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1"/>
+      <c r="Y10" s="1"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="1"/>
@@ -589,6 +643,9 @@
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="1"/>
@@ -613,6 +670,9 @@
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
+      <c r="Y12" s="1"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="1"/>
@@ -637,6 +697,9 @@
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
+      <c r="X13" s="1"/>
+      <c r="Y13" s="1"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="1"/>
@@ -661,6 +724,9 @@
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
+      <c r="W14" s="1"/>
+      <c r="X14" s="1"/>
+      <c r="Y14" s="1"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="1"/>
@@ -685,6 +751,9 @@
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
+      <c r="W15" s="1"/>
+      <c r="X15" s="1"/>
+      <c r="Y15" s="1"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="1"/>
@@ -709,6 +778,9 @@
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
+      <c r="W16" s="1"/>
+      <c r="X16" s="1"/>
+      <c r="Y16" s="1"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="1"/>
@@ -733,6 +805,9 @@
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
+      <c r="W17" s="1"/>
+      <c r="X17" s="1"/>
+      <c r="Y17" s="1"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="1"/>
@@ -757,6 +832,9 @@
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
+      <c r="W18" s="1"/>
+      <c r="X18" s="1"/>
+      <c r="Y18" s="1"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="1"/>
@@ -781,6 +859,9 @@
       <c r="T19" s="1"/>
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
+      <c r="X19" s="1"/>
+      <c r="Y19" s="1"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="1"/>
@@ -805,6 +886,9 @@
       <c r="T20" s="1"/>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
+      <c r="W20" s="1"/>
+      <c r="X20" s="1"/>
+      <c r="Y20" s="1"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1"/>
@@ -829,6 +913,9 @@
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
+      <c r="W21" s="1"/>
+      <c r="X21" s="1"/>
+      <c r="Y21" s="1"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1"/>
@@ -853,6 +940,9 @@
       <c r="T22" s="1"/>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
+      <c r="W22" s="1"/>
+      <c r="X22" s="1"/>
+      <c r="Y22" s="1"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="1"/>
@@ -877,6 +967,9 @@
       <c r="T23" s="1"/>
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
+      <c r="W23" s="1"/>
+      <c r="X23" s="1"/>
+      <c r="Y23" s="1"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1"/>
@@ -901,6 +994,9 @@
       <c r="T24" s="1"/>
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
+      <c r="W24" s="1"/>
+      <c r="X24" s="1"/>
+      <c r="Y24" s="1"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="1"/>
@@ -925,6 +1021,9 @@
       <c r="T25" s="1"/>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
+      <c r="W25" s="1"/>
+      <c r="X25" s="1"/>
+      <c r="Y25" s="1"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="1"/>
@@ -949,6 +1048,9 @@
       <c r="T26" s="1"/>
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
+      <c r="X26" s="1"/>
+      <c r="Y26" s="1"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="1"/>
@@ -973,6 +1075,9 @@
       <c r="T27" s="1"/>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
+      <c r="W27" s="1"/>
+      <c r="X27" s="1"/>
+      <c r="Y27" s="1"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="1"/>
@@ -997,6 +1102,9 @@
       <c r="T28" s="1"/>
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
+      <c r="X28" s="1"/>
+      <c r="Y28" s="1"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="1"/>
@@ -1021,6 +1129,9 @@
       <c r="T29" s="1"/>
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
+      <c r="W29" s="1"/>
+      <c r="X29" s="1"/>
+      <c r="Y29" s="1"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="1"/>
@@ -1045,6 +1156,9 @@
       <c r="T30" s="1"/>
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
+      <c r="W30" s="1"/>
+      <c r="X30" s="1"/>
+      <c r="Y30" s="1"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="1"/>
@@ -1069,6 +1183,9 @@
       <c r="T31" s="1"/>
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
+      <c r="W31" s="1"/>
+      <c r="X31" s="1"/>
+      <c r="Y31" s="1"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="1"/>
@@ -1093,6 +1210,9 @@
       <c r="T32" s="1"/>
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
+      <c r="W32" s="1"/>
+      <c r="X32" s="1"/>
+      <c r="Y32" s="1"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="1"/>
@@ -1117,6 +1237,9 @@
       <c r="T33" s="1"/>
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
+      <c r="W33" s="1"/>
+      <c r="X33" s="1"/>
+      <c r="Y33" s="1"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="1"/>
@@ -1141,6 +1264,9 @@
       <c r="T34" s="1"/>
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
+      <c r="W34" s="1"/>
+      <c r="X34" s="1"/>
+      <c r="Y34" s="1"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="1"/>
@@ -1165,6 +1291,9 @@
       <c r="T35" s="1"/>
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
+      <c r="W35" s="1"/>
+      <c r="X35" s="1"/>
+      <c r="Y35" s="1"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="1"/>
@@ -1189,6 +1318,9 @@
       <c r="T36" s="1"/>
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
+      <c r="W36" s="1"/>
+      <c r="X36" s="1"/>
+      <c r="Y36" s="1"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="1"/>
@@ -1213,6 +1345,9 @@
       <c r="T37" s="1"/>
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
+      <c r="W37" s="1"/>
+      <c r="X37" s="1"/>
+      <c r="Y37" s="1"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="1"/>
@@ -1237,6 +1372,9 @@
       <c r="T38" s="1"/>
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
+      <c r="W38" s="1"/>
+      <c r="X38" s="1"/>
+      <c r="Y38" s="1"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="1"/>
@@ -1261,6 +1399,9 @@
       <c r="T39" s="1"/>
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
+      <c r="W39" s="1"/>
+      <c r="X39" s="1"/>
+      <c r="Y39" s="1"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="1"/>
@@ -1285,6 +1426,9 @@
       <c r="T40" s="1"/>
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
+      <c r="W40" s="1"/>
+      <c r="X40" s="1"/>
+      <c r="Y40" s="1"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="1"/>
@@ -1309,6 +1453,9 @@
       <c r="T41" s="1"/>
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
+      <c r="W41" s="1"/>
+      <c r="X41" s="1"/>
+      <c r="Y41" s="1"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="1"/>
@@ -1333,6 +1480,9 @@
       <c r="T42" s="1"/>
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
+      <c r="W42" s="1"/>
+      <c r="X42" s="1"/>
+      <c r="Y42" s="1"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="1"/>
@@ -1357,6 +1507,9 @@
       <c r="T43" s="1"/>
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
+      <c r="W43" s="1"/>
+      <c r="X43" s="1"/>
+      <c r="Y43" s="1"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="1"/>
@@ -1381,6 +1534,9 @@
       <c r="T44" s="1"/>
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
+      <c r="W44" s="1"/>
+      <c r="X44" s="1"/>
+      <c r="Y44" s="1"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="1"/>
@@ -1405,6 +1561,9 @@
       <c r="T45" s="1"/>
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
+      <c r="W45" s="1"/>
+      <c r="X45" s="1"/>
+      <c r="Y45" s="1"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="1"/>
@@ -1429,6 +1588,9 @@
       <c r="T46" s="1"/>
       <c r="U46" s="1"/>
       <c r="V46" s="1"/>
+      <c r="W46" s="1"/>
+      <c r="X46" s="1"/>
+      <c r="Y46" s="1"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="1"/>
@@ -1453,6 +1615,9 @@
       <c r="T47" s="1"/>
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
+      <c r="W47" s="1"/>
+      <c r="X47" s="1"/>
+      <c r="Y47" s="1"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="1"/>
@@ -1477,6 +1642,9 @@
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
+      <c r="W48" s="1"/>
+      <c r="X48" s="1"/>
+      <c r="Y48" s="1"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="1"/>
@@ -1501,6 +1669,9 @@
       <c r="T49" s="1"/>
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
+      <c r="W49" s="1"/>
+      <c r="X49" s="1"/>
+      <c r="Y49" s="1"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="1"/>
@@ -1525,6 +1696,9 @@
       <c r="T50" s="1"/>
       <c r="U50" s="1"/>
       <c r="V50" s="1"/>
+      <c r="W50" s="1"/>
+      <c r="X50" s="1"/>
+      <c r="Y50" s="1"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="1"/>
@@ -1549,6 +1723,9 @@
       <c r="T51" s="1"/>
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
+      <c r="W51" s="1"/>
+      <c r="X51" s="1"/>
+      <c r="Y51" s="1"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="1"/>
@@ -1573,6 +1750,9 @@
       <c r="T52" s="1"/>
       <c r="U52" s="1"/>
       <c r="V52" s="1"/>
+      <c r="W52" s="1"/>
+      <c r="X52" s="1"/>
+      <c r="Y52" s="1"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="1"/>
@@ -1597,6 +1777,9 @@
       <c r="T53" s="1"/>
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
+      <c r="W53" s="1"/>
+      <c r="X53" s="1"/>
+      <c r="Y53" s="1"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="1"/>
@@ -1621,6 +1804,9 @@
       <c r="T54" s="1"/>
       <c r="U54" s="1"/>
       <c r="V54" s="1"/>
+      <c r="W54" s="1"/>
+      <c r="X54" s="1"/>
+      <c r="Y54" s="1"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="1"/>
@@ -1645,6 +1831,9 @@
       <c r="T55" s="1"/>
       <c r="U55" s="1"/>
       <c r="V55" s="1"/>
+      <c r="W55" s="1"/>
+      <c r="X55" s="1"/>
+      <c r="Y55" s="1"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="1"/>
@@ -1669,6 +1858,9 @@
       <c r="T56" s="1"/>
       <c r="U56" s="1"/>
       <c r="V56" s="1"/>
+      <c r="W56" s="1"/>
+      <c r="X56" s="1"/>
+      <c r="Y56" s="1"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="1"/>
@@ -1693,6 +1885,9 @@
       <c r="T57" s="1"/>
       <c r="U57" s="1"/>
       <c r="V57" s="1"/>
+      <c r="W57" s="1"/>
+      <c r="X57" s="1"/>
+      <c r="Y57" s="1"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="1"/>
@@ -1717,6 +1912,9 @@
       <c r="T58" s="1"/>
       <c r="U58" s="1"/>
       <c r="V58" s="1"/>
+      <c r="W58" s="1"/>
+      <c r="X58" s="1"/>
+      <c r="Y58" s="1"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="1"/>
@@ -1741,6 +1939,9 @@
       <c r="T59" s="1"/>
       <c r="U59" s="1"/>
       <c r="V59" s="1"/>
+      <c r="W59" s="1"/>
+      <c r="X59" s="1"/>
+      <c r="Y59" s="1"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="1"/>
@@ -1765,6 +1966,9 @@
       <c r="T60" s="1"/>
       <c r="U60" s="1"/>
       <c r="V60" s="1"/>
+      <c r="W60" s="1"/>
+      <c r="X60" s="1"/>
+      <c r="Y60" s="1"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="1"/>
@@ -1789,6 +1993,9 @@
       <c r="T61" s="1"/>
       <c r="U61" s="1"/>
       <c r="V61" s="1"/>
+      <c r="W61" s="1"/>
+      <c r="X61" s="1"/>
+      <c r="Y61" s="1"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="1"/>
@@ -1813,6 +2020,9 @@
       <c r="T62" s="1"/>
       <c r="U62" s="1"/>
       <c r="V62" s="1"/>
+      <c r="W62" s="1"/>
+      <c r="X62" s="1"/>
+      <c r="Y62" s="1"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="1"/>
@@ -1837,6 +2047,9 @@
       <c r="T63" s="1"/>
       <c r="U63" s="1"/>
       <c r="V63" s="1"/>
+      <c r="W63" s="1"/>
+      <c r="X63" s="1"/>
+      <c r="Y63" s="1"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="1"/>
@@ -1861,6 +2074,9 @@
       <c r="T64" s="1"/>
       <c r="U64" s="1"/>
       <c r="V64" s="1"/>
+      <c r="W64" s="1"/>
+      <c r="X64" s="1"/>
+      <c r="Y64" s="1"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="1"/>
@@ -1885,6 +2101,9 @@
       <c r="T65" s="1"/>
       <c r="U65" s="1"/>
       <c r="V65" s="1"/>
+      <c r="W65" s="1"/>
+      <c r="X65" s="1"/>
+      <c r="Y65" s="1"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="1"/>
@@ -1909,6 +2128,9 @@
       <c r="T66" s="1"/>
       <c r="U66" s="1"/>
       <c r="V66" s="1"/>
+      <c r="W66" s="1"/>
+      <c r="X66" s="1"/>
+      <c r="Y66" s="1"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="1"/>
@@ -1933,6 +2155,9 @@
       <c r="T67" s="1"/>
       <c r="U67" s="1"/>
       <c r="V67" s="1"/>
+      <c r="W67" s="1"/>
+      <c r="X67" s="1"/>
+      <c r="Y67" s="1"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="1"/>
@@ -1957,6 +2182,9 @@
       <c r="T68" s="1"/>
       <c r="U68" s="1"/>
       <c r="V68" s="1"/>
+      <c r="W68" s="1"/>
+      <c r="X68" s="1"/>
+      <c r="Y68" s="1"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="1"/>
@@ -1981,6 +2209,9 @@
       <c r="T69" s="1"/>
       <c r="U69" s="1"/>
       <c r="V69" s="1"/>
+      <c r="W69" s="1"/>
+      <c r="X69" s="1"/>
+      <c r="Y69" s="1"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="1"/>
@@ -2005,6 +2236,9 @@
       <c r="T70" s="1"/>
       <c r="U70" s="1"/>
       <c r="V70" s="1"/>
+      <c r="W70" s="1"/>
+      <c r="X70" s="1"/>
+      <c r="Y70" s="1"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="1"/>
@@ -2029,6 +2263,9 @@
       <c r="T71" s="1"/>
       <c r="U71" s="1"/>
       <c r="V71" s="1"/>
+      <c r="W71" s="1"/>
+      <c r="X71" s="1"/>
+      <c r="Y71" s="1"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="1"/>
@@ -2053,6 +2290,9 @@
       <c r="T72" s="1"/>
       <c r="U72" s="1"/>
       <c r="V72" s="1"/>
+      <c r="W72" s="1"/>
+      <c r="X72" s="1"/>
+      <c r="Y72" s="1"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="1"/>
@@ -2077,6 +2317,9 @@
       <c r="T73" s="1"/>
       <c r="U73" s="1"/>
       <c r="V73" s="1"/>
+      <c r="W73" s="1"/>
+      <c r="X73" s="1"/>
+      <c r="Y73" s="1"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="1"/>
@@ -2101,6 +2344,9 @@
       <c r="T74" s="1"/>
       <c r="U74" s="1"/>
       <c r="V74" s="1"/>
+      <c r="W74" s="1"/>
+      <c r="X74" s="1"/>
+      <c r="Y74" s="1"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="1"/>
@@ -2125,6 +2371,9 @@
       <c r="T75" s="1"/>
       <c r="U75" s="1"/>
       <c r="V75" s="1"/>
+      <c r="W75" s="1"/>
+      <c r="X75" s="1"/>
+      <c r="Y75" s="1"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="1"/>
@@ -2149,6 +2398,9 @@
       <c r="T76" s="1"/>
       <c r="U76" s="1"/>
       <c r="V76" s="1"/>
+      <c r="W76" s="1"/>
+      <c r="X76" s="1"/>
+      <c r="Y76" s="1"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="1"/>
@@ -2173,6 +2425,9 @@
       <c r="T77" s="1"/>
       <c r="U77" s="1"/>
       <c r="V77" s="1"/>
+      <c r="W77" s="1"/>
+      <c r="X77" s="1"/>
+      <c r="Y77" s="1"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="1"/>
@@ -2197,6 +2452,9 @@
       <c r="T78" s="1"/>
       <c r="U78" s="1"/>
       <c r="V78" s="1"/>
+      <c r="W78" s="1"/>
+      <c r="X78" s="1"/>
+      <c r="Y78" s="1"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="1"/>
@@ -2221,6 +2479,9 @@
       <c r="T79" s="1"/>
       <c r="U79" s="1"/>
       <c r="V79" s="1"/>
+      <c r="W79" s="1"/>
+      <c r="X79" s="1"/>
+      <c r="Y79" s="1"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="1"/>
@@ -2245,6 +2506,9 @@
       <c r="T80" s="1"/>
       <c r="U80" s="1"/>
       <c r="V80" s="1"/>
+      <c r="W80" s="1"/>
+      <c r="X80" s="1"/>
+      <c r="Y80" s="1"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="1"/>
@@ -2269,6 +2533,9 @@
       <c r="T81" s="1"/>
       <c r="U81" s="1"/>
       <c r="V81" s="1"/>
+      <c r="W81" s="1"/>
+      <c r="X81" s="1"/>
+      <c r="Y81" s="1"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="1"/>
@@ -2293,6 +2560,9 @@
       <c r="T82" s="1"/>
       <c r="U82" s="1"/>
       <c r="V82" s="1"/>
+      <c r="W82" s="1"/>
+      <c r="X82" s="1"/>
+      <c r="Y82" s="1"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="1"/>
@@ -2317,6 +2587,9 @@
       <c r="T83" s="1"/>
       <c r="U83" s="1"/>
       <c r="V83" s="1"/>
+      <c r="W83" s="1"/>
+      <c r="X83" s="1"/>
+      <c r="Y83" s="1"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="1"/>
@@ -2341,6 +2614,9 @@
       <c r="T84" s="1"/>
       <c r="U84" s="1"/>
       <c r="V84" s="1"/>
+      <c r="W84" s="1"/>
+      <c r="X84" s="1"/>
+      <c r="Y84" s="1"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="1"/>
@@ -2365,6 +2641,9 @@
       <c r="T85" s="1"/>
       <c r="U85" s="1"/>
       <c r="V85" s="1"/>
+      <c r="W85" s="1"/>
+      <c r="X85" s="1"/>
+      <c r="Y85" s="1"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="1"/>
@@ -2389,6 +2668,9 @@
       <c r="T86" s="1"/>
       <c r="U86" s="1"/>
       <c r="V86" s="1"/>
+      <c r="W86" s="1"/>
+      <c r="X86" s="1"/>
+      <c r="Y86" s="1"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="1"/>
@@ -2413,6 +2695,9 @@
       <c r="T87" s="1"/>
       <c r="U87" s="1"/>
       <c r="V87" s="1"/>
+      <c r="W87" s="1"/>
+      <c r="X87" s="1"/>
+      <c r="Y87" s="1"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="1"/>
@@ -2437,6 +2722,9 @@
       <c r="T88" s="1"/>
       <c r="U88" s="1"/>
       <c r="V88" s="1"/>
+      <c r="W88" s="1"/>
+      <c r="X88" s="1"/>
+      <c r="Y88" s="1"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="1"/>
@@ -2461,6 +2749,9 @@
       <c r="T89" s="1"/>
       <c r="U89" s="1"/>
       <c r="V89" s="1"/>
+      <c r="W89" s="1"/>
+      <c r="X89" s="1"/>
+      <c r="Y89" s="1"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="1"/>
@@ -2485,6 +2776,9 @@
       <c r="T90" s="1"/>
       <c r="U90" s="1"/>
       <c r="V90" s="1"/>
+      <c r="W90" s="1"/>
+      <c r="X90" s="1"/>
+      <c r="Y90" s="1"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="1"/>
@@ -2509,6 +2803,9 @@
       <c r="T91" s="1"/>
       <c r="U91" s="1"/>
       <c r="V91" s="1"/>
+      <c r="W91" s="1"/>
+      <c r="X91" s="1"/>
+      <c r="Y91" s="1"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="1"/>
@@ -2533,6 +2830,9 @@
       <c r="T92" s="1"/>
       <c r="U92" s="1"/>
       <c r="V92" s="1"/>
+      <c r="W92" s="1"/>
+      <c r="X92" s="1"/>
+      <c r="Y92" s="1"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="1"/>
@@ -2557,6 +2857,9 @@
       <c r="T93" s="1"/>
       <c r="U93" s="1"/>
       <c r="V93" s="1"/>
+      <c r="W93" s="1"/>
+      <c r="X93" s="1"/>
+      <c r="Y93" s="1"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="1"/>
@@ -2581,6 +2884,9 @@
       <c r="T94" s="1"/>
       <c r="U94" s="1"/>
       <c r="V94" s="1"/>
+      <c r="W94" s="1"/>
+      <c r="X94" s="1"/>
+      <c r="Y94" s="1"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="1"/>
@@ -2605,6 +2911,9 @@
       <c r="T95" s="1"/>
       <c r="U95" s="1"/>
       <c r="V95" s="1"/>
+      <c r="W95" s="1"/>
+      <c r="X95" s="1"/>
+      <c r="Y95" s="1"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="1"/>
@@ -2629,6 +2938,9 @@
       <c r="T96" s="1"/>
       <c r="U96" s="1"/>
       <c r="V96" s="1"/>
+      <c r="W96" s="1"/>
+      <c r="X96" s="1"/>
+      <c r="Y96" s="1"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="1"/>
@@ -2653,6 +2965,9 @@
       <c r="T97" s="1"/>
       <c r="U97" s="1"/>
       <c r="V97" s="1"/>
+      <c r="W97" s="1"/>
+      <c r="X97" s="1"/>
+      <c r="Y97" s="1"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="1"/>
@@ -2677,6 +2992,9 @@
       <c r="T98" s="1"/>
       <c r="U98" s="1"/>
       <c r="V98" s="1"/>
+      <c r="W98" s="1"/>
+      <c r="X98" s="1"/>
+      <c r="Y98" s="1"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="1"/>
@@ -2701,6 +3019,9 @@
       <c r="T99" s="1"/>
       <c r="U99" s="1"/>
       <c r="V99" s="1"/>
+      <c r="W99" s="1"/>
+      <c r="X99" s="1"/>
+      <c r="Y99" s="1"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="1"/>
@@ -2725,6 +3046,9 @@
       <c r="T100" s="1"/>
       <c r="U100" s="1"/>
       <c r="V100" s="1"/>
+      <c r="W100" s="1"/>
+      <c r="X100" s="1"/>
+      <c r="Y100" s="1"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="1"/>
@@ -2749,6 +3073,9 @@
       <c r="T101" s="1"/>
       <c r="U101" s="1"/>
       <c r="V101" s="1"/>
+      <c r="W101" s="1"/>
+      <c r="X101" s="1"/>
+      <c r="Y101" s="1"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="1"/>
@@ -2773,6 +3100,9 @@
       <c r="T102" s="1"/>
       <c r="U102" s="1"/>
       <c r="V102" s="1"/>
+      <c r="W102" s="1"/>
+      <c r="X102" s="1"/>
+      <c r="Y102" s="1"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="1"/>
@@ -2797,6 +3127,9 @@
       <c r="T103" s="1"/>
       <c r="U103" s="1"/>
       <c r="V103" s="1"/>
+      <c r="W103" s="1"/>
+      <c r="X103" s="1"/>
+      <c r="Y103" s="1"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="1"/>
@@ -2821,6 +3154,9 @@
       <c r="T104" s="1"/>
       <c r="U104" s="1"/>
       <c r="V104" s="1"/>
+      <c r="W104" s="1"/>
+      <c r="X104" s="1"/>
+      <c r="Y104" s="1"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="1"/>
@@ -2845,6 +3181,9 @@
       <c r="T105" s="1"/>
       <c r="U105" s="1"/>
       <c r="V105" s="1"/>
+      <c r="W105" s="1"/>
+      <c r="X105" s="1"/>
+      <c r="Y105" s="1"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="1"/>
@@ -2869,6 +3208,9 @@
       <c r="T106" s="1"/>
       <c r="U106" s="1"/>
       <c r="V106" s="1"/>
+      <c r="W106" s="1"/>
+      <c r="X106" s="1"/>
+      <c r="Y106" s="1"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="1"/>
@@ -2893,6 +3235,9 @@
       <c r="T107" s="1"/>
       <c r="U107" s="1"/>
       <c r="V107" s="1"/>
+      <c r="W107" s="1"/>
+      <c r="X107" s="1"/>
+      <c r="Y107" s="1"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="1"/>
@@ -2917,6 +3262,9 @@
       <c r="T108" s="1"/>
       <c r="U108" s="1"/>
       <c r="V108" s="1"/>
+      <c r="W108" s="1"/>
+      <c r="X108" s="1"/>
+      <c r="Y108" s="1"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="1"/>
@@ -2941,6 +3289,9 @@
       <c r="T109" s="1"/>
       <c r="U109" s="1"/>
       <c r="V109" s="1"/>
+      <c r="W109" s="1"/>
+      <c r="X109" s="1"/>
+      <c r="Y109" s="1"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="1"/>
@@ -2965,6 +3316,9 @@
       <c r="T110" s="1"/>
       <c r="U110" s="1"/>
       <c r="V110" s="1"/>
+      <c r="W110" s="1"/>
+      <c r="X110" s="1"/>
+      <c r="Y110" s="1"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="1"/>
@@ -2989,6 +3343,9 @@
       <c r="T111" s="1"/>
       <c r="U111" s="1"/>
       <c r="V111" s="1"/>
+      <c r="W111" s="1"/>
+      <c r="X111" s="1"/>
+      <c r="Y111" s="1"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="1"/>
@@ -3013,6 +3370,9 @@
       <c r="T112" s="1"/>
       <c r="U112" s="1"/>
       <c r="V112" s="1"/>
+      <c r="W112" s="1"/>
+      <c r="X112" s="1"/>
+      <c r="Y112" s="1"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="1"/>
@@ -3037,6 +3397,9 @@
       <c r="T113" s="1"/>
       <c r="U113" s="1"/>
       <c r="V113" s="1"/>
+      <c r="W113" s="1"/>
+      <c r="X113" s="1"/>
+      <c r="Y113" s="1"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="1"/>
@@ -3061,6 +3424,9 @@
       <c r="T114" s="1"/>
       <c r="U114" s="1"/>
       <c r="V114" s="1"/>
+      <c r="W114" s="1"/>
+      <c r="X114" s="1"/>
+      <c r="Y114" s="1"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="1"/>
@@ -3085,6 +3451,9 @@
       <c r="T115" s="1"/>
       <c r="U115" s="1"/>
       <c r="V115" s="1"/>
+      <c r="W115" s="1"/>
+      <c r="X115" s="1"/>
+      <c r="Y115" s="1"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="1"/>
@@ -3109,6 +3478,9 @@
       <c r="T116" s="1"/>
       <c r="U116" s="1"/>
       <c r="V116" s="1"/>
+      <c r="W116" s="1"/>
+      <c r="X116" s="1"/>
+      <c r="Y116" s="1"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="1"/>
@@ -3133,6 +3505,9 @@
       <c r="T117" s="1"/>
       <c r="U117" s="1"/>
       <c r="V117" s="1"/>
+      <c r="W117" s="1"/>
+      <c r="X117" s="1"/>
+      <c r="Y117" s="1"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="1"/>
@@ -3157,6 +3532,9 @@
       <c r="T118" s="1"/>
       <c r="U118" s="1"/>
       <c r="V118" s="1"/>
+      <c r="W118" s="1"/>
+      <c r="X118" s="1"/>
+      <c r="Y118" s="1"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="1"/>
@@ -3181,6 +3559,9 @@
       <c r="T119" s="1"/>
       <c r="U119" s="1"/>
       <c r="V119" s="1"/>
+      <c r="W119" s="1"/>
+      <c r="X119" s="1"/>
+      <c r="Y119" s="1"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="1"/>
@@ -3205,6 +3586,9 @@
       <c r="T120" s="1"/>
       <c r="U120" s="1"/>
       <c r="V120" s="1"/>
+      <c r="W120" s="1"/>
+      <c r="X120" s="1"/>
+      <c r="Y120" s="1"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="1"/>
@@ -3229,6 +3613,9 @@
       <c r="T121" s="1"/>
       <c r="U121" s="1"/>
       <c r="V121" s="1"/>
+      <c r="W121" s="1"/>
+      <c r="X121" s="1"/>
+      <c r="Y121" s="1"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="1"/>
@@ -3253,6 +3640,9 @@
       <c r="T122" s="1"/>
       <c r="U122" s="1"/>
       <c r="V122" s="1"/>
+      <c r="W122" s="1"/>
+      <c r="X122" s="1"/>
+      <c r="Y122" s="1"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="1"/>
@@ -3277,6 +3667,9 @@
       <c r="T123" s="1"/>
       <c r="U123" s="1"/>
       <c r="V123" s="1"/>
+      <c r="W123" s="1"/>
+      <c r="X123" s="1"/>
+      <c r="Y123" s="1"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="1"/>
@@ -3301,6 +3694,9 @@
       <c r="T124" s="1"/>
       <c r="U124" s="1"/>
       <c r="V124" s="1"/>
+      <c r="W124" s="1"/>
+      <c r="X124" s="1"/>
+      <c r="Y124" s="1"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="1"/>
@@ -3325,6 +3721,9 @@
       <c r="T125" s="1"/>
       <c r="U125" s="1"/>
       <c r="V125" s="1"/>
+      <c r="W125" s="1"/>
+      <c r="X125" s="1"/>
+      <c r="Y125" s="1"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="1"/>
@@ -3349,6 +3748,9 @@
       <c r="T126" s="1"/>
       <c r="U126" s="1"/>
       <c r="V126" s="1"/>
+      <c r="W126" s="1"/>
+      <c r="X126" s="1"/>
+      <c r="Y126" s="1"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="1"/>
@@ -3373,6 +3775,9 @@
       <c r="T127" s="1"/>
       <c r="U127" s="1"/>
       <c r="V127" s="1"/>
+      <c r="W127" s="1"/>
+      <c r="X127" s="1"/>
+      <c r="Y127" s="1"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="1"/>
@@ -3397,6 +3802,9 @@
       <c r="T128" s="1"/>
       <c r="U128" s="1"/>
       <c r="V128" s="1"/>
+      <c r="W128" s="1"/>
+      <c r="X128" s="1"/>
+      <c r="Y128" s="1"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="1"/>
@@ -3421,6 +3829,9 @@
       <c r="T129" s="1"/>
       <c r="U129" s="1"/>
       <c r="V129" s="1"/>
+      <c r="W129" s="1"/>
+      <c r="X129" s="1"/>
+      <c r="Y129" s="1"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="1"/>
@@ -3445,6 +3856,9 @@
       <c r="T130" s="1"/>
       <c r="U130" s="1"/>
       <c r="V130" s="1"/>
+      <c r="W130" s="1"/>
+      <c r="X130" s="1"/>
+      <c r="Y130" s="1"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="1"/>
@@ -3469,6 +3883,9 @@
       <c r="T131" s="1"/>
       <c r="U131" s="1"/>
       <c r="V131" s="1"/>
+      <c r="W131" s="1"/>
+      <c r="X131" s="1"/>
+      <c r="Y131" s="1"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="1"/>
@@ -3493,6 +3910,9 @@
       <c r="T132" s="1"/>
       <c r="U132" s="1"/>
       <c r="V132" s="1"/>
+      <c r="W132" s="1"/>
+      <c r="X132" s="1"/>
+      <c r="Y132" s="1"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="1"/>
@@ -3517,6 +3937,9 @@
       <c r="T133" s="1"/>
       <c r="U133" s="1"/>
       <c r="V133" s="1"/>
+      <c r="W133" s="1"/>
+      <c r="X133" s="1"/>
+      <c r="Y133" s="1"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="1"/>
@@ -3541,6 +3964,9 @@
       <c r="T134" s="1"/>
       <c r="U134" s="1"/>
       <c r="V134" s="1"/>
+      <c r="W134" s="1"/>
+      <c r="X134" s="1"/>
+      <c r="Y134" s="1"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="1"/>
@@ -3565,6 +3991,9 @@
       <c r="T135" s="1"/>
       <c r="U135" s="1"/>
       <c r="V135" s="1"/>
+      <c r="W135" s="1"/>
+      <c r="X135" s="1"/>
+      <c r="Y135" s="1"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="1"/>
@@ -3589,6 +4018,9 @@
       <c r="T136" s="1"/>
       <c r="U136" s="1"/>
       <c r="V136" s="1"/>
+      <c r="W136" s="1"/>
+      <c r="X136" s="1"/>
+      <c r="Y136" s="1"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="1"/>
@@ -3613,6 +4045,9 @@
       <c r="T137" s="1"/>
       <c r="U137" s="1"/>
       <c r="V137" s="1"/>
+      <c r="W137" s="1"/>
+      <c r="X137" s="1"/>
+      <c r="Y137" s="1"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="1"/>
@@ -3637,6 +4072,9 @@
       <c r="T138" s="1"/>
       <c r="U138" s="1"/>
       <c r="V138" s="1"/>
+      <c r="W138" s="1"/>
+      <c r="X138" s="1"/>
+      <c r="Y138" s="1"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="1"/>
@@ -3661,6 +4099,9 @@
       <c r="T139" s="1"/>
       <c r="U139" s="1"/>
       <c r="V139" s="1"/>
+      <c r="W139" s="1"/>
+      <c r="X139" s="1"/>
+      <c r="Y139" s="1"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="1"/>
@@ -3685,6 +4126,9 @@
       <c r="T140" s="1"/>
       <c r="U140" s="1"/>
       <c r="V140" s="1"/>
+      <c r="W140" s="1"/>
+      <c r="X140" s="1"/>
+      <c r="Y140" s="1"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="1"/>
@@ -3709,6 +4153,9 @@
       <c r="T141" s="1"/>
       <c r="U141" s="1"/>
       <c r="V141" s="1"/>
+      <c r="W141" s="1"/>
+      <c r="X141" s="1"/>
+      <c r="Y141" s="1"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="1"/>
@@ -3733,6 +4180,9 @@
       <c r="T142" s="1"/>
       <c r="U142" s="1"/>
       <c r="V142" s="1"/>
+      <c r="W142" s="1"/>
+      <c r="X142" s="1"/>
+      <c r="Y142" s="1"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="1"/>
@@ -3757,6 +4207,9 @@
       <c r="T143" s="1"/>
       <c r="U143" s="1"/>
       <c r="V143" s="1"/>
+      <c r="W143" s="1"/>
+      <c r="X143" s="1"/>
+      <c r="Y143" s="1"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="1"/>
@@ -3781,6 +4234,9 @@
       <c r="T144" s="1"/>
       <c r="U144" s="1"/>
       <c r="V144" s="1"/>
+      <c r="W144" s="1"/>
+      <c r="X144" s="1"/>
+      <c r="Y144" s="1"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="1"/>
@@ -3805,6 +4261,9 @@
       <c r="T145" s="1"/>
       <c r="U145" s="1"/>
       <c r="V145" s="1"/>
+      <c r="W145" s="1"/>
+      <c r="X145" s="1"/>
+      <c r="Y145" s="1"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="1"/>
@@ -3829,6 +4288,9 @@
       <c r="T146" s="1"/>
       <c r="U146" s="1"/>
       <c r="V146" s="1"/>
+      <c r="W146" s="1"/>
+      <c r="X146" s="1"/>
+      <c r="Y146" s="1"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="1"/>
@@ -3853,6 +4315,9 @@
       <c r="T147" s="1"/>
       <c r="U147" s="1"/>
       <c r="V147" s="1"/>
+      <c r="W147" s="1"/>
+      <c r="X147" s="1"/>
+      <c r="Y147" s="1"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="1"/>
@@ -3877,6 +4342,9 @@
       <c r="T148" s="1"/>
       <c r="U148" s="1"/>
       <c r="V148" s="1"/>
+      <c r="W148" s="1"/>
+      <c r="X148" s="1"/>
+      <c r="Y148" s="1"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="1"/>
@@ -3901,6 +4369,9 @@
       <c r="T149" s="1"/>
       <c r="U149" s="1"/>
       <c r="V149" s="1"/>
+      <c r="W149" s="1"/>
+      <c r="X149" s="1"/>
+      <c r="Y149" s="1"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="1"/>
@@ -3925,6 +4396,9 @@
       <c r="T150" s="1"/>
       <c r="U150" s="1"/>
       <c r="V150" s="1"/>
+      <c r="W150" s="1"/>
+      <c r="X150" s="1"/>
+      <c r="Y150" s="1"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="1"/>
@@ -3949,6 +4423,9 @@
       <c r="T151" s="1"/>
       <c r="U151" s="1"/>
       <c r="V151" s="1"/>
+      <c r="W151" s="1"/>
+      <c r="X151" s="1"/>
+      <c r="Y151" s="1"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="1"/>
@@ -3973,6 +4450,9 @@
       <c r="T152" s="1"/>
       <c r="U152" s="1"/>
       <c r="V152" s="1"/>
+      <c r="W152" s="1"/>
+      <c r="X152" s="1"/>
+      <c r="Y152" s="1"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="1"/>
@@ -3997,6 +4477,9 @@
       <c r="T153" s="1"/>
       <c r="U153" s="1"/>
       <c r="V153" s="1"/>
+      <c r="W153" s="1"/>
+      <c r="X153" s="1"/>
+      <c r="Y153" s="1"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="1"/>
@@ -4021,6 +4504,9 @@
       <c r="T154" s="1"/>
       <c r="U154" s="1"/>
       <c r="V154" s="1"/>
+      <c r="W154" s="1"/>
+      <c r="X154" s="1"/>
+      <c r="Y154" s="1"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="1"/>
@@ -4045,6 +4531,9 @@
       <c r="T155" s="1"/>
       <c r="U155" s="1"/>
       <c r="V155" s="1"/>
+      <c r="W155" s="1"/>
+      <c r="X155" s="1"/>
+      <c r="Y155" s="1"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="1"/>
@@ -4069,6 +4558,9 @@
       <c r="T156" s="1"/>
       <c r="U156" s="1"/>
       <c r="V156" s="1"/>
+      <c r="W156" s="1"/>
+      <c r="X156" s="1"/>
+      <c r="Y156" s="1"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="1"/>
@@ -4093,6 +4585,9 @@
       <c r="T157" s="1"/>
       <c r="U157" s="1"/>
       <c r="V157" s="1"/>
+      <c r="W157" s="1"/>
+      <c r="X157" s="1"/>
+      <c r="Y157" s="1"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="1"/>
@@ -4117,6 +4612,9 @@
       <c r="T158" s="1"/>
       <c r="U158" s="1"/>
       <c r="V158" s="1"/>
+      <c r="W158" s="1"/>
+      <c r="X158" s="1"/>
+      <c r="Y158" s="1"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="1"/>
@@ -4141,6 +4639,9 @@
       <c r="T159" s="1"/>
       <c r="U159" s="1"/>
       <c r="V159" s="1"/>
+      <c r="W159" s="1"/>
+      <c r="X159" s="1"/>
+      <c r="Y159" s="1"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="1"/>
@@ -4165,6 +4666,9 @@
       <c r="T160" s="1"/>
       <c r="U160" s="1"/>
       <c r="V160" s="1"/>
+      <c r="W160" s="1"/>
+      <c r="X160" s="1"/>
+      <c r="Y160" s="1"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="1"/>
@@ -4189,6 +4693,9 @@
       <c r="T161" s="1"/>
       <c r="U161" s="1"/>
       <c r="V161" s="1"/>
+      <c r="W161" s="1"/>
+      <c r="X161" s="1"/>
+      <c r="Y161" s="1"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="1"/>
@@ -4213,6 +4720,9 @@
       <c r="T162" s="1"/>
       <c r="U162" s="1"/>
       <c r="V162" s="1"/>
+      <c r="W162" s="1"/>
+      <c r="X162" s="1"/>
+      <c r="Y162" s="1"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="1"/>
@@ -4237,6 +4747,9 @@
       <c r="T163" s="1"/>
       <c r="U163" s="1"/>
       <c r="V163" s="1"/>
+      <c r="W163" s="1"/>
+      <c r="X163" s="1"/>
+      <c r="Y163" s="1"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="1"/>
@@ -4261,6 +4774,9 @@
       <c r="T164" s="1"/>
       <c r="U164" s="1"/>
       <c r="V164" s="1"/>
+      <c r="W164" s="1"/>
+      <c r="X164" s="1"/>
+      <c r="Y164" s="1"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="1"/>
@@ -4285,6 +4801,9 @@
       <c r="T165" s="1"/>
       <c r="U165" s="1"/>
       <c r="V165" s="1"/>
+      <c r="W165" s="1"/>
+      <c r="X165" s="1"/>
+      <c r="Y165" s="1"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="1"/>
@@ -4309,6 +4828,9 @@
       <c r="T166" s="1"/>
       <c r="U166" s="1"/>
       <c r="V166" s="1"/>
+      <c r="W166" s="1"/>
+      <c r="X166" s="1"/>
+      <c r="Y166" s="1"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="1"/>
@@ -4333,6 +4855,9 @@
       <c r="T167" s="1"/>
       <c r="U167" s="1"/>
       <c r="V167" s="1"/>
+      <c r="W167" s="1"/>
+      <c r="X167" s="1"/>
+      <c r="Y167" s="1"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="1"/>
@@ -4357,6 +4882,9 @@
       <c r="T168" s="1"/>
       <c r="U168" s="1"/>
       <c r="V168" s="1"/>
+      <c r="W168" s="1"/>
+      <c r="X168" s="1"/>
+      <c r="Y168" s="1"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="1"/>
@@ -4381,6 +4909,9 @@
       <c r="T169" s="1"/>
       <c r="U169" s="1"/>
       <c r="V169" s="1"/>
+      <c r="W169" s="1"/>
+      <c r="X169" s="1"/>
+      <c r="Y169" s="1"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="1"/>
@@ -4405,6 +4936,9 @@
       <c r="T170" s="1"/>
       <c r="U170" s="1"/>
       <c r="V170" s="1"/>
+      <c r="W170" s="1"/>
+      <c r="X170" s="1"/>
+      <c r="Y170" s="1"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="1"/>
@@ -4429,6 +4963,9 @@
       <c r="T171" s="1"/>
       <c r="U171" s="1"/>
       <c r="V171" s="1"/>
+      <c r="W171" s="1"/>
+      <c r="X171" s="1"/>
+      <c r="Y171" s="1"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="1"/>
@@ -4453,6 +4990,9 @@
       <c r="T172" s="1"/>
       <c r="U172" s="1"/>
       <c r="V172" s="1"/>
+      <c r="W172" s="1"/>
+      <c r="X172" s="1"/>
+      <c r="Y172" s="1"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="1"/>
@@ -4477,6 +5017,9 @@
       <c r="T173" s="1"/>
       <c r="U173" s="1"/>
       <c r="V173" s="1"/>
+      <c r="W173" s="1"/>
+      <c r="X173" s="1"/>
+      <c r="Y173" s="1"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="1"/>
@@ -4501,6 +5044,9 @@
       <c r="T174" s="1"/>
       <c r="U174" s="1"/>
       <c r="V174" s="1"/>
+      <c r="W174" s="1"/>
+      <c r="X174" s="1"/>
+      <c r="Y174" s="1"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="1"/>
@@ -4525,6 +5071,9 @@
       <c r="T175" s="1"/>
       <c r="U175" s="1"/>
       <c r="V175" s="1"/>
+      <c r="W175" s="1"/>
+      <c r="X175" s="1"/>
+      <c r="Y175" s="1"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="1"/>
@@ -4549,6 +5098,9 @@
       <c r="T176" s="1"/>
       <c r="U176" s="1"/>
       <c r="V176" s="1"/>
+      <c r="W176" s="1"/>
+      <c r="X176" s="1"/>
+      <c r="Y176" s="1"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="1"/>
@@ -4573,6 +5125,9 @@
       <c r="T177" s="1"/>
       <c r="U177" s="1"/>
       <c r="V177" s="1"/>
+      <c r="W177" s="1"/>
+      <c r="X177" s="1"/>
+      <c r="Y177" s="1"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="1"/>
@@ -4597,6 +5152,9 @@
       <c r="T178" s="1"/>
       <c r="U178" s="1"/>
       <c r="V178" s="1"/>
+      <c r="W178" s="1"/>
+      <c r="X178" s="1"/>
+      <c r="Y178" s="1"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="1"/>
@@ -4621,6 +5179,9 @@
       <c r="T179" s="1"/>
       <c r="U179" s="1"/>
       <c r="V179" s="1"/>
+      <c r="W179" s="1"/>
+      <c r="X179" s="1"/>
+      <c r="Y179" s="1"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="1"/>
@@ -4645,6 +5206,9 @@
       <c r="T180" s="1"/>
       <c r="U180" s="1"/>
       <c r="V180" s="1"/>
+      <c r="W180" s="1"/>
+      <c r="X180" s="1"/>
+      <c r="Y180" s="1"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="1"/>
@@ -4669,6 +5233,9 @@
       <c r="T181" s="1"/>
       <c r="U181" s="1"/>
       <c r="V181" s="1"/>
+      <c r="W181" s="1"/>
+      <c r="X181" s="1"/>
+      <c r="Y181" s="1"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="1"/>
@@ -4693,6 +5260,9 @@
       <c r="T182" s="1"/>
       <c r="U182" s="1"/>
       <c r="V182" s="1"/>
+      <c r="W182" s="1"/>
+      <c r="X182" s="1"/>
+      <c r="Y182" s="1"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="1"/>
@@ -4717,6 +5287,9 @@
       <c r="T183" s="1"/>
       <c r="U183" s="1"/>
       <c r="V183" s="1"/>
+      <c r="W183" s="1"/>
+      <c r="X183" s="1"/>
+      <c r="Y183" s="1"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="1"/>
@@ -4741,6 +5314,9 @@
       <c r="T184" s="1"/>
       <c r="U184" s="1"/>
       <c r="V184" s="1"/>
+      <c r="W184" s="1"/>
+      <c r="X184" s="1"/>
+      <c r="Y184" s="1"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="1"/>
@@ -4765,6 +5341,9 @@
       <c r="T185" s="1"/>
       <c r="U185" s="1"/>
       <c r="V185" s="1"/>
+      <c r="W185" s="1"/>
+      <c r="X185" s="1"/>
+      <c r="Y185" s="1"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="1"/>
@@ -4789,6 +5368,9 @@
       <c r="T186" s="1"/>
       <c r="U186" s="1"/>
       <c r="V186" s="1"/>
+      <c r="W186" s="1"/>
+      <c r="X186" s="1"/>
+      <c r="Y186" s="1"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="1"/>
@@ -4813,6 +5395,9 @@
       <c r="T187" s="1"/>
       <c r="U187" s="1"/>
       <c r="V187" s="1"/>
+      <c r="W187" s="1"/>
+      <c r="X187" s="1"/>
+      <c r="Y187" s="1"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="1"/>
@@ -4837,6 +5422,9 @@
       <c r="T188" s="1"/>
       <c r="U188" s="1"/>
       <c r="V188" s="1"/>
+      <c r="W188" s="1"/>
+      <c r="X188" s="1"/>
+      <c r="Y188" s="1"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="1"/>
@@ -4861,6 +5449,9 @@
       <c r="T189" s="1"/>
       <c r="U189" s="1"/>
       <c r="V189" s="1"/>
+      <c r="W189" s="1"/>
+      <c r="X189" s="1"/>
+      <c r="Y189" s="1"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="1"/>
@@ -4885,6 +5476,9 @@
       <c r="T190" s="1"/>
       <c r="U190" s="1"/>
       <c r="V190" s="1"/>
+      <c r="W190" s="1"/>
+      <c r="X190" s="1"/>
+      <c r="Y190" s="1"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="1"/>
@@ -4909,6 +5503,9 @@
       <c r="T191" s="1"/>
       <c r="U191" s="1"/>
       <c r="V191" s="1"/>
+      <c r="W191" s="1"/>
+      <c r="X191" s="1"/>
+      <c r="Y191" s="1"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="1"/>
@@ -4933,6 +5530,9 @@
       <c r="T192" s="1"/>
       <c r="U192" s="1"/>
       <c r="V192" s="1"/>
+      <c r="W192" s="1"/>
+      <c r="X192" s="1"/>
+      <c r="Y192" s="1"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="1"/>
@@ -4957,6 +5557,9 @@
       <c r="T193" s="1"/>
       <c r="U193" s="1"/>
       <c r="V193" s="1"/>
+      <c r="W193" s="1"/>
+      <c r="X193" s="1"/>
+      <c r="Y193" s="1"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="1"/>
@@ -4981,6 +5584,9 @@
       <c r="T194" s="1"/>
       <c r="U194" s="1"/>
       <c r="V194" s="1"/>
+      <c r="W194" s="1"/>
+      <c r="X194" s="1"/>
+      <c r="Y194" s="1"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="1"/>
@@ -5005,6 +5611,9 @@
       <c r="T195" s="1"/>
       <c r="U195" s="1"/>
       <c r="V195" s="1"/>
+      <c r="W195" s="1"/>
+      <c r="X195" s="1"/>
+      <c r="Y195" s="1"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="1"/>
@@ -5029,6 +5638,9 @@
       <c r="T196" s="1"/>
       <c r="U196" s="1"/>
       <c r="V196" s="1"/>
+      <c r="W196" s="1"/>
+      <c r="X196" s="1"/>
+      <c r="Y196" s="1"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="1"/>
@@ -5053,6 +5665,9 @@
       <c r="T197" s="1"/>
       <c r="U197" s="1"/>
       <c r="V197" s="1"/>
+      <c r="W197" s="1"/>
+      <c r="X197" s="1"/>
+      <c r="Y197" s="1"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="1"/>
@@ -5077,6 +5692,9 @@
       <c r="T198" s="1"/>
       <c r="U198" s="1"/>
       <c r="V198" s="1"/>
+      <c r="W198" s="1"/>
+      <c r="X198" s="1"/>
+      <c r="Y198" s="1"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="1"/>
@@ -5101,6 +5719,9 @@
       <c r="T199" s="1"/>
       <c r="U199" s="1"/>
       <c r="V199" s="1"/>
+      <c r="W199" s="1"/>
+      <c r="X199" s="1"/>
+      <c r="Y199" s="1"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="1"/>
@@ -5125,6 +5746,9 @@
       <c r="T200" s="1"/>
       <c r="U200" s="1"/>
       <c r="V200" s="1"/>
+      <c r="W200" s="1"/>
+      <c r="X200" s="1"/>
+      <c r="Y200" s="1"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="1"/>
@@ -5149,6 +5773,9 @@
       <c r="T201" s="1"/>
       <c r="U201" s="1"/>
       <c r="V201" s="1"/>
+      <c r="W201" s="1"/>
+      <c r="X201" s="1"/>
+      <c r="Y201" s="1"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="1"/>
@@ -5173,6 +5800,9 @@
       <c r="T202" s="1"/>
       <c r="U202" s="1"/>
       <c r="V202" s="1"/>
+      <c r="W202" s="1"/>
+      <c r="X202" s="1"/>
+      <c r="Y202" s="1"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="1"/>
@@ -5197,6 +5827,9 @@
       <c r="T203" s="1"/>
       <c r="U203" s="1"/>
       <c r="V203" s="1"/>
+      <c r="W203" s="1"/>
+      <c r="X203" s="1"/>
+      <c r="Y203" s="1"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="1"/>
@@ -5221,6 +5854,9 @@
       <c r="T204" s="1"/>
       <c r="U204" s="1"/>
       <c r="V204" s="1"/>
+      <c r="W204" s="1"/>
+      <c r="X204" s="1"/>
+      <c r="Y204" s="1"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="1"/>
@@ -5245,6 +5881,9 @@
       <c r="T205" s="1"/>
       <c r="U205" s="1"/>
       <c r="V205" s="1"/>
+      <c r="W205" s="1"/>
+      <c r="X205" s="1"/>
+      <c r="Y205" s="1"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="1"/>
@@ -5269,6 +5908,9 @@
       <c r="T206" s="1"/>
       <c r="U206" s="1"/>
       <c r="V206" s="1"/>
+      <c r="W206" s="1"/>
+      <c r="X206" s="1"/>
+      <c r="Y206" s="1"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="1"/>
@@ -5293,6 +5935,9 @@
       <c r="T207" s="1"/>
       <c r="U207" s="1"/>
       <c r="V207" s="1"/>
+      <c r="W207" s="1"/>
+      <c r="X207" s="1"/>
+      <c r="Y207" s="1"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="1"/>
@@ -5317,6 +5962,9 @@
       <c r="T208" s="1"/>
       <c r="U208" s="1"/>
       <c r="V208" s="1"/>
+      <c r="W208" s="1"/>
+      <c r="X208" s="1"/>
+      <c r="Y208" s="1"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="1"/>
@@ -5341,6 +5989,9 @@
       <c r="T209" s="1"/>
       <c r="U209" s="1"/>
       <c r="V209" s="1"/>
+      <c r="W209" s="1"/>
+      <c r="X209" s="1"/>
+      <c r="Y209" s="1"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="1"/>
@@ -5365,6 +6016,9 @@
       <c r="T210" s="1"/>
       <c r="U210" s="1"/>
       <c r="V210" s="1"/>
+      <c r="W210" s="1"/>
+      <c r="X210" s="1"/>
+      <c r="Y210" s="1"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="1"/>
@@ -5389,6 +6043,9 @@
       <c r="T211" s="1"/>
       <c r="U211" s="1"/>
       <c r="V211" s="1"/>
+      <c r="W211" s="1"/>
+      <c r="X211" s="1"/>
+      <c r="Y211" s="1"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="1"/>
@@ -5413,6 +6070,9 @@
       <c r="T212" s="1"/>
       <c r="U212" s="1"/>
       <c r="V212" s="1"/>
+      <c r="W212" s="1"/>
+      <c r="X212" s="1"/>
+      <c r="Y212" s="1"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="1"/>
@@ -5437,6 +6097,9 @@
       <c r="T213" s="1"/>
       <c r="U213" s="1"/>
       <c r="V213" s="1"/>
+      <c r="W213" s="1"/>
+      <c r="X213" s="1"/>
+      <c r="Y213" s="1"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="1"/>
@@ -5461,6 +6124,9 @@
       <c r="T214" s="1"/>
       <c r="U214" s="1"/>
       <c r="V214" s="1"/>
+      <c r="W214" s="1"/>
+      <c r="X214" s="1"/>
+      <c r="Y214" s="1"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="1"/>
@@ -5485,6 +6151,9 @@
       <c r="T215" s="1"/>
       <c r="U215" s="1"/>
       <c r="V215" s="1"/>
+      <c r="W215" s="1"/>
+      <c r="X215" s="1"/>
+      <c r="Y215" s="1"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="1"/>
@@ -5509,6 +6178,9 @@
       <c r="T216" s="1"/>
       <c r="U216" s="1"/>
       <c r="V216" s="1"/>
+      <c r="W216" s="1"/>
+      <c r="X216" s="1"/>
+      <c r="Y216" s="1"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="1"/>
@@ -5533,6 +6205,9 @@
       <c r="T217" s="1"/>
       <c r="U217" s="1"/>
       <c r="V217" s="1"/>
+      <c r="W217" s="1"/>
+      <c r="X217" s="1"/>
+      <c r="Y217" s="1"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="1"/>
@@ -5557,6 +6232,9 @@
       <c r="T218" s="1"/>
       <c r="U218" s="1"/>
       <c r="V218" s="1"/>
+      <c r="W218" s="1"/>
+      <c r="X218" s="1"/>
+      <c r="Y218" s="1"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="1"/>
@@ -5581,6 +6259,9 @@
       <c r="T219" s="1"/>
       <c r="U219" s="1"/>
       <c r="V219" s="1"/>
+      <c r="W219" s="1"/>
+      <c r="X219" s="1"/>
+      <c r="Y219" s="1"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="1"/>
@@ -5605,6 +6286,9 @@
       <c r="T220" s="1"/>
       <c r="U220" s="1"/>
       <c r="V220" s="1"/>
+      <c r="W220" s="1"/>
+      <c r="X220" s="1"/>
+      <c r="Y220" s="1"/>
     </row>
     <row r="221" ht="15.75" customHeight="1"/>
     <row r="222" ht="15.75" customHeight="1"/>

--- a/Templates/Tables/BlockInfo/BlockInfoTable.xlsx
+++ b/Templates/Tables/BlockInfo/BlockInfoTable.xlsx
@@ -11,7 +11,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Replace</t>
+  </si>
   <si>
     <t>Name</t>
   </si>
@@ -34,20 +40,17 @@
     <t>SizeZ</t>
   </si>
   <si>
-    <t>Description</t>
+    <t>샘플 블럭 정보</t>
   </si>
   <si>
     <t>Sample</t>
-  </si>
-  <si>
-    <t>샘플 블럭 정보</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -55,6 +58,9 @@
     </font>
     <font>
       <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <name val="Arial"/>
     </font>
     <font>
@@ -88,19 +94,22 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -315,23 +324,23 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="10" width="14.43"/>
+    <col customWidth="1" min="1" max="11" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
@@ -340,10 +349,12 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1"/>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -360,33 +371,36 @@
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="B2" s="4">
         <v>0.0</v>
       </c>
-      <c r="D2" s="1">
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="F2" s="1">
         <v>-1.0</v>
       </c>
-      <c r="E2" s="4">
+      <c r="G2" s="1">
         <v>0.0</v>
       </c>
-      <c r="F2" s="4">
+      <c r="H2" s="1">
         <v>0.0</v>
       </c>
-      <c r="G2" s="4">
+      <c r="I2" s="1">
         <v>0.0</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -403,10 +417,11 @@
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
+      <c r="B3" s="2"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -430,10 +445,11 @@
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
+      <c r="Z3" s="1"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
+      <c r="B4" s="2"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -457,10 +473,11 @@
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
+      <c r="Z4" s="1"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
+      <c r="B5" s="2"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -484,10 +501,11 @@
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
+      <c r="Z5" s="1"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
+      <c r="B6" s="2"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
@@ -511,10 +529,11 @@
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
+      <c r="Z6" s="1"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
+      <c r="B7" s="2"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -538,10 +557,11 @@
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
+      <c r="Z7" s="1"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
+      <c r="B8" s="2"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -565,10 +585,11 @@
       <c r="W8" s="1"/>
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
+      <c r="Z8" s="1"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
+      <c r="B9" s="2"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -592,10 +613,11 @@
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
+      <c r="B10" s="2"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -619,10 +641,11 @@
       <c r="W10" s="1"/>
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
+      <c r="Z10" s="1"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
+      <c r="B11" s="2"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -646,10 +669,11 @@
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
+      <c r="Z11" s="1"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
+      <c r="B12" s="2"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -673,10 +697,11 @@
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
+      <c r="Z12" s="1"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
+      <c r="B13" s="2"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -700,10 +725,11 @@
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
+      <c r="Z13" s="1"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
+      <c r="B14" s="2"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -727,10 +753,11 @@
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
+      <c r="Z14" s="1"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
+      <c r="B15" s="2"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -754,10 +781,11 @@
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
+      <c r="Z15" s="1"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
+      <c r="B16" s="2"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -781,10 +809,11 @@
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
+      <c r="Z16" s="1"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
+      <c r="B17" s="2"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -808,10 +837,11 @@
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
+      <c r="Z17" s="1"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="B18" s="2"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -835,10 +865,11 @@
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
+      <c r="Z18" s="1"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
+      <c r="B19" s="2"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
@@ -862,10 +893,11 @@
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
+      <c r="Z19" s="1"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
+      <c r="B20" s="2"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -889,10 +921,11 @@
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
+      <c r="Z20" s="1"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
+      <c r="B21" s="2"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -916,10 +949,11 @@
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
+      <c r="Z21" s="1"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
+      <c r="B22" s="2"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -943,10 +977,11 @@
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
+      <c r="Z22" s="1"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
+      <c r="B23" s="2"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -970,10 +1005,11 @@
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
+      <c r="Z23" s="1"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
+      <c r="B24" s="2"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -997,10 +1033,11 @@
       <c r="W24" s="1"/>
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
+      <c r="Z24" s="1"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
+      <c r="B25" s="2"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -1024,10 +1061,11 @@
       <c r="W25" s="1"/>
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
+      <c r="Z25" s="1"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
+      <c r="B26" s="2"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -1051,10 +1089,11 @@
       <c r="W26" s="1"/>
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
+      <c r="Z26" s="1"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
+      <c r="B27" s="2"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -1078,10 +1117,11 @@
       <c r="W27" s="1"/>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
+      <c r="Z27" s="1"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
+      <c r="B28" s="2"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -1105,10 +1145,11 @@
       <c r="W28" s="1"/>
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
+      <c r="Z28" s="1"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
+      <c r="B29" s="2"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -1132,10 +1173,11 @@
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
       <c r="Y29" s="1"/>
+      <c r="Z29" s="1"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
+      <c r="B30" s="2"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -1159,10 +1201,11 @@
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
+      <c r="Z30" s="1"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
+      <c r="B31" s="2"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -1186,10 +1229,11 @@
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
+      <c r="Z31" s="1"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
+      <c r="B32" s="2"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -1213,10 +1257,11 @@
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
+      <c r="Z32" s="1"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
+      <c r="B33" s="2"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -1240,10 +1285,11 @@
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
+      <c r="Z33" s="1"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
+      <c r="B34" s="2"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -1267,10 +1313,11 @@
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
+      <c r="Z34" s="1"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
+      <c r="B35" s="2"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -1294,10 +1341,11 @@
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
+      <c r="Z35" s="1"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
+      <c r="B36" s="2"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -1321,10 +1369,11 @@
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
+      <c r="Z36" s="1"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
+      <c r="B37" s="2"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -1348,10 +1397,11 @@
       <c r="W37" s="1"/>
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
+      <c r="Z37" s="1"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
+      <c r="B38" s="2"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -1375,10 +1425,11 @@
       <c r="W38" s="1"/>
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
+      <c r="Z38" s="1"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
+      <c r="B39" s="2"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
@@ -1402,10 +1453,11 @@
       <c r="W39" s="1"/>
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
+      <c r="Z39" s="1"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
+      <c r="B40" s="2"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
@@ -1429,10 +1481,11 @@
       <c r="W40" s="1"/>
       <c r="X40" s="1"/>
       <c r="Y40" s="1"/>
+      <c r="Z40" s="1"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
+      <c r="B41" s="2"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
@@ -1456,10 +1509,11 @@
       <c r="W41" s="1"/>
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
+      <c r="Z41" s="1"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
+      <c r="B42" s="2"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -1483,10 +1537,11 @@
       <c r="W42" s="1"/>
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
+      <c r="Z42" s="1"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
+      <c r="B43" s="2"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -1510,10 +1565,11 @@
       <c r="W43" s="1"/>
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
+      <c r="Z43" s="1"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
+      <c r="B44" s="2"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -1537,10 +1593,11 @@
       <c r="W44" s="1"/>
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
+      <c r="Z44" s="1"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
+      <c r="B45" s="2"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
@@ -1564,10 +1621,11 @@
       <c r="W45" s="1"/>
       <c r="X45" s="1"/>
       <c r="Y45" s="1"/>
+      <c r="Z45" s="1"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
+      <c r="B46" s="2"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -1591,10 +1649,11 @@
       <c r="W46" s="1"/>
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
+      <c r="Z46" s="1"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
+      <c r="B47" s="2"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -1618,10 +1677,11 @@
       <c r="W47" s="1"/>
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
+      <c r="Z47" s="1"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
+      <c r="B48" s="2"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -1645,10 +1705,11 @@
       <c r="W48" s="1"/>
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
+      <c r="Z48" s="1"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
+      <c r="B49" s="2"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -1672,10 +1733,11 @@
       <c r="W49" s="1"/>
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
+      <c r="Z49" s="1"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
+      <c r="B50" s="2"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -1699,10 +1761,11 @@
       <c r="W50" s="1"/>
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
+      <c r="Z50" s="1"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="1"/>
-      <c r="B51" s="1"/>
+      <c r="B51" s="2"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -1726,10 +1789,11 @@
       <c r="W51" s="1"/>
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
+      <c r="Z51" s="1"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
+      <c r="B52" s="2"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -1753,10 +1817,11 @@
       <c r="W52" s="1"/>
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
+      <c r="Z52" s="1"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
+      <c r="B53" s="2"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -1780,10 +1845,11 @@
       <c r="W53" s="1"/>
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
+      <c r="Z53" s="1"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
+      <c r="B54" s="2"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -1807,10 +1873,11 @@
       <c r="W54" s="1"/>
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
+      <c r="Z54" s="1"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
+      <c r="B55" s="2"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
@@ -1834,10 +1901,11 @@
       <c r="W55" s="1"/>
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
+      <c r="Z55" s="1"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
+      <c r="B56" s="2"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -1861,10 +1929,11 @@
       <c r="W56" s="1"/>
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
+      <c r="Z56" s="1"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="1"/>
-      <c r="B57" s="1"/>
+      <c r="B57" s="2"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -1888,10 +1957,11 @@
       <c r="W57" s="1"/>
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
+      <c r="Z57" s="1"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
+      <c r="B58" s="2"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
@@ -1915,10 +1985,11 @@
       <c r="W58" s="1"/>
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
+      <c r="Z58" s="1"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
+      <c r="B59" s="2"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -1942,10 +2013,11 @@
       <c r="W59" s="1"/>
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
+      <c r="Z59" s="1"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="1"/>
-      <c r="B60" s="1"/>
+      <c r="B60" s="2"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -1969,10 +2041,11 @@
       <c r="W60" s="1"/>
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
+      <c r="Z60" s="1"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="1"/>
-      <c r="B61" s="1"/>
+      <c r="B61" s="2"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
@@ -1996,10 +2069,11 @@
       <c r="W61" s="1"/>
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
+      <c r="Z61" s="1"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="1"/>
-      <c r="B62" s="1"/>
+      <c r="B62" s="2"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
@@ -2023,10 +2097,11 @@
       <c r="W62" s="1"/>
       <c r="X62" s="1"/>
       <c r="Y62" s="1"/>
+      <c r="Z62" s="1"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="1"/>
-      <c r="B63" s="1"/>
+      <c r="B63" s="2"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -2050,10 +2125,11 @@
       <c r="W63" s="1"/>
       <c r="X63" s="1"/>
       <c r="Y63" s="1"/>
+      <c r="Z63" s="1"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
+      <c r="B64" s="2"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -2077,10 +2153,11 @@
       <c r="W64" s="1"/>
       <c r="X64" s="1"/>
       <c r="Y64" s="1"/>
+      <c r="Z64" s="1"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="1"/>
-      <c r="B65" s="1"/>
+      <c r="B65" s="2"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
@@ -2104,10 +2181,11 @@
       <c r="W65" s="1"/>
       <c r="X65" s="1"/>
       <c r="Y65" s="1"/>
+      <c r="Z65" s="1"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="1"/>
-      <c r="B66" s="1"/>
+      <c r="B66" s="2"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
@@ -2131,10 +2209,11 @@
       <c r="W66" s="1"/>
       <c r="X66" s="1"/>
       <c r="Y66" s="1"/>
+      <c r="Z66" s="1"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="1"/>
-      <c r="B67" s="1"/>
+      <c r="B67" s="2"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
@@ -2158,10 +2237,11 @@
       <c r="W67" s="1"/>
       <c r="X67" s="1"/>
       <c r="Y67" s="1"/>
+      <c r="Z67" s="1"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
+      <c r="B68" s="2"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
@@ -2185,10 +2265,11 @@
       <c r="W68" s="1"/>
       <c r="X68" s="1"/>
       <c r="Y68" s="1"/>
+      <c r="Z68" s="1"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
+      <c r="B69" s="2"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
@@ -2212,10 +2293,11 @@
       <c r="W69" s="1"/>
       <c r="X69" s="1"/>
       <c r="Y69" s="1"/>
+      <c r="Z69" s="1"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="1"/>
-      <c r="B70" s="1"/>
+      <c r="B70" s="2"/>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
@@ -2239,10 +2321,11 @@
       <c r="W70" s="1"/>
       <c r="X70" s="1"/>
       <c r="Y70" s="1"/>
+      <c r="Z70" s="1"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="1"/>
-      <c r="B71" s="1"/>
+      <c r="B71" s="2"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
@@ -2266,10 +2349,11 @@
       <c r="W71" s="1"/>
       <c r="X71" s="1"/>
       <c r="Y71" s="1"/>
+      <c r="Z71" s="1"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="1"/>
-      <c r="B72" s="1"/>
+      <c r="B72" s="2"/>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
@@ -2293,10 +2377,11 @@
       <c r="W72" s="1"/>
       <c r="X72" s="1"/>
       <c r="Y72" s="1"/>
+      <c r="Z72" s="1"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="1"/>
-      <c r="B73" s="1"/>
+      <c r="B73" s="2"/>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
@@ -2320,10 +2405,11 @@
       <c r="W73" s="1"/>
       <c r="X73" s="1"/>
       <c r="Y73" s="1"/>
+      <c r="Z73" s="1"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="1"/>
-      <c r="B74" s="1"/>
+      <c r="B74" s="2"/>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
@@ -2347,10 +2433,11 @@
       <c r="W74" s="1"/>
       <c r="X74" s="1"/>
       <c r="Y74" s="1"/>
+      <c r="Z74" s="1"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="1"/>
-      <c r="B75" s="1"/>
+      <c r="B75" s="2"/>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
@@ -2374,10 +2461,11 @@
       <c r="W75" s="1"/>
       <c r="X75" s="1"/>
       <c r="Y75" s="1"/>
+      <c r="Z75" s="1"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="1"/>
-      <c r="B76" s="1"/>
+      <c r="B76" s="2"/>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
@@ -2401,10 +2489,11 @@
       <c r="W76" s="1"/>
       <c r="X76" s="1"/>
       <c r="Y76" s="1"/>
+      <c r="Z76" s="1"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="1"/>
-      <c r="B77" s="1"/>
+      <c r="B77" s="2"/>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
@@ -2428,10 +2517,11 @@
       <c r="W77" s="1"/>
       <c r="X77" s="1"/>
       <c r="Y77" s="1"/>
+      <c r="Z77" s="1"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="1"/>
-      <c r="B78" s="1"/>
+      <c r="B78" s="2"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
@@ -2455,10 +2545,11 @@
       <c r="W78" s="1"/>
       <c r="X78" s="1"/>
       <c r="Y78" s="1"/>
+      <c r="Z78" s="1"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="1"/>
-      <c r="B79" s="1"/>
+      <c r="B79" s="2"/>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
@@ -2482,10 +2573,11 @@
       <c r="W79" s="1"/>
       <c r="X79" s="1"/>
       <c r="Y79" s="1"/>
+      <c r="Z79" s="1"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="1"/>
-      <c r="B80" s="1"/>
+      <c r="B80" s="2"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
@@ -2509,10 +2601,11 @@
       <c r="W80" s="1"/>
       <c r="X80" s="1"/>
       <c r="Y80" s="1"/>
+      <c r="Z80" s="1"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="1"/>
-      <c r="B81" s="1"/>
+      <c r="B81" s="2"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
@@ -2536,10 +2629,11 @@
       <c r="W81" s="1"/>
       <c r="X81" s="1"/>
       <c r="Y81" s="1"/>
+      <c r="Z81" s="1"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="1"/>
-      <c r="B82" s="1"/>
+      <c r="B82" s="2"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
@@ -2563,10 +2657,11 @@
       <c r="W82" s="1"/>
       <c r="X82" s="1"/>
       <c r="Y82" s="1"/>
+      <c r="Z82" s="1"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
+      <c r="B83" s="2"/>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
@@ -2590,10 +2685,11 @@
       <c r="W83" s="1"/>
       <c r="X83" s="1"/>
       <c r="Y83" s="1"/>
+      <c r="Z83" s="1"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="1"/>
-      <c r="B84" s="1"/>
+      <c r="B84" s="2"/>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
@@ -2617,10 +2713,11 @@
       <c r="W84" s="1"/>
       <c r="X84" s="1"/>
       <c r="Y84" s="1"/>
+      <c r="Z84" s="1"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="1"/>
-      <c r="B85" s="1"/>
+      <c r="B85" s="2"/>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
@@ -2644,10 +2741,11 @@
       <c r="W85" s="1"/>
       <c r="X85" s="1"/>
       <c r="Y85" s="1"/>
+      <c r="Z85" s="1"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="1"/>
-      <c r="B86" s="1"/>
+      <c r="B86" s="2"/>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
@@ -2671,10 +2769,11 @@
       <c r="W86" s="1"/>
       <c r="X86" s="1"/>
       <c r="Y86" s="1"/>
+      <c r="Z86" s="1"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="1"/>
-      <c r="B87" s="1"/>
+      <c r="B87" s="2"/>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
@@ -2698,10 +2797,11 @@
       <c r="W87" s="1"/>
       <c r="X87" s="1"/>
       <c r="Y87" s="1"/>
+      <c r="Z87" s="1"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="1"/>
-      <c r="B88" s="1"/>
+      <c r="B88" s="2"/>
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
@@ -2725,10 +2825,11 @@
       <c r="W88" s="1"/>
       <c r="X88" s="1"/>
       <c r="Y88" s="1"/>
+      <c r="Z88" s="1"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="1"/>
-      <c r="B89" s="1"/>
+      <c r="B89" s="2"/>
       <c r="C89" s="1"/>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
@@ -2752,10 +2853,11 @@
       <c r="W89" s="1"/>
       <c r="X89" s="1"/>
       <c r="Y89" s="1"/>
+      <c r="Z89" s="1"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="1"/>
-      <c r="B90" s="1"/>
+      <c r="B90" s="2"/>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
@@ -2779,10 +2881,11 @@
       <c r="W90" s="1"/>
       <c r="X90" s="1"/>
       <c r="Y90" s="1"/>
+      <c r="Z90" s="1"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="1"/>
-      <c r="B91" s="1"/>
+      <c r="B91" s="2"/>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
@@ -2806,10 +2909,11 @@
       <c r="W91" s="1"/>
       <c r="X91" s="1"/>
       <c r="Y91" s="1"/>
+      <c r="Z91" s="1"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="1"/>
-      <c r="B92" s="1"/>
+      <c r="B92" s="2"/>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
@@ -2833,10 +2937,11 @@
       <c r="W92" s="1"/>
       <c r="X92" s="1"/>
       <c r="Y92" s="1"/>
+      <c r="Z92" s="1"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="1"/>
-      <c r="B93" s="1"/>
+      <c r="B93" s="2"/>
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
@@ -2860,10 +2965,11 @@
       <c r="W93" s="1"/>
       <c r="X93" s="1"/>
       <c r="Y93" s="1"/>
+      <c r="Z93" s="1"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="1"/>
-      <c r="B94" s="1"/>
+      <c r="B94" s="2"/>
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
@@ -2887,10 +2993,11 @@
       <c r="W94" s="1"/>
       <c r="X94" s="1"/>
       <c r="Y94" s="1"/>
+      <c r="Z94" s="1"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="1"/>
-      <c r="B95" s="1"/>
+      <c r="B95" s="2"/>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
@@ -2914,10 +3021,11 @@
       <c r="W95" s="1"/>
       <c r="X95" s="1"/>
       <c r="Y95" s="1"/>
+      <c r="Z95" s="1"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="1"/>
-      <c r="B96" s="1"/>
+      <c r="B96" s="2"/>
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
@@ -2941,10 +3049,11 @@
       <c r="W96" s="1"/>
       <c r="X96" s="1"/>
       <c r="Y96" s="1"/>
+      <c r="Z96" s="1"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="1"/>
-      <c r="B97" s="1"/>
+      <c r="B97" s="2"/>
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
@@ -2968,10 +3077,11 @@
       <c r="W97" s="1"/>
       <c r="X97" s="1"/>
       <c r="Y97" s="1"/>
+      <c r="Z97" s="1"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="1"/>
-      <c r="B98" s="1"/>
+      <c r="B98" s="2"/>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
@@ -2995,10 +3105,11 @@
       <c r="W98" s="1"/>
       <c r="X98" s="1"/>
       <c r="Y98" s="1"/>
+      <c r="Z98" s="1"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="1"/>
-      <c r="B99" s="1"/>
+      <c r="B99" s="2"/>
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
@@ -3022,10 +3133,11 @@
       <c r="W99" s="1"/>
       <c r="X99" s="1"/>
       <c r="Y99" s="1"/>
+      <c r="Z99" s="1"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="1"/>
-      <c r="B100" s="1"/>
+      <c r="B100" s="2"/>
       <c r="C100" s="1"/>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
@@ -3049,10 +3161,11 @@
       <c r="W100" s="1"/>
       <c r="X100" s="1"/>
       <c r="Y100" s="1"/>
+      <c r="Z100" s="1"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="1"/>
-      <c r="B101" s="1"/>
+      <c r="B101" s="2"/>
       <c r="C101" s="1"/>
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
@@ -3076,10 +3189,11 @@
       <c r="W101" s="1"/>
       <c r="X101" s="1"/>
       <c r="Y101" s="1"/>
+      <c r="Z101" s="1"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="1"/>
-      <c r="B102" s="1"/>
+      <c r="B102" s="2"/>
       <c r="C102" s="1"/>
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
@@ -3103,10 +3217,11 @@
       <c r="W102" s="1"/>
       <c r="X102" s="1"/>
       <c r="Y102" s="1"/>
+      <c r="Z102" s="1"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="1"/>
-      <c r="B103" s="1"/>
+      <c r="B103" s="2"/>
       <c r="C103" s="1"/>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
@@ -3130,10 +3245,11 @@
       <c r="W103" s="1"/>
       <c r="X103" s="1"/>
       <c r="Y103" s="1"/>
+      <c r="Z103" s="1"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="1"/>
-      <c r="B104" s="1"/>
+      <c r="B104" s="2"/>
       <c r="C104" s="1"/>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
@@ -3157,10 +3273,11 @@
       <c r="W104" s="1"/>
       <c r="X104" s="1"/>
       <c r="Y104" s="1"/>
+      <c r="Z104" s="1"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="1"/>
-      <c r="B105" s="1"/>
+      <c r="B105" s="2"/>
       <c r="C105" s="1"/>
       <c r="D105" s="1"/>
       <c r="E105" s="1"/>
@@ -3184,10 +3301,11 @@
       <c r="W105" s="1"/>
       <c r="X105" s="1"/>
       <c r="Y105" s="1"/>
+      <c r="Z105" s="1"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="1"/>
-      <c r="B106" s="1"/>
+      <c r="B106" s="2"/>
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
       <c r="E106" s="1"/>
@@ -3211,10 +3329,11 @@
       <c r="W106" s="1"/>
       <c r="X106" s="1"/>
       <c r="Y106" s="1"/>
+      <c r="Z106" s="1"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="1"/>
-      <c r="B107" s="1"/>
+      <c r="B107" s="2"/>
       <c r="C107" s="1"/>
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
@@ -3238,10 +3357,11 @@
       <c r="W107" s="1"/>
       <c r="X107" s="1"/>
       <c r="Y107" s="1"/>
+      <c r="Z107" s="1"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="1"/>
-      <c r="B108" s="1"/>
+      <c r="B108" s="2"/>
       <c r="C108" s="1"/>
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
@@ -3265,10 +3385,11 @@
       <c r="W108" s="1"/>
       <c r="X108" s="1"/>
       <c r="Y108" s="1"/>
+      <c r="Z108" s="1"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="1"/>
-      <c r="B109" s="1"/>
+      <c r="B109" s="2"/>
       <c r="C109" s="1"/>
       <c r="D109" s="1"/>
       <c r="E109" s="1"/>
@@ -3292,10 +3413,11 @@
       <c r="W109" s="1"/>
       <c r="X109" s="1"/>
       <c r="Y109" s="1"/>
+      <c r="Z109" s="1"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="1"/>
-      <c r="B110" s="1"/>
+      <c r="B110" s="2"/>
       <c r="C110" s="1"/>
       <c r="D110" s="1"/>
       <c r="E110" s="1"/>
@@ -3319,10 +3441,11 @@
       <c r="W110" s="1"/>
       <c r="X110" s="1"/>
       <c r="Y110" s="1"/>
+      <c r="Z110" s="1"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="1"/>
-      <c r="B111" s="1"/>
+      <c r="B111" s="2"/>
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
       <c r="E111" s="1"/>
@@ -3346,10 +3469,11 @@
       <c r="W111" s="1"/>
       <c r="X111" s="1"/>
       <c r="Y111" s="1"/>
+      <c r="Z111" s="1"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="1"/>
-      <c r="B112" s="1"/>
+      <c r="B112" s="2"/>
       <c r="C112" s="1"/>
       <c r="D112" s="1"/>
       <c r="E112" s="1"/>
@@ -3373,10 +3497,11 @@
       <c r="W112" s="1"/>
       <c r="X112" s="1"/>
       <c r="Y112" s="1"/>
+      <c r="Z112" s="1"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="1"/>
-      <c r="B113" s="1"/>
+      <c r="B113" s="2"/>
       <c r="C113" s="1"/>
       <c r="D113" s="1"/>
       <c r="E113" s="1"/>
@@ -3400,10 +3525,11 @@
       <c r="W113" s="1"/>
       <c r="X113" s="1"/>
       <c r="Y113" s="1"/>
+      <c r="Z113" s="1"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="1"/>
-      <c r="B114" s="1"/>
+      <c r="B114" s="2"/>
       <c r="C114" s="1"/>
       <c r="D114" s="1"/>
       <c r="E114" s="1"/>
@@ -3427,10 +3553,11 @@
       <c r="W114" s="1"/>
       <c r="X114" s="1"/>
       <c r="Y114" s="1"/>
+      <c r="Z114" s="1"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="1"/>
-      <c r="B115" s="1"/>
+      <c r="B115" s="2"/>
       <c r="C115" s="1"/>
       <c r="D115" s="1"/>
       <c r="E115" s="1"/>
@@ -3454,10 +3581,11 @@
       <c r="W115" s="1"/>
       <c r="X115" s="1"/>
       <c r="Y115" s="1"/>
+      <c r="Z115" s="1"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="1"/>
-      <c r="B116" s="1"/>
+      <c r="B116" s="2"/>
       <c r="C116" s="1"/>
       <c r="D116" s="1"/>
       <c r="E116" s="1"/>
@@ -3481,10 +3609,11 @@
       <c r="W116" s="1"/>
       <c r="X116" s="1"/>
       <c r="Y116" s="1"/>
+      <c r="Z116" s="1"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="1"/>
-      <c r="B117" s="1"/>
+      <c r="B117" s="2"/>
       <c r="C117" s="1"/>
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
@@ -3508,10 +3637,11 @@
       <c r="W117" s="1"/>
       <c r="X117" s="1"/>
       <c r="Y117" s="1"/>
+      <c r="Z117" s="1"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="1"/>
-      <c r="B118" s="1"/>
+      <c r="B118" s="2"/>
       <c r="C118" s="1"/>
       <c r="D118" s="1"/>
       <c r="E118" s="1"/>
@@ -3535,10 +3665,11 @@
       <c r="W118" s="1"/>
       <c r="X118" s="1"/>
       <c r="Y118" s="1"/>
+      <c r="Z118" s="1"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="1"/>
-      <c r="B119" s="1"/>
+      <c r="B119" s="2"/>
       <c r="C119" s="1"/>
       <c r="D119" s="1"/>
       <c r="E119" s="1"/>
@@ -3562,10 +3693,11 @@
       <c r="W119" s="1"/>
       <c r="X119" s="1"/>
       <c r="Y119" s="1"/>
+      <c r="Z119" s="1"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="1"/>
-      <c r="B120" s="1"/>
+      <c r="B120" s="2"/>
       <c r="C120" s="1"/>
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
@@ -3589,10 +3721,11 @@
       <c r="W120" s="1"/>
       <c r="X120" s="1"/>
       <c r="Y120" s="1"/>
+      <c r="Z120" s="1"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="1"/>
-      <c r="B121" s="1"/>
+      <c r="B121" s="2"/>
       <c r="C121" s="1"/>
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
@@ -3616,10 +3749,11 @@
       <c r="W121" s="1"/>
       <c r="X121" s="1"/>
       <c r="Y121" s="1"/>
+      <c r="Z121" s="1"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="1"/>
-      <c r="B122" s="1"/>
+      <c r="B122" s="2"/>
       <c r="C122" s="1"/>
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
@@ -3643,10 +3777,11 @@
       <c r="W122" s="1"/>
       <c r="X122" s="1"/>
       <c r="Y122" s="1"/>
+      <c r="Z122" s="1"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="1"/>
-      <c r="B123" s="1"/>
+      <c r="B123" s="2"/>
       <c r="C123" s="1"/>
       <c r="D123" s="1"/>
       <c r="E123" s="1"/>
@@ -3670,10 +3805,11 @@
       <c r="W123" s="1"/>
       <c r="X123" s="1"/>
       <c r="Y123" s="1"/>
+      <c r="Z123" s="1"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="1"/>
-      <c r="B124" s="1"/>
+      <c r="B124" s="2"/>
       <c r="C124" s="1"/>
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
@@ -3697,10 +3833,11 @@
       <c r="W124" s="1"/>
       <c r="X124" s="1"/>
       <c r="Y124" s="1"/>
+      <c r="Z124" s="1"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="1"/>
-      <c r="B125" s="1"/>
+      <c r="B125" s="2"/>
       <c r="C125" s="1"/>
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
@@ -3724,10 +3861,11 @@
       <c r="W125" s="1"/>
       <c r="X125" s="1"/>
       <c r="Y125" s="1"/>
+      <c r="Z125" s="1"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="1"/>
-      <c r="B126" s="1"/>
+      <c r="B126" s="2"/>
       <c r="C126" s="1"/>
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
@@ -3751,10 +3889,11 @@
       <c r="W126" s="1"/>
       <c r="X126" s="1"/>
       <c r="Y126" s="1"/>
+      <c r="Z126" s="1"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="1"/>
-      <c r="B127" s="1"/>
+      <c r="B127" s="2"/>
       <c r="C127" s="1"/>
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
@@ -3778,10 +3917,11 @@
       <c r="W127" s="1"/>
       <c r="X127" s="1"/>
       <c r="Y127" s="1"/>
+      <c r="Z127" s="1"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="1"/>
-      <c r="B128" s="1"/>
+      <c r="B128" s="2"/>
       <c r="C128" s="1"/>
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
@@ -3805,10 +3945,11 @@
       <c r="W128" s="1"/>
       <c r="X128" s="1"/>
       <c r="Y128" s="1"/>
+      <c r="Z128" s="1"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="1"/>
-      <c r="B129" s="1"/>
+      <c r="B129" s="2"/>
       <c r="C129" s="1"/>
       <c r="D129" s="1"/>
       <c r="E129" s="1"/>
@@ -3832,10 +3973,11 @@
       <c r="W129" s="1"/>
       <c r="X129" s="1"/>
       <c r="Y129" s="1"/>
+      <c r="Z129" s="1"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="1"/>
-      <c r="B130" s="1"/>
+      <c r="B130" s="2"/>
       <c r="C130" s="1"/>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
@@ -3859,10 +4001,11 @@
       <c r="W130" s="1"/>
       <c r="X130" s="1"/>
       <c r="Y130" s="1"/>
+      <c r="Z130" s="1"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="1"/>
-      <c r="B131" s="1"/>
+      <c r="B131" s="2"/>
       <c r="C131" s="1"/>
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
@@ -3886,10 +4029,11 @@
       <c r="W131" s="1"/>
       <c r="X131" s="1"/>
       <c r="Y131" s="1"/>
+      <c r="Z131" s="1"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="1"/>
-      <c r="B132" s="1"/>
+      <c r="B132" s="2"/>
       <c r="C132" s="1"/>
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
@@ -3913,10 +4057,11 @@
       <c r="W132" s="1"/>
       <c r="X132" s="1"/>
       <c r="Y132" s="1"/>
+      <c r="Z132" s="1"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="1"/>
-      <c r="B133" s="1"/>
+      <c r="B133" s="2"/>
       <c r="C133" s="1"/>
       <c r="D133" s="1"/>
       <c r="E133" s="1"/>
@@ -3940,10 +4085,11 @@
       <c r="W133" s="1"/>
       <c r="X133" s="1"/>
       <c r="Y133" s="1"/>
+      <c r="Z133" s="1"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="1"/>
-      <c r="B134" s="1"/>
+      <c r="B134" s="2"/>
       <c r="C134" s="1"/>
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
@@ -3967,10 +4113,11 @@
       <c r="W134" s="1"/>
       <c r="X134" s="1"/>
       <c r="Y134" s="1"/>
+      <c r="Z134" s="1"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="1"/>
-      <c r="B135" s="1"/>
+      <c r="B135" s="2"/>
       <c r="C135" s="1"/>
       <c r="D135" s="1"/>
       <c r="E135" s="1"/>
@@ -3994,10 +4141,11 @@
       <c r="W135" s="1"/>
       <c r="X135" s="1"/>
       <c r="Y135" s="1"/>
+      <c r="Z135" s="1"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="1"/>
-      <c r="B136" s="1"/>
+      <c r="B136" s="2"/>
       <c r="C136" s="1"/>
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
@@ -4021,10 +4169,11 @@
       <c r="W136" s="1"/>
       <c r="X136" s="1"/>
       <c r="Y136" s="1"/>
+      <c r="Z136" s="1"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="1"/>
-      <c r="B137" s="1"/>
+      <c r="B137" s="2"/>
       <c r="C137" s="1"/>
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
@@ -4048,10 +4197,11 @@
       <c r="W137" s="1"/>
       <c r="X137" s="1"/>
       <c r="Y137" s="1"/>
+      <c r="Z137" s="1"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="1"/>
-      <c r="B138" s="1"/>
+      <c r="B138" s="2"/>
       <c r="C138" s="1"/>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
@@ -4075,10 +4225,11 @@
       <c r="W138" s="1"/>
       <c r="X138" s="1"/>
       <c r="Y138" s="1"/>
+      <c r="Z138" s="1"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="1"/>
-      <c r="B139" s="1"/>
+      <c r="B139" s="2"/>
       <c r="C139" s="1"/>
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
@@ -4102,10 +4253,11 @@
       <c r="W139" s="1"/>
       <c r="X139" s="1"/>
       <c r="Y139" s="1"/>
+      <c r="Z139" s="1"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="1"/>
-      <c r="B140" s="1"/>
+      <c r="B140" s="2"/>
       <c r="C140" s="1"/>
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
@@ -4129,10 +4281,11 @@
       <c r="W140" s="1"/>
       <c r="X140" s="1"/>
       <c r="Y140" s="1"/>
+      <c r="Z140" s="1"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="1"/>
-      <c r="B141" s="1"/>
+      <c r="B141" s="2"/>
       <c r="C141" s="1"/>
       <c r="D141" s="1"/>
       <c r="E141" s="1"/>
@@ -4156,10 +4309,11 @@
       <c r="W141" s="1"/>
       <c r="X141" s="1"/>
       <c r="Y141" s="1"/>
+      <c r="Z141" s="1"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="1"/>
-      <c r="B142" s="1"/>
+      <c r="B142" s="2"/>
       <c r="C142" s="1"/>
       <c r="D142" s="1"/>
       <c r="E142" s="1"/>
@@ -4183,10 +4337,11 @@
       <c r="W142" s="1"/>
       <c r="X142" s="1"/>
       <c r="Y142" s="1"/>
+      <c r="Z142" s="1"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="1"/>
-      <c r="B143" s="1"/>
+      <c r="B143" s="2"/>
       <c r="C143" s="1"/>
       <c r="D143" s="1"/>
       <c r="E143" s="1"/>
@@ -4210,10 +4365,11 @@
       <c r="W143" s="1"/>
       <c r="X143" s="1"/>
       <c r="Y143" s="1"/>
+      <c r="Z143" s="1"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="1"/>
-      <c r="B144" s="1"/>
+      <c r="B144" s="2"/>
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
@@ -4237,10 +4393,11 @@
       <c r="W144" s="1"/>
       <c r="X144" s="1"/>
       <c r="Y144" s="1"/>
+      <c r="Z144" s="1"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="1"/>
-      <c r="B145" s="1"/>
+      <c r="B145" s="2"/>
       <c r="C145" s="1"/>
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
@@ -4264,10 +4421,11 @@
       <c r="W145" s="1"/>
       <c r="X145" s="1"/>
       <c r="Y145" s="1"/>
+      <c r="Z145" s="1"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="1"/>
-      <c r="B146" s="1"/>
+      <c r="B146" s="2"/>
       <c r="C146" s="1"/>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
@@ -4291,10 +4449,11 @@
       <c r="W146" s="1"/>
       <c r="X146" s="1"/>
       <c r="Y146" s="1"/>
+      <c r="Z146" s="1"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="1"/>
-      <c r="B147" s="1"/>
+      <c r="B147" s="2"/>
       <c r="C147" s="1"/>
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
@@ -4318,10 +4477,11 @@
       <c r="W147" s="1"/>
       <c r="X147" s="1"/>
       <c r="Y147" s="1"/>
+      <c r="Z147" s="1"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="1"/>
-      <c r="B148" s="1"/>
+      <c r="B148" s="2"/>
       <c r="C148" s="1"/>
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
@@ -4345,10 +4505,11 @@
       <c r="W148" s="1"/>
       <c r="X148" s="1"/>
       <c r="Y148" s="1"/>
+      <c r="Z148" s="1"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="1"/>
-      <c r="B149" s="1"/>
+      <c r="B149" s="2"/>
       <c r="C149" s="1"/>
       <c r="D149" s="1"/>
       <c r="E149" s="1"/>
@@ -4372,10 +4533,11 @@
       <c r="W149" s="1"/>
       <c r="X149" s="1"/>
       <c r="Y149" s="1"/>
+      <c r="Z149" s="1"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="1"/>
-      <c r="B150" s="1"/>
+      <c r="B150" s="2"/>
       <c r="C150" s="1"/>
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
@@ -4399,10 +4561,11 @@
       <c r="W150" s="1"/>
       <c r="X150" s="1"/>
       <c r="Y150" s="1"/>
+      <c r="Z150" s="1"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="1"/>
-      <c r="B151" s="1"/>
+      <c r="B151" s="2"/>
       <c r="C151" s="1"/>
       <c r="D151" s="1"/>
       <c r="E151" s="1"/>
@@ -4426,10 +4589,11 @@
       <c r="W151" s="1"/>
       <c r="X151" s="1"/>
       <c r="Y151" s="1"/>
+      <c r="Z151" s="1"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="1"/>
-      <c r="B152" s="1"/>
+      <c r="B152" s="2"/>
       <c r="C152" s="1"/>
       <c r="D152" s="1"/>
       <c r="E152" s="1"/>
@@ -4453,10 +4617,11 @@
       <c r="W152" s="1"/>
       <c r="X152" s="1"/>
       <c r="Y152" s="1"/>
+      <c r="Z152" s="1"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="1"/>
-      <c r="B153" s="1"/>
+      <c r="B153" s="2"/>
       <c r="C153" s="1"/>
       <c r="D153" s="1"/>
       <c r="E153" s="1"/>
@@ -4480,10 +4645,11 @@
       <c r="W153" s="1"/>
       <c r="X153" s="1"/>
       <c r="Y153" s="1"/>
+      <c r="Z153" s="1"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="1"/>
-      <c r="B154" s="1"/>
+      <c r="B154" s="2"/>
       <c r="C154" s="1"/>
       <c r="D154" s="1"/>
       <c r="E154" s="1"/>
@@ -4507,10 +4673,11 @@
       <c r="W154" s="1"/>
       <c r="X154" s="1"/>
       <c r="Y154" s="1"/>
+      <c r="Z154" s="1"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="1"/>
-      <c r="B155" s="1"/>
+      <c r="B155" s="2"/>
       <c r="C155" s="1"/>
       <c r="D155" s="1"/>
       <c r="E155" s="1"/>
@@ -4534,10 +4701,11 @@
       <c r="W155" s="1"/>
       <c r="X155" s="1"/>
       <c r="Y155" s="1"/>
+      <c r="Z155" s="1"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="1"/>
-      <c r="B156" s="1"/>
+      <c r="B156" s="2"/>
       <c r="C156" s="1"/>
       <c r="D156" s="1"/>
       <c r="E156" s="1"/>
@@ -4561,10 +4729,11 @@
       <c r="W156" s="1"/>
       <c r="X156" s="1"/>
       <c r="Y156" s="1"/>
+      <c r="Z156" s="1"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="1"/>
-      <c r="B157" s="1"/>
+      <c r="B157" s="2"/>
       <c r="C157" s="1"/>
       <c r="D157" s="1"/>
       <c r="E157" s="1"/>
@@ -4588,10 +4757,11 @@
       <c r="W157" s="1"/>
       <c r="X157" s="1"/>
       <c r="Y157" s="1"/>
+      <c r="Z157" s="1"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="1"/>
-      <c r="B158" s="1"/>
+      <c r="B158" s="2"/>
       <c r="C158" s="1"/>
       <c r="D158" s="1"/>
       <c r="E158" s="1"/>
@@ -4615,10 +4785,11 @@
       <c r="W158" s="1"/>
       <c r="X158" s="1"/>
       <c r="Y158" s="1"/>
+      <c r="Z158" s="1"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="1"/>
-      <c r="B159" s="1"/>
+      <c r="B159" s="2"/>
       <c r="C159" s="1"/>
       <c r="D159" s="1"/>
       <c r="E159" s="1"/>
@@ -4642,10 +4813,11 @@
       <c r="W159" s="1"/>
       <c r="X159" s="1"/>
       <c r="Y159" s="1"/>
+      <c r="Z159" s="1"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="1"/>
-      <c r="B160" s="1"/>
+      <c r="B160" s="2"/>
       <c r="C160" s="1"/>
       <c r="D160" s="1"/>
       <c r="E160" s="1"/>
@@ -4669,10 +4841,11 @@
       <c r="W160" s="1"/>
       <c r="X160" s="1"/>
       <c r="Y160" s="1"/>
+      <c r="Z160" s="1"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="1"/>
-      <c r="B161" s="1"/>
+      <c r="B161" s="2"/>
       <c r="C161" s="1"/>
       <c r="D161" s="1"/>
       <c r="E161" s="1"/>
@@ -4696,10 +4869,11 @@
       <c r="W161" s="1"/>
       <c r="X161" s="1"/>
       <c r="Y161" s="1"/>
+      <c r="Z161" s="1"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="1"/>
-      <c r="B162" s="1"/>
+      <c r="B162" s="2"/>
       <c r="C162" s="1"/>
       <c r="D162" s="1"/>
       <c r="E162" s="1"/>
@@ -4723,10 +4897,11 @@
       <c r="W162" s="1"/>
       <c r="X162" s="1"/>
       <c r="Y162" s="1"/>
+      <c r="Z162" s="1"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="1"/>
-      <c r="B163" s="1"/>
+      <c r="B163" s="2"/>
       <c r="C163" s="1"/>
       <c r="D163" s="1"/>
       <c r="E163" s="1"/>
@@ -4750,10 +4925,11 @@
       <c r="W163" s="1"/>
       <c r="X163" s="1"/>
       <c r="Y163" s="1"/>
+      <c r="Z163" s="1"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="1"/>
-      <c r="B164" s="1"/>
+      <c r="B164" s="2"/>
       <c r="C164" s="1"/>
       <c r="D164" s="1"/>
       <c r="E164" s="1"/>
@@ -4777,10 +4953,11 @@
       <c r="W164" s="1"/>
       <c r="X164" s="1"/>
       <c r="Y164" s="1"/>
+      <c r="Z164" s="1"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="1"/>
-      <c r="B165" s="1"/>
+      <c r="B165" s="2"/>
       <c r="C165" s="1"/>
       <c r="D165" s="1"/>
       <c r="E165" s="1"/>
@@ -4804,10 +4981,11 @@
       <c r="W165" s="1"/>
       <c r="X165" s="1"/>
       <c r="Y165" s="1"/>
+      <c r="Z165" s="1"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="1"/>
-      <c r="B166" s="1"/>
+      <c r="B166" s="2"/>
       <c r="C166" s="1"/>
       <c r="D166" s="1"/>
       <c r="E166" s="1"/>
@@ -4831,10 +5009,11 @@
       <c r="W166" s="1"/>
       <c r="X166" s="1"/>
       <c r="Y166" s="1"/>
+      <c r="Z166" s="1"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="1"/>
-      <c r="B167" s="1"/>
+      <c r="B167" s="2"/>
       <c r="C167" s="1"/>
       <c r="D167" s="1"/>
       <c r="E167" s="1"/>
@@ -4858,10 +5037,11 @@
       <c r="W167" s="1"/>
       <c r="X167" s="1"/>
       <c r="Y167" s="1"/>
+      <c r="Z167" s="1"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="1"/>
-      <c r="B168" s="1"/>
+      <c r="B168" s="2"/>
       <c r="C168" s="1"/>
       <c r="D168" s="1"/>
       <c r="E168" s="1"/>
@@ -4885,10 +5065,11 @@
       <c r="W168" s="1"/>
       <c r="X168" s="1"/>
       <c r="Y168" s="1"/>
+      <c r="Z168" s="1"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="1"/>
-      <c r="B169" s="1"/>
+      <c r="B169" s="2"/>
       <c r="C169" s="1"/>
       <c r="D169" s="1"/>
       <c r="E169" s="1"/>
@@ -4912,10 +5093,11 @@
       <c r="W169" s="1"/>
       <c r="X169" s="1"/>
       <c r="Y169" s="1"/>
+      <c r="Z169" s="1"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="1"/>
-      <c r="B170" s="1"/>
+      <c r="B170" s="2"/>
       <c r="C170" s="1"/>
       <c r="D170" s="1"/>
       <c r="E170" s="1"/>
@@ -4939,10 +5121,11 @@
       <c r="W170" s="1"/>
       <c r="X170" s="1"/>
       <c r="Y170" s="1"/>
+      <c r="Z170" s="1"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="1"/>
-      <c r="B171" s="1"/>
+      <c r="B171" s="2"/>
       <c r="C171" s="1"/>
       <c r="D171" s="1"/>
       <c r="E171" s="1"/>
@@ -4966,10 +5149,11 @@
       <c r="W171" s="1"/>
       <c r="X171" s="1"/>
       <c r="Y171" s="1"/>
+      <c r="Z171" s="1"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="1"/>
-      <c r="B172" s="1"/>
+      <c r="B172" s="2"/>
       <c r="C172" s="1"/>
       <c r="D172" s="1"/>
       <c r="E172" s="1"/>
@@ -4993,10 +5177,11 @@
       <c r="W172" s="1"/>
       <c r="X172" s="1"/>
       <c r="Y172" s="1"/>
+      <c r="Z172" s="1"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="1"/>
-      <c r="B173" s="1"/>
+      <c r="B173" s="2"/>
       <c r="C173" s="1"/>
       <c r="D173" s="1"/>
       <c r="E173" s="1"/>
@@ -5020,10 +5205,11 @@
       <c r="W173" s="1"/>
       <c r="X173" s="1"/>
       <c r="Y173" s="1"/>
+      <c r="Z173" s="1"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="1"/>
-      <c r="B174" s="1"/>
+      <c r="B174" s="2"/>
       <c r="C174" s="1"/>
       <c r="D174" s="1"/>
       <c r="E174" s="1"/>
@@ -5047,10 +5233,11 @@
       <c r="W174" s="1"/>
       <c r="X174" s="1"/>
       <c r="Y174" s="1"/>
+      <c r="Z174" s="1"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="1"/>
-      <c r="B175" s="1"/>
+      <c r="B175" s="2"/>
       <c r="C175" s="1"/>
       <c r="D175" s="1"/>
       <c r="E175" s="1"/>
@@ -5074,10 +5261,11 @@
       <c r="W175" s="1"/>
       <c r="X175" s="1"/>
       <c r="Y175" s="1"/>
+      <c r="Z175" s="1"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="1"/>
-      <c r="B176" s="1"/>
+      <c r="B176" s="2"/>
       <c r="C176" s="1"/>
       <c r="D176" s="1"/>
       <c r="E176" s="1"/>
@@ -5101,10 +5289,11 @@
       <c r="W176" s="1"/>
       <c r="X176" s="1"/>
       <c r="Y176" s="1"/>
+      <c r="Z176" s="1"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="1"/>
-      <c r="B177" s="1"/>
+      <c r="B177" s="2"/>
       <c r="C177" s="1"/>
       <c r="D177" s="1"/>
       <c r="E177" s="1"/>
@@ -5128,10 +5317,11 @@
       <c r="W177" s="1"/>
       <c r="X177" s="1"/>
       <c r="Y177" s="1"/>
+      <c r="Z177" s="1"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="1"/>
-      <c r="B178" s="1"/>
+      <c r="B178" s="2"/>
       <c r="C178" s="1"/>
       <c r="D178" s="1"/>
       <c r="E178" s="1"/>
@@ -5155,10 +5345,11 @@
       <c r="W178" s="1"/>
       <c r="X178" s="1"/>
       <c r="Y178" s="1"/>
+      <c r="Z178" s="1"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="1"/>
-      <c r="B179" s="1"/>
+      <c r="B179" s="2"/>
       <c r="C179" s="1"/>
       <c r="D179" s="1"/>
       <c r="E179" s="1"/>
@@ -5182,10 +5373,11 @@
       <c r="W179" s="1"/>
       <c r="X179" s="1"/>
       <c r="Y179" s="1"/>
+      <c r="Z179" s="1"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="1"/>
-      <c r="B180" s="1"/>
+      <c r="B180" s="2"/>
       <c r="C180" s="1"/>
       <c r="D180" s="1"/>
       <c r="E180" s="1"/>
@@ -5209,10 +5401,11 @@
       <c r="W180" s="1"/>
       <c r="X180" s="1"/>
       <c r="Y180" s="1"/>
+      <c r="Z180" s="1"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="1"/>
-      <c r="B181" s="1"/>
+      <c r="B181" s="2"/>
       <c r="C181" s="1"/>
       <c r="D181" s="1"/>
       <c r="E181" s="1"/>
@@ -5236,10 +5429,11 @@
       <c r="W181" s="1"/>
       <c r="X181" s="1"/>
       <c r="Y181" s="1"/>
+      <c r="Z181" s="1"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="1"/>
-      <c r="B182" s="1"/>
+      <c r="B182" s="2"/>
       <c r="C182" s="1"/>
       <c r="D182" s="1"/>
       <c r="E182" s="1"/>
@@ -5263,10 +5457,11 @@
       <c r="W182" s="1"/>
       <c r="X182" s="1"/>
       <c r="Y182" s="1"/>
+      <c r="Z182" s="1"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="1"/>
-      <c r="B183" s="1"/>
+      <c r="B183" s="2"/>
       <c r="C183" s="1"/>
       <c r="D183" s="1"/>
       <c r="E183" s="1"/>
@@ -5290,10 +5485,11 @@
       <c r="W183" s="1"/>
       <c r="X183" s="1"/>
       <c r="Y183" s="1"/>
+      <c r="Z183" s="1"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="1"/>
-      <c r="B184" s="1"/>
+      <c r="B184" s="2"/>
       <c r="C184" s="1"/>
       <c r="D184" s="1"/>
       <c r="E184" s="1"/>
@@ -5317,10 +5513,11 @@
       <c r="W184" s="1"/>
       <c r="X184" s="1"/>
       <c r="Y184" s="1"/>
+      <c r="Z184" s="1"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="1"/>
-      <c r="B185" s="1"/>
+      <c r="B185" s="2"/>
       <c r="C185" s="1"/>
       <c r="D185" s="1"/>
       <c r="E185" s="1"/>
@@ -5344,10 +5541,11 @@
       <c r="W185" s="1"/>
       <c r="X185" s="1"/>
       <c r="Y185" s="1"/>
+      <c r="Z185" s="1"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="1"/>
-      <c r="B186" s="1"/>
+      <c r="B186" s="2"/>
       <c r="C186" s="1"/>
       <c r="D186" s="1"/>
       <c r="E186" s="1"/>
@@ -5371,10 +5569,11 @@
       <c r="W186" s="1"/>
       <c r="X186" s="1"/>
       <c r="Y186" s="1"/>
+      <c r="Z186" s="1"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="1"/>
-      <c r="B187" s="1"/>
+      <c r="B187" s="2"/>
       <c r="C187" s="1"/>
       <c r="D187" s="1"/>
       <c r="E187" s="1"/>
@@ -5398,10 +5597,11 @@
       <c r="W187" s="1"/>
       <c r="X187" s="1"/>
       <c r="Y187" s="1"/>
+      <c r="Z187" s="1"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="1"/>
-      <c r="B188" s="1"/>
+      <c r="B188" s="2"/>
       <c r="C188" s="1"/>
       <c r="D188" s="1"/>
       <c r="E188" s="1"/>
@@ -5425,10 +5625,11 @@
       <c r="W188" s="1"/>
       <c r="X188" s="1"/>
       <c r="Y188" s="1"/>
+      <c r="Z188" s="1"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="1"/>
-      <c r="B189" s="1"/>
+      <c r="B189" s="2"/>
       <c r="C189" s="1"/>
       <c r="D189" s="1"/>
       <c r="E189" s="1"/>
@@ -5452,10 +5653,11 @@
       <c r="W189" s="1"/>
       <c r="X189" s="1"/>
       <c r="Y189" s="1"/>
+      <c r="Z189" s="1"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="1"/>
-      <c r="B190" s="1"/>
+      <c r="B190" s="2"/>
       <c r="C190" s="1"/>
       <c r="D190" s="1"/>
       <c r="E190" s="1"/>
@@ -5479,10 +5681,11 @@
       <c r="W190" s="1"/>
       <c r="X190" s="1"/>
       <c r="Y190" s="1"/>
+      <c r="Z190" s="1"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="1"/>
-      <c r="B191" s="1"/>
+      <c r="B191" s="2"/>
       <c r="C191" s="1"/>
       <c r="D191" s="1"/>
       <c r="E191" s="1"/>
@@ -5506,10 +5709,11 @@
       <c r="W191" s="1"/>
       <c r="X191" s="1"/>
       <c r="Y191" s="1"/>
+      <c r="Z191" s="1"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="1"/>
-      <c r="B192" s="1"/>
+      <c r="B192" s="2"/>
       <c r="C192" s="1"/>
       <c r="D192" s="1"/>
       <c r="E192" s="1"/>
@@ -5533,10 +5737,11 @@
       <c r="W192" s="1"/>
       <c r="X192" s="1"/>
       <c r="Y192" s="1"/>
+      <c r="Z192" s="1"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="1"/>
-      <c r="B193" s="1"/>
+      <c r="B193" s="2"/>
       <c r="C193" s="1"/>
       <c r="D193" s="1"/>
       <c r="E193" s="1"/>
@@ -5560,10 +5765,11 @@
       <c r="W193" s="1"/>
       <c r="X193" s="1"/>
       <c r="Y193" s="1"/>
+      <c r="Z193" s="1"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="1"/>
-      <c r="B194" s="1"/>
+      <c r="B194" s="2"/>
       <c r="C194" s="1"/>
       <c r="D194" s="1"/>
       <c r="E194" s="1"/>
@@ -5587,10 +5793,11 @@
       <c r="W194" s="1"/>
       <c r="X194" s="1"/>
       <c r="Y194" s="1"/>
+      <c r="Z194" s="1"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="1"/>
-      <c r="B195" s="1"/>
+      <c r="B195" s="2"/>
       <c r="C195" s="1"/>
       <c r="D195" s="1"/>
       <c r="E195" s="1"/>
@@ -5614,10 +5821,11 @@
       <c r="W195" s="1"/>
       <c r="X195" s="1"/>
       <c r="Y195" s="1"/>
+      <c r="Z195" s="1"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="1"/>
-      <c r="B196" s="1"/>
+      <c r="B196" s="2"/>
       <c r="C196" s="1"/>
       <c r="D196" s="1"/>
       <c r="E196" s="1"/>
@@ -5641,10 +5849,11 @@
       <c r="W196" s="1"/>
       <c r="X196" s="1"/>
       <c r="Y196" s="1"/>
+      <c r="Z196" s="1"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="1"/>
-      <c r="B197" s="1"/>
+      <c r="B197" s="2"/>
       <c r="C197" s="1"/>
       <c r="D197" s="1"/>
       <c r="E197" s="1"/>
@@ -5668,10 +5877,11 @@
       <c r="W197" s="1"/>
       <c r="X197" s="1"/>
       <c r="Y197" s="1"/>
+      <c r="Z197" s="1"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="1"/>
-      <c r="B198" s="1"/>
+      <c r="B198" s="2"/>
       <c r="C198" s="1"/>
       <c r="D198" s="1"/>
       <c r="E198" s="1"/>
@@ -5695,10 +5905,11 @@
       <c r="W198" s="1"/>
       <c r="X198" s="1"/>
       <c r="Y198" s="1"/>
+      <c r="Z198" s="1"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="1"/>
-      <c r="B199" s="1"/>
+      <c r="B199" s="2"/>
       <c r="C199" s="1"/>
       <c r="D199" s="1"/>
       <c r="E199" s="1"/>
@@ -5722,10 +5933,11 @@
       <c r="W199" s="1"/>
       <c r="X199" s="1"/>
       <c r="Y199" s="1"/>
+      <c r="Z199" s="1"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="1"/>
-      <c r="B200" s="1"/>
+      <c r="B200" s="2"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
       <c r="E200" s="1"/>
@@ -5749,10 +5961,11 @@
       <c r="W200" s="1"/>
       <c r="X200" s="1"/>
       <c r="Y200" s="1"/>
+      <c r="Z200" s="1"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="1"/>
-      <c r="B201" s="1"/>
+      <c r="B201" s="2"/>
       <c r="C201" s="1"/>
       <c r="D201" s="1"/>
       <c r="E201" s="1"/>
@@ -5776,10 +5989,11 @@
       <c r="W201" s="1"/>
       <c r="X201" s="1"/>
       <c r="Y201" s="1"/>
+      <c r="Z201" s="1"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="1"/>
-      <c r="B202" s="1"/>
+      <c r="B202" s="2"/>
       <c r="C202" s="1"/>
       <c r="D202" s="1"/>
       <c r="E202" s="1"/>
@@ -5803,10 +6017,11 @@
       <c r="W202" s="1"/>
       <c r="X202" s="1"/>
       <c r="Y202" s="1"/>
+      <c r="Z202" s="1"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="1"/>
-      <c r="B203" s="1"/>
+      <c r="B203" s="2"/>
       <c r="C203" s="1"/>
       <c r="D203" s="1"/>
       <c r="E203" s="1"/>
@@ -5830,10 +6045,11 @@
       <c r="W203" s="1"/>
       <c r="X203" s="1"/>
       <c r="Y203" s="1"/>
+      <c r="Z203" s="1"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="1"/>
-      <c r="B204" s="1"/>
+      <c r="B204" s="2"/>
       <c r="C204" s="1"/>
       <c r="D204" s="1"/>
       <c r="E204" s="1"/>
@@ -5857,10 +6073,11 @@
       <c r="W204" s="1"/>
       <c r="X204" s="1"/>
       <c r="Y204" s="1"/>
+      <c r="Z204" s="1"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="1"/>
-      <c r="B205" s="1"/>
+      <c r="B205" s="2"/>
       <c r="C205" s="1"/>
       <c r="D205" s="1"/>
       <c r="E205" s="1"/>
@@ -5884,10 +6101,11 @@
       <c r="W205" s="1"/>
       <c r="X205" s="1"/>
       <c r="Y205" s="1"/>
+      <c r="Z205" s="1"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="1"/>
-      <c r="B206" s="1"/>
+      <c r="B206" s="2"/>
       <c r="C206" s="1"/>
       <c r="D206" s="1"/>
       <c r="E206" s="1"/>
@@ -5911,10 +6129,11 @@
       <c r="W206" s="1"/>
       <c r="X206" s="1"/>
       <c r="Y206" s="1"/>
+      <c r="Z206" s="1"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="1"/>
-      <c r="B207" s="1"/>
+      <c r="B207" s="2"/>
       <c r="C207" s="1"/>
       <c r="D207" s="1"/>
       <c r="E207" s="1"/>
@@ -5938,10 +6157,11 @@
       <c r="W207" s="1"/>
       <c r="X207" s="1"/>
       <c r="Y207" s="1"/>
+      <c r="Z207" s="1"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="1"/>
-      <c r="B208" s="1"/>
+      <c r="B208" s="2"/>
       <c r="C208" s="1"/>
       <c r="D208" s="1"/>
       <c r="E208" s="1"/>
@@ -5965,10 +6185,11 @@
       <c r="W208" s="1"/>
       <c r="X208" s="1"/>
       <c r="Y208" s="1"/>
+      <c r="Z208" s="1"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="1"/>
-      <c r="B209" s="1"/>
+      <c r="B209" s="2"/>
       <c r="C209" s="1"/>
       <c r="D209" s="1"/>
       <c r="E209" s="1"/>
@@ -5992,10 +6213,11 @@
       <c r="W209" s="1"/>
       <c r="X209" s="1"/>
       <c r="Y209" s="1"/>
+      <c r="Z209" s="1"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="1"/>
-      <c r="B210" s="1"/>
+      <c r="B210" s="2"/>
       <c r="C210" s="1"/>
       <c r="D210" s="1"/>
       <c r="E210" s="1"/>
@@ -6019,10 +6241,11 @@
       <c r="W210" s="1"/>
       <c r="X210" s="1"/>
       <c r="Y210" s="1"/>
+      <c r="Z210" s="1"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="1"/>
-      <c r="B211" s="1"/>
+      <c r="B211" s="2"/>
       <c r="C211" s="1"/>
       <c r="D211" s="1"/>
       <c r="E211" s="1"/>
@@ -6046,10 +6269,11 @@
       <c r="W211" s="1"/>
       <c r="X211" s="1"/>
       <c r="Y211" s="1"/>
+      <c r="Z211" s="1"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="1"/>
-      <c r="B212" s="1"/>
+      <c r="B212" s="2"/>
       <c r="C212" s="1"/>
       <c r="D212" s="1"/>
       <c r="E212" s="1"/>
@@ -6073,10 +6297,11 @@
       <c r="W212" s="1"/>
       <c r="X212" s="1"/>
       <c r="Y212" s="1"/>
+      <c r="Z212" s="1"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="1"/>
-      <c r="B213" s="1"/>
+      <c r="B213" s="2"/>
       <c r="C213" s="1"/>
       <c r="D213" s="1"/>
       <c r="E213" s="1"/>
@@ -6100,10 +6325,11 @@
       <c r="W213" s="1"/>
       <c r="X213" s="1"/>
       <c r="Y213" s="1"/>
+      <c r="Z213" s="1"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="1"/>
-      <c r="B214" s="1"/>
+      <c r="B214" s="2"/>
       <c r="C214" s="1"/>
       <c r="D214" s="1"/>
       <c r="E214" s="1"/>
@@ -6127,10 +6353,11 @@
       <c r="W214" s="1"/>
       <c r="X214" s="1"/>
       <c r="Y214" s="1"/>
+      <c r="Z214" s="1"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="1"/>
-      <c r="B215" s="1"/>
+      <c r="B215" s="2"/>
       <c r="C215" s="1"/>
       <c r="D215" s="1"/>
       <c r="E215" s="1"/>
@@ -6154,10 +6381,11 @@
       <c r="W215" s="1"/>
       <c r="X215" s="1"/>
       <c r="Y215" s="1"/>
+      <c r="Z215" s="1"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="1"/>
-      <c r="B216" s="1"/>
+      <c r="B216" s="2"/>
       <c r="C216" s="1"/>
       <c r="D216" s="1"/>
       <c r="E216" s="1"/>
@@ -6181,10 +6409,11 @@
       <c r="W216" s="1"/>
       <c r="X216" s="1"/>
       <c r="Y216" s="1"/>
+      <c r="Z216" s="1"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="1"/>
-      <c r="B217" s="1"/>
+      <c r="B217" s="2"/>
       <c r="C217" s="1"/>
       <c r="D217" s="1"/>
       <c r="E217" s="1"/>
@@ -6208,10 +6437,11 @@
       <c r="W217" s="1"/>
       <c r="X217" s="1"/>
       <c r="Y217" s="1"/>
+      <c r="Z217" s="1"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="1"/>
-      <c r="B218" s="1"/>
+      <c r="B218" s="2"/>
       <c r="C218" s="1"/>
       <c r="D218" s="1"/>
       <c r="E218" s="1"/>
@@ -6235,10 +6465,11 @@
       <c r="W218" s="1"/>
       <c r="X218" s="1"/>
       <c r="Y218" s="1"/>
+      <c r="Z218" s="1"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="1"/>
-      <c r="B219" s="1"/>
+      <c r="B219" s="2"/>
       <c r="C219" s="1"/>
       <c r="D219" s="1"/>
       <c r="E219" s="1"/>
@@ -6262,10 +6493,11 @@
       <c r="W219" s="1"/>
       <c r="X219" s="1"/>
       <c r="Y219" s="1"/>
+      <c r="Z219" s="1"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="1"/>
-      <c r="B220" s="1"/>
+      <c r="B220" s="2"/>
       <c r="C220" s="1"/>
       <c r="D220" s="1"/>
       <c r="E220" s="1"/>
@@ -6289,787 +6521,2348 @@
       <c r="W220" s="1"/>
       <c r="X220" s="1"/>
       <c r="Y220" s="1"/>
-    </row>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
+      <c r="Z220" s="1"/>
+    </row>
+    <row r="221" ht="15.75" customHeight="1">
+      <c r="B221" s="5"/>
+    </row>
+    <row r="222" ht="15.75" customHeight="1">
+      <c r="B222" s="5"/>
+    </row>
+    <row r="223" ht="15.75" customHeight="1">
+      <c r="B223" s="5"/>
+    </row>
+    <row r="224" ht="15.75" customHeight="1">
+      <c r="B224" s="5"/>
+    </row>
+    <row r="225" ht="15.75" customHeight="1">
+      <c r="B225" s="5"/>
+    </row>
+    <row r="226" ht="15.75" customHeight="1">
+      <c r="B226" s="5"/>
+    </row>
+    <row r="227" ht="15.75" customHeight="1">
+      <c r="B227" s="5"/>
+    </row>
+    <row r="228" ht="15.75" customHeight="1">
+      <c r="B228" s="5"/>
+    </row>
+    <row r="229" ht="15.75" customHeight="1">
+      <c r="B229" s="5"/>
+    </row>
+    <row r="230" ht="15.75" customHeight="1">
+      <c r="B230" s="5"/>
+    </row>
+    <row r="231" ht="15.75" customHeight="1">
+      <c r="B231" s="5"/>
+    </row>
+    <row r="232" ht="15.75" customHeight="1">
+      <c r="B232" s="5"/>
+    </row>
+    <row r="233" ht="15.75" customHeight="1">
+      <c r="B233" s="5"/>
+    </row>
+    <row r="234" ht="15.75" customHeight="1">
+      <c r="B234" s="5"/>
+    </row>
+    <row r="235" ht="15.75" customHeight="1">
+      <c r="B235" s="5"/>
+    </row>
+    <row r="236" ht="15.75" customHeight="1">
+      <c r="B236" s="5"/>
+    </row>
+    <row r="237" ht="15.75" customHeight="1">
+      <c r="B237" s="5"/>
+    </row>
+    <row r="238" ht="15.75" customHeight="1">
+      <c r="B238" s="5"/>
+    </row>
+    <row r="239" ht="15.75" customHeight="1">
+      <c r="B239" s="5"/>
+    </row>
+    <row r="240" ht="15.75" customHeight="1">
+      <c r="B240" s="5"/>
+    </row>
+    <row r="241" ht="15.75" customHeight="1">
+      <c r="B241" s="5"/>
+    </row>
+    <row r="242" ht="15.75" customHeight="1">
+      <c r="B242" s="5"/>
+    </row>
+    <row r="243" ht="15.75" customHeight="1">
+      <c r="B243" s="5"/>
+    </row>
+    <row r="244" ht="15.75" customHeight="1">
+      <c r="B244" s="5"/>
+    </row>
+    <row r="245" ht="15.75" customHeight="1">
+      <c r="B245" s="5"/>
+    </row>
+    <row r="246" ht="15.75" customHeight="1">
+      <c r="B246" s="5"/>
+    </row>
+    <row r="247" ht="15.75" customHeight="1">
+      <c r="B247" s="5"/>
+    </row>
+    <row r="248" ht="15.75" customHeight="1">
+      <c r="B248" s="5"/>
+    </row>
+    <row r="249" ht="15.75" customHeight="1">
+      <c r="B249" s="5"/>
+    </row>
+    <row r="250" ht="15.75" customHeight="1">
+      <c r="B250" s="5"/>
+    </row>
+    <row r="251" ht="15.75" customHeight="1">
+      <c r="B251" s="5"/>
+    </row>
+    <row r="252" ht="15.75" customHeight="1">
+      <c r="B252" s="5"/>
+    </row>
+    <row r="253" ht="15.75" customHeight="1">
+      <c r="B253" s="5"/>
+    </row>
+    <row r="254" ht="15.75" customHeight="1">
+      <c r="B254" s="5"/>
+    </row>
+    <row r="255" ht="15.75" customHeight="1">
+      <c r="B255" s="5"/>
+    </row>
+    <row r="256" ht="15.75" customHeight="1">
+      <c r="B256" s="5"/>
+    </row>
+    <row r="257" ht="15.75" customHeight="1">
+      <c r="B257" s="5"/>
+    </row>
+    <row r="258" ht="15.75" customHeight="1">
+      <c r="B258" s="5"/>
+    </row>
+    <row r="259" ht="15.75" customHeight="1">
+      <c r="B259" s="5"/>
+    </row>
+    <row r="260" ht="15.75" customHeight="1">
+      <c r="B260" s="5"/>
+    </row>
+    <row r="261" ht="15.75" customHeight="1">
+      <c r="B261" s="5"/>
+    </row>
+    <row r="262" ht="15.75" customHeight="1">
+      <c r="B262" s="5"/>
+    </row>
+    <row r="263" ht="15.75" customHeight="1">
+      <c r="B263" s="5"/>
+    </row>
+    <row r="264" ht="15.75" customHeight="1">
+      <c r="B264" s="5"/>
+    </row>
+    <row r="265" ht="15.75" customHeight="1">
+      <c r="B265" s="5"/>
+    </row>
+    <row r="266" ht="15.75" customHeight="1">
+      <c r="B266" s="5"/>
+    </row>
+    <row r="267" ht="15.75" customHeight="1">
+      <c r="B267" s="5"/>
+    </row>
+    <row r="268" ht="15.75" customHeight="1">
+      <c r="B268" s="5"/>
+    </row>
+    <row r="269" ht="15.75" customHeight="1">
+      <c r="B269" s="5"/>
+    </row>
+    <row r="270" ht="15.75" customHeight="1">
+      <c r="B270" s="5"/>
+    </row>
+    <row r="271" ht="15.75" customHeight="1">
+      <c r="B271" s="5"/>
+    </row>
+    <row r="272" ht="15.75" customHeight="1">
+      <c r="B272" s="5"/>
+    </row>
+    <row r="273" ht="15.75" customHeight="1">
+      <c r="B273" s="5"/>
+    </row>
+    <row r="274" ht="15.75" customHeight="1">
+      <c r="B274" s="5"/>
+    </row>
+    <row r="275" ht="15.75" customHeight="1">
+      <c r="B275" s="5"/>
+    </row>
+    <row r="276" ht="15.75" customHeight="1">
+      <c r="B276" s="5"/>
+    </row>
+    <row r="277" ht="15.75" customHeight="1">
+      <c r="B277" s="5"/>
+    </row>
+    <row r="278" ht="15.75" customHeight="1">
+      <c r="B278" s="5"/>
+    </row>
+    <row r="279" ht="15.75" customHeight="1">
+      <c r="B279" s="5"/>
+    </row>
+    <row r="280" ht="15.75" customHeight="1">
+      <c r="B280" s="5"/>
+    </row>
+    <row r="281" ht="15.75" customHeight="1">
+      <c r="B281" s="5"/>
+    </row>
+    <row r="282" ht="15.75" customHeight="1">
+      <c r="B282" s="5"/>
+    </row>
+    <row r="283" ht="15.75" customHeight="1">
+      <c r="B283" s="5"/>
+    </row>
+    <row r="284" ht="15.75" customHeight="1">
+      <c r="B284" s="5"/>
+    </row>
+    <row r="285" ht="15.75" customHeight="1">
+      <c r="B285" s="5"/>
+    </row>
+    <row r="286" ht="15.75" customHeight="1">
+      <c r="B286" s="5"/>
+    </row>
+    <row r="287" ht="15.75" customHeight="1">
+      <c r="B287" s="5"/>
+    </row>
+    <row r="288" ht="15.75" customHeight="1">
+      <c r="B288" s="5"/>
+    </row>
+    <row r="289" ht="15.75" customHeight="1">
+      <c r="B289" s="5"/>
+    </row>
+    <row r="290" ht="15.75" customHeight="1">
+      <c r="B290" s="5"/>
+    </row>
+    <row r="291" ht="15.75" customHeight="1">
+      <c r="B291" s="5"/>
+    </row>
+    <row r="292" ht="15.75" customHeight="1">
+      <c r="B292" s="5"/>
+    </row>
+    <row r="293" ht="15.75" customHeight="1">
+      <c r="B293" s="5"/>
+    </row>
+    <row r="294" ht="15.75" customHeight="1">
+      <c r="B294" s="5"/>
+    </row>
+    <row r="295" ht="15.75" customHeight="1">
+      <c r="B295" s="5"/>
+    </row>
+    <row r="296" ht="15.75" customHeight="1">
+      <c r="B296" s="5"/>
+    </row>
+    <row r="297" ht="15.75" customHeight="1">
+      <c r="B297" s="5"/>
+    </row>
+    <row r="298" ht="15.75" customHeight="1">
+      <c r="B298" s="5"/>
+    </row>
+    <row r="299" ht="15.75" customHeight="1">
+      <c r="B299" s="5"/>
+    </row>
+    <row r="300" ht="15.75" customHeight="1">
+      <c r="B300" s="5"/>
+    </row>
+    <row r="301" ht="15.75" customHeight="1">
+      <c r="B301" s="5"/>
+    </row>
+    <row r="302" ht="15.75" customHeight="1">
+      <c r="B302" s="5"/>
+    </row>
+    <row r="303" ht="15.75" customHeight="1">
+      <c r="B303" s="5"/>
+    </row>
+    <row r="304" ht="15.75" customHeight="1">
+      <c r="B304" s="5"/>
+    </row>
+    <row r="305" ht="15.75" customHeight="1">
+      <c r="B305" s="5"/>
+    </row>
+    <row r="306" ht="15.75" customHeight="1">
+      <c r="B306" s="5"/>
+    </row>
+    <row r="307" ht="15.75" customHeight="1">
+      <c r="B307" s="5"/>
+    </row>
+    <row r="308" ht="15.75" customHeight="1">
+      <c r="B308" s="5"/>
+    </row>
+    <row r="309" ht="15.75" customHeight="1">
+      <c r="B309" s="5"/>
+    </row>
+    <row r="310" ht="15.75" customHeight="1">
+      <c r="B310" s="5"/>
+    </row>
+    <row r="311" ht="15.75" customHeight="1">
+      <c r="B311" s="5"/>
+    </row>
+    <row r="312" ht="15.75" customHeight="1">
+      <c r="B312" s="5"/>
+    </row>
+    <row r="313" ht="15.75" customHeight="1">
+      <c r="B313" s="5"/>
+    </row>
+    <row r="314" ht="15.75" customHeight="1">
+      <c r="B314" s="5"/>
+    </row>
+    <row r="315" ht="15.75" customHeight="1">
+      <c r="B315" s="5"/>
+    </row>
+    <row r="316" ht="15.75" customHeight="1">
+      <c r="B316" s="5"/>
+    </row>
+    <row r="317" ht="15.75" customHeight="1">
+      <c r="B317" s="5"/>
+    </row>
+    <row r="318" ht="15.75" customHeight="1">
+      <c r="B318" s="5"/>
+    </row>
+    <row r="319" ht="15.75" customHeight="1">
+      <c r="B319" s="5"/>
+    </row>
+    <row r="320" ht="15.75" customHeight="1">
+      <c r="B320" s="5"/>
+    </row>
+    <row r="321" ht="15.75" customHeight="1">
+      <c r="B321" s="5"/>
+    </row>
+    <row r="322" ht="15.75" customHeight="1">
+      <c r="B322" s="5"/>
+    </row>
+    <row r="323" ht="15.75" customHeight="1">
+      <c r="B323" s="5"/>
+    </row>
+    <row r="324" ht="15.75" customHeight="1">
+      <c r="B324" s="5"/>
+    </row>
+    <row r="325" ht="15.75" customHeight="1">
+      <c r="B325" s="5"/>
+    </row>
+    <row r="326" ht="15.75" customHeight="1">
+      <c r="B326" s="5"/>
+    </row>
+    <row r="327" ht="15.75" customHeight="1">
+      <c r="B327" s="5"/>
+    </row>
+    <row r="328" ht="15.75" customHeight="1">
+      <c r="B328" s="5"/>
+    </row>
+    <row r="329" ht="15.75" customHeight="1">
+      <c r="B329" s="5"/>
+    </row>
+    <row r="330" ht="15.75" customHeight="1">
+      <c r="B330" s="5"/>
+    </row>
+    <row r="331" ht="15.75" customHeight="1">
+      <c r="B331" s="5"/>
+    </row>
+    <row r="332" ht="15.75" customHeight="1">
+      <c r="B332" s="5"/>
+    </row>
+    <row r="333" ht="15.75" customHeight="1">
+      <c r="B333" s="5"/>
+    </row>
+    <row r="334" ht="15.75" customHeight="1">
+      <c r="B334" s="5"/>
+    </row>
+    <row r="335" ht="15.75" customHeight="1">
+      <c r="B335" s="5"/>
+    </row>
+    <row r="336" ht="15.75" customHeight="1">
+      <c r="B336" s="5"/>
+    </row>
+    <row r="337" ht="15.75" customHeight="1">
+      <c r="B337" s="5"/>
+    </row>
+    <row r="338" ht="15.75" customHeight="1">
+      <c r="B338" s="5"/>
+    </row>
+    <row r="339" ht="15.75" customHeight="1">
+      <c r="B339" s="5"/>
+    </row>
+    <row r="340" ht="15.75" customHeight="1">
+      <c r="B340" s="5"/>
+    </row>
+    <row r="341" ht="15.75" customHeight="1">
+      <c r="B341" s="5"/>
+    </row>
+    <row r="342" ht="15.75" customHeight="1">
+      <c r="B342" s="5"/>
+    </row>
+    <row r="343" ht="15.75" customHeight="1">
+      <c r="B343" s="5"/>
+    </row>
+    <row r="344" ht="15.75" customHeight="1">
+      <c r="B344" s="5"/>
+    </row>
+    <row r="345" ht="15.75" customHeight="1">
+      <c r="B345" s="5"/>
+    </row>
+    <row r="346" ht="15.75" customHeight="1">
+      <c r="B346" s="5"/>
+    </row>
+    <row r="347" ht="15.75" customHeight="1">
+      <c r="B347" s="5"/>
+    </row>
+    <row r="348" ht="15.75" customHeight="1">
+      <c r="B348" s="5"/>
+    </row>
+    <row r="349" ht="15.75" customHeight="1">
+      <c r="B349" s="5"/>
+    </row>
+    <row r="350" ht="15.75" customHeight="1">
+      <c r="B350" s="5"/>
+    </row>
+    <row r="351" ht="15.75" customHeight="1">
+      <c r="B351" s="5"/>
+    </row>
+    <row r="352" ht="15.75" customHeight="1">
+      <c r="B352" s="5"/>
+    </row>
+    <row r="353" ht="15.75" customHeight="1">
+      <c r="B353" s="5"/>
+    </row>
+    <row r="354" ht="15.75" customHeight="1">
+      <c r="B354" s="5"/>
+    </row>
+    <row r="355" ht="15.75" customHeight="1">
+      <c r="B355" s="5"/>
+    </row>
+    <row r="356" ht="15.75" customHeight="1">
+      <c r="B356" s="5"/>
+    </row>
+    <row r="357" ht="15.75" customHeight="1">
+      <c r="B357" s="5"/>
+    </row>
+    <row r="358" ht="15.75" customHeight="1">
+      <c r="B358" s="5"/>
+    </row>
+    <row r="359" ht="15.75" customHeight="1">
+      <c r="B359" s="5"/>
+    </row>
+    <row r="360" ht="15.75" customHeight="1">
+      <c r="B360" s="5"/>
+    </row>
+    <row r="361" ht="15.75" customHeight="1">
+      <c r="B361" s="5"/>
+    </row>
+    <row r="362" ht="15.75" customHeight="1">
+      <c r="B362" s="5"/>
+    </row>
+    <row r="363" ht="15.75" customHeight="1">
+      <c r="B363" s="5"/>
+    </row>
+    <row r="364" ht="15.75" customHeight="1">
+      <c r="B364" s="5"/>
+    </row>
+    <row r="365" ht="15.75" customHeight="1">
+      <c r="B365" s="5"/>
+    </row>
+    <row r="366" ht="15.75" customHeight="1">
+      <c r="B366" s="5"/>
+    </row>
+    <row r="367" ht="15.75" customHeight="1">
+      <c r="B367" s="5"/>
+    </row>
+    <row r="368" ht="15.75" customHeight="1">
+      <c r="B368" s="5"/>
+    </row>
+    <row r="369" ht="15.75" customHeight="1">
+      <c r="B369" s="5"/>
+    </row>
+    <row r="370" ht="15.75" customHeight="1">
+      <c r="B370" s="5"/>
+    </row>
+    <row r="371" ht="15.75" customHeight="1">
+      <c r="B371" s="5"/>
+    </row>
+    <row r="372" ht="15.75" customHeight="1">
+      <c r="B372" s="5"/>
+    </row>
+    <row r="373" ht="15.75" customHeight="1">
+      <c r="B373" s="5"/>
+    </row>
+    <row r="374" ht="15.75" customHeight="1">
+      <c r="B374" s="5"/>
+    </row>
+    <row r="375" ht="15.75" customHeight="1">
+      <c r="B375" s="5"/>
+    </row>
+    <row r="376" ht="15.75" customHeight="1">
+      <c r="B376" s="5"/>
+    </row>
+    <row r="377" ht="15.75" customHeight="1">
+      <c r="B377" s="5"/>
+    </row>
+    <row r="378" ht="15.75" customHeight="1">
+      <c r="B378" s="5"/>
+    </row>
+    <row r="379" ht="15.75" customHeight="1">
+      <c r="B379" s="5"/>
+    </row>
+    <row r="380" ht="15.75" customHeight="1">
+      <c r="B380" s="5"/>
+    </row>
+    <row r="381" ht="15.75" customHeight="1">
+      <c r="B381" s="5"/>
+    </row>
+    <row r="382" ht="15.75" customHeight="1">
+      <c r="B382" s="5"/>
+    </row>
+    <row r="383" ht="15.75" customHeight="1">
+      <c r="B383" s="5"/>
+    </row>
+    <row r="384" ht="15.75" customHeight="1">
+      <c r="B384" s="5"/>
+    </row>
+    <row r="385" ht="15.75" customHeight="1">
+      <c r="B385" s="5"/>
+    </row>
+    <row r="386" ht="15.75" customHeight="1">
+      <c r="B386" s="5"/>
+    </row>
+    <row r="387" ht="15.75" customHeight="1">
+      <c r="B387" s="5"/>
+    </row>
+    <row r="388" ht="15.75" customHeight="1">
+      <c r="B388" s="5"/>
+    </row>
+    <row r="389" ht="15.75" customHeight="1">
+      <c r="B389" s="5"/>
+    </row>
+    <row r="390" ht="15.75" customHeight="1">
+      <c r="B390" s="5"/>
+    </row>
+    <row r="391" ht="15.75" customHeight="1">
+      <c r="B391" s="5"/>
+    </row>
+    <row r="392" ht="15.75" customHeight="1">
+      <c r="B392" s="5"/>
+    </row>
+    <row r="393" ht="15.75" customHeight="1">
+      <c r="B393" s="5"/>
+    </row>
+    <row r="394" ht="15.75" customHeight="1">
+      <c r="B394" s="5"/>
+    </row>
+    <row r="395" ht="15.75" customHeight="1">
+      <c r="B395" s="5"/>
+    </row>
+    <row r="396" ht="15.75" customHeight="1">
+      <c r="B396" s="5"/>
+    </row>
+    <row r="397" ht="15.75" customHeight="1">
+      <c r="B397" s="5"/>
+    </row>
+    <row r="398" ht="15.75" customHeight="1">
+      <c r="B398" s="5"/>
+    </row>
+    <row r="399" ht="15.75" customHeight="1">
+      <c r="B399" s="5"/>
+    </row>
+    <row r="400" ht="15.75" customHeight="1">
+      <c r="B400" s="5"/>
+    </row>
+    <row r="401" ht="15.75" customHeight="1">
+      <c r="B401" s="5"/>
+    </row>
+    <row r="402" ht="15.75" customHeight="1">
+      <c r="B402" s="5"/>
+    </row>
+    <row r="403" ht="15.75" customHeight="1">
+      <c r="B403" s="5"/>
+    </row>
+    <row r="404" ht="15.75" customHeight="1">
+      <c r="B404" s="5"/>
+    </row>
+    <row r="405" ht="15.75" customHeight="1">
+      <c r="B405" s="5"/>
+    </row>
+    <row r="406" ht="15.75" customHeight="1">
+      <c r="B406" s="5"/>
+    </row>
+    <row r="407" ht="15.75" customHeight="1">
+      <c r="B407" s="5"/>
+    </row>
+    <row r="408" ht="15.75" customHeight="1">
+      <c r="B408" s="5"/>
+    </row>
+    <row r="409" ht="15.75" customHeight="1">
+      <c r="B409" s="5"/>
+    </row>
+    <row r="410" ht="15.75" customHeight="1">
+      <c r="B410" s="5"/>
+    </row>
+    <row r="411" ht="15.75" customHeight="1">
+      <c r="B411" s="5"/>
+    </row>
+    <row r="412" ht="15.75" customHeight="1">
+      <c r="B412" s="5"/>
+    </row>
+    <row r="413" ht="15.75" customHeight="1">
+      <c r="B413" s="5"/>
+    </row>
+    <row r="414" ht="15.75" customHeight="1">
+      <c r="B414" s="5"/>
+    </row>
+    <row r="415" ht="15.75" customHeight="1">
+      <c r="B415" s="5"/>
+    </row>
+    <row r="416" ht="15.75" customHeight="1">
+      <c r="B416" s="5"/>
+    </row>
+    <row r="417" ht="15.75" customHeight="1">
+      <c r="B417" s="5"/>
+    </row>
+    <row r="418" ht="15.75" customHeight="1">
+      <c r="B418" s="5"/>
+    </row>
+    <row r="419" ht="15.75" customHeight="1">
+      <c r="B419" s="5"/>
+    </row>
+    <row r="420" ht="15.75" customHeight="1">
+      <c r="B420" s="5"/>
+    </row>
+    <row r="421" ht="15.75" customHeight="1">
+      <c r="B421" s="5"/>
+    </row>
+    <row r="422" ht="15.75" customHeight="1">
+      <c r="B422" s="5"/>
+    </row>
+    <row r="423" ht="15.75" customHeight="1">
+      <c r="B423" s="5"/>
+    </row>
+    <row r="424" ht="15.75" customHeight="1">
+      <c r="B424" s="5"/>
+    </row>
+    <row r="425" ht="15.75" customHeight="1">
+      <c r="B425" s="5"/>
+    </row>
+    <row r="426" ht="15.75" customHeight="1">
+      <c r="B426" s="5"/>
+    </row>
+    <row r="427" ht="15.75" customHeight="1">
+      <c r="B427" s="5"/>
+    </row>
+    <row r="428" ht="15.75" customHeight="1">
+      <c r="B428" s="5"/>
+    </row>
+    <row r="429" ht="15.75" customHeight="1">
+      <c r="B429" s="5"/>
+    </row>
+    <row r="430" ht="15.75" customHeight="1">
+      <c r="B430" s="5"/>
+    </row>
+    <row r="431" ht="15.75" customHeight="1">
+      <c r="B431" s="5"/>
+    </row>
+    <row r="432" ht="15.75" customHeight="1">
+      <c r="B432" s="5"/>
+    </row>
+    <row r="433" ht="15.75" customHeight="1">
+      <c r="B433" s="5"/>
+    </row>
+    <row r="434" ht="15.75" customHeight="1">
+      <c r="B434" s="5"/>
+    </row>
+    <row r="435" ht="15.75" customHeight="1">
+      <c r="B435" s="5"/>
+    </row>
+    <row r="436" ht="15.75" customHeight="1">
+      <c r="B436" s="5"/>
+    </row>
+    <row r="437" ht="15.75" customHeight="1">
+      <c r="B437" s="5"/>
+    </row>
+    <row r="438" ht="15.75" customHeight="1">
+      <c r="B438" s="5"/>
+    </row>
+    <row r="439" ht="15.75" customHeight="1">
+      <c r="B439" s="5"/>
+    </row>
+    <row r="440" ht="15.75" customHeight="1">
+      <c r="B440" s="5"/>
+    </row>
+    <row r="441" ht="15.75" customHeight="1">
+      <c r="B441" s="5"/>
+    </row>
+    <row r="442" ht="15.75" customHeight="1">
+      <c r="B442" s="5"/>
+    </row>
+    <row r="443" ht="15.75" customHeight="1">
+      <c r="B443" s="5"/>
+    </row>
+    <row r="444" ht="15.75" customHeight="1">
+      <c r="B444" s="5"/>
+    </row>
+    <row r="445" ht="15.75" customHeight="1">
+      <c r="B445" s="5"/>
+    </row>
+    <row r="446" ht="15.75" customHeight="1">
+      <c r="B446" s="5"/>
+    </row>
+    <row r="447" ht="15.75" customHeight="1">
+      <c r="B447" s="5"/>
+    </row>
+    <row r="448" ht="15.75" customHeight="1">
+      <c r="B448" s="5"/>
+    </row>
+    <row r="449" ht="15.75" customHeight="1">
+      <c r="B449" s="5"/>
+    </row>
+    <row r="450" ht="15.75" customHeight="1">
+      <c r="B450" s="5"/>
+    </row>
+    <row r="451" ht="15.75" customHeight="1">
+      <c r="B451" s="5"/>
+    </row>
+    <row r="452" ht="15.75" customHeight="1">
+      <c r="B452" s="5"/>
+    </row>
+    <row r="453" ht="15.75" customHeight="1">
+      <c r="B453" s="5"/>
+    </row>
+    <row r="454" ht="15.75" customHeight="1">
+      <c r="B454" s="5"/>
+    </row>
+    <row r="455" ht="15.75" customHeight="1">
+      <c r="B455" s="5"/>
+    </row>
+    <row r="456" ht="15.75" customHeight="1">
+      <c r="B456" s="5"/>
+    </row>
+    <row r="457" ht="15.75" customHeight="1">
+      <c r="B457" s="5"/>
+    </row>
+    <row r="458" ht="15.75" customHeight="1">
+      <c r="B458" s="5"/>
+    </row>
+    <row r="459" ht="15.75" customHeight="1">
+      <c r="B459" s="5"/>
+    </row>
+    <row r="460" ht="15.75" customHeight="1">
+      <c r="B460" s="5"/>
+    </row>
+    <row r="461" ht="15.75" customHeight="1">
+      <c r="B461" s="5"/>
+    </row>
+    <row r="462" ht="15.75" customHeight="1">
+      <c r="B462" s="5"/>
+    </row>
+    <row r="463" ht="15.75" customHeight="1">
+      <c r="B463" s="5"/>
+    </row>
+    <row r="464" ht="15.75" customHeight="1">
+      <c r="B464" s="5"/>
+    </row>
+    <row r="465" ht="15.75" customHeight="1">
+      <c r="B465" s="5"/>
+    </row>
+    <row r="466" ht="15.75" customHeight="1">
+      <c r="B466" s="5"/>
+    </row>
+    <row r="467" ht="15.75" customHeight="1">
+      <c r="B467" s="5"/>
+    </row>
+    <row r="468" ht="15.75" customHeight="1">
+      <c r="B468" s="5"/>
+    </row>
+    <row r="469" ht="15.75" customHeight="1">
+      <c r="B469" s="5"/>
+    </row>
+    <row r="470" ht="15.75" customHeight="1">
+      <c r="B470" s="5"/>
+    </row>
+    <row r="471" ht="15.75" customHeight="1">
+      <c r="B471" s="5"/>
+    </row>
+    <row r="472" ht="15.75" customHeight="1">
+      <c r="B472" s="5"/>
+    </row>
+    <row r="473" ht="15.75" customHeight="1">
+      <c r="B473" s="5"/>
+    </row>
+    <row r="474" ht="15.75" customHeight="1">
+      <c r="B474" s="5"/>
+    </row>
+    <row r="475" ht="15.75" customHeight="1">
+      <c r="B475" s="5"/>
+    </row>
+    <row r="476" ht="15.75" customHeight="1">
+      <c r="B476" s="5"/>
+    </row>
+    <row r="477" ht="15.75" customHeight="1">
+      <c r="B477" s="5"/>
+    </row>
+    <row r="478" ht="15.75" customHeight="1">
+      <c r="B478" s="5"/>
+    </row>
+    <row r="479" ht="15.75" customHeight="1">
+      <c r="B479" s="5"/>
+    </row>
+    <row r="480" ht="15.75" customHeight="1">
+      <c r="B480" s="5"/>
+    </row>
+    <row r="481" ht="15.75" customHeight="1">
+      <c r="B481" s="5"/>
+    </row>
+    <row r="482" ht="15.75" customHeight="1">
+      <c r="B482" s="5"/>
+    </row>
+    <row r="483" ht="15.75" customHeight="1">
+      <c r="B483" s="5"/>
+    </row>
+    <row r="484" ht="15.75" customHeight="1">
+      <c r="B484" s="5"/>
+    </row>
+    <row r="485" ht="15.75" customHeight="1">
+      <c r="B485" s="5"/>
+    </row>
+    <row r="486" ht="15.75" customHeight="1">
+      <c r="B486" s="5"/>
+    </row>
+    <row r="487" ht="15.75" customHeight="1">
+      <c r="B487" s="5"/>
+    </row>
+    <row r="488" ht="15.75" customHeight="1">
+      <c r="B488" s="5"/>
+    </row>
+    <row r="489" ht="15.75" customHeight="1">
+      <c r="B489" s="5"/>
+    </row>
+    <row r="490" ht="15.75" customHeight="1">
+      <c r="B490" s="5"/>
+    </row>
+    <row r="491" ht="15.75" customHeight="1">
+      <c r="B491" s="5"/>
+    </row>
+    <row r="492" ht="15.75" customHeight="1">
+      <c r="B492" s="5"/>
+    </row>
+    <row r="493" ht="15.75" customHeight="1">
+      <c r="B493" s="5"/>
+    </row>
+    <row r="494" ht="15.75" customHeight="1">
+      <c r="B494" s="5"/>
+    </row>
+    <row r="495" ht="15.75" customHeight="1">
+      <c r="B495" s="5"/>
+    </row>
+    <row r="496" ht="15.75" customHeight="1">
+      <c r="B496" s="5"/>
+    </row>
+    <row r="497" ht="15.75" customHeight="1">
+      <c r="B497" s="5"/>
+    </row>
+    <row r="498" ht="15.75" customHeight="1">
+      <c r="B498" s="5"/>
+    </row>
+    <row r="499" ht="15.75" customHeight="1">
+      <c r="B499" s="5"/>
+    </row>
+    <row r="500" ht="15.75" customHeight="1">
+      <c r="B500" s="5"/>
+    </row>
+    <row r="501" ht="15.75" customHeight="1">
+      <c r="B501" s="5"/>
+    </row>
+    <row r="502" ht="15.75" customHeight="1">
+      <c r="B502" s="5"/>
+    </row>
+    <row r="503" ht="15.75" customHeight="1">
+      <c r="B503" s="5"/>
+    </row>
+    <row r="504" ht="15.75" customHeight="1">
+      <c r="B504" s="5"/>
+    </row>
+    <row r="505" ht="15.75" customHeight="1">
+      <c r="B505" s="5"/>
+    </row>
+    <row r="506" ht="15.75" customHeight="1">
+      <c r="B506" s="5"/>
+    </row>
+    <row r="507" ht="15.75" customHeight="1">
+      <c r="B507" s="5"/>
+    </row>
+    <row r="508" ht="15.75" customHeight="1">
+      <c r="B508" s="5"/>
+    </row>
+    <row r="509" ht="15.75" customHeight="1">
+      <c r="B509" s="5"/>
+    </row>
+    <row r="510" ht="15.75" customHeight="1">
+      <c r="B510" s="5"/>
+    </row>
+    <row r="511" ht="15.75" customHeight="1">
+      <c r="B511" s="5"/>
+    </row>
+    <row r="512" ht="15.75" customHeight="1">
+      <c r="B512" s="5"/>
+    </row>
+    <row r="513" ht="15.75" customHeight="1">
+      <c r="B513" s="5"/>
+    </row>
+    <row r="514" ht="15.75" customHeight="1">
+      <c r="B514" s="5"/>
+    </row>
+    <row r="515" ht="15.75" customHeight="1">
+      <c r="B515" s="5"/>
+    </row>
+    <row r="516" ht="15.75" customHeight="1">
+      <c r="B516" s="5"/>
+    </row>
+    <row r="517" ht="15.75" customHeight="1">
+      <c r="B517" s="5"/>
+    </row>
+    <row r="518" ht="15.75" customHeight="1">
+      <c r="B518" s="5"/>
+    </row>
+    <row r="519" ht="15.75" customHeight="1">
+      <c r="B519" s="5"/>
+    </row>
+    <row r="520" ht="15.75" customHeight="1">
+      <c r="B520" s="5"/>
+    </row>
+    <row r="521" ht="15.75" customHeight="1">
+      <c r="B521" s="5"/>
+    </row>
+    <row r="522" ht="15.75" customHeight="1">
+      <c r="B522" s="5"/>
+    </row>
+    <row r="523" ht="15.75" customHeight="1">
+      <c r="B523" s="5"/>
+    </row>
+    <row r="524" ht="15.75" customHeight="1">
+      <c r="B524" s="5"/>
+    </row>
+    <row r="525" ht="15.75" customHeight="1">
+      <c r="B525" s="5"/>
+    </row>
+    <row r="526" ht="15.75" customHeight="1">
+      <c r="B526" s="5"/>
+    </row>
+    <row r="527" ht="15.75" customHeight="1">
+      <c r="B527" s="5"/>
+    </row>
+    <row r="528" ht="15.75" customHeight="1">
+      <c r="B528" s="5"/>
+    </row>
+    <row r="529" ht="15.75" customHeight="1">
+      <c r="B529" s="5"/>
+    </row>
+    <row r="530" ht="15.75" customHeight="1">
+      <c r="B530" s="5"/>
+    </row>
+    <row r="531" ht="15.75" customHeight="1">
+      <c r="B531" s="5"/>
+    </row>
+    <row r="532" ht="15.75" customHeight="1">
+      <c r="B532" s="5"/>
+    </row>
+    <row r="533" ht="15.75" customHeight="1">
+      <c r="B533" s="5"/>
+    </row>
+    <row r="534" ht="15.75" customHeight="1">
+      <c r="B534" s="5"/>
+    </row>
+    <row r="535" ht="15.75" customHeight="1">
+      <c r="B535" s="5"/>
+    </row>
+    <row r="536" ht="15.75" customHeight="1">
+      <c r="B536" s="5"/>
+    </row>
+    <row r="537" ht="15.75" customHeight="1">
+      <c r="B537" s="5"/>
+    </row>
+    <row r="538" ht="15.75" customHeight="1">
+      <c r="B538" s="5"/>
+    </row>
+    <row r="539" ht="15.75" customHeight="1">
+      <c r="B539" s="5"/>
+    </row>
+    <row r="540" ht="15.75" customHeight="1">
+      <c r="B540" s="5"/>
+    </row>
+    <row r="541" ht="15.75" customHeight="1">
+      <c r="B541" s="5"/>
+    </row>
+    <row r="542" ht="15.75" customHeight="1">
+      <c r="B542" s="5"/>
+    </row>
+    <row r="543" ht="15.75" customHeight="1">
+      <c r="B543" s="5"/>
+    </row>
+    <row r="544" ht="15.75" customHeight="1">
+      <c r="B544" s="5"/>
+    </row>
+    <row r="545" ht="15.75" customHeight="1">
+      <c r="B545" s="5"/>
+    </row>
+    <row r="546" ht="15.75" customHeight="1">
+      <c r="B546" s="5"/>
+    </row>
+    <row r="547" ht="15.75" customHeight="1">
+      <c r="B547" s="5"/>
+    </row>
+    <row r="548" ht="15.75" customHeight="1">
+      <c r="B548" s="5"/>
+    </row>
+    <row r="549" ht="15.75" customHeight="1">
+      <c r="B549" s="5"/>
+    </row>
+    <row r="550" ht="15.75" customHeight="1">
+      <c r="B550" s="5"/>
+    </row>
+    <row r="551" ht="15.75" customHeight="1">
+      <c r="B551" s="5"/>
+    </row>
+    <row r="552" ht="15.75" customHeight="1">
+      <c r="B552" s="5"/>
+    </row>
+    <row r="553" ht="15.75" customHeight="1">
+      <c r="B553" s="5"/>
+    </row>
+    <row r="554" ht="15.75" customHeight="1">
+      <c r="B554" s="5"/>
+    </row>
+    <row r="555" ht="15.75" customHeight="1">
+      <c r="B555" s="5"/>
+    </row>
+    <row r="556" ht="15.75" customHeight="1">
+      <c r="B556" s="5"/>
+    </row>
+    <row r="557" ht="15.75" customHeight="1">
+      <c r="B557" s="5"/>
+    </row>
+    <row r="558" ht="15.75" customHeight="1">
+      <c r="B558" s="5"/>
+    </row>
+    <row r="559" ht="15.75" customHeight="1">
+      <c r="B559" s="5"/>
+    </row>
+    <row r="560" ht="15.75" customHeight="1">
+      <c r="B560" s="5"/>
+    </row>
+    <row r="561" ht="15.75" customHeight="1">
+      <c r="B561" s="5"/>
+    </row>
+    <row r="562" ht="15.75" customHeight="1">
+      <c r="B562" s="5"/>
+    </row>
+    <row r="563" ht="15.75" customHeight="1">
+      <c r="B563" s="5"/>
+    </row>
+    <row r="564" ht="15.75" customHeight="1">
+      <c r="B564" s="5"/>
+    </row>
+    <row r="565" ht="15.75" customHeight="1">
+      <c r="B565" s="5"/>
+    </row>
+    <row r="566" ht="15.75" customHeight="1">
+      <c r="B566" s="5"/>
+    </row>
+    <row r="567" ht="15.75" customHeight="1">
+      <c r="B567" s="5"/>
+    </row>
+    <row r="568" ht="15.75" customHeight="1">
+      <c r="B568" s="5"/>
+    </row>
+    <row r="569" ht="15.75" customHeight="1">
+      <c r="B569" s="5"/>
+    </row>
+    <row r="570" ht="15.75" customHeight="1">
+      <c r="B570" s="5"/>
+    </row>
+    <row r="571" ht="15.75" customHeight="1">
+      <c r="B571" s="5"/>
+    </row>
+    <row r="572" ht="15.75" customHeight="1">
+      <c r="B572" s="5"/>
+    </row>
+    <row r="573" ht="15.75" customHeight="1">
+      <c r="B573" s="5"/>
+    </row>
+    <row r="574" ht="15.75" customHeight="1">
+      <c r="B574" s="5"/>
+    </row>
+    <row r="575" ht="15.75" customHeight="1">
+      <c r="B575" s="5"/>
+    </row>
+    <row r="576" ht="15.75" customHeight="1">
+      <c r="B576" s="5"/>
+    </row>
+    <row r="577" ht="15.75" customHeight="1">
+      <c r="B577" s="5"/>
+    </row>
+    <row r="578" ht="15.75" customHeight="1">
+      <c r="B578" s="5"/>
+    </row>
+    <row r="579" ht="15.75" customHeight="1">
+      <c r="B579" s="5"/>
+    </row>
+    <row r="580" ht="15.75" customHeight="1">
+      <c r="B580" s="5"/>
+    </row>
+    <row r="581" ht="15.75" customHeight="1">
+      <c r="B581" s="5"/>
+    </row>
+    <row r="582" ht="15.75" customHeight="1">
+      <c r="B582" s="5"/>
+    </row>
+    <row r="583" ht="15.75" customHeight="1">
+      <c r="B583" s="5"/>
+    </row>
+    <row r="584" ht="15.75" customHeight="1">
+      <c r="B584" s="5"/>
+    </row>
+    <row r="585" ht="15.75" customHeight="1">
+      <c r="B585" s="5"/>
+    </row>
+    <row r="586" ht="15.75" customHeight="1">
+      <c r="B586" s="5"/>
+    </row>
+    <row r="587" ht="15.75" customHeight="1">
+      <c r="B587" s="5"/>
+    </row>
+    <row r="588" ht="15.75" customHeight="1">
+      <c r="B588" s="5"/>
+    </row>
+    <row r="589" ht="15.75" customHeight="1">
+      <c r="B589" s="5"/>
+    </row>
+    <row r="590" ht="15.75" customHeight="1">
+      <c r="B590" s="5"/>
+    </row>
+    <row r="591" ht="15.75" customHeight="1">
+      <c r="B591" s="5"/>
+    </row>
+    <row r="592" ht="15.75" customHeight="1">
+      <c r="B592" s="5"/>
+    </row>
+    <row r="593" ht="15.75" customHeight="1">
+      <c r="B593" s="5"/>
+    </row>
+    <row r="594" ht="15.75" customHeight="1">
+      <c r="B594" s="5"/>
+    </row>
+    <row r="595" ht="15.75" customHeight="1">
+      <c r="B595" s="5"/>
+    </row>
+    <row r="596" ht="15.75" customHeight="1">
+      <c r="B596" s="5"/>
+    </row>
+    <row r="597" ht="15.75" customHeight="1">
+      <c r="B597" s="5"/>
+    </row>
+    <row r="598" ht="15.75" customHeight="1">
+      <c r="B598" s="5"/>
+    </row>
+    <row r="599" ht="15.75" customHeight="1">
+      <c r="B599" s="5"/>
+    </row>
+    <row r="600" ht="15.75" customHeight="1">
+      <c r="B600" s="5"/>
+    </row>
+    <row r="601" ht="15.75" customHeight="1">
+      <c r="B601" s="5"/>
+    </row>
+    <row r="602" ht="15.75" customHeight="1">
+      <c r="B602" s="5"/>
+    </row>
+    <row r="603" ht="15.75" customHeight="1">
+      <c r="B603" s="5"/>
+    </row>
+    <row r="604" ht="15.75" customHeight="1">
+      <c r="B604" s="5"/>
+    </row>
+    <row r="605" ht="15.75" customHeight="1">
+      <c r="B605" s="5"/>
+    </row>
+    <row r="606" ht="15.75" customHeight="1">
+      <c r="B606" s="5"/>
+    </row>
+    <row r="607" ht="15.75" customHeight="1">
+      <c r="B607" s="5"/>
+    </row>
+    <row r="608" ht="15.75" customHeight="1">
+      <c r="B608" s="5"/>
+    </row>
+    <row r="609" ht="15.75" customHeight="1">
+      <c r="B609" s="5"/>
+    </row>
+    <row r="610" ht="15.75" customHeight="1">
+      <c r="B610" s="5"/>
+    </row>
+    <row r="611" ht="15.75" customHeight="1">
+      <c r="B611" s="5"/>
+    </row>
+    <row r="612" ht="15.75" customHeight="1">
+      <c r="B612" s="5"/>
+    </row>
+    <row r="613" ht="15.75" customHeight="1">
+      <c r="B613" s="5"/>
+    </row>
+    <row r="614" ht="15.75" customHeight="1">
+      <c r="B614" s="5"/>
+    </row>
+    <row r="615" ht="15.75" customHeight="1">
+      <c r="B615" s="5"/>
+    </row>
+    <row r="616" ht="15.75" customHeight="1">
+      <c r="B616" s="5"/>
+    </row>
+    <row r="617" ht="15.75" customHeight="1">
+      <c r="B617" s="5"/>
+    </row>
+    <row r="618" ht="15.75" customHeight="1">
+      <c r="B618" s="5"/>
+    </row>
+    <row r="619" ht="15.75" customHeight="1">
+      <c r="B619" s="5"/>
+    </row>
+    <row r="620" ht="15.75" customHeight="1">
+      <c r="B620" s="5"/>
+    </row>
+    <row r="621" ht="15.75" customHeight="1">
+      <c r="B621" s="5"/>
+    </row>
+    <row r="622" ht="15.75" customHeight="1">
+      <c r="B622" s="5"/>
+    </row>
+    <row r="623" ht="15.75" customHeight="1">
+      <c r="B623" s="5"/>
+    </row>
+    <row r="624" ht="15.75" customHeight="1">
+      <c r="B624" s="5"/>
+    </row>
+    <row r="625" ht="15.75" customHeight="1">
+      <c r="B625" s="5"/>
+    </row>
+    <row r="626" ht="15.75" customHeight="1">
+      <c r="B626" s="5"/>
+    </row>
+    <row r="627" ht="15.75" customHeight="1">
+      <c r="B627" s="5"/>
+    </row>
+    <row r="628" ht="15.75" customHeight="1">
+      <c r="B628" s="5"/>
+    </row>
+    <row r="629" ht="15.75" customHeight="1">
+      <c r="B629" s="5"/>
+    </row>
+    <row r="630" ht="15.75" customHeight="1">
+      <c r="B630" s="5"/>
+    </row>
+    <row r="631" ht="15.75" customHeight="1">
+      <c r="B631" s="5"/>
+    </row>
+    <row r="632" ht="15.75" customHeight="1">
+      <c r="B632" s="5"/>
+    </row>
+    <row r="633" ht="15.75" customHeight="1">
+      <c r="B633" s="5"/>
+    </row>
+    <row r="634" ht="15.75" customHeight="1">
+      <c r="B634" s="5"/>
+    </row>
+    <row r="635" ht="15.75" customHeight="1">
+      <c r="B635" s="5"/>
+    </row>
+    <row r="636" ht="15.75" customHeight="1">
+      <c r="B636" s="5"/>
+    </row>
+    <row r="637" ht="15.75" customHeight="1">
+      <c r="B637" s="5"/>
+    </row>
+    <row r="638" ht="15.75" customHeight="1">
+      <c r="B638" s="5"/>
+    </row>
+    <row r="639" ht="15.75" customHeight="1">
+      <c r="B639" s="5"/>
+    </row>
+    <row r="640" ht="15.75" customHeight="1">
+      <c r="B640" s="5"/>
+    </row>
+    <row r="641" ht="15.75" customHeight="1">
+      <c r="B641" s="5"/>
+    </row>
+    <row r="642" ht="15.75" customHeight="1">
+      <c r="B642" s="5"/>
+    </row>
+    <row r="643" ht="15.75" customHeight="1">
+      <c r="B643" s="5"/>
+    </row>
+    <row r="644" ht="15.75" customHeight="1">
+      <c r="B644" s="5"/>
+    </row>
+    <row r="645" ht="15.75" customHeight="1">
+      <c r="B645" s="5"/>
+    </row>
+    <row r="646" ht="15.75" customHeight="1">
+      <c r="B646" s="5"/>
+    </row>
+    <row r="647" ht="15.75" customHeight="1">
+      <c r="B647" s="5"/>
+    </row>
+    <row r="648" ht="15.75" customHeight="1">
+      <c r="B648" s="5"/>
+    </row>
+    <row r="649" ht="15.75" customHeight="1">
+      <c r="B649" s="5"/>
+    </row>
+    <row r="650" ht="15.75" customHeight="1">
+      <c r="B650" s="5"/>
+    </row>
+    <row r="651" ht="15.75" customHeight="1">
+      <c r="B651" s="5"/>
+    </row>
+    <row r="652" ht="15.75" customHeight="1">
+      <c r="B652" s="5"/>
+    </row>
+    <row r="653" ht="15.75" customHeight="1">
+      <c r="B653" s="5"/>
+    </row>
+    <row r="654" ht="15.75" customHeight="1">
+      <c r="B654" s="5"/>
+    </row>
+    <row r="655" ht="15.75" customHeight="1">
+      <c r="B655" s="5"/>
+    </row>
+    <row r="656" ht="15.75" customHeight="1">
+      <c r="B656" s="5"/>
+    </row>
+    <row r="657" ht="15.75" customHeight="1">
+      <c r="B657" s="5"/>
+    </row>
+    <row r="658" ht="15.75" customHeight="1">
+      <c r="B658" s="5"/>
+    </row>
+    <row r="659" ht="15.75" customHeight="1">
+      <c r="B659" s="5"/>
+    </row>
+    <row r="660" ht="15.75" customHeight="1">
+      <c r="B660" s="5"/>
+    </row>
+    <row r="661" ht="15.75" customHeight="1">
+      <c r="B661" s="5"/>
+    </row>
+    <row r="662" ht="15.75" customHeight="1">
+      <c r="B662" s="5"/>
+    </row>
+    <row r="663" ht="15.75" customHeight="1">
+      <c r="B663" s="5"/>
+    </row>
+    <row r="664" ht="15.75" customHeight="1">
+      <c r="B664" s="5"/>
+    </row>
+    <row r="665" ht="15.75" customHeight="1">
+      <c r="B665" s="5"/>
+    </row>
+    <row r="666" ht="15.75" customHeight="1">
+      <c r="B666" s="5"/>
+    </row>
+    <row r="667" ht="15.75" customHeight="1">
+      <c r="B667" s="5"/>
+    </row>
+    <row r="668" ht="15.75" customHeight="1">
+      <c r="B668" s="5"/>
+    </row>
+    <row r="669" ht="15.75" customHeight="1">
+      <c r="B669" s="5"/>
+    </row>
+    <row r="670" ht="15.75" customHeight="1">
+      <c r="B670" s="5"/>
+    </row>
+    <row r="671" ht="15.75" customHeight="1">
+      <c r="B671" s="5"/>
+    </row>
+    <row r="672" ht="15.75" customHeight="1">
+      <c r="B672" s="5"/>
+    </row>
+    <row r="673" ht="15.75" customHeight="1">
+      <c r="B673" s="5"/>
+    </row>
+    <row r="674" ht="15.75" customHeight="1">
+      <c r="B674" s="5"/>
+    </row>
+    <row r="675" ht="15.75" customHeight="1">
+      <c r="B675" s="5"/>
+    </row>
+    <row r="676" ht="15.75" customHeight="1">
+      <c r="B676" s="5"/>
+    </row>
+    <row r="677" ht="15.75" customHeight="1">
+      <c r="B677" s="5"/>
+    </row>
+    <row r="678" ht="15.75" customHeight="1">
+      <c r="B678" s="5"/>
+    </row>
+    <row r="679" ht="15.75" customHeight="1">
+      <c r="B679" s="5"/>
+    </row>
+    <row r="680" ht="15.75" customHeight="1">
+      <c r="B680" s="5"/>
+    </row>
+    <row r="681" ht="15.75" customHeight="1">
+      <c r="B681" s="5"/>
+    </row>
+    <row r="682" ht="15.75" customHeight="1">
+      <c r="B682" s="5"/>
+    </row>
+    <row r="683" ht="15.75" customHeight="1">
+      <c r="B683" s="5"/>
+    </row>
+    <row r="684" ht="15.75" customHeight="1">
+      <c r="B684" s="5"/>
+    </row>
+    <row r="685" ht="15.75" customHeight="1">
+      <c r="B685" s="5"/>
+    </row>
+    <row r="686" ht="15.75" customHeight="1">
+      <c r="B686" s="5"/>
+    </row>
+    <row r="687" ht="15.75" customHeight="1">
+      <c r="B687" s="5"/>
+    </row>
+    <row r="688" ht="15.75" customHeight="1">
+      <c r="B688" s="5"/>
+    </row>
+    <row r="689" ht="15.75" customHeight="1">
+      <c r="B689" s="5"/>
+    </row>
+    <row r="690" ht="15.75" customHeight="1">
+      <c r="B690" s="5"/>
+    </row>
+    <row r="691" ht="15.75" customHeight="1">
+      <c r="B691" s="5"/>
+    </row>
+    <row r="692" ht="15.75" customHeight="1">
+      <c r="B692" s="5"/>
+    </row>
+    <row r="693" ht="15.75" customHeight="1">
+      <c r="B693" s="5"/>
+    </row>
+    <row r="694" ht="15.75" customHeight="1">
+      <c r="B694" s="5"/>
+    </row>
+    <row r="695" ht="15.75" customHeight="1">
+      <c r="B695" s="5"/>
+    </row>
+    <row r="696" ht="15.75" customHeight="1">
+      <c r="B696" s="5"/>
+    </row>
+    <row r="697" ht="15.75" customHeight="1">
+      <c r="B697" s="5"/>
+    </row>
+    <row r="698" ht="15.75" customHeight="1">
+      <c r="B698" s="5"/>
+    </row>
+    <row r="699" ht="15.75" customHeight="1">
+      <c r="B699" s="5"/>
+    </row>
+    <row r="700" ht="15.75" customHeight="1">
+      <c r="B700" s="5"/>
+    </row>
+    <row r="701" ht="15.75" customHeight="1">
+      <c r="B701" s="5"/>
+    </row>
+    <row r="702" ht="15.75" customHeight="1">
+      <c r="B702" s="5"/>
+    </row>
+    <row r="703" ht="15.75" customHeight="1">
+      <c r="B703" s="5"/>
+    </row>
+    <row r="704" ht="15.75" customHeight="1">
+      <c r="B704" s="5"/>
+    </row>
+    <row r="705" ht="15.75" customHeight="1">
+      <c r="B705" s="5"/>
+    </row>
+    <row r="706" ht="15.75" customHeight="1">
+      <c r="B706" s="5"/>
+    </row>
+    <row r="707" ht="15.75" customHeight="1">
+      <c r="B707" s="5"/>
+    </row>
+    <row r="708" ht="15.75" customHeight="1">
+      <c r="B708" s="5"/>
+    </row>
+    <row r="709" ht="15.75" customHeight="1">
+      <c r="B709" s="5"/>
+    </row>
+    <row r="710" ht="15.75" customHeight="1">
+      <c r="B710" s="5"/>
+    </row>
+    <row r="711" ht="15.75" customHeight="1">
+      <c r="B711" s="5"/>
+    </row>
+    <row r="712" ht="15.75" customHeight="1">
+      <c r="B712" s="5"/>
+    </row>
+    <row r="713" ht="15.75" customHeight="1">
+      <c r="B713" s="5"/>
+    </row>
+    <row r="714" ht="15.75" customHeight="1">
+      <c r="B714" s="5"/>
+    </row>
+    <row r="715" ht="15.75" customHeight="1">
+      <c r="B715" s="5"/>
+    </row>
+    <row r="716" ht="15.75" customHeight="1">
+      <c r="B716" s="5"/>
+    </row>
+    <row r="717" ht="15.75" customHeight="1">
+      <c r="B717" s="5"/>
+    </row>
+    <row r="718" ht="15.75" customHeight="1">
+      <c r="B718" s="5"/>
+    </row>
+    <row r="719" ht="15.75" customHeight="1">
+      <c r="B719" s="5"/>
+    </row>
+    <row r="720" ht="15.75" customHeight="1">
+      <c r="B720" s="5"/>
+    </row>
+    <row r="721" ht="15.75" customHeight="1">
+      <c r="B721" s="5"/>
+    </row>
+    <row r="722" ht="15.75" customHeight="1">
+      <c r="B722" s="5"/>
+    </row>
+    <row r="723" ht="15.75" customHeight="1">
+      <c r="B723" s="5"/>
+    </row>
+    <row r="724" ht="15.75" customHeight="1">
+      <c r="B724" s="5"/>
+    </row>
+    <row r="725" ht="15.75" customHeight="1">
+      <c r="B725" s="5"/>
+    </row>
+    <row r="726" ht="15.75" customHeight="1">
+      <c r="B726" s="5"/>
+    </row>
+    <row r="727" ht="15.75" customHeight="1">
+      <c r="B727" s="5"/>
+    </row>
+    <row r="728" ht="15.75" customHeight="1">
+      <c r="B728" s="5"/>
+    </row>
+    <row r="729" ht="15.75" customHeight="1">
+      <c r="B729" s="5"/>
+    </row>
+    <row r="730" ht="15.75" customHeight="1">
+      <c r="B730" s="5"/>
+    </row>
+    <row r="731" ht="15.75" customHeight="1">
+      <c r="B731" s="5"/>
+    </row>
+    <row r="732" ht="15.75" customHeight="1">
+      <c r="B732" s="5"/>
+    </row>
+    <row r="733" ht="15.75" customHeight="1">
+      <c r="B733" s="5"/>
+    </row>
+    <row r="734" ht="15.75" customHeight="1">
+      <c r="B734" s="5"/>
+    </row>
+    <row r="735" ht="15.75" customHeight="1">
+      <c r="B735" s="5"/>
+    </row>
+    <row r="736" ht="15.75" customHeight="1">
+      <c r="B736" s="5"/>
+    </row>
+    <row r="737" ht="15.75" customHeight="1">
+      <c r="B737" s="5"/>
+    </row>
+    <row r="738" ht="15.75" customHeight="1">
+      <c r="B738" s="5"/>
+    </row>
+    <row r="739" ht="15.75" customHeight="1">
+      <c r="B739" s="5"/>
+    </row>
+    <row r="740" ht="15.75" customHeight="1">
+      <c r="B740" s="5"/>
+    </row>
+    <row r="741" ht="15.75" customHeight="1">
+      <c r="B741" s="5"/>
+    </row>
+    <row r="742" ht="15.75" customHeight="1">
+      <c r="B742" s="5"/>
+    </row>
+    <row r="743" ht="15.75" customHeight="1">
+      <c r="B743" s="5"/>
+    </row>
+    <row r="744" ht="15.75" customHeight="1">
+      <c r="B744" s="5"/>
+    </row>
+    <row r="745" ht="15.75" customHeight="1">
+      <c r="B745" s="5"/>
+    </row>
+    <row r="746" ht="15.75" customHeight="1">
+      <c r="B746" s="5"/>
+    </row>
+    <row r="747" ht="15.75" customHeight="1">
+      <c r="B747" s="5"/>
+    </row>
+    <row r="748" ht="15.75" customHeight="1">
+      <c r="B748" s="5"/>
+    </row>
+    <row r="749" ht="15.75" customHeight="1">
+      <c r="B749" s="5"/>
+    </row>
+    <row r="750" ht="15.75" customHeight="1">
+      <c r="B750" s="5"/>
+    </row>
+    <row r="751" ht="15.75" customHeight="1">
+      <c r="B751" s="5"/>
+    </row>
+    <row r="752" ht="15.75" customHeight="1">
+      <c r="B752" s="5"/>
+    </row>
+    <row r="753" ht="15.75" customHeight="1">
+      <c r="B753" s="5"/>
+    </row>
+    <row r="754" ht="15.75" customHeight="1">
+      <c r="B754" s="5"/>
+    </row>
+    <row r="755" ht="15.75" customHeight="1">
+      <c r="B755" s="5"/>
+    </row>
+    <row r="756" ht="15.75" customHeight="1">
+      <c r="B756" s="5"/>
+    </row>
+    <row r="757" ht="15.75" customHeight="1">
+      <c r="B757" s="5"/>
+    </row>
+    <row r="758" ht="15.75" customHeight="1">
+      <c r="B758" s="5"/>
+    </row>
+    <row r="759" ht="15.75" customHeight="1">
+      <c r="B759" s="5"/>
+    </row>
+    <row r="760" ht="15.75" customHeight="1">
+      <c r="B760" s="5"/>
+    </row>
+    <row r="761" ht="15.75" customHeight="1">
+      <c r="B761" s="5"/>
+    </row>
+    <row r="762" ht="15.75" customHeight="1">
+      <c r="B762" s="5"/>
+    </row>
+    <row r="763" ht="15.75" customHeight="1">
+      <c r="B763" s="5"/>
+    </row>
+    <row r="764" ht="15.75" customHeight="1">
+      <c r="B764" s="5"/>
+    </row>
+    <row r="765" ht="15.75" customHeight="1">
+      <c r="B765" s="5"/>
+    </row>
+    <row r="766" ht="15.75" customHeight="1">
+      <c r="B766" s="5"/>
+    </row>
+    <row r="767" ht="15.75" customHeight="1">
+      <c r="B767" s="5"/>
+    </row>
+    <row r="768" ht="15.75" customHeight="1">
+      <c r="B768" s="5"/>
+    </row>
+    <row r="769" ht="15.75" customHeight="1">
+      <c r="B769" s="5"/>
+    </row>
+    <row r="770" ht="15.75" customHeight="1">
+      <c r="B770" s="5"/>
+    </row>
+    <row r="771" ht="15.75" customHeight="1">
+      <c r="B771" s="5"/>
+    </row>
+    <row r="772" ht="15.75" customHeight="1">
+      <c r="B772" s="5"/>
+    </row>
+    <row r="773" ht="15.75" customHeight="1">
+      <c r="B773" s="5"/>
+    </row>
+    <row r="774" ht="15.75" customHeight="1">
+      <c r="B774" s="5"/>
+    </row>
+    <row r="775" ht="15.75" customHeight="1">
+      <c r="B775" s="5"/>
+    </row>
+    <row r="776" ht="15.75" customHeight="1">
+      <c r="B776" s="5"/>
+    </row>
+    <row r="777" ht="15.75" customHeight="1">
+      <c r="B777" s="5"/>
+    </row>
+    <row r="778" ht="15.75" customHeight="1">
+      <c r="B778" s="5"/>
+    </row>
+    <row r="779" ht="15.75" customHeight="1">
+      <c r="B779" s="5"/>
+    </row>
+    <row r="780" ht="15.75" customHeight="1">
+      <c r="B780" s="5"/>
+    </row>
+    <row r="781" ht="15.75" customHeight="1">
+      <c r="B781" s="5"/>
+    </row>
+    <row r="782" ht="15.75" customHeight="1">
+      <c r="B782" s="5"/>
+    </row>
+    <row r="783" ht="15.75" customHeight="1">
+      <c r="B783" s="5"/>
+    </row>
+    <row r="784" ht="15.75" customHeight="1">
+      <c r="B784" s="5"/>
+    </row>
+    <row r="785" ht="15.75" customHeight="1">
+      <c r="B785" s="5"/>
+    </row>
+    <row r="786" ht="15.75" customHeight="1">
+      <c r="B786" s="5"/>
+    </row>
+    <row r="787" ht="15.75" customHeight="1">
+      <c r="B787" s="5"/>
+    </row>
+    <row r="788" ht="15.75" customHeight="1">
+      <c r="B788" s="5"/>
+    </row>
+    <row r="789" ht="15.75" customHeight="1">
+      <c r="B789" s="5"/>
+    </row>
+    <row r="790" ht="15.75" customHeight="1">
+      <c r="B790" s="5"/>
+    </row>
+    <row r="791" ht="15.75" customHeight="1">
+      <c r="B791" s="5"/>
+    </row>
+    <row r="792" ht="15.75" customHeight="1">
+      <c r="B792" s="5"/>
+    </row>
+    <row r="793" ht="15.75" customHeight="1">
+      <c r="B793" s="5"/>
+    </row>
+    <row r="794" ht="15.75" customHeight="1">
+      <c r="B794" s="5"/>
+    </row>
+    <row r="795" ht="15.75" customHeight="1">
+      <c r="B795" s="5"/>
+    </row>
+    <row r="796" ht="15.75" customHeight="1">
+      <c r="B796" s="5"/>
+    </row>
+    <row r="797" ht="15.75" customHeight="1">
+      <c r="B797" s="5"/>
+    </row>
+    <row r="798" ht="15.75" customHeight="1">
+      <c r="B798" s="5"/>
+    </row>
+    <row r="799" ht="15.75" customHeight="1">
+      <c r="B799" s="5"/>
+    </row>
+    <row r="800" ht="15.75" customHeight="1">
+      <c r="B800" s="5"/>
+    </row>
+    <row r="801" ht="15.75" customHeight="1">
+      <c r="B801" s="5"/>
+    </row>
+    <row r="802" ht="15.75" customHeight="1">
+      <c r="B802" s="5"/>
+    </row>
+    <row r="803" ht="15.75" customHeight="1">
+      <c r="B803" s="5"/>
+    </row>
+    <row r="804" ht="15.75" customHeight="1">
+      <c r="B804" s="5"/>
+    </row>
+    <row r="805" ht="15.75" customHeight="1">
+      <c r="B805" s="5"/>
+    </row>
+    <row r="806" ht="15.75" customHeight="1">
+      <c r="B806" s="5"/>
+    </row>
+    <row r="807" ht="15.75" customHeight="1">
+      <c r="B807" s="5"/>
+    </row>
+    <row r="808" ht="15.75" customHeight="1">
+      <c r="B808" s="5"/>
+    </row>
+    <row r="809" ht="15.75" customHeight="1">
+      <c r="B809" s="5"/>
+    </row>
+    <row r="810" ht="15.75" customHeight="1">
+      <c r="B810" s="5"/>
+    </row>
+    <row r="811" ht="15.75" customHeight="1">
+      <c r="B811" s="5"/>
+    </row>
+    <row r="812" ht="15.75" customHeight="1">
+      <c r="B812" s="5"/>
+    </row>
+    <row r="813" ht="15.75" customHeight="1">
+      <c r="B813" s="5"/>
+    </row>
+    <row r="814" ht="15.75" customHeight="1">
+      <c r="B814" s="5"/>
+    </row>
+    <row r="815" ht="15.75" customHeight="1">
+      <c r="B815" s="5"/>
+    </row>
+    <row r="816" ht="15.75" customHeight="1">
+      <c r="B816" s="5"/>
+    </row>
+    <row r="817" ht="15.75" customHeight="1">
+      <c r="B817" s="5"/>
+    </row>
+    <row r="818" ht="15.75" customHeight="1">
+      <c r="B818" s="5"/>
+    </row>
+    <row r="819" ht="15.75" customHeight="1">
+      <c r="B819" s="5"/>
+    </row>
+    <row r="820" ht="15.75" customHeight="1">
+      <c r="B820" s="5"/>
+    </row>
+    <row r="821" ht="15.75" customHeight="1">
+      <c r="B821" s="5"/>
+    </row>
+    <row r="822" ht="15.75" customHeight="1">
+      <c r="B822" s="5"/>
+    </row>
+    <row r="823" ht="15.75" customHeight="1">
+      <c r="B823" s="5"/>
+    </row>
+    <row r="824" ht="15.75" customHeight="1">
+      <c r="B824" s="5"/>
+    </row>
+    <row r="825" ht="15.75" customHeight="1">
+      <c r="B825" s="5"/>
+    </row>
+    <row r="826" ht="15.75" customHeight="1">
+      <c r="B826" s="5"/>
+    </row>
+    <row r="827" ht="15.75" customHeight="1">
+      <c r="B827" s="5"/>
+    </row>
+    <row r="828" ht="15.75" customHeight="1">
+      <c r="B828" s="5"/>
+    </row>
+    <row r="829" ht="15.75" customHeight="1">
+      <c r="B829" s="5"/>
+    </row>
+    <row r="830" ht="15.75" customHeight="1">
+      <c r="B830" s="5"/>
+    </row>
+    <row r="831" ht="15.75" customHeight="1">
+      <c r="B831" s="5"/>
+    </row>
+    <row r="832" ht="15.75" customHeight="1">
+      <c r="B832" s="5"/>
+    </row>
+    <row r="833" ht="15.75" customHeight="1">
+      <c r="B833" s="5"/>
+    </row>
+    <row r="834" ht="15.75" customHeight="1">
+      <c r="B834" s="5"/>
+    </row>
+    <row r="835" ht="15.75" customHeight="1">
+      <c r="B835" s="5"/>
+    </row>
+    <row r="836" ht="15.75" customHeight="1">
+      <c r="B836" s="5"/>
+    </row>
+    <row r="837" ht="15.75" customHeight="1">
+      <c r="B837" s="5"/>
+    </row>
+    <row r="838" ht="15.75" customHeight="1">
+      <c r="B838" s="5"/>
+    </row>
+    <row r="839" ht="15.75" customHeight="1">
+      <c r="B839" s="5"/>
+    </row>
+    <row r="840" ht="15.75" customHeight="1">
+      <c r="B840" s="5"/>
+    </row>
+    <row r="841" ht="15.75" customHeight="1">
+      <c r="B841" s="5"/>
+    </row>
+    <row r="842" ht="15.75" customHeight="1">
+      <c r="B842" s="5"/>
+    </row>
+    <row r="843" ht="15.75" customHeight="1">
+      <c r="B843" s="5"/>
+    </row>
+    <row r="844" ht="15.75" customHeight="1">
+      <c r="B844" s="5"/>
+    </row>
+    <row r="845" ht="15.75" customHeight="1">
+      <c r="B845" s="5"/>
+    </row>
+    <row r="846" ht="15.75" customHeight="1">
+      <c r="B846" s="5"/>
+    </row>
+    <row r="847" ht="15.75" customHeight="1">
+      <c r="B847" s="5"/>
+    </row>
+    <row r="848" ht="15.75" customHeight="1">
+      <c r="B848" s="5"/>
+    </row>
+    <row r="849" ht="15.75" customHeight="1">
+      <c r="B849" s="5"/>
+    </row>
+    <row r="850" ht="15.75" customHeight="1">
+      <c r="B850" s="5"/>
+    </row>
+    <row r="851" ht="15.75" customHeight="1">
+      <c r="B851" s="5"/>
+    </row>
+    <row r="852" ht="15.75" customHeight="1">
+      <c r="B852" s="5"/>
+    </row>
+    <row r="853" ht="15.75" customHeight="1">
+      <c r="B853" s="5"/>
+    </row>
+    <row r="854" ht="15.75" customHeight="1">
+      <c r="B854" s="5"/>
+    </row>
+    <row r="855" ht="15.75" customHeight="1">
+      <c r="B855" s="5"/>
+    </row>
+    <row r="856" ht="15.75" customHeight="1">
+      <c r="B856" s="5"/>
+    </row>
+    <row r="857" ht="15.75" customHeight="1">
+      <c r="B857" s="5"/>
+    </row>
+    <row r="858" ht="15.75" customHeight="1">
+      <c r="B858" s="5"/>
+    </row>
+    <row r="859" ht="15.75" customHeight="1">
+      <c r="B859" s="5"/>
+    </row>
+    <row r="860" ht="15.75" customHeight="1">
+      <c r="B860" s="5"/>
+    </row>
+    <row r="861" ht="15.75" customHeight="1">
+      <c r="B861" s="5"/>
+    </row>
+    <row r="862" ht="15.75" customHeight="1">
+      <c r="B862" s="5"/>
+    </row>
+    <row r="863" ht="15.75" customHeight="1">
+      <c r="B863" s="5"/>
+    </row>
+    <row r="864" ht="15.75" customHeight="1">
+      <c r="B864" s="5"/>
+    </row>
+    <row r="865" ht="15.75" customHeight="1">
+      <c r="B865" s="5"/>
+    </row>
+    <row r="866" ht="15.75" customHeight="1">
+      <c r="B866" s="5"/>
+    </row>
+    <row r="867" ht="15.75" customHeight="1">
+      <c r="B867" s="5"/>
+    </row>
+    <row r="868" ht="15.75" customHeight="1">
+      <c r="B868" s="5"/>
+    </row>
+    <row r="869" ht="15.75" customHeight="1">
+      <c r="B869" s="5"/>
+    </row>
+    <row r="870" ht="15.75" customHeight="1">
+      <c r="B870" s="5"/>
+    </row>
+    <row r="871" ht="15.75" customHeight="1">
+      <c r="B871" s="5"/>
+    </row>
+    <row r="872" ht="15.75" customHeight="1">
+      <c r="B872" s="5"/>
+    </row>
+    <row r="873" ht="15.75" customHeight="1">
+      <c r="B873" s="5"/>
+    </row>
+    <row r="874" ht="15.75" customHeight="1">
+      <c r="B874" s="5"/>
+    </row>
+    <row r="875" ht="15.75" customHeight="1">
+      <c r="B875" s="5"/>
+    </row>
+    <row r="876" ht="15.75" customHeight="1">
+      <c r="B876" s="5"/>
+    </row>
+    <row r="877" ht="15.75" customHeight="1">
+      <c r="B877" s="5"/>
+    </row>
+    <row r="878" ht="15.75" customHeight="1">
+      <c r="B878" s="5"/>
+    </row>
+    <row r="879" ht="15.75" customHeight="1">
+      <c r="B879" s="5"/>
+    </row>
+    <row r="880" ht="15.75" customHeight="1">
+      <c r="B880" s="5"/>
+    </row>
+    <row r="881" ht="15.75" customHeight="1">
+      <c r="B881" s="5"/>
+    </row>
+    <row r="882" ht="15.75" customHeight="1">
+      <c r="B882" s="5"/>
+    </row>
+    <row r="883" ht="15.75" customHeight="1">
+      <c r="B883" s="5"/>
+    </row>
+    <row r="884" ht="15.75" customHeight="1">
+      <c r="B884" s="5"/>
+    </row>
+    <row r="885" ht="15.75" customHeight="1">
+      <c r="B885" s="5"/>
+    </row>
+    <row r="886" ht="15.75" customHeight="1">
+      <c r="B886" s="5"/>
+    </row>
+    <row r="887" ht="15.75" customHeight="1">
+      <c r="B887" s="5"/>
+    </row>
+    <row r="888" ht="15.75" customHeight="1">
+      <c r="B888" s="5"/>
+    </row>
+    <row r="889" ht="15.75" customHeight="1">
+      <c r="B889" s="5"/>
+    </row>
+    <row r="890" ht="15.75" customHeight="1">
+      <c r="B890" s="5"/>
+    </row>
+    <row r="891" ht="15.75" customHeight="1">
+      <c r="B891" s="5"/>
+    </row>
+    <row r="892" ht="15.75" customHeight="1">
+      <c r="B892" s="5"/>
+    </row>
+    <row r="893" ht="15.75" customHeight="1">
+      <c r="B893" s="5"/>
+    </row>
+    <row r="894" ht="15.75" customHeight="1">
+      <c r="B894" s="5"/>
+    </row>
+    <row r="895" ht="15.75" customHeight="1">
+      <c r="B895" s="5"/>
+    </row>
+    <row r="896" ht="15.75" customHeight="1">
+      <c r="B896" s="5"/>
+    </row>
+    <row r="897" ht="15.75" customHeight="1">
+      <c r="B897" s="5"/>
+    </row>
+    <row r="898" ht="15.75" customHeight="1">
+      <c r="B898" s="5"/>
+    </row>
+    <row r="899" ht="15.75" customHeight="1">
+      <c r="B899" s="5"/>
+    </row>
+    <row r="900" ht="15.75" customHeight="1">
+      <c r="B900" s="5"/>
+    </row>
+    <row r="901" ht="15.75" customHeight="1">
+      <c r="B901" s="5"/>
+    </row>
+    <row r="902" ht="15.75" customHeight="1">
+      <c r="B902" s="5"/>
+    </row>
+    <row r="903" ht="15.75" customHeight="1">
+      <c r="B903" s="5"/>
+    </row>
+    <row r="904" ht="15.75" customHeight="1">
+      <c r="B904" s="5"/>
+    </row>
+    <row r="905" ht="15.75" customHeight="1">
+      <c r="B905" s="5"/>
+    </row>
+    <row r="906" ht="15.75" customHeight="1">
+      <c r="B906" s="5"/>
+    </row>
+    <row r="907" ht="15.75" customHeight="1">
+      <c r="B907" s="5"/>
+    </row>
+    <row r="908" ht="15.75" customHeight="1">
+      <c r="B908" s="5"/>
+    </row>
+    <row r="909" ht="15.75" customHeight="1">
+      <c r="B909" s="5"/>
+    </row>
+    <row r="910" ht="15.75" customHeight="1">
+      <c r="B910" s="5"/>
+    </row>
+    <row r="911" ht="15.75" customHeight="1">
+      <c r="B911" s="5"/>
+    </row>
+    <row r="912" ht="15.75" customHeight="1">
+      <c r="B912" s="5"/>
+    </row>
+    <row r="913" ht="15.75" customHeight="1">
+      <c r="B913" s="5"/>
+    </row>
+    <row r="914" ht="15.75" customHeight="1">
+      <c r="B914" s="5"/>
+    </row>
+    <row r="915" ht="15.75" customHeight="1">
+      <c r="B915" s="5"/>
+    </row>
+    <row r="916" ht="15.75" customHeight="1">
+      <c r="B916" s="5"/>
+    </row>
+    <row r="917" ht="15.75" customHeight="1">
+      <c r="B917" s="5"/>
+    </row>
+    <row r="918" ht="15.75" customHeight="1">
+      <c r="B918" s="5"/>
+    </row>
+    <row r="919" ht="15.75" customHeight="1">
+      <c r="B919" s="5"/>
+    </row>
+    <row r="920" ht="15.75" customHeight="1">
+      <c r="B920" s="5"/>
+    </row>
+    <row r="921" ht="15.75" customHeight="1">
+      <c r="B921" s="5"/>
+    </row>
+    <row r="922" ht="15.75" customHeight="1">
+      <c r="B922" s="5"/>
+    </row>
+    <row r="923" ht="15.75" customHeight="1">
+      <c r="B923" s="5"/>
+    </row>
+    <row r="924" ht="15.75" customHeight="1">
+      <c r="B924" s="5"/>
+    </row>
+    <row r="925" ht="15.75" customHeight="1">
+      <c r="B925" s="5"/>
+    </row>
+    <row r="926" ht="15.75" customHeight="1">
+      <c r="B926" s="5"/>
+    </row>
+    <row r="927" ht="15.75" customHeight="1">
+      <c r="B927" s="5"/>
+    </row>
+    <row r="928" ht="15.75" customHeight="1">
+      <c r="B928" s="5"/>
+    </row>
+    <row r="929" ht="15.75" customHeight="1">
+      <c r="B929" s="5"/>
+    </row>
+    <row r="930" ht="15.75" customHeight="1">
+      <c r="B930" s="5"/>
+    </row>
+    <row r="931" ht="15.75" customHeight="1">
+      <c r="B931" s="5"/>
+    </row>
+    <row r="932" ht="15.75" customHeight="1">
+      <c r="B932" s="5"/>
+    </row>
+    <row r="933" ht="15.75" customHeight="1">
+      <c r="B933" s="5"/>
+    </row>
+    <row r="934" ht="15.75" customHeight="1">
+      <c r="B934" s="5"/>
+    </row>
+    <row r="935" ht="15.75" customHeight="1">
+      <c r="B935" s="5"/>
+    </row>
+    <row r="936" ht="15.75" customHeight="1">
+      <c r="B936" s="5"/>
+    </row>
+    <row r="937" ht="15.75" customHeight="1">
+      <c r="B937" s="5"/>
+    </row>
+    <row r="938" ht="15.75" customHeight="1">
+      <c r="B938" s="5"/>
+    </row>
+    <row r="939" ht="15.75" customHeight="1">
+      <c r="B939" s="5"/>
+    </row>
+    <row r="940" ht="15.75" customHeight="1">
+      <c r="B940" s="5"/>
+    </row>
+    <row r="941" ht="15.75" customHeight="1">
+      <c r="B941" s="5"/>
+    </row>
+    <row r="942" ht="15.75" customHeight="1">
+      <c r="B942" s="5"/>
+    </row>
+    <row r="943" ht="15.75" customHeight="1">
+      <c r="B943" s="5"/>
+    </row>
+    <row r="944" ht="15.75" customHeight="1">
+      <c r="B944" s="5"/>
+    </row>
+    <row r="945" ht="15.75" customHeight="1">
+      <c r="B945" s="5"/>
+    </row>
+    <row r="946" ht="15.75" customHeight="1">
+      <c r="B946" s="5"/>
+    </row>
+    <row r="947" ht="15.75" customHeight="1">
+      <c r="B947" s="5"/>
+    </row>
+    <row r="948" ht="15.75" customHeight="1">
+      <c r="B948" s="5"/>
+    </row>
+    <row r="949" ht="15.75" customHeight="1">
+      <c r="B949" s="5"/>
+    </row>
+    <row r="950" ht="15.75" customHeight="1">
+      <c r="B950" s="5"/>
+    </row>
+    <row r="951" ht="15.75" customHeight="1">
+      <c r="B951" s="5"/>
+    </row>
+    <row r="952" ht="15.75" customHeight="1">
+      <c r="B952" s="5"/>
+    </row>
+    <row r="953" ht="15.75" customHeight="1">
+      <c r="B953" s="5"/>
+    </row>
+    <row r="954" ht="15.75" customHeight="1">
+      <c r="B954" s="5"/>
+    </row>
+    <row r="955" ht="15.75" customHeight="1">
+      <c r="B955" s="5"/>
+    </row>
+    <row r="956" ht="15.75" customHeight="1">
+      <c r="B956" s="5"/>
+    </row>
+    <row r="957" ht="15.75" customHeight="1">
+      <c r="B957" s="5"/>
+    </row>
+    <row r="958" ht="15.75" customHeight="1">
+      <c r="B958" s="5"/>
+    </row>
+    <row r="959" ht="15.75" customHeight="1">
+      <c r="B959" s="5"/>
+    </row>
+    <row r="960" ht="15.75" customHeight="1">
+      <c r="B960" s="5"/>
+    </row>
+    <row r="961" ht="15.75" customHeight="1">
+      <c r="B961" s="5"/>
+    </row>
+    <row r="962" ht="15.75" customHeight="1">
+      <c r="B962" s="5"/>
+    </row>
+    <row r="963" ht="15.75" customHeight="1">
+      <c r="B963" s="5"/>
+    </row>
+    <row r="964" ht="15.75" customHeight="1">
+      <c r="B964" s="5"/>
+    </row>
+    <row r="965" ht="15.75" customHeight="1">
+      <c r="B965" s="5"/>
+    </row>
+    <row r="966" ht="15.75" customHeight="1">
+      <c r="B966" s="5"/>
+    </row>
+    <row r="967" ht="15.75" customHeight="1">
+      <c r="B967" s="5"/>
+    </row>
+    <row r="968" ht="15.75" customHeight="1">
+      <c r="B968" s="5"/>
+    </row>
+    <row r="969" ht="15.75" customHeight="1">
+      <c r="B969" s="5"/>
+    </row>
+    <row r="970" ht="15.75" customHeight="1">
+      <c r="B970" s="5"/>
+    </row>
+    <row r="971" ht="15.75" customHeight="1">
+      <c r="B971" s="5"/>
+    </row>
+    <row r="972" ht="15.75" customHeight="1">
+      <c r="B972" s="5"/>
+    </row>
+    <row r="973" ht="15.75" customHeight="1">
+      <c r="B973" s="5"/>
+    </row>
+    <row r="974" ht="15.75" customHeight="1">
+      <c r="B974" s="5"/>
+    </row>
+    <row r="975" ht="15.75" customHeight="1">
+      <c r="B975" s="5"/>
+    </row>
+    <row r="976" ht="15.75" customHeight="1">
+      <c r="B976" s="5"/>
+    </row>
+    <row r="977" ht="15.75" customHeight="1">
+      <c r="B977" s="5"/>
+    </row>
+    <row r="978" ht="15.75" customHeight="1">
+      <c r="B978" s="5"/>
+    </row>
+    <row r="979" ht="15.75" customHeight="1">
+      <c r="B979" s="5"/>
+    </row>
+    <row r="980" ht="15.75" customHeight="1">
+      <c r="B980" s="5"/>
+    </row>
+    <row r="981" ht="15.75" customHeight="1">
+      <c r="B981" s="5"/>
+    </row>
+    <row r="982" ht="15.75" customHeight="1">
+      <c r="B982" s="5"/>
+    </row>
+    <row r="983" ht="15.75" customHeight="1">
+      <c r="B983" s="5"/>
+    </row>
+    <row r="984" ht="15.75" customHeight="1">
+      <c r="B984" s="5"/>
+    </row>
+    <row r="985" ht="15.75" customHeight="1">
+      <c r="B985" s="5"/>
+    </row>
+    <row r="986" ht="15.75" customHeight="1">
+      <c r="B986" s="5"/>
+    </row>
+    <row r="987" ht="15.75" customHeight="1">
+      <c r="B987" s="5"/>
+    </row>
+    <row r="988" ht="15.75" customHeight="1">
+      <c r="B988" s="5"/>
+    </row>
+    <row r="989" ht="15.75" customHeight="1">
+      <c r="B989" s="5"/>
+    </row>
+    <row r="990" ht="15.75" customHeight="1">
+      <c r="B990" s="5"/>
+    </row>
+    <row r="991" ht="15.75" customHeight="1">
+      <c r="B991" s="5"/>
+    </row>
+    <row r="992" ht="15.75" customHeight="1">
+      <c r="B992" s="5"/>
+    </row>
+    <row r="993" ht="15.75" customHeight="1">
+      <c r="B993" s="5"/>
+    </row>
+    <row r="994" ht="15.75" customHeight="1">
+      <c r="B994" s="5"/>
+    </row>
+    <row r="995" ht="15.75" customHeight="1">
+      <c r="B995" s="5"/>
+    </row>
+    <row r="996" ht="15.75" customHeight="1">
+      <c r="B996" s="5"/>
+    </row>
+    <row r="997" ht="15.75" customHeight="1">
+      <c r="B997" s="5"/>
+    </row>
+    <row r="998" ht="15.75" customHeight="1">
+      <c r="B998" s="5"/>
+    </row>
+    <row r="999" ht="15.75" customHeight="1">
+      <c r="B999" s="5"/>
+    </row>
+    <row r="1000" ht="15.75" customHeight="1">
+      <c r="B1000" s="5"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/BlockInfo/BlockInfoTable.xlsx
+++ b/Templates/Tables/BlockInfo/BlockInfoTable.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>Description</t>
   </si>
@@ -23,6 +23,9 @@
   </si>
   <si>
     <t>Desc</t>
+  </si>
+  <si>
+    <t>ResID</t>
   </si>
   <si>
     <t>BlockKinds</t>
@@ -50,17 +53,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <name val="Arial"/>
     </font>
     <font>
@@ -99,17 +100,17 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -322,9 +323,9 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="11" width="14.43"/>
+    <col customWidth="1" min="1" max="27" width="14.38"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -340,22 +341,24 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1"/>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -372,28 +375,29 @@
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="5">
         <v>0.0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="3">
         <v>0.0</v>
       </c>
       <c r="F2" s="1">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G2" s="1">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="H2" s="1">
         <v>0.0</v>
@@ -401,7 +405,9 @@
       <c r="I2" s="1">
         <v>0.0</v>
       </c>
-      <c r="J2" s="1"/>
+      <c r="J2" s="1">
+        <v>0.0</v>
+      </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -418,6 +424,7 @@
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1"/>
@@ -446,6 +453,7 @@
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
+      <c r="AA3" s="1"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1"/>
@@ -474,6 +482,7 @@
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
+      <c r="AA4" s="1"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1"/>
@@ -502,6 +511,7 @@
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
+      <c r="AA5" s="1"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1"/>
@@ -530,6 +540,7 @@
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
+      <c r="AA6" s="1"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1"/>
@@ -558,6 +569,7 @@
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1"/>
@@ -586,6 +598,7 @@
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
+      <c r="AA8" s="1"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="1"/>
@@ -614,6 +627,7 @@
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="1"/>
@@ -642,6 +656,7 @@
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
+      <c r="AA10" s="1"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="1"/>
@@ -670,6 +685,7 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
+      <c r="AA11" s="1"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="1"/>
@@ -698,6 +714,7 @@
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
+      <c r="AA12" s="1"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="1"/>
@@ -726,6 +743,7 @@
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
+      <c r="AA13" s="1"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="1"/>
@@ -754,6 +772,7 @@
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
+      <c r="AA14" s="1"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="1"/>
@@ -782,6 +801,7 @@
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
+      <c r="AA15" s="1"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="1"/>
@@ -810,6 +830,7 @@
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
+      <c r="AA16" s="1"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="1"/>
@@ -838,6 +859,7 @@
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
+      <c r="AA17" s="1"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="1"/>
@@ -866,6 +888,7 @@
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
+      <c r="AA18" s="1"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="1"/>
@@ -894,6 +917,7 @@
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
+      <c r="AA19" s="1"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="1"/>
@@ -922,6 +946,7 @@
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
+      <c r="AA20" s="1"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1"/>
@@ -950,6 +975,7 @@
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
+      <c r="AA21" s="1"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1"/>
@@ -978,6 +1004,7 @@
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
+      <c r="AA22" s="1"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="1"/>
@@ -1006,6 +1033,7 @@
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
+      <c r="AA23" s="1"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1"/>
@@ -1034,6 +1062,7 @@
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
+      <c r="AA24" s="1"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="1"/>
@@ -1062,6 +1091,7 @@
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
+      <c r="AA25" s="1"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="1"/>
@@ -1090,6 +1120,7 @@
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
+      <c r="AA26" s="1"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="1"/>
@@ -1118,6 +1149,7 @@
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
+      <c r="AA27" s="1"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="1"/>
@@ -1146,6 +1178,7 @@
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
+      <c r="AA28" s="1"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="1"/>
@@ -1174,6 +1207,7 @@
       <c r="X29" s="1"/>
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
+      <c r="AA29" s="1"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="1"/>
@@ -1202,6 +1236,7 @@
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
+      <c r="AA30" s="1"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="1"/>
@@ -1230,6 +1265,7 @@
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
+      <c r="AA31" s="1"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="1"/>
@@ -1258,6 +1294,7 @@
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
+      <c r="AA32" s="1"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="1"/>
@@ -1286,6 +1323,7 @@
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
+      <c r="AA33" s="1"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="1"/>
@@ -1314,6 +1352,7 @@
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
+      <c r="AA34" s="1"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="1"/>
@@ -1342,6 +1381,7 @@
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
+      <c r="AA35" s="1"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="1"/>
@@ -1370,6 +1410,7 @@
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
+      <c r="AA36" s="1"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="1"/>
@@ -1398,6 +1439,7 @@
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
+      <c r="AA37" s="1"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="1"/>
@@ -1426,6 +1468,7 @@
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
+      <c r="AA38" s="1"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="1"/>
@@ -1454,6 +1497,7 @@
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
+      <c r="AA39" s="1"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="1"/>
@@ -1482,6 +1526,7 @@
       <c r="X40" s="1"/>
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
+      <c r="AA40" s="1"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="1"/>
@@ -1510,6 +1555,7 @@
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
+      <c r="AA41" s="1"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="1"/>
@@ -1538,6 +1584,7 @@
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
+      <c r="AA42" s="1"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="1"/>
@@ -1566,6 +1613,7 @@
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
+      <c r="AA43" s="1"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="1"/>
@@ -1594,6 +1642,7 @@
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
+      <c r="AA44" s="1"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="1"/>
@@ -1622,6 +1671,7 @@
       <c r="X45" s="1"/>
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
+      <c r="AA45" s="1"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="1"/>
@@ -1650,6 +1700,7 @@
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
+      <c r="AA46" s="1"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="1"/>
@@ -1678,6 +1729,7 @@
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
+      <c r="AA47" s="1"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="1"/>
@@ -1706,6 +1758,7 @@
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
+      <c r="AA48" s="1"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="1"/>
@@ -1734,6 +1787,7 @@
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
+      <c r="AA49" s="1"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="1"/>
@@ -1762,6 +1816,7 @@
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
+      <c r="AA50" s="1"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="1"/>
@@ -1790,6 +1845,7 @@
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
+      <c r="AA51" s="1"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="1"/>
@@ -1818,6 +1874,7 @@
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
+      <c r="AA52" s="1"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="1"/>
@@ -1846,6 +1903,7 @@
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
+      <c r="AA53" s="1"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="1"/>
@@ -1874,6 +1932,7 @@
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
+      <c r="AA54" s="1"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="1"/>
@@ -1902,6 +1961,7 @@
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
+      <c r="AA55" s="1"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="1"/>
@@ -1930,6 +1990,7 @@
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
+      <c r="AA56" s="1"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="1"/>
@@ -1958,6 +2019,7 @@
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
+      <c r="AA57" s="1"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="1"/>
@@ -1986,6 +2048,7 @@
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
+      <c r="AA58" s="1"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="1"/>
@@ -2014,6 +2077,7 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
+      <c r="AA59" s="1"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="1"/>
@@ -2042,6 +2106,7 @@
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
+      <c r="AA60" s="1"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="1"/>
@@ -2070,6 +2135,7 @@
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
+      <c r="AA61" s="1"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="1"/>
@@ -2098,6 +2164,7 @@
       <c r="X62" s="1"/>
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
+      <c r="AA62" s="1"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="1"/>
@@ -2126,6 +2193,7 @@
       <c r="X63" s="1"/>
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
+      <c r="AA63" s="1"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="1"/>
@@ -2154,6 +2222,7 @@
       <c r="X64" s="1"/>
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
+      <c r="AA64" s="1"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="1"/>
@@ -2182,6 +2251,7 @@
       <c r="X65" s="1"/>
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
+      <c r="AA65" s="1"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="1"/>
@@ -2210,6 +2280,7 @@
       <c r="X66" s="1"/>
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
+      <c r="AA66" s="1"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="1"/>
@@ -2238,6 +2309,7 @@
       <c r="X67" s="1"/>
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
+      <c r="AA67" s="1"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="1"/>
@@ -2266,6 +2338,7 @@
       <c r="X68" s="1"/>
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
+      <c r="AA68" s="1"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="1"/>
@@ -2294,6 +2367,7 @@
       <c r="X69" s="1"/>
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
+      <c r="AA69" s="1"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="1"/>
@@ -2322,6 +2396,7 @@
       <c r="X70" s="1"/>
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
+      <c r="AA70" s="1"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="1"/>
@@ -2350,6 +2425,7 @@
       <c r="X71" s="1"/>
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
+      <c r="AA71" s="1"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="1"/>
@@ -2378,6 +2454,7 @@
       <c r="X72" s="1"/>
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
+      <c r="AA72" s="1"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="1"/>
@@ -2406,6 +2483,7 @@
       <c r="X73" s="1"/>
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
+      <c r="AA73" s="1"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="1"/>
@@ -2434,6 +2512,7 @@
       <c r="X74" s="1"/>
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
+      <c r="AA74" s="1"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="1"/>
@@ -2462,6 +2541,7 @@
       <c r="X75" s="1"/>
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
+      <c r="AA75" s="1"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="1"/>
@@ -2490,6 +2570,7 @@
       <c r="X76" s="1"/>
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
+      <c r="AA76" s="1"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="1"/>
@@ -2518,6 +2599,7 @@
       <c r="X77" s="1"/>
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
+      <c r="AA77" s="1"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="1"/>
@@ -2546,6 +2628,7 @@
       <c r="X78" s="1"/>
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
+      <c r="AA78" s="1"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="1"/>
@@ -2574,6 +2657,7 @@
       <c r="X79" s="1"/>
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
+      <c r="AA79" s="1"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="1"/>
@@ -2602,6 +2686,7 @@
       <c r="X80" s="1"/>
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
+      <c r="AA80" s="1"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="1"/>
@@ -2630,6 +2715,7 @@
       <c r="X81" s="1"/>
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
+      <c r="AA81" s="1"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="1"/>
@@ -2658,6 +2744,7 @@
       <c r="X82" s="1"/>
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
+      <c r="AA82" s="1"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="1"/>
@@ -2686,6 +2773,7 @@
       <c r="X83" s="1"/>
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
+      <c r="AA83" s="1"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="1"/>
@@ -2714,6 +2802,7 @@
       <c r="X84" s="1"/>
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
+      <c r="AA84" s="1"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="1"/>
@@ -2742,6 +2831,7 @@
       <c r="X85" s="1"/>
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
+      <c r="AA85" s="1"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="1"/>
@@ -2770,6 +2860,7 @@
       <c r="X86" s="1"/>
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
+      <c r="AA86" s="1"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="1"/>
@@ -2798,6 +2889,7 @@
       <c r="X87" s="1"/>
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
+      <c r="AA87" s="1"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="1"/>
@@ -2826,6 +2918,7 @@
       <c r="X88" s="1"/>
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
+      <c r="AA88" s="1"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="1"/>
@@ -2854,6 +2947,7 @@
       <c r="X89" s="1"/>
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
+      <c r="AA89" s="1"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="1"/>
@@ -2882,6 +2976,7 @@
       <c r="X90" s="1"/>
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
+      <c r="AA90" s="1"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="1"/>
@@ -2910,6 +3005,7 @@
       <c r="X91" s="1"/>
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
+      <c r="AA91" s="1"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="1"/>
@@ -2938,6 +3034,7 @@
       <c r="X92" s="1"/>
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
+      <c r="AA92" s="1"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="1"/>
@@ -2966,6 +3063,7 @@
       <c r="X93" s="1"/>
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
+      <c r="AA93" s="1"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="1"/>
@@ -2994,6 +3092,7 @@
       <c r="X94" s="1"/>
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
+      <c r="AA94" s="1"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="1"/>
@@ -3022,6 +3121,7 @@
       <c r="X95" s="1"/>
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
+      <c r="AA95" s="1"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="1"/>
@@ -3050,6 +3150,7 @@
       <c r="X96" s="1"/>
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
+      <c r="AA96" s="1"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="1"/>
@@ -3078,6 +3179,7 @@
       <c r="X97" s="1"/>
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
+      <c r="AA97" s="1"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="1"/>
@@ -3106,6 +3208,7 @@
       <c r="X98" s="1"/>
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
+      <c r="AA98" s="1"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="1"/>
@@ -3134,6 +3237,7 @@
       <c r="X99" s="1"/>
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
+      <c r="AA99" s="1"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="1"/>
@@ -3162,6 +3266,7 @@
       <c r="X100" s="1"/>
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
+      <c r="AA100" s="1"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="1"/>
@@ -3190,6 +3295,7 @@
       <c r="X101" s="1"/>
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
+      <c r="AA101" s="1"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="1"/>
@@ -3218,6 +3324,7 @@
       <c r="X102" s="1"/>
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
+      <c r="AA102" s="1"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="1"/>
@@ -3246,6 +3353,7 @@
       <c r="X103" s="1"/>
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
+      <c r="AA103" s="1"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="1"/>
@@ -3274,6 +3382,7 @@
       <c r="X104" s="1"/>
       <c r="Y104" s="1"/>
       <c r="Z104" s="1"/>
+      <c r="AA104" s="1"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="1"/>
@@ -3302,6 +3411,7 @@
       <c r="X105" s="1"/>
       <c r="Y105" s="1"/>
       <c r="Z105" s="1"/>
+      <c r="AA105" s="1"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="1"/>
@@ -3330,6 +3440,7 @@
       <c r="X106" s="1"/>
       <c r="Y106" s="1"/>
       <c r="Z106" s="1"/>
+      <c r="AA106" s="1"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="1"/>
@@ -3358,6 +3469,7 @@
       <c r="X107" s="1"/>
       <c r="Y107" s="1"/>
       <c r="Z107" s="1"/>
+      <c r="AA107" s="1"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="1"/>
@@ -3386,6 +3498,7 @@
       <c r="X108" s="1"/>
       <c r="Y108" s="1"/>
       <c r="Z108" s="1"/>
+      <c r="AA108" s="1"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="1"/>
@@ -3414,6 +3527,7 @@
       <c r="X109" s="1"/>
       <c r="Y109" s="1"/>
       <c r="Z109" s="1"/>
+      <c r="AA109" s="1"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="1"/>
@@ -3442,6 +3556,7 @@
       <c r="X110" s="1"/>
       <c r="Y110" s="1"/>
       <c r="Z110" s="1"/>
+      <c r="AA110" s="1"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="1"/>
@@ -3470,6 +3585,7 @@
       <c r="X111" s="1"/>
       <c r="Y111" s="1"/>
       <c r="Z111" s="1"/>
+      <c r="AA111" s="1"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="1"/>
@@ -3498,6 +3614,7 @@
       <c r="X112" s="1"/>
       <c r="Y112" s="1"/>
       <c r="Z112" s="1"/>
+      <c r="AA112" s="1"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="1"/>
@@ -3526,6 +3643,7 @@
       <c r="X113" s="1"/>
       <c r="Y113" s="1"/>
       <c r="Z113" s="1"/>
+      <c r="AA113" s="1"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="1"/>
@@ -3554,6 +3672,7 @@
       <c r="X114" s="1"/>
       <c r="Y114" s="1"/>
       <c r="Z114" s="1"/>
+      <c r="AA114" s="1"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="1"/>
@@ -3582,6 +3701,7 @@
       <c r="X115" s="1"/>
       <c r="Y115" s="1"/>
       <c r="Z115" s="1"/>
+      <c r="AA115" s="1"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="1"/>
@@ -3610,6 +3730,7 @@
       <c r="X116" s="1"/>
       <c r="Y116" s="1"/>
       <c r="Z116" s="1"/>
+      <c r="AA116" s="1"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="1"/>
@@ -3638,6 +3759,7 @@
       <c r="X117" s="1"/>
       <c r="Y117" s="1"/>
       <c r="Z117" s="1"/>
+      <c r="AA117" s="1"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="1"/>
@@ -3666,6 +3788,7 @@
       <c r="X118" s="1"/>
       <c r="Y118" s="1"/>
       <c r="Z118" s="1"/>
+      <c r="AA118" s="1"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="1"/>
@@ -3694,6 +3817,7 @@
       <c r="X119" s="1"/>
       <c r="Y119" s="1"/>
       <c r="Z119" s="1"/>
+      <c r="AA119" s="1"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="1"/>
@@ -3722,6 +3846,7 @@
       <c r="X120" s="1"/>
       <c r="Y120" s="1"/>
       <c r="Z120" s="1"/>
+      <c r="AA120" s="1"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="1"/>
@@ -3750,6 +3875,7 @@
       <c r="X121" s="1"/>
       <c r="Y121" s="1"/>
       <c r="Z121" s="1"/>
+      <c r="AA121" s="1"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="1"/>
@@ -3778,6 +3904,7 @@
       <c r="X122" s="1"/>
       <c r="Y122" s="1"/>
       <c r="Z122" s="1"/>
+      <c r="AA122" s="1"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="1"/>
@@ -3806,6 +3933,7 @@
       <c r="X123" s="1"/>
       <c r="Y123" s="1"/>
       <c r="Z123" s="1"/>
+      <c r="AA123" s="1"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="1"/>
@@ -3834,6 +3962,7 @@
       <c r="X124" s="1"/>
       <c r="Y124" s="1"/>
       <c r="Z124" s="1"/>
+      <c r="AA124" s="1"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="1"/>
@@ -3862,6 +3991,7 @@
       <c r="X125" s="1"/>
       <c r="Y125" s="1"/>
       <c r="Z125" s="1"/>
+      <c r="AA125" s="1"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="1"/>
@@ -3890,6 +4020,7 @@
       <c r="X126" s="1"/>
       <c r="Y126" s="1"/>
       <c r="Z126" s="1"/>
+      <c r="AA126" s="1"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="1"/>
@@ -3918,6 +4049,7 @@
       <c r="X127" s="1"/>
       <c r="Y127" s="1"/>
       <c r="Z127" s="1"/>
+      <c r="AA127" s="1"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="1"/>
@@ -3946,6 +4078,7 @@
       <c r="X128" s="1"/>
       <c r="Y128" s="1"/>
       <c r="Z128" s="1"/>
+      <c r="AA128" s="1"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="1"/>
@@ -3974,6 +4107,7 @@
       <c r="X129" s="1"/>
       <c r="Y129" s="1"/>
       <c r="Z129" s="1"/>
+      <c r="AA129" s="1"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="1"/>
@@ -4002,6 +4136,7 @@
       <c r="X130" s="1"/>
       <c r="Y130" s="1"/>
       <c r="Z130" s="1"/>
+      <c r="AA130" s="1"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="1"/>
@@ -4030,6 +4165,7 @@
       <c r="X131" s="1"/>
       <c r="Y131" s="1"/>
       <c r="Z131" s="1"/>
+      <c r="AA131" s="1"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="1"/>
@@ -4058,6 +4194,7 @@
       <c r="X132" s="1"/>
       <c r="Y132" s="1"/>
       <c r="Z132" s="1"/>
+      <c r="AA132" s="1"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="1"/>
@@ -4086,6 +4223,7 @@
       <c r="X133" s="1"/>
       <c r="Y133" s="1"/>
       <c r="Z133" s="1"/>
+      <c r="AA133" s="1"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="1"/>
@@ -4114,6 +4252,7 @@
       <c r="X134" s="1"/>
       <c r="Y134" s="1"/>
       <c r="Z134" s="1"/>
+      <c r="AA134" s="1"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="1"/>
@@ -4142,6 +4281,7 @@
       <c r="X135" s="1"/>
       <c r="Y135" s="1"/>
       <c r="Z135" s="1"/>
+      <c r="AA135" s="1"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="1"/>
@@ -4170,6 +4310,7 @@
       <c r="X136" s="1"/>
       <c r="Y136" s="1"/>
       <c r="Z136" s="1"/>
+      <c r="AA136" s="1"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="1"/>
@@ -4198,6 +4339,7 @@
       <c r="X137" s="1"/>
       <c r="Y137" s="1"/>
       <c r="Z137" s="1"/>
+      <c r="AA137" s="1"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="1"/>
@@ -4226,6 +4368,7 @@
       <c r="X138" s="1"/>
       <c r="Y138" s="1"/>
       <c r="Z138" s="1"/>
+      <c r="AA138" s="1"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="1"/>
@@ -4254,6 +4397,7 @@
       <c r="X139" s="1"/>
       <c r="Y139" s="1"/>
       <c r="Z139" s="1"/>
+      <c r="AA139" s="1"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="1"/>
@@ -4282,6 +4426,7 @@
       <c r="X140" s="1"/>
       <c r="Y140" s="1"/>
       <c r="Z140" s="1"/>
+      <c r="AA140" s="1"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="1"/>
@@ -4310,6 +4455,7 @@
       <c r="X141" s="1"/>
       <c r="Y141" s="1"/>
       <c r="Z141" s="1"/>
+      <c r="AA141" s="1"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="1"/>
@@ -4338,6 +4484,7 @@
       <c r="X142" s="1"/>
       <c r="Y142" s="1"/>
       <c r="Z142" s="1"/>
+      <c r="AA142" s="1"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="1"/>
@@ -4366,6 +4513,7 @@
       <c r="X143" s="1"/>
       <c r="Y143" s="1"/>
       <c r="Z143" s="1"/>
+      <c r="AA143" s="1"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="1"/>
@@ -4394,6 +4542,7 @@
       <c r="X144" s="1"/>
       <c r="Y144" s="1"/>
       <c r="Z144" s="1"/>
+      <c r="AA144" s="1"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="1"/>
@@ -4422,6 +4571,7 @@
       <c r="X145" s="1"/>
       <c r="Y145" s="1"/>
       <c r="Z145" s="1"/>
+      <c r="AA145" s="1"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="1"/>
@@ -4450,6 +4600,7 @@
       <c r="X146" s="1"/>
       <c r="Y146" s="1"/>
       <c r="Z146" s="1"/>
+      <c r="AA146" s="1"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="1"/>
@@ -4478,6 +4629,7 @@
       <c r="X147" s="1"/>
       <c r="Y147" s="1"/>
       <c r="Z147" s="1"/>
+      <c r="AA147" s="1"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="1"/>
@@ -4506,6 +4658,7 @@
       <c r="X148" s="1"/>
       <c r="Y148" s="1"/>
       <c r="Z148" s="1"/>
+      <c r="AA148" s="1"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="1"/>
@@ -4534,6 +4687,7 @@
       <c r="X149" s="1"/>
       <c r="Y149" s="1"/>
       <c r="Z149" s="1"/>
+      <c r="AA149" s="1"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="1"/>
@@ -4562,6 +4716,7 @@
       <c r="X150" s="1"/>
       <c r="Y150" s="1"/>
       <c r="Z150" s="1"/>
+      <c r="AA150" s="1"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="1"/>
@@ -4590,6 +4745,7 @@
       <c r="X151" s="1"/>
       <c r="Y151" s="1"/>
       <c r="Z151" s="1"/>
+      <c r="AA151" s="1"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="1"/>
@@ -4618,6 +4774,7 @@
       <c r="X152" s="1"/>
       <c r="Y152" s="1"/>
       <c r="Z152" s="1"/>
+      <c r="AA152" s="1"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="1"/>
@@ -4646,6 +4803,7 @@
       <c r="X153" s="1"/>
       <c r="Y153" s="1"/>
       <c r="Z153" s="1"/>
+      <c r="AA153" s="1"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="1"/>
@@ -4674,6 +4832,7 @@
       <c r="X154" s="1"/>
       <c r="Y154" s="1"/>
       <c r="Z154" s="1"/>
+      <c r="AA154" s="1"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="1"/>
@@ -4702,6 +4861,7 @@
       <c r="X155" s="1"/>
       <c r="Y155" s="1"/>
       <c r="Z155" s="1"/>
+      <c r="AA155" s="1"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="1"/>
@@ -4730,6 +4890,7 @@
       <c r="X156" s="1"/>
       <c r="Y156" s="1"/>
       <c r="Z156" s="1"/>
+      <c r="AA156" s="1"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="1"/>
@@ -4758,6 +4919,7 @@
       <c r="X157" s="1"/>
       <c r="Y157" s="1"/>
       <c r="Z157" s="1"/>
+      <c r="AA157" s="1"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="1"/>
@@ -4786,6 +4948,7 @@
       <c r="X158" s="1"/>
       <c r="Y158" s="1"/>
       <c r="Z158" s="1"/>
+      <c r="AA158" s="1"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="1"/>
@@ -4814,6 +4977,7 @@
       <c r="X159" s="1"/>
       <c r="Y159" s="1"/>
       <c r="Z159" s="1"/>
+      <c r="AA159" s="1"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="1"/>
@@ -4842,6 +5006,7 @@
       <c r="X160" s="1"/>
       <c r="Y160" s="1"/>
       <c r="Z160" s="1"/>
+      <c r="AA160" s="1"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="1"/>
@@ -4870,6 +5035,7 @@
       <c r="X161" s="1"/>
       <c r="Y161" s="1"/>
       <c r="Z161" s="1"/>
+      <c r="AA161" s="1"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="1"/>
@@ -4898,6 +5064,7 @@
       <c r="X162" s="1"/>
       <c r="Y162" s="1"/>
       <c r="Z162" s="1"/>
+      <c r="AA162" s="1"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="1"/>
@@ -4926,6 +5093,7 @@
       <c r="X163" s="1"/>
       <c r="Y163" s="1"/>
       <c r="Z163" s="1"/>
+      <c r="AA163" s="1"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="1"/>
@@ -4954,6 +5122,7 @@
       <c r="X164" s="1"/>
       <c r="Y164" s="1"/>
       <c r="Z164" s="1"/>
+      <c r="AA164" s="1"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="1"/>
@@ -4982,6 +5151,7 @@
       <c r="X165" s="1"/>
       <c r="Y165" s="1"/>
       <c r="Z165" s="1"/>
+      <c r="AA165" s="1"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="1"/>
@@ -5010,6 +5180,7 @@
       <c r="X166" s="1"/>
       <c r="Y166" s="1"/>
       <c r="Z166" s="1"/>
+      <c r="AA166" s="1"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="1"/>
@@ -5038,6 +5209,7 @@
       <c r="X167" s="1"/>
       <c r="Y167" s="1"/>
       <c r="Z167" s="1"/>
+      <c r="AA167" s="1"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="1"/>
@@ -5066,6 +5238,7 @@
       <c r="X168" s="1"/>
       <c r="Y168" s="1"/>
       <c r="Z168" s="1"/>
+      <c r="AA168" s="1"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="1"/>
@@ -5094,6 +5267,7 @@
       <c r="X169" s="1"/>
       <c r="Y169" s="1"/>
       <c r="Z169" s="1"/>
+      <c r="AA169" s="1"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="1"/>
@@ -5122,6 +5296,7 @@
       <c r="X170" s="1"/>
       <c r="Y170" s="1"/>
       <c r="Z170" s="1"/>
+      <c r="AA170" s="1"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="1"/>
@@ -5150,6 +5325,7 @@
       <c r="X171" s="1"/>
       <c r="Y171" s="1"/>
       <c r="Z171" s="1"/>
+      <c r="AA171" s="1"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="1"/>
@@ -5178,6 +5354,7 @@
       <c r="X172" s="1"/>
       <c r="Y172" s="1"/>
       <c r="Z172" s="1"/>
+      <c r="AA172" s="1"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="1"/>
@@ -5206,6 +5383,7 @@
       <c r="X173" s="1"/>
       <c r="Y173" s="1"/>
       <c r="Z173" s="1"/>
+      <c r="AA173" s="1"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="1"/>
@@ -5234,6 +5412,7 @@
       <c r="X174" s="1"/>
       <c r="Y174" s="1"/>
       <c r="Z174" s="1"/>
+      <c r="AA174" s="1"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="1"/>
@@ -5262,6 +5441,7 @@
       <c r="X175" s="1"/>
       <c r="Y175" s="1"/>
       <c r="Z175" s="1"/>
+      <c r="AA175" s="1"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="1"/>
@@ -5290,6 +5470,7 @@
       <c r="X176" s="1"/>
       <c r="Y176" s="1"/>
       <c r="Z176" s="1"/>
+      <c r="AA176" s="1"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="1"/>
@@ -5318,6 +5499,7 @@
       <c r="X177" s="1"/>
       <c r="Y177" s="1"/>
       <c r="Z177" s="1"/>
+      <c r="AA177" s="1"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="1"/>
@@ -5346,6 +5528,7 @@
       <c r="X178" s="1"/>
       <c r="Y178" s="1"/>
       <c r="Z178" s="1"/>
+      <c r="AA178" s="1"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="1"/>
@@ -5374,6 +5557,7 @@
       <c r="X179" s="1"/>
       <c r="Y179" s="1"/>
       <c r="Z179" s="1"/>
+      <c r="AA179" s="1"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="1"/>
@@ -5402,6 +5586,7 @@
       <c r="X180" s="1"/>
       <c r="Y180" s="1"/>
       <c r="Z180" s="1"/>
+      <c r="AA180" s="1"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="1"/>
@@ -5430,6 +5615,7 @@
       <c r="X181" s="1"/>
       <c r="Y181" s="1"/>
       <c r="Z181" s="1"/>
+      <c r="AA181" s="1"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="1"/>
@@ -5458,6 +5644,7 @@
       <c r="X182" s="1"/>
       <c r="Y182" s="1"/>
       <c r="Z182" s="1"/>
+      <c r="AA182" s="1"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="1"/>
@@ -5486,6 +5673,7 @@
       <c r="X183" s="1"/>
       <c r="Y183" s="1"/>
       <c r="Z183" s="1"/>
+      <c r="AA183" s="1"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="1"/>
@@ -5514,6 +5702,7 @@
       <c r="X184" s="1"/>
       <c r="Y184" s="1"/>
       <c r="Z184" s="1"/>
+      <c r="AA184" s="1"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="1"/>
@@ -5542,6 +5731,7 @@
       <c r="X185" s="1"/>
       <c r="Y185" s="1"/>
       <c r="Z185" s="1"/>
+      <c r="AA185" s="1"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="1"/>
@@ -5570,6 +5760,7 @@
       <c r="X186" s="1"/>
       <c r="Y186" s="1"/>
       <c r="Z186" s="1"/>
+      <c r="AA186" s="1"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="1"/>
@@ -5598,6 +5789,7 @@
       <c r="X187" s="1"/>
       <c r="Y187" s="1"/>
       <c r="Z187" s="1"/>
+      <c r="AA187" s="1"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="1"/>
@@ -5626,6 +5818,7 @@
       <c r="X188" s="1"/>
       <c r="Y188" s="1"/>
       <c r="Z188" s="1"/>
+      <c r="AA188" s="1"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="1"/>
@@ -5654,6 +5847,7 @@
       <c r="X189" s="1"/>
       <c r="Y189" s="1"/>
       <c r="Z189" s="1"/>
+      <c r="AA189" s="1"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="1"/>
@@ -5682,6 +5876,7 @@
       <c r="X190" s="1"/>
       <c r="Y190" s="1"/>
       <c r="Z190" s="1"/>
+      <c r="AA190" s="1"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="1"/>
@@ -5710,6 +5905,7 @@
       <c r="X191" s="1"/>
       <c r="Y191" s="1"/>
       <c r="Z191" s="1"/>
+      <c r="AA191" s="1"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="1"/>
@@ -5738,6 +5934,7 @@
       <c r="X192" s="1"/>
       <c r="Y192" s="1"/>
       <c r="Z192" s="1"/>
+      <c r="AA192" s="1"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="1"/>
@@ -5766,6 +5963,7 @@
       <c r="X193" s="1"/>
       <c r="Y193" s="1"/>
       <c r="Z193" s="1"/>
+      <c r="AA193" s="1"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="1"/>
@@ -5794,6 +5992,7 @@
       <c r="X194" s="1"/>
       <c r="Y194" s="1"/>
       <c r="Z194" s="1"/>
+      <c r="AA194" s="1"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="1"/>
@@ -5822,6 +6021,7 @@
       <c r="X195" s="1"/>
       <c r="Y195" s="1"/>
       <c r="Z195" s="1"/>
+      <c r="AA195" s="1"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="1"/>
@@ -5850,6 +6050,7 @@
       <c r="X196" s="1"/>
       <c r="Y196" s="1"/>
       <c r="Z196" s="1"/>
+      <c r="AA196" s="1"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="1"/>
@@ -5878,6 +6079,7 @@
       <c r="X197" s="1"/>
       <c r="Y197" s="1"/>
       <c r="Z197" s="1"/>
+      <c r="AA197" s="1"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="1"/>
@@ -5906,6 +6108,7 @@
       <c r="X198" s="1"/>
       <c r="Y198" s="1"/>
       <c r="Z198" s="1"/>
+      <c r="AA198" s="1"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="1"/>
@@ -5934,6 +6137,7 @@
       <c r="X199" s="1"/>
       <c r="Y199" s="1"/>
       <c r="Z199" s="1"/>
+      <c r="AA199" s="1"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="1"/>
@@ -5962,6 +6166,7 @@
       <c r="X200" s="1"/>
       <c r="Y200" s="1"/>
       <c r="Z200" s="1"/>
+      <c r="AA200" s="1"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="1"/>
@@ -5990,6 +6195,7 @@
       <c r="X201" s="1"/>
       <c r="Y201" s="1"/>
       <c r="Z201" s="1"/>
+      <c r="AA201" s="1"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="1"/>
@@ -6018,6 +6224,7 @@
       <c r="X202" s="1"/>
       <c r="Y202" s="1"/>
       <c r="Z202" s="1"/>
+      <c r="AA202" s="1"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="1"/>
@@ -6046,6 +6253,7 @@
       <c r="X203" s="1"/>
       <c r="Y203" s="1"/>
       <c r="Z203" s="1"/>
+      <c r="AA203" s="1"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="1"/>
@@ -6074,6 +6282,7 @@
       <c r="X204" s="1"/>
       <c r="Y204" s="1"/>
       <c r="Z204" s="1"/>
+      <c r="AA204" s="1"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="1"/>
@@ -6102,6 +6311,7 @@
       <c r="X205" s="1"/>
       <c r="Y205" s="1"/>
       <c r="Z205" s="1"/>
+      <c r="AA205" s="1"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="1"/>
@@ -6130,6 +6340,7 @@
       <c r="X206" s="1"/>
       <c r="Y206" s="1"/>
       <c r="Z206" s="1"/>
+      <c r="AA206" s="1"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="1"/>
@@ -6158,6 +6369,7 @@
       <c r="X207" s="1"/>
       <c r="Y207" s="1"/>
       <c r="Z207" s="1"/>
+      <c r="AA207" s="1"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="1"/>
@@ -6186,6 +6398,7 @@
       <c r="X208" s="1"/>
       <c r="Y208" s="1"/>
       <c r="Z208" s="1"/>
+      <c r="AA208" s="1"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="1"/>
@@ -6214,6 +6427,7 @@
       <c r="X209" s="1"/>
       <c r="Y209" s="1"/>
       <c r="Z209" s="1"/>
+      <c r="AA209" s="1"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="1"/>
@@ -6242,6 +6456,7 @@
       <c r="X210" s="1"/>
       <c r="Y210" s="1"/>
       <c r="Z210" s="1"/>
+      <c r="AA210" s="1"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="1"/>
@@ -6270,6 +6485,7 @@
       <c r="X211" s="1"/>
       <c r="Y211" s="1"/>
       <c r="Z211" s="1"/>
+      <c r="AA211" s="1"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="1"/>
@@ -6298,6 +6514,7 @@
       <c r="X212" s="1"/>
       <c r="Y212" s="1"/>
       <c r="Z212" s="1"/>
+      <c r="AA212" s="1"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="1"/>
@@ -6326,6 +6543,7 @@
       <c r="X213" s="1"/>
       <c r="Y213" s="1"/>
       <c r="Z213" s="1"/>
+      <c r="AA213" s="1"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="1"/>
@@ -6354,6 +6572,7 @@
       <c r="X214" s="1"/>
       <c r="Y214" s="1"/>
       <c r="Z214" s="1"/>
+      <c r="AA214" s="1"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="1"/>
@@ -6382,6 +6601,7 @@
       <c r="X215" s="1"/>
       <c r="Y215" s="1"/>
       <c r="Z215" s="1"/>
+      <c r="AA215" s="1"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="1"/>
@@ -6410,6 +6630,7 @@
       <c r="X216" s="1"/>
       <c r="Y216" s="1"/>
       <c r="Z216" s="1"/>
+      <c r="AA216" s="1"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="1"/>
@@ -6438,6 +6659,7 @@
       <c r="X217" s="1"/>
       <c r="Y217" s="1"/>
       <c r="Z217" s="1"/>
+      <c r="AA217" s="1"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="1"/>
@@ -6466,6 +6688,7 @@
       <c r="X218" s="1"/>
       <c r="Y218" s="1"/>
       <c r="Z218" s="1"/>
+      <c r="AA218" s="1"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="1"/>
@@ -6494,6 +6717,7 @@
       <c r="X219" s="1"/>
       <c r="Y219" s="1"/>
       <c r="Z219" s="1"/>
+      <c r="AA219" s="1"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="1"/>
@@ -6522,2347 +6746,788 @@
       <c r="X220" s="1"/>
       <c r="Y220" s="1"/>
       <c r="Z220" s="1"/>
-    </row>
-    <row r="221" ht="15.75" customHeight="1">
-      <c r="B221" s="5"/>
-    </row>
-    <row r="222" ht="15.75" customHeight="1">
-      <c r="B222" s="5"/>
-    </row>
-    <row r="223" ht="15.75" customHeight="1">
-      <c r="B223" s="5"/>
-    </row>
-    <row r="224" ht="15.75" customHeight="1">
-      <c r="B224" s="5"/>
-    </row>
-    <row r="225" ht="15.75" customHeight="1">
-      <c r="B225" s="5"/>
-    </row>
-    <row r="226" ht="15.75" customHeight="1">
-      <c r="B226" s="5"/>
-    </row>
-    <row r="227" ht="15.75" customHeight="1">
-      <c r="B227" s="5"/>
-    </row>
-    <row r="228" ht="15.75" customHeight="1">
-      <c r="B228" s="5"/>
-    </row>
-    <row r="229" ht="15.75" customHeight="1">
-      <c r="B229" s="5"/>
-    </row>
-    <row r="230" ht="15.75" customHeight="1">
-      <c r="B230" s="5"/>
-    </row>
-    <row r="231" ht="15.75" customHeight="1">
-      <c r="B231" s="5"/>
-    </row>
-    <row r="232" ht="15.75" customHeight="1">
-      <c r="B232" s="5"/>
-    </row>
-    <row r="233" ht="15.75" customHeight="1">
-      <c r="B233" s="5"/>
-    </row>
-    <row r="234" ht="15.75" customHeight="1">
-      <c r="B234" s="5"/>
-    </row>
-    <row r="235" ht="15.75" customHeight="1">
-      <c r="B235" s="5"/>
-    </row>
-    <row r="236" ht="15.75" customHeight="1">
-      <c r="B236" s="5"/>
-    </row>
-    <row r="237" ht="15.75" customHeight="1">
-      <c r="B237" s="5"/>
-    </row>
-    <row r="238" ht="15.75" customHeight="1">
-      <c r="B238" s="5"/>
-    </row>
-    <row r="239" ht="15.75" customHeight="1">
-      <c r="B239" s="5"/>
-    </row>
-    <row r="240" ht="15.75" customHeight="1">
-      <c r="B240" s="5"/>
-    </row>
-    <row r="241" ht="15.75" customHeight="1">
-      <c r="B241" s="5"/>
-    </row>
-    <row r="242" ht="15.75" customHeight="1">
-      <c r="B242" s="5"/>
-    </row>
-    <row r="243" ht="15.75" customHeight="1">
-      <c r="B243" s="5"/>
-    </row>
-    <row r="244" ht="15.75" customHeight="1">
-      <c r="B244" s="5"/>
-    </row>
-    <row r="245" ht="15.75" customHeight="1">
-      <c r="B245" s="5"/>
-    </row>
-    <row r="246" ht="15.75" customHeight="1">
-      <c r="B246" s="5"/>
-    </row>
-    <row r="247" ht="15.75" customHeight="1">
-      <c r="B247" s="5"/>
-    </row>
-    <row r="248" ht="15.75" customHeight="1">
-      <c r="B248" s="5"/>
-    </row>
-    <row r="249" ht="15.75" customHeight="1">
-      <c r="B249" s="5"/>
-    </row>
-    <row r="250" ht="15.75" customHeight="1">
-      <c r="B250" s="5"/>
-    </row>
-    <row r="251" ht="15.75" customHeight="1">
-      <c r="B251" s="5"/>
-    </row>
-    <row r="252" ht="15.75" customHeight="1">
-      <c r="B252" s="5"/>
-    </row>
-    <row r="253" ht="15.75" customHeight="1">
-      <c r="B253" s="5"/>
-    </row>
-    <row r="254" ht="15.75" customHeight="1">
-      <c r="B254" s="5"/>
-    </row>
-    <row r="255" ht="15.75" customHeight="1">
-      <c r="B255" s="5"/>
-    </row>
-    <row r="256" ht="15.75" customHeight="1">
-      <c r="B256" s="5"/>
-    </row>
-    <row r="257" ht="15.75" customHeight="1">
-      <c r="B257" s="5"/>
-    </row>
-    <row r="258" ht="15.75" customHeight="1">
-      <c r="B258" s="5"/>
-    </row>
-    <row r="259" ht="15.75" customHeight="1">
-      <c r="B259" s="5"/>
-    </row>
-    <row r="260" ht="15.75" customHeight="1">
-      <c r="B260" s="5"/>
-    </row>
-    <row r="261" ht="15.75" customHeight="1">
-      <c r="B261" s="5"/>
-    </row>
-    <row r="262" ht="15.75" customHeight="1">
-      <c r="B262" s="5"/>
-    </row>
-    <row r="263" ht="15.75" customHeight="1">
-      <c r="B263" s="5"/>
-    </row>
-    <row r="264" ht="15.75" customHeight="1">
-      <c r="B264" s="5"/>
-    </row>
-    <row r="265" ht="15.75" customHeight="1">
-      <c r="B265" s="5"/>
-    </row>
-    <row r="266" ht="15.75" customHeight="1">
-      <c r="B266" s="5"/>
-    </row>
-    <row r="267" ht="15.75" customHeight="1">
-      <c r="B267" s="5"/>
-    </row>
-    <row r="268" ht="15.75" customHeight="1">
-      <c r="B268" s="5"/>
-    </row>
-    <row r="269" ht="15.75" customHeight="1">
-      <c r="B269" s="5"/>
-    </row>
-    <row r="270" ht="15.75" customHeight="1">
-      <c r="B270" s="5"/>
-    </row>
-    <row r="271" ht="15.75" customHeight="1">
-      <c r="B271" s="5"/>
-    </row>
-    <row r="272" ht="15.75" customHeight="1">
-      <c r="B272" s="5"/>
-    </row>
-    <row r="273" ht="15.75" customHeight="1">
-      <c r="B273" s="5"/>
-    </row>
-    <row r="274" ht="15.75" customHeight="1">
-      <c r="B274" s="5"/>
-    </row>
-    <row r="275" ht="15.75" customHeight="1">
-      <c r="B275" s="5"/>
-    </row>
-    <row r="276" ht="15.75" customHeight="1">
-      <c r="B276" s="5"/>
-    </row>
-    <row r="277" ht="15.75" customHeight="1">
-      <c r="B277" s="5"/>
-    </row>
-    <row r="278" ht="15.75" customHeight="1">
-      <c r="B278" s="5"/>
-    </row>
-    <row r="279" ht="15.75" customHeight="1">
-      <c r="B279" s="5"/>
-    </row>
-    <row r="280" ht="15.75" customHeight="1">
-      <c r="B280" s="5"/>
-    </row>
-    <row r="281" ht="15.75" customHeight="1">
-      <c r="B281" s="5"/>
-    </row>
-    <row r="282" ht="15.75" customHeight="1">
-      <c r="B282" s="5"/>
-    </row>
-    <row r="283" ht="15.75" customHeight="1">
-      <c r="B283" s="5"/>
-    </row>
-    <row r="284" ht="15.75" customHeight="1">
-      <c r="B284" s="5"/>
-    </row>
-    <row r="285" ht="15.75" customHeight="1">
-      <c r="B285" s="5"/>
-    </row>
-    <row r="286" ht="15.75" customHeight="1">
-      <c r="B286" s="5"/>
-    </row>
-    <row r="287" ht="15.75" customHeight="1">
-      <c r="B287" s="5"/>
-    </row>
-    <row r="288" ht="15.75" customHeight="1">
-      <c r="B288" s="5"/>
-    </row>
-    <row r="289" ht="15.75" customHeight="1">
-      <c r="B289" s="5"/>
-    </row>
-    <row r="290" ht="15.75" customHeight="1">
-      <c r="B290" s="5"/>
-    </row>
-    <row r="291" ht="15.75" customHeight="1">
-      <c r="B291" s="5"/>
-    </row>
-    <row r="292" ht="15.75" customHeight="1">
-      <c r="B292" s="5"/>
-    </row>
-    <row r="293" ht="15.75" customHeight="1">
-      <c r="B293" s="5"/>
-    </row>
-    <row r="294" ht="15.75" customHeight="1">
-      <c r="B294" s="5"/>
-    </row>
-    <row r="295" ht="15.75" customHeight="1">
-      <c r="B295" s="5"/>
-    </row>
-    <row r="296" ht="15.75" customHeight="1">
-      <c r="B296" s="5"/>
-    </row>
-    <row r="297" ht="15.75" customHeight="1">
-      <c r="B297" s="5"/>
-    </row>
-    <row r="298" ht="15.75" customHeight="1">
-      <c r="B298" s="5"/>
-    </row>
-    <row r="299" ht="15.75" customHeight="1">
-      <c r="B299" s="5"/>
-    </row>
-    <row r="300" ht="15.75" customHeight="1">
-      <c r="B300" s="5"/>
-    </row>
-    <row r="301" ht="15.75" customHeight="1">
-      <c r="B301" s="5"/>
-    </row>
-    <row r="302" ht="15.75" customHeight="1">
-      <c r="B302" s="5"/>
-    </row>
-    <row r="303" ht="15.75" customHeight="1">
-      <c r="B303" s="5"/>
-    </row>
-    <row r="304" ht="15.75" customHeight="1">
-      <c r="B304" s="5"/>
-    </row>
-    <row r="305" ht="15.75" customHeight="1">
-      <c r="B305" s="5"/>
-    </row>
-    <row r="306" ht="15.75" customHeight="1">
-      <c r="B306" s="5"/>
-    </row>
-    <row r="307" ht="15.75" customHeight="1">
-      <c r="B307" s="5"/>
-    </row>
-    <row r="308" ht="15.75" customHeight="1">
-      <c r="B308" s="5"/>
-    </row>
-    <row r="309" ht="15.75" customHeight="1">
-      <c r="B309" s="5"/>
-    </row>
-    <row r="310" ht="15.75" customHeight="1">
-      <c r="B310" s="5"/>
-    </row>
-    <row r="311" ht="15.75" customHeight="1">
-      <c r="B311" s="5"/>
-    </row>
-    <row r="312" ht="15.75" customHeight="1">
-      <c r="B312" s="5"/>
-    </row>
-    <row r="313" ht="15.75" customHeight="1">
-      <c r="B313" s="5"/>
-    </row>
-    <row r="314" ht="15.75" customHeight="1">
-      <c r="B314" s="5"/>
-    </row>
-    <row r="315" ht="15.75" customHeight="1">
-      <c r="B315" s="5"/>
-    </row>
-    <row r="316" ht="15.75" customHeight="1">
-      <c r="B316" s="5"/>
-    </row>
-    <row r="317" ht="15.75" customHeight="1">
-      <c r="B317" s="5"/>
-    </row>
-    <row r="318" ht="15.75" customHeight="1">
-      <c r="B318" s="5"/>
-    </row>
-    <row r="319" ht="15.75" customHeight="1">
-      <c r="B319" s="5"/>
-    </row>
-    <row r="320" ht="15.75" customHeight="1">
-      <c r="B320" s="5"/>
-    </row>
-    <row r="321" ht="15.75" customHeight="1">
-      <c r="B321" s="5"/>
-    </row>
-    <row r="322" ht="15.75" customHeight="1">
-      <c r="B322" s="5"/>
-    </row>
-    <row r="323" ht="15.75" customHeight="1">
-      <c r="B323" s="5"/>
-    </row>
-    <row r="324" ht="15.75" customHeight="1">
-      <c r="B324" s="5"/>
-    </row>
-    <row r="325" ht="15.75" customHeight="1">
-      <c r="B325" s="5"/>
-    </row>
-    <row r="326" ht="15.75" customHeight="1">
-      <c r="B326" s="5"/>
-    </row>
-    <row r="327" ht="15.75" customHeight="1">
-      <c r="B327" s="5"/>
-    </row>
-    <row r="328" ht="15.75" customHeight="1">
-      <c r="B328" s="5"/>
-    </row>
-    <row r="329" ht="15.75" customHeight="1">
-      <c r="B329" s="5"/>
-    </row>
-    <row r="330" ht="15.75" customHeight="1">
-      <c r="B330" s="5"/>
-    </row>
-    <row r="331" ht="15.75" customHeight="1">
-      <c r="B331" s="5"/>
-    </row>
-    <row r="332" ht="15.75" customHeight="1">
-      <c r="B332" s="5"/>
-    </row>
-    <row r="333" ht="15.75" customHeight="1">
-      <c r="B333" s="5"/>
-    </row>
-    <row r="334" ht="15.75" customHeight="1">
-      <c r="B334" s="5"/>
-    </row>
-    <row r="335" ht="15.75" customHeight="1">
-      <c r="B335" s="5"/>
-    </row>
-    <row r="336" ht="15.75" customHeight="1">
-      <c r="B336" s="5"/>
-    </row>
-    <row r="337" ht="15.75" customHeight="1">
-      <c r="B337" s="5"/>
-    </row>
-    <row r="338" ht="15.75" customHeight="1">
-      <c r="B338" s="5"/>
-    </row>
-    <row r="339" ht="15.75" customHeight="1">
-      <c r="B339" s="5"/>
-    </row>
-    <row r="340" ht="15.75" customHeight="1">
-      <c r="B340" s="5"/>
-    </row>
-    <row r="341" ht="15.75" customHeight="1">
-      <c r="B341" s="5"/>
-    </row>
-    <row r="342" ht="15.75" customHeight="1">
-      <c r="B342" s="5"/>
-    </row>
-    <row r="343" ht="15.75" customHeight="1">
-      <c r="B343" s="5"/>
-    </row>
-    <row r="344" ht="15.75" customHeight="1">
-      <c r="B344" s="5"/>
-    </row>
-    <row r="345" ht="15.75" customHeight="1">
-      <c r="B345" s="5"/>
-    </row>
-    <row r="346" ht="15.75" customHeight="1">
-      <c r="B346" s="5"/>
-    </row>
-    <row r="347" ht="15.75" customHeight="1">
-      <c r="B347" s="5"/>
-    </row>
-    <row r="348" ht="15.75" customHeight="1">
-      <c r="B348" s="5"/>
-    </row>
-    <row r="349" ht="15.75" customHeight="1">
-      <c r="B349" s="5"/>
-    </row>
-    <row r="350" ht="15.75" customHeight="1">
-      <c r="B350" s="5"/>
-    </row>
-    <row r="351" ht="15.75" customHeight="1">
-      <c r="B351" s="5"/>
-    </row>
-    <row r="352" ht="15.75" customHeight="1">
-      <c r="B352" s="5"/>
-    </row>
-    <row r="353" ht="15.75" customHeight="1">
-      <c r="B353" s="5"/>
-    </row>
-    <row r="354" ht="15.75" customHeight="1">
-      <c r="B354" s="5"/>
-    </row>
-    <row r="355" ht="15.75" customHeight="1">
-      <c r="B355" s="5"/>
-    </row>
-    <row r="356" ht="15.75" customHeight="1">
-      <c r="B356" s="5"/>
-    </row>
-    <row r="357" ht="15.75" customHeight="1">
-      <c r="B357" s="5"/>
-    </row>
-    <row r="358" ht="15.75" customHeight="1">
-      <c r="B358" s="5"/>
-    </row>
-    <row r="359" ht="15.75" customHeight="1">
-      <c r="B359" s="5"/>
-    </row>
-    <row r="360" ht="15.75" customHeight="1">
-      <c r="B360" s="5"/>
-    </row>
-    <row r="361" ht="15.75" customHeight="1">
-      <c r="B361" s="5"/>
-    </row>
-    <row r="362" ht="15.75" customHeight="1">
-      <c r="B362" s="5"/>
-    </row>
-    <row r="363" ht="15.75" customHeight="1">
-      <c r="B363" s="5"/>
-    </row>
-    <row r="364" ht="15.75" customHeight="1">
-      <c r="B364" s="5"/>
-    </row>
-    <row r="365" ht="15.75" customHeight="1">
-      <c r="B365" s="5"/>
-    </row>
-    <row r="366" ht="15.75" customHeight="1">
-      <c r="B366" s="5"/>
-    </row>
-    <row r="367" ht="15.75" customHeight="1">
-      <c r="B367" s="5"/>
-    </row>
-    <row r="368" ht="15.75" customHeight="1">
-      <c r="B368" s="5"/>
-    </row>
-    <row r="369" ht="15.75" customHeight="1">
-      <c r="B369" s="5"/>
-    </row>
-    <row r="370" ht="15.75" customHeight="1">
-      <c r="B370" s="5"/>
-    </row>
-    <row r="371" ht="15.75" customHeight="1">
-      <c r="B371" s="5"/>
-    </row>
-    <row r="372" ht="15.75" customHeight="1">
-      <c r="B372" s="5"/>
-    </row>
-    <row r="373" ht="15.75" customHeight="1">
-      <c r="B373" s="5"/>
-    </row>
-    <row r="374" ht="15.75" customHeight="1">
-      <c r="B374" s="5"/>
-    </row>
-    <row r="375" ht="15.75" customHeight="1">
-      <c r="B375" s="5"/>
-    </row>
-    <row r="376" ht="15.75" customHeight="1">
-      <c r="B376" s="5"/>
-    </row>
-    <row r="377" ht="15.75" customHeight="1">
-      <c r="B377" s="5"/>
-    </row>
-    <row r="378" ht="15.75" customHeight="1">
-      <c r="B378" s="5"/>
-    </row>
-    <row r="379" ht="15.75" customHeight="1">
-      <c r="B379" s="5"/>
-    </row>
-    <row r="380" ht="15.75" customHeight="1">
-      <c r="B380" s="5"/>
-    </row>
-    <row r="381" ht="15.75" customHeight="1">
-      <c r="B381" s="5"/>
-    </row>
-    <row r="382" ht="15.75" customHeight="1">
-      <c r="B382" s="5"/>
-    </row>
-    <row r="383" ht="15.75" customHeight="1">
-      <c r="B383" s="5"/>
-    </row>
-    <row r="384" ht="15.75" customHeight="1">
-      <c r="B384" s="5"/>
-    </row>
-    <row r="385" ht="15.75" customHeight="1">
-      <c r="B385" s="5"/>
-    </row>
-    <row r="386" ht="15.75" customHeight="1">
-      <c r="B386" s="5"/>
-    </row>
-    <row r="387" ht="15.75" customHeight="1">
-      <c r="B387" s="5"/>
-    </row>
-    <row r="388" ht="15.75" customHeight="1">
-      <c r="B388" s="5"/>
-    </row>
-    <row r="389" ht="15.75" customHeight="1">
-      <c r="B389" s="5"/>
-    </row>
-    <row r="390" ht="15.75" customHeight="1">
-      <c r="B390" s="5"/>
-    </row>
-    <row r="391" ht="15.75" customHeight="1">
-      <c r="B391" s="5"/>
-    </row>
-    <row r="392" ht="15.75" customHeight="1">
-      <c r="B392" s="5"/>
-    </row>
-    <row r="393" ht="15.75" customHeight="1">
-      <c r="B393" s="5"/>
-    </row>
-    <row r="394" ht="15.75" customHeight="1">
-      <c r="B394" s="5"/>
-    </row>
-    <row r="395" ht="15.75" customHeight="1">
-      <c r="B395" s="5"/>
-    </row>
-    <row r="396" ht="15.75" customHeight="1">
-      <c r="B396" s="5"/>
-    </row>
-    <row r="397" ht="15.75" customHeight="1">
-      <c r="B397" s="5"/>
-    </row>
-    <row r="398" ht="15.75" customHeight="1">
-      <c r="B398" s="5"/>
-    </row>
-    <row r="399" ht="15.75" customHeight="1">
-      <c r="B399" s="5"/>
-    </row>
-    <row r="400" ht="15.75" customHeight="1">
-      <c r="B400" s="5"/>
-    </row>
-    <row r="401" ht="15.75" customHeight="1">
-      <c r="B401" s="5"/>
-    </row>
-    <row r="402" ht="15.75" customHeight="1">
-      <c r="B402" s="5"/>
-    </row>
-    <row r="403" ht="15.75" customHeight="1">
-      <c r="B403" s="5"/>
-    </row>
-    <row r="404" ht="15.75" customHeight="1">
-      <c r="B404" s="5"/>
-    </row>
-    <row r="405" ht="15.75" customHeight="1">
-      <c r="B405" s="5"/>
-    </row>
-    <row r="406" ht="15.75" customHeight="1">
-      <c r="B406" s="5"/>
-    </row>
-    <row r="407" ht="15.75" customHeight="1">
-      <c r="B407" s="5"/>
-    </row>
-    <row r="408" ht="15.75" customHeight="1">
-      <c r="B408" s="5"/>
-    </row>
-    <row r="409" ht="15.75" customHeight="1">
-      <c r="B409" s="5"/>
-    </row>
-    <row r="410" ht="15.75" customHeight="1">
-      <c r="B410" s="5"/>
-    </row>
-    <row r="411" ht="15.75" customHeight="1">
-      <c r="B411" s="5"/>
-    </row>
-    <row r="412" ht="15.75" customHeight="1">
-      <c r="B412" s="5"/>
-    </row>
-    <row r="413" ht="15.75" customHeight="1">
-      <c r="B413" s="5"/>
-    </row>
-    <row r="414" ht="15.75" customHeight="1">
-      <c r="B414" s="5"/>
-    </row>
-    <row r="415" ht="15.75" customHeight="1">
-      <c r="B415" s="5"/>
-    </row>
-    <row r="416" ht="15.75" customHeight="1">
-      <c r="B416" s="5"/>
-    </row>
-    <row r="417" ht="15.75" customHeight="1">
-      <c r="B417" s="5"/>
-    </row>
-    <row r="418" ht="15.75" customHeight="1">
-      <c r="B418" s="5"/>
-    </row>
-    <row r="419" ht="15.75" customHeight="1">
-      <c r="B419" s="5"/>
-    </row>
-    <row r="420" ht="15.75" customHeight="1">
-      <c r="B420" s="5"/>
-    </row>
-    <row r="421" ht="15.75" customHeight="1">
-      <c r="B421" s="5"/>
-    </row>
-    <row r="422" ht="15.75" customHeight="1">
-      <c r="B422" s="5"/>
-    </row>
-    <row r="423" ht="15.75" customHeight="1">
-      <c r="B423" s="5"/>
-    </row>
-    <row r="424" ht="15.75" customHeight="1">
-      <c r="B424" s="5"/>
-    </row>
-    <row r="425" ht="15.75" customHeight="1">
-      <c r="B425" s="5"/>
-    </row>
-    <row r="426" ht="15.75" customHeight="1">
-      <c r="B426" s="5"/>
-    </row>
-    <row r="427" ht="15.75" customHeight="1">
-      <c r="B427" s="5"/>
-    </row>
-    <row r="428" ht="15.75" customHeight="1">
-      <c r="B428" s="5"/>
-    </row>
-    <row r="429" ht="15.75" customHeight="1">
-      <c r="B429" s="5"/>
-    </row>
-    <row r="430" ht="15.75" customHeight="1">
-      <c r="B430" s="5"/>
-    </row>
-    <row r="431" ht="15.75" customHeight="1">
-      <c r="B431" s="5"/>
-    </row>
-    <row r="432" ht="15.75" customHeight="1">
-      <c r="B432" s="5"/>
-    </row>
-    <row r="433" ht="15.75" customHeight="1">
-      <c r="B433" s="5"/>
-    </row>
-    <row r="434" ht="15.75" customHeight="1">
-      <c r="B434" s="5"/>
-    </row>
-    <row r="435" ht="15.75" customHeight="1">
-      <c r="B435" s="5"/>
-    </row>
-    <row r="436" ht="15.75" customHeight="1">
-      <c r="B436" s="5"/>
-    </row>
-    <row r="437" ht="15.75" customHeight="1">
-      <c r="B437" s="5"/>
-    </row>
-    <row r="438" ht="15.75" customHeight="1">
-      <c r="B438" s="5"/>
-    </row>
-    <row r="439" ht="15.75" customHeight="1">
-      <c r="B439" s="5"/>
-    </row>
-    <row r="440" ht="15.75" customHeight="1">
-      <c r="B440" s="5"/>
-    </row>
-    <row r="441" ht="15.75" customHeight="1">
-      <c r="B441" s="5"/>
-    </row>
-    <row r="442" ht="15.75" customHeight="1">
-      <c r="B442" s="5"/>
-    </row>
-    <row r="443" ht="15.75" customHeight="1">
-      <c r="B443" s="5"/>
-    </row>
-    <row r="444" ht="15.75" customHeight="1">
-      <c r="B444" s="5"/>
-    </row>
-    <row r="445" ht="15.75" customHeight="1">
-      <c r="B445" s="5"/>
-    </row>
-    <row r="446" ht="15.75" customHeight="1">
-      <c r="B446" s="5"/>
-    </row>
-    <row r="447" ht="15.75" customHeight="1">
-      <c r="B447" s="5"/>
-    </row>
-    <row r="448" ht="15.75" customHeight="1">
-      <c r="B448" s="5"/>
-    </row>
-    <row r="449" ht="15.75" customHeight="1">
-      <c r="B449" s="5"/>
-    </row>
-    <row r="450" ht="15.75" customHeight="1">
-      <c r="B450" s="5"/>
-    </row>
-    <row r="451" ht="15.75" customHeight="1">
-      <c r="B451" s="5"/>
-    </row>
-    <row r="452" ht="15.75" customHeight="1">
-      <c r="B452" s="5"/>
-    </row>
-    <row r="453" ht="15.75" customHeight="1">
-      <c r="B453" s="5"/>
-    </row>
-    <row r="454" ht="15.75" customHeight="1">
-      <c r="B454" s="5"/>
-    </row>
-    <row r="455" ht="15.75" customHeight="1">
-      <c r="B455" s="5"/>
-    </row>
-    <row r="456" ht="15.75" customHeight="1">
-      <c r="B456" s="5"/>
-    </row>
-    <row r="457" ht="15.75" customHeight="1">
-      <c r="B457" s="5"/>
-    </row>
-    <row r="458" ht="15.75" customHeight="1">
-      <c r="B458" s="5"/>
-    </row>
-    <row r="459" ht="15.75" customHeight="1">
-      <c r="B459" s="5"/>
-    </row>
-    <row r="460" ht="15.75" customHeight="1">
-      <c r="B460" s="5"/>
-    </row>
-    <row r="461" ht="15.75" customHeight="1">
-      <c r="B461" s="5"/>
-    </row>
-    <row r="462" ht="15.75" customHeight="1">
-      <c r="B462" s="5"/>
-    </row>
-    <row r="463" ht="15.75" customHeight="1">
-      <c r="B463" s="5"/>
-    </row>
-    <row r="464" ht="15.75" customHeight="1">
-      <c r="B464" s="5"/>
-    </row>
-    <row r="465" ht="15.75" customHeight="1">
-      <c r="B465" s="5"/>
-    </row>
-    <row r="466" ht="15.75" customHeight="1">
-      <c r="B466" s="5"/>
-    </row>
-    <row r="467" ht="15.75" customHeight="1">
-      <c r="B467" s="5"/>
-    </row>
-    <row r="468" ht="15.75" customHeight="1">
-      <c r="B468" s="5"/>
-    </row>
-    <row r="469" ht="15.75" customHeight="1">
-      <c r="B469" s="5"/>
-    </row>
-    <row r="470" ht="15.75" customHeight="1">
-      <c r="B470" s="5"/>
-    </row>
-    <row r="471" ht="15.75" customHeight="1">
-      <c r="B471" s="5"/>
-    </row>
-    <row r="472" ht="15.75" customHeight="1">
-      <c r="B472" s="5"/>
-    </row>
-    <row r="473" ht="15.75" customHeight="1">
-      <c r="B473" s="5"/>
-    </row>
-    <row r="474" ht="15.75" customHeight="1">
-      <c r="B474" s="5"/>
-    </row>
-    <row r="475" ht="15.75" customHeight="1">
-      <c r="B475" s="5"/>
-    </row>
-    <row r="476" ht="15.75" customHeight="1">
-      <c r="B476" s="5"/>
-    </row>
-    <row r="477" ht="15.75" customHeight="1">
-      <c r="B477" s="5"/>
-    </row>
-    <row r="478" ht="15.75" customHeight="1">
-      <c r="B478" s="5"/>
-    </row>
-    <row r="479" ht="15.75" customHeight="1">
-      <c r="B479" s="5"/>
-    </row>
-    <row r="480" ht="15.75" customHeight="1">
-      <c r="B480" s="5"/>
-    </row>
-    <row r="481" ht="15.75" customHeight="1">
-      <c r="B481" s="5"/>
-    </row>
-    <row r="482" ht="15.75" customHeight="1">
-      <c r="B482" s="5"/>
-    </row>
-    <row r="483" ht="15.75" customHeight="1">
-      <c r="B483" s="5"/>
-    </row>
-    <row r="484" ht="15.75" customHeight="1">
-      <c r="B484" s="5"/>
-    </row>
-    <row r="485" ht="15.75" customHeight="1">
-      <c r="B485" s="5"/>
-    </row>
-    <row r="486" ht="15.75" customHeight="1">
-      <c r="B486" s="5"/>
-    </row>
-    <row r="487" ht="15.75" customHeight="1">
-      <c r="B487" s="5"/>
-    </row>
-    <row r="488" ht="15.75" customHeight="1">
-      <c r="B488" s="5"/>
-    </row>
-    <row r="489" ht="15.75" customHeight="1">
-      <c r="B489" s="5"/>
-    </row>
-    <row r="490" ht="15.75" customHeight="1">
-      <c r="B490" s="5"/>
-    </row>
-    <row r="491" ht="15.75" customHeight="1">
-      <c r="B491" s="5"/>
-    </row>
-    <row r="492" ht="15.75" customHeight="1">
-      <c r="B492" s="5"/>
-    </row>
-    <row r="493" ht="15.75" customHeight="1">
-      <c r="B493" s="5"/>
-    </row>
-    <row r="494" ht="15.75" customHeight="1">
-      <c r="B494" s="5"/>
-    </row>
-    <row r="495" ht="15.75" customHeight="1">
-      <c r="B495" s="5"/>
-    </row>
-    <row r="496" ht="15.75" customHeight="1">
-      <c r="B496" s="5"/>
-    </row>
-    <row r="497" ht="15.75" customHeight="1">
-      <c r="B497" s="5"/>
-    </row>
-    <row r="498" ht="15.75" customHeight="1">
-      <c r="B498" s="5"/>
-    </row>
-    <row r="499" ht="15.75" customHeight="1">
-      <c r="B499" s="5"/>
-    </row>
-    <row r="500" ht="15.75" customHeight="1">
-      <c r="B500" s="5"/>
-    </row>
-    <row r="501" ht="15.75" customHeight="1">
-      <c r="B501" s="5"/>
-    </row>
-    <row r="502" ht="15.75" customHeight="1">
-      <c r="B502" s="5"/>
-    </row>
-    <row r="503" ht="15.75" customHeight="1">
-      <c r="B503" s="5"/>
-    </row>
-    <row r="504" ht="15.75" customHeight="1">
-      <c r="B504" s="5"/>
-    </row>
-    <row r="505" ht="15.75" customHeight="1">
-      <c r="B505" s="5"/>
-    </row>
-    <row r="506" ht="15.75" customHeight="1">
-      <c r="B506" s="5"/>
-    </row>
-    <row r="507" ht="15.75" customHeight="1">
-      <c r="B507" s="5"/>
-    </row>
-    <row r="508" ht="15.75" customHeight="1">
-      <c r="B508" s="5"/>
-    </row>
-    <row r="509" ht="15.75" customHeight="1">
-      <c r="B509" s="5"/>
-    </row>
-    <row r="510" ht="15.75" customHeight="1">
-      <c r="B510" s="5"/>
-    </row>
-    <row r="511" ht="15.75" customHeight="1">
-      <c r="B511" s="5"/>
-    </row>
-    <row r="512" ht="15.75" customHeight="1">
-      <c r="B512" s="5"/>
-    </row>
-    <row r="513" ht="15.75" customHeight="1">
-      <c r="B513" s="5"/>
-    </row>
-    <row r="514" ht="15.75" customHeight="1">
-      <c r="B514" s="5"/>
-    </row>
-    <row r="515" ht="15.75" customHeight="1">
-      <c r="B515" s="5"/>
-    </row>
-    <row r="516" ht="15.75" customHeight="1">
-      <c r="B516" s="5"/>
-    </row>
-    <row r="517" ht="15.75" customHeight="1">
-      <c r="B517" s="5"/>
-    </row>
-    <row r="518" ht="15.75" customHeight="1">
-      <c r="B518" s="5"/>
-    </row>
-    <row r="519" ht="15.75" customHeight="1">
-      <c r="B519" s="5"/>
-    </row>
-    <row r="520" ht="15.75" customHeight="1">
-      <c r="B520" s="5"/>
-    </row>
-    <row r="521" ht="15.75" customHeight="1">
-      <c r="B521" s="5"/>
-    </row>
-    <row r="522" ht="15.75" customHeight="1">
-      <c r="B522" s="5"/>
-    </row>
-    <row r="523" ht="15.75" customHeight="1">
-      <c r="B523" s="5"/>
-    </row>
-    <row r="524" ht="15.75" customHeight="1">
-      <c r="B524" s="5"/>
-    </row>
-    <row r="525" ht="15.75" customHeight="1">
-      <c r="B525" s="5"/>
-    </row>
-    <row r="526" ht="15.75" customHeight="1">
-      <c r="B526" s="5"/>
-    </row>
-    <row r="527" ht="15.75" customHeight="1">
-      <c r="B527" s="5"/>
-    </row>
-    <row r="528" ht="15.75" customHeight="1">
-      <c r="B528" s="5"/>
-    </row>
-    <row r="529" ht="15.75" customHeight="1">
-      <c r="B529" s="5"/>
-    </row>
-    <row r="530" ht="15.75" customHeight="1">
-      <c r="B530" s="5"/>
-    </row>
-    <row r="531" ht="15.75" customHeight="1">
-      <c r="B531" s="5"/>
-    </row>
-    <row r="532" ht="15.75" customHeight="1">
-      <c r="B532" s="5"/>
-    </row>
-    <row r="533" ht="15.75" customHeight="1">
-      <c r="B533" s="5"/>
-    </row>
-    <row r="534" ht="15.75" customHeight="1">
-      <c r="B534" s="5"/>
-    </row>
-    <row r="535" ht="15.75" customHeight="1">
-      <c r="B535" s="5"/>
-    </row>
-    <row r="536" ht="15.75" customHeight="1">
-      <c r="B536" s="5"/>
-    </row>
-    <row r="537" ht="15.75" customHeight="1">
-      <c r="B537" s="5"/>
-    </row>
-    <row r="538" ht="15.75" customHeight="1">
-      <c r="B538" s="5"/>
-    </row>
-    <row r="539" ht="15.75" customHeight="1">
-      <c r="B539" s="5"/>
-    </row>
-    <row r="540" ht="15.75" customHeight="1">
-      <c r="B540" s="5"/>
-    </row>
-    <row r="541" ht="15.75" customHeight="1">
-      <c r="B541" s="5"/>
-    </row>
-    <row r="542" ht="15.75" customHeight="1">
-      <c r="B542" s="5"/>
-    </row>
-    <row r="543" ht="15.75" customHeight="1">
-      <c r="B543" s="5"/>
-    </row>
-    <row r="544" ht="15.75" customHeight="1">
-      <c r="B544" s="5"/>
-    </row>
-    <row r="545" ht="15.75" customHeight="1">
-      <c r="B545" s="5"/>
-    </row>
-    <row r="546" ht="15.75" customHeight="1">
-      <c r="B546" s="5"/>
-    </row>
-    <row r="547" ht="15.75" customHeight="1">
-      <c r="B547" s="5"/>
-    </row>
-    <row r="548" ht="15.75" customHeight="1">
-      <c r="B548" s="5"/>
-    </row>
-    <row r="549" ht="15.75" customHeight="1">
-      <c r="B549" s="5"/>
-    </row>
-    <row r="550" ht="15.75" customHeight="1">
-      <c r="B550" s="5"/>
-    </row>
-    <row r="551" ht="15.75" customHeight="1">
-      <c r="B551" s="5"/>
-    </row>
-    <row r="552" ht="15.75" customHeight="1">
-      <c r="B552" s="5"/>
-    </row>
-    <row r="553" ht="15.75" customHeight="1">
-      <c r="B553" s="5"/>
-    </row>
-    <row r="554" ht="15.75" customHeight="1">
-      <c r="B554" s="5"/>
-    </row>
-    <row r="555" ht="15.75" customHeight="1">
-      <c r="B555" s="5"/>
-    </row>
-    <row r="556" ht="15.75" customHeight="1">
-      <c r="B556" s="5"/>
-    </row>
-    <row r="557" ht="15.75" customHeight="1">
-      <c r="B557" s="5"/>
-    </row>
-    <row r="558" ht="15.75" customHeight="1">
-      <c r="B558" s="5"/>
-    </row>
-    <row r="559" ht="15.75" customHeight="1">
-      <c r="B559" s="5"/>
-    </row>
-    <row r="560" ht="15.75" customHeight="1">
-      <c r="B560" s="5"/>
-    </row>
-    <row r="561" ht="15.75" customHeight="1">
-      <c r="B561" s="5"/>
-    </row>
-    <row r="562" ht="15.75" customHeight="1">
-      <c r="B562" s="5"/>
-    </row>
-    <row r="563" ht="15.75" customHeight="1">
-      <c r="B563" s="5"/>
-    </row>
-    <row r="564" ht="15.75" customHeight="1">
-      <c r="B564" s="5"/>
-    </row>
-    <row r="565" ht="15.75" customHeight="1">
-      <c r="B565" s="5"/>
-    </row>
-    <row r="566" ht="15.75" customHeight="1">
-      <c r="B566" s="5"/>
-    </row>
-    <row r="567" ht="15.75" customHeight="1">
-      <c r="B567" s="5"/>
-    </row>
-    <row r="568" ht="15.75" customHeight="1">
-      <c r="B568" s="5"/>
-    </row>
-    <row r="569" ht="15.75" customHeight="1">
-      <c r="B569" s="5"/>
-    </row>
-    <row r="570" ht="15.75" customHeight="1">
-      <c r="B570" s="5"/>
-    </row>
-    <row r="571" ht="15.75" customHeight="1">
-      <c r="B571" s="5"/>
-    </row>
-    <row r="572" ht="15.75" customHeight="1">
-      <c r="B572" s="5"/>
-    </row>
-    <row r="573" ht="15.75" customHeight="1">
-      <c r="B573" s="5"/>
-    </row>
-    <row r="574" ht="15.75" customHeight="1">
-      <c r="B574" s="5"/>
-    </row>
-    <row r="575" ht="15.75" customHeight="1">
-      <c r="B575" s="5"/>
-    </row>
-    <row r="576" ht="15.75" customHeight="1">
-      <c r="B576" s="5"/>
-    </row>
-    <row r="577" ht="15.75" customHeight="1">
-      <c r="B577" s="5"/>
-    </row>
-    <row r="578" ht="15.75" customHeight="1">
-      <c r="B578" s="5"/>
-    </row>
-    <row r="579" ht="15.75" customHeight="1">
-      <c r="B579" s="5"/>
-    </row>
-    <row r="580" ht="15.75" customHeight="1">
-      <c r="B580" s="5"/>
-    </row>
-    <row r="581" ht="15.75" customHeight="1">
-      <c r="B581" s="5"/>
-    </row>
-    <row r="582" ht="15.75" customHeight="1">
-      <c r="B582" s="5"/>
-    </row>
-    <row r="583" ht="15.75" customHeight="1">
-      <c r="B583" s="5"/>
-    </row>
-    <row r="584" ht="15.75" customHeight="1">
-      <c r="B584" s="5"/>
-    </row>
-    <row r="585" ht="15.75" customHeight="1">
-      <c r="B585" s="5"/>
-    </row>
-    <row r="586" ht="15.75" customHeight="1">
-      <c r="B586" s="5"/>
-    </row>
-    <row r="587" ht="15.75" customHeight="1">
-      <c r="B587" s="5"/>
-    </row>
-    <row r="588" ht="15.75" customHeight="1">
-      <c r="B588" s="5"/>
-    </row>
-    <row r="589" ht="15.75" customHeight="1">
-      <c r="B589" s="5"/>
-    </row>
-    <row r="590" ht="15.75" customHeight="1">
-      <c r="B590" s="5"/>
-    </row>
-    <row r="591" ht="15.75" customHeight="1">
-      <c r="B591" s="5"/>
-    </row>
-    <row r="592" ht="15.75" customHeight="1">
-      <c r="B592" s="5"/>
-    </row>
-    <row r="593" ht="15.75" customHeight="1">
-      <c r="B593" s="5"/>
-    </row>
-    <row r="594" ht="15.75" customHeight="1">
-      <c r="B594" s="5"/>
-    </row>
-    <row r="595" ht="15.75" customHeight="1">
-      <c r="B595" s="5"/>
-    </row>
-    <row r="596" ht="15.75" customHeight="1">
-      <c r="B596" s="5"/>
-    </row>
-    <row r="597" ht="15.75" customHeight="1">
-      <c r="B597" s="5"/>
-    </row>
-    <row r="598" ht="15.75" customHeight="1">
-      <c r="B598" s="5"/>
-    </row>
-    <row r="599" ht="15.75" customHeight="1">
-      <c r="B599" s="5"/>
-    </row>
-    <row r="600" ht="15.75" customHeight="1">
-      <c r="B600" s="5"/>
-    </row>
-    <row r="601" ht="15.75" customHeight="1">
-      <c r="B601" s="5"/>
-    </row>
-    <row r="602" ht="15.75" customHeight="1">
-      <c r="B602" s="5"/>
-    </row>
-    <row r="603" ht="15.75" customHeight="1">
-      <c r="B603" s="5"/>
-    </row>
-    <row r="604" ht="15.75" customHeight="1">
-      <c r="B604" s="5"/>
-    </row>
-    <row r="605" ht="15.75" customHeight="1">
-      <c r="B605" s="5"/>
-    </row>
-    <row r="606" ht="15.75" customHeight="1">
-      <c r="B606" s="5"/>
-    </row>
-    <row r="607" ht="15.75" customHeight="1">
-      <c r="B607" s="5"/>
-    </row>
-    <row r="608" ht="15.75" customHeight="1">
-      <c r="B608" s="5"/>
-    </row>
-    <row r="609" ht="15.75" customHeight="1">
-      <c r="B609" s="5"/>
-    </row>
-    <row r="610" ht="15.75" customHeight="1">
-      <c r="B610" s="5"/>
-    </row>
-    <row r="611" ht="15.75" customHeight="1">
-      <c r="B611" s="5"/>
-    </row>
-    <row r="612" ht="15.75" customHeight="1">
-      <c r="B612" s="5"/>
-    </row>
-    <row r="613" ht="15.75" customHeight="1">
-      <c r="B613" s="5"/>
-    </row>
-    <row r="614" ht="15.75" customHeight="1">
-      <c r="B614" s="5"/>
-    </row>
-    <row r="615" ht="15.75" customHeight="1">
-      <c r="B615" s="5"/>
-    </row>
-    <row r="616" ht="15.75" customHeight="1">
-      <c r="B616" s="5"/>
-    </row>
-    <row r="617" ht="15.75" customHeight="1">
-      <c r="B617" s="5"/>
-    </row>
-    <row r="618" ht="15.75" customHeight="1">
-      <c r="B618" s="5"/>
-    </row>
-    <row r="619" ht="15.75" customHeight="1">
-      <c r="B619" s="5"/>
-    </row>
-    <row r="620" ht="15.75" customHeight="1">
-      <c r="B620" s="5"/>
-    </row>
-    <row r="621" ht="15.75" customHeight="1">
-      <c r="B621" s="5"/>
-    </row>
-    <row r="622" ht="15.75" customHeight="1">
-      <c r="B622" s="5"/>
-    </row>
-    <row r="623" ht="15.75" customHeight="1">
-      <c r="B623" s="5"/>
-    </row>
-    <row r="624" ht="15.75" customHeight="1">
-      <c r="B624" s="5"/>
-    </row>
-    <row r="625" ht="15.75" customHeight="1">
-      <c r="B625" s="5"/>
-    </row>
-    <row r="626" ht="15.75" customHeight="1">
-      <c r="B626" s="5"/>
-    </row>
-    <row r="627" ht="15.75" customHeight="1">
-      <c r="B627" s="5"/>
-    </row>
-    <row r="628" ht="15.75" customHeight="1">
-      <c r="B628" s="5"/>
-    </row>
-    <row r="629" ht="15.75" customHeight="1">
-      <c r="B629" s="5"/>
-    </row>
-    <row r="630" ht="15.75" customHeight="1">
-      <c r="B630" s="5"/>
-    </row>
-    <row r="631" ht="15.75" customHeight="1">
-      <c r="B631" s="5"/>
-    </row>
-    <row r="632" ht="15.75" customHeight="1">
-      <c r="B632" s="5"/>
-    </row>
-    <row r="633" ht="15.75" customHeight="1">
-      <c r="B633" s="5"/>
-    </row>
-    <row r="634" ht="15.75" customHeight="1">
-      <c r="B634" s="5"/>
-    </row>
-    <row r="635" ht="15.75" customHeight="1">
-      <c r="B635" s="5"/>
-    </row>
-    <row r="636" ht="15.75" customHeight="1">
-      <c r="B636" s="5"/>
-    </row>
-    <row r="637" ht="15.75" customHeight="1">
-      <c r="B637" s="5"/>
-    </row>
-    <row r="638" ht="15.75" customHeight="1">
-      <c r="B638" s="5"/>
-    </row>
-    <row r="639" ht="15.75" customHeight="1">
-      <c r="B639" s="5"/>
-    </row>
-    <row r="640" ht="15.75" customHeight="1">
-      <c r="B640" s="5"/>
-    </row>
-    <row r="641" ht="15.75" customHeight="1">
-      <c r="B641" s="5"/>
-    </row>
-    <row r="642" ht="15.75" customHeight="1">
-      <c r="B642" s="5"/>
-    </row>
-    <row r="643" ht="15.75" customHeight="1">
-      <c r="B643" s="5"/>
-    </row>
-    <row r="644" ht="15.75" customHeight="1">
-      <c r="B644" s="5"/>
-    </row>
-    <row r="645" ht="15.75" customHeight="1">
-      <c r="B645" s="5"/>
-    </row>
-    <row r="646" ht="15.75" customHeight="1">
-      <c r="B646" s="5"/>
-    </row>
-    <row r="647" ht="15.75" customHeight="1">
-      <c r="B647" s="5"/>
-    </row>
-    <row r="648" ht="15.75" customHeight="1">
-      <c r="B648" s="5"/>
-    </row>
-    <row r="649" ht="15.75" customHeight="1">
-      <c r="B649" s="5"/>
-    </row>
-    <row r="650" ht="15.75" customHeight="1">
-      <c r="B650" s="5"/>
-    </row>
-    <row r="651" ht="15.75" customHeight="1">
-      <c r="B651" s="5"/>
-    </row>
-    <row r="652" ht="15.75" customHeight="1">
-      <c r="B652" s="5"/>
-    </row>
-    <row r="653" ht="15.75" customHeight="1">
-      <c r="B653" s="5"/>
-    </row>
-    <row r="654" ht="15.75" customHeight="1">
-      <c r="B654" s="5"/>
-    </row>
-    <row r="655" ht="15.75" customHeight="1">
-      <c r="B655" s="5"/>
-    </row>
-    <row r="656" ht="15.75" customHeight="1">
-      <c r="B656" s="5"/>
-    </row>
-    <row r="657" ht="15.75" customHeight="1">
-      <c r="B657" s="5"/>
-    </row>
-    <row r="658" ht="15.75" customHeight="1">
-      <c r="B658" s="5"/>
-    </row>
-    <row r="659" ht="15.75" customHeight="1">
-      <c r="B659" s="5"/>
-    </row>
-    <row r="660" ht="15.75" customHeight="1">
-      <c r="B660" s="5"/>
-    </row>
-    <row r="661" ht="15.75" customHeight="1">
-      <c r="B661" s="5"/>
-    </row>
-    <row r="662" ht="15.75" customHeight="1">
-      <c r="B662" s="5"/>
-    </row>
-    <row r="663" ht="15.75" customHeight="1">
-      <c r="B663" s="5"/>
-    </row>
-    <row r="664" ht="15.75" customHeight="1">
-      <c r="B664" s="5"/>
-    </row>
-    <row r="665" ht="15.75" customHeight="1">
-      <c r="B665" s="5"/>
-    </row>
-    <row r="666" ht="15.75" customHeight="1">
-      <c r="B666" s="5"/>
-    </row>
-    <row r="667" ht="15.75" customHeight="1">
-      <c r="B667" s="5"/>
-    </row>
-    <row r="668" ht="15.75" customHeight="1">
-      <c r="B668" s="5"/>
-    </row>
-    <row r="669" ht="15.75" customHeight="1">
-      <c r="B669" s="5"/>
-    </row>
-    <row r="670" ht="15.75" customHeight="1">
-      <c r="B670" s="5"/>
-    </row>
-    <row r="671" ht="15.75" customHeight="1">
-      <c r="B671" s="5"/>
-    </row>
-    <row r="672" ht="15.75" customHeight="1">
-      <c r="B672" s="5"/>
-    </row>
-    <row r="673" ht="15.75" customHeight="1">
-      <c r="B673" s="5"/>
-    </row>
-    <row r="674" ht="15.75" customHeight="1">
-      <c r="B674" s="5"/>
-    </row>
-    <row r="675" ht="15.75" customHeight="1">
-      <c r="B675" s="5"/>
-    </row>
-    <row r="676" ht="15.75" customHeight="1">
-      <c r="B676" s="5"/>
-    </row>
-    <row r="677" ht="15.75" customHeight="1">
-      <c r="B677" s="5"/>
-    </row>
-    <row r="678" ht="15.75" customHeight="1">
-      <c r="B678" s="5"/>
-    </row>
-    <row r="679" ht="15.75" customHeight="1">
-      <c r="B679" s="5"/>
-    </row>
-    <row r="680" ht="15.75" customHeight="1">
-      <c r="B680" s="5"/>
-    </row>
-    <row r="681" ht="15.75" customHeight="1">
-      <c r="B681" s="5"/>
-    </row>
-    <row r="682" ht="15.75" customHeight="1">
-      <c r="B682" s="5"/>
-    </row>
-    <row r="683" ht="15.75" customHeight="1">
-      <c r="B683" s="5"/>
-    </row>
-    <row r="684" ht="15.75" customHeight="1">
-      <c r="B684" s="5"/>
-    </row>
-    <row r="685" ht="15.75" customHeight="1">
-      <c r="B685" s="5"/>
-    </row>
-    <row r="686" ht="15.75" customHeight="1">
-      <c r="B686" s="5"/>
-    </row>
-    <row r="687" ht="15.75" customHeight="1">
-      <c r="B687" s="5"/>
-    </row>
-    <row r="688" ht="15.75" customHeight="1">
-      <c r="B688" s="5"/>
-    </row>
-    <row r="689" ht="15.75" customHeight="1">
-      <c r="B689" s="5"/>
-    </row>
-    <row r="690" ht="15.75" customHeight="1">
-      <c r="B690" s="5"/>
-    </row>
-    <row r="691" ht="15.75" customHeight="1">
-      <c r="B691" s="5"/>
-    </row>
-    <row r="692" ht="15.75" customHeight="1">
-      <c r="B692" s="5"/>
-    </row>
-    <row r="693" ht="15.75" customHeight="1">
-      <c r="B693" s="5"/>
-    </row>
-    <row r="694" ht="15.75" customHeight="1">
-      <c r="B694" s="5"/>
-    </row>
-    <row r="695" ht="15.75" customHeight="1">
-      <c r="B695" s="5"/>
-    </row>
-    <row r="696" ht="15.75" customHeight="1">
-      <c r="B696" s="5"/>
-    </row>
-    <row r="697" ht="15.75" customHeight="1">
-      <c r="B697" s="5"/>
-    </row>
-    <row r="698" ht="15.75" customHeight="1">
-      <c r="B698" s="5"/>
-    </row>
-    <row r="699" ht="15.75" customHeight="1">
-      <c r="B699" s="5"/>
-    </row>
-    <row r="700" ht="15.75" customHeight="1">
-      <c r="B700" s="5"/>
-    </row>
-    <row r="701" ht="15.75" customHeight="1">
-      <c r="B701" s="5"/>
-    </row>
-    <row r="702" ht="15.75" customHeight="1">
-      <c r="B702" s="5"/>
-    </row>
-    <row r="703" ht="15.75" customHeight="1">
-      <c r="B703" s="5"/>
-    </row>
-    <row r="704" ht="15.75" customHeight="1">
-      <c r="B704" s="5"/>
-    </row>
-    <row r="705" ht="15.75" customHeight="1">
-      <c r="B705" s="5"/>
-    </row>
-    <row r="706" ht="15.75" customHeight="1">
-      <c r="B706" s="5"/>
-    </row>
-    <row r="707" ht="15.75" customHeight="1">
-      <c r="B707" s="5"/>
-    </row>
-    <row r="708" ht="15.75" customHeight="1">
-      <c r="B708" s="5"/>
-    </row>
-    <row r="709" ht="15.75" customHeight="1">
-      <c r="B709" s="5"/>
-    </row>
-    <row r="710" ht="15.75" customHeight="1">
-      <c r="B710" s="5"/>
-    </row>
-    <row r="711" ht="15.75" customHeight="1">
-      <c r="B711" s="5"/>
-    </row>
-    <row r="712" ht="15.75" customHeight="1">
-      <c r="B712" s="5"/>
-    </row>
-    <row r="713" ht="15.75" customHeight="1">
-      <c r="B713" s="5"/>
-    </row>
-    <row r="714" ht="15.75" customHeight="1">
-      <c r="B714" s="5"/>
-    </row>
-    <row r="715" ht="15.75" customHeight="1">
-      <c r="B715" s="5"/>
-    </row>
-    <row r="716" ht="15.75" customHeight="1">
-      <c r="B716" s="5"/>
-    </row>
-    <row r="717" ht="15.75" customHeight="1">
-      <c r="B717" s="5"/>
-    </row>
-    <row r="718" ht="15.75" customHeight="1">
-      <c r="B718" s="5"/>
-    </row>
-    <row r="719" ht="15.75" customHeight="1">
-      <c r="B719" s="5"/>
-    </row>
-    <row r="720" ht="15.75" customHeight="1">
-      <c r="B720" s="5"/>
-    </row>
-    <row r="721" ht="15.75" customHeight="1">
-      <c r="B721" s="5"/>
-    </row>
-    <row r="722" ht="15.75" customHeight="1">
-      <c r="B722" s="5"/>
-    </row>
-    <row r="723" ht="15.75" customHeight="1">
-      <c r="B723" s="5"/>
-    </row>
-    <row r="724" ht="15.75" customHeight="1">
-      <c r="B724" s="5"/>
-    </row>
-    <row r="725" ht="15.75" customHeight="1">
-      <c r="B725" s="5"/>
-    </row>
-    <row r="726" ht="15.75" customHeight="1">
-      <c r="B726" s="5"/>
-    </row>
-    <row r="727" ht="15.75" customHeight="1">
-      <c r="B727" s="5"/>
-    </row>
-    <row r="728" ht="15.75" customHeight="1">
-      <c r="B728" s="5"/>
-    </row>
-    <row r="729" ht="15.75" customHeight="1">
-      <c r="B729" s="5"/>
-    </row>
-    <row r="730" ht="15.75" customHeight="1">
-      <c r="B730" s="5"/>
-    </row>
-    <row r="731" ht="15.75" customHeight="1">
-      <c r="B731" s="5"/>
-    </row>
-    <row r="732" ht="15.75" customHeight="1">
-      <c r="B732" s="5"/>
-    </row>
-    <row r="733" ht="15.75" customHeight="1">
-      <c r="B733" s="5"/>
-    </row>
-    <row r="734" ht="15.75" customHeight="1">
-      <c r="B734" s="5"/>
-    </row>
-    <row r="735" ht="15.75" customHeight="1">
-      <c r="B735" s="5"/>
-    </row>
-    <row r="736" ht="15.75" customHeight="1">
-      <c r="B736" s="5"/>
-    </row>
-    <row r="737" ht="15.75" customHeight="1">
-      <c r="B737" s="5"/>
-    </row>
-    <row r="738" ht="15.75" customHeight="1">
-      <c r="B738" s="5"/>
-    </row>
-    <row r="739" ht="15.75" customHeight="1">
-      <c r="B739" s="5"/>
-    </row>
-    <row r="740" ht="15.75" customHeight="1">
-      <c r="B740" s="5"/>
-    </row>
-    <row r="741" ht="15.75" customHeight="1">
-      <c r="B741" s="5"/>
-    </row>
-    <row r="742" ht="15.75" customHeight="1">
-      <c r="B742" s="5"/>
-    </row>
-    <row r="743" ht="15.75" customHeight="1">
-      <c r="B743" s="5"/>
-    </row>
-    <row r="744" ht="15.75" customHeight="1">
-      <c r="B744" s="5"/>
-    </row>
-    <row r="745" ht="15.75" customHeight="1">
-      <c r="B745" s="5"/>
-    </row>
-    <row r="746" ht="15.75" customHeight="1">
-      <c r="B746" s="5"/>
-    </row>
-    <row r="747" ht="15.75" customHeight="1">
-      <c r="B747" s="5"/>
-    </row>
-    <row r="748" ht="15.75" customHeight="1">
-      <c r="B748" s="5"/>
-    </row>
-    <row r="749" ht="15.75" customHeight="1">
-      <c r="B749" s="5"/>
-    </row>
-    <row r="750" ht="15.75" customHeight="1">
-      <c r="B750" s="5"/>
-    </row>
-    <row r="751" ht="15.75" customHeight="1">
-      <c r="B751" s="5"/>
-    </row>
-    <row r="752" ht="15.75" customHeight="1">
-      <c r="B752" s="5"/>
-    </row>
-    <row r="753" ht="15.75" customHeight="1">
-      <c r="B753" s="5"/>
-    </row>
-    <row r="754" ht="15.75" customHeight="1">
-      <c r="B754" s="5"/>
-    </row>
-    <row r="755" ht="15.75" customHeight="1">
-      <c r="B755" s="5"/>
-    </row>
-    <row r="756" ht="15.75" customHeight="1">
-      <c r="B756" s="5"/>
-    </row>
-    <row r="757" ht="15.75" customHeight="1">
-      <c r="B757" s="5"/>
-    </row>
-    <row r="758" ht="15.75" customHeight="1">
-      <c r="B758" s="5"/>
-    </row>
-    <row r="759" ht="15.75" customHeight="1">
-      <c r="B759" s="5"/>
-    </row>
-    <row r="760" ht="15.75" customHeight="1">
-      <c r="B760" s="5"/>
-    </row>
-    <row r="761" ht="15.75" customHeight="1">
-      <c r="B761" s="5"/>
-    </row>
-    <row r="762" ht="15.75" customHeight="1">
-      <c r="B762" s="5"/>
-    </row>
-    <row r="763" ht="15.75" customHeight="1">
-      <c r="B763" s="5"/>
-    </row>
-    <row r="764" ht="15.75" customHeight="1">
-      <c r="B764" s="5"/>
-    </row>
-    <row r="765" ht="15.75" customHeight="1">
-      <c r="B765" s="5"/>
-    </row>
-    <row r="766" ht="15.75" customHeight="1">
-      <c r="B766" s="5"/>
-    </row>
-    <row r="767" ht="15.75" customHeight="1">
-      <c r="B767" s="5"/>
-    </row>
-    <row r="768" ht="15.75" customHeight="1">
-      <c r="B768" s="5"/>
-    </row>
-    <row r="769" ht="15.75" customHeight="1">
-      <c r="B769" s="5"/>
-    </row>
-    <row r="770" ht="15.75" customHeight="1">
-      <c r="B770" s="5"/>
-    </row>
-    <row r="771" ht="15.75" customHeight="1">
-      <c r="B771" s="5"/>
-    </row>
-    <row r="772" ht="15.75" customHeight="1">
-      <c r="B772" s="5"/>
-    </row>
-    <row r="773" ht="15.75" customHeight="1">
-      <c r="B773" s="5"/>
-    </row>
-    <row r="774" ht="15.75" customHeight="1">
-      <c r="B774" s="5"/>
-    </row>
-    <row r="775" ht="15.75" customHeight="1">
-      <c r="B775" s="5"/>
-    </row>
-    <row r="776" ht="15.75" customHeight="1">
-      <c r="B776" s="5"/>
-    </row>
-    <row r="777" ht="15.75" customHeight="1">
-      <c r="B777" s="5"/>
-    </row>
-    <row r="778" ht="15.75" customHeight="1">
-      <c r="B778" s="5"/>
-    </row>
-    <row r="779" ht="15.75" customHeight="1">
-      <c r="B779" s="5"/>
-    </row>
-    <row r="780" ht="15.75" customHeight="1">
-      <c r="B780" s="5"/>
-    </row>
-    <row r="781" ht="15.75" customHeight="1">
-      <c r="B781" s="5"/>
-    </row>
-    <row r="782" ht="15.75" customHeight="1">
-      <c r="B782" s="5"/>
-    </row>
-    <row r="783" ht="15.75" customHeight="1">
-      <c r="B783" s="5"/>
-    </row>
-    <row r="784" ht="15.75" customHeight="1">
-      <c r="B784" s="5"/>
-    </row>
-    <row r="785" ht="15.75" customHeight="1">
-      <c r="B785" s="5"/>
-    </row>
-    <row r="786" ht="15.75" customHeight="1">
-      <c r="B786" s="5"/>
-    </row>
-    <row r="787" ht="15.75" customHeight="1">
-      <c r="B787" s="5"/>
-    </row>
-    <row r="788" ht="15.75" customHeight="1">
-      <c r="B788" s="5"/>
-    </row>
-    <row r="789" ht="15.75" customHeight="1">
-      <c r="B789" s="5"/>
-    </row>
-    <row r="790" ht="15.75" customHeight="1">
-      <c r="B790" s="5"/>
-    </row>
-    <row r="791" ht="15.75" customHeight="1">
-      <c r="B791" s="5"/>
-    </row>
-    <row r="792" ht="15.75" customHeight="1">
-      <c r="B792" s="5"/>
-    </row>
-    <row r="793" ht="15.75" customHeight="1">
-      <c r="B793" s="5"/>
-    </row>
-    <row r="794" ht="15.75" customHeight="1">
-      <c r="B794" s="5"/>
-    </row>
-    <row r="795" ht="15.75" customHeight="1">
-      <c r="B795" s="5"/>
-    </row>
-    <row r="796" ht="15.75" customHeight="1">
-      <c r="B796" s="5"/>
-    </row>
-    <row r="797" ht="15.75" customHeight="1">
-      <c r="B797" s="5"/>
-    </row>
-    <row r="798" ht="15.75" customHeight="1">
-      <c r="B798" s="5"/>
-    </row>
-    <row r="799" ht="15.75" customHeight="1">
-      <c r="B799" s="5"/>
-    </row>
-    <row r="800" ht="15.75" customHeight="1">
-      <c r="B800" s="5"/>
-    </row>
-    <row r="801" ht="15.75" customHeight="1">
-      <c r="B801" s="5"/>
-    </row>
-    <row r="802" ht="15.75" customHeight="1">
-      <c r="B802" s="5"/>
-    </row>
-    <row r="803" ht="15.75" customHeight="1">
-      <c r="B803" s="5"/>
-    </row>
-    <row r="804" ht="15.75" customHeight="1">
-      <c r="B804" s="5"/>
-    </row>
-    <row r="805" ht="15.75" customHeight="1">
-      <c r="B805" s="5"/>
-    </row>
-    <row r="806" ht="15.75" customHeight="1">
-      <c r="B806" s="5"/>
-    </row>
-    <row r="807" ht="15.75" customHeight="1">
-      <c r="B807" s="5"/>
-    </row>
-    <row r="808" ht="15.75" customHeight="1">
-      <c r="B808" s="5"/>
-    </row>
-    <row r="809" ht="15.75" customHeight="1">
-      <c r="B809" s="5"/>
-    </row>
-    <row r="810" ht="15.75" customHeight="1">
-      <c r="B810" s="5"/>
-    </row>
-    <row r="811" ht="15.75" customHeight="1">
-      <c r="B811" s="5"/>
-    </row>
-    <row r="812" ht="15.75" customHeight="1">
-      <c r="B812" s="5"/>
-    </row>
-    <row r="813" ht="15.75" customHeight="1">
-      <c r="B813" s="5"/>
-    </row>
-    <row r="814" ht="15.75" customHeight="1">
-      <c r="B814" s="5"/>
-    </row>
-    <row r="815" ht="15.75" customHeight="1">
-      <c r="B815" s="5"/>
-    </row>
-    <row r="816" ht="15.75" customHeight="1">
-      <c r="B816" s="5"/>
-    </row>
-    <row r="817" ht="15.75" customHeight="1">
-      <c r="B817" s="5"/>
-    </row>
-    <row r="818" ht="15.75" customHeight="1">
-      <c r="B818" s="5"/>
-    </row>
-    <row r="819" ht="15.75" customHeight="1">
-      <c r="B819" s="5"/>
-    </row>
-    <row r="820" ht="15.75" customHeight="1">
-      <c r="B820" s="5"/>
-    </row>
-    <row r="821" ht="15.75" customHeight="1">
-      <c r="B821" s="5"/>
-    </row>
-    <row r="822" ht="15.75" customHeight="1">
-      <c r="B822" s="5"/>
-    </row>
-    <row r="823" ht="15.75" customHeight="1">
-      <c r="B823" s="5"/>
-    </row>
-    <row r="824" ht="15.75" customHeight="1">
-      <c r="B824" s="5"/>
-    </row>
-    <row r="825" ht="15.75" customHeight="1">
-      <c r="B825" s="5"/>
-    </row>
-    <row r="826" ht="15.75" customHeight="1">
-      <c r="B826" s="5"/>
-    </row>
-    <row r="827" ht="15.75" customHeight="1">
-      <c r="B827" s="5"/>
-    </row>
-    <row r="828" ht="15.75" customHeight="1">
-      <c r="B828" s="5"/>
-    </row>
-    <row r="829" ht="15.75" customHeight="1">
-      <c r="B829" s="5"/>
-    </row>
-    <row r="830" ht="15.75" customHeight="1">
-      <c r="B830" s="5"/>
-    </row>
-    <row r="831" ht="15.75" customHeight="1">
-      <c r="B831" s="5"/>
-    </row>
-    <row r="832" ht="15.75" customHeight="1">
-      <c r="B832" s="5"/>
-    </row>
-    <row r="833" ht="15.75" customHeight="1">
-      <c r="B833" s="5"/>
-    </row>
-    <row r="834" ht="15.75" customHeight="1">
-      <c r="B834" s="5"/>
-    </row>
-    <row r="835" ht="15.75" customHeight="1">
-      <c r="B835" s="5"/>
-    </row>
-    <row r="836" ht="15.75" customHeight="1">
-      <c r="B836" s="5"/>
-    </row>
-    <row r="837" ht="15.75" customHeight="1">
-      <c r="B837" s="5"/>
-    </row>
-    <row r="838" ht="15.75" customHeight="1">
-      <c r="B838" s="5"/>
-    </row>
-    <row r="839" ht="15.75" customHeight="1">
-      <c r="B839" s="5"/>
-    </row>
-    <row r="840" ht="15.75" customHeight="1">
-      <c r="B840" s="5"/>
-    </row>
-    <row r="841" ht="15.75" customHeight="1">
-      <c r="B841" s="5"/>
-    </row>
-    <row r="842" ht="15.75" customHeight="1">
-      <c r="B842" s="5"/>
-    </row>
-    <row r="843" ht="15.75" customHeight="1">
-      <c r="B843" s="5"/>
-    </row>
-    <row r="844" ht="15.75" customHeight="1">
-      <c r="B844" s="5"/>
-    </row>
-    <row r="845" ht="15.75" customHeight="1">
-      <c r="B845" s="5"/>
-    </row>
-    <row r="846" ht="15.75" customHeight="1">
-      <c r="B846" s="5"/>
-    </row>
-    <row r="847" ht="15.75" customHeight="1">
-      <c r="B847" s="5"/>
-    </row>
-    <row r="848" ht="15.75" customHeight="1">
-      <c r="B848" s="5"/>
-    </row>
-    <row r="849" ht="15.75" customHeight="1">
-      <c r="B849" s="5"/>
-    </row>
-    <row r="850" ht="15.75" customHeight="1">
-      <c r="B850" s="5"/>
-    </row>
-    <row r="851" ht="15.75" customHeight="1">
-      <c r="B851" s="5"/>
-    </row>
-    <row r="852" ht="15.75" customHeight="1">
-      <c r="B852" s="5"/>
-    </row>
-    <row r="853" ht="15.75" customHeight="1">
-      <c r="B853" s="5"/>
-    </row>
-    <row r="854" ht="15.75" customHeight="1">
-      <c r="B854" s="5"/>
-    </row>
-    <row r="855" ht="15.75" customHeight="1">
-      <c r="B855" s="5"/>
-    </row>
-    <row r="856" ht="15.75" customHeight="1">
-      <c r="B856" s="5"/>
-    </row>
-    <row r="857" ht="15.75" customHeight="1">
-      <c r="B857" s="5"/>
-    </row>
-    <row r="858" ht="15.75" customHeight="1">
-      <c r="B858" s="5"/>
-    </row>
-    <row r="859" ht="15.75" customHeight="1">
-      <c r="B859" s="5"/>
-    </row>
-    <row r="860" ht="15.75" customHeight="1">
-      <c r="B860" s="5"/>
-    </row>
-    <row r="861" ht="15.75" customHeight="1">
-      <c r="B861" s="5"/>
-    </row>
-    <row r="862" ht="15.75" customHeight="1">
-      <c r="B862" s="5"/>
-    </row>
-    <row r="863" ht="15.75" customHeight="1">
-      <c r="B863" s="5"/>
-    </row>
-    <row r="864" ht="15.75" customHeight="1">
-      <c r="B864" s="5"/>
-    </row>
-    <row r="865" ht="15.75" customHeight="1">
-      <c r="B865" s="5"/>
-    </row>
-    <row r="866" ht="15.75" customHeight="1">
-      <c r="B866" s="5"/>
-    </row>
-    <row r="867" ht="15.75" customHeight="1">
-      <c r="B867" s="5"/>
-    </row>
-    <row r="868" ht="15.75" customHeight="1">
-      <c r="B868" s="5"/>
-    </row>
-    <row r="869" ht="15.75" customHeight="1">
-      <c r="B869" s="5"/>
-    </row>
-    <row r="870" ht="15.75" customHeight="1">
-      <c r="B870" s="5"/>
-    </row>
-    <row r="871" ht="15.75" customHeight="1">
-      <c r="B871" s="5"/>
-    </row>
-    <row r="872" ht="15.75" customHeight="1">
-      <c r="B872" s="5"/>
-    </row>
-    <row r="873" ht="15.75" customHeight="1">
-      <c r="B873" s="5"/>
-    </row>
-    <row r="874" ht="15.75" customHeight="1">
-      <c r="B874" s="5"/>
-    </row>
-    <row r="875" ht="15.75" customHeight="1">
-      <c r="B875" s="5"/>
-    </row>
-    <row r="876" ht="15.75" customHeight="1">
-      <c r="B876" s="5"/>
-    </row>
-    <row r="877" ht="15.75" customHeight="1">
-      <c r="B877" s="5"/>
-    </row>
-    <row r="878" ht="15.75" customHeight="1">
-      <c r="B878" s="5"/>
-    </row>
-    <row r="879" ht="15.75" customHeight="1">
-      <c r="B879" s="5"/>
-    </row>
-    <row r="880" ht="15.75" customHeight="1">
-      <c r="B880" s="5"/>
-    </row>
-    <row r="881" ht="15.75" customHeight="1">
-      <c r="B881" s="5"/>
-    </row>
-    <row r="882" ht="15.75" customHeight="1">
-      <c r="B882" s="5"/>
-    </row>
-    <row r="883" ht="15.75" customHeight="1">
-      <c r="B883" s="5"/>
-    </row>
-    <row r="884" ht="15.75" customHeight="1">
-      <c r="B884" s="5"/>
-    </row>
-    <row r="885" ht="15.75" customHeight="1">
-      <c r="B885" s="5"/>
-    </row>
-    <row r="886" ht="15.75" customHeight="1">
-      <c r="B886" s="5"/>
-    </row>
-    <row r="887" ht="15.75" customHeight="1">
-      <c r="B887" s="5"/>
-    </row>
-    <row r="888" ht="15.75" customHeight="1">
-      <c r="B888" s="5"/>
-    </row>
-    <row r="889" ht="15.75" customHeight="1">
-      <c r="B889" s="5"/>
-    </row>
-    <row r="890" ht="15.75" customHeight="1">
-      <c r="B890" s="5"/>
-    </row>
-    <row r="891" ht="15.75" customHeight="1">
-      <c r="B891" s="5"/>
-    </row>
-    <row r="892" ht="15.75" customHeight="1">
-      <c r="B892" s="5"/>
-    </row>
-    <row r="893" ht="15.75" customHeight="1">
-      <c r="B893" s="5"/>
-    </row>
-    <row r="894" ht="15.75" customHeight="1">
-      <c r="B894" s="5"/>
-    </row>
-    <row r="895" ht="15.75" customHeight="1">
-      <c r="B895" s="5"/>
-    </row>
-    <row r="896" ht="15.75" customHeight="1">
-      <c r="B896" s="5"/>
-    </row>
-    <row r="897" ht="15.75" customHeight="1">
-      <c r="B897" s="5"/>
-    </row>
-    <row r="898" ht="15.75" customHeight="1">
-      <c r="B898" s="5"/>
-    </row>
-    <row r="899" ht="15.75" customHeight="1">
-      <c r="B899" s="5"/>
-    </row>
-    <row r="900" ht="15.75" customHeight="1">
-      <c r="B900" s="5"/>
-    </row>
-    <row r="901" ht="15.75" customHeight="1">
-      <c r="B901" s="5"/>
-    </row>
-    <row r="902" ht="15.75" customHeight="1">
-      <c r="B902" s="5"/>
-    </row>
-    <row r="903" ht="15.75" customHeight="1">
-      <c r="B903" s="5"/>
-    </row>
-    <row r="904" ht="15.75" customHeight="1">
-      <c r="B904" s="5"/>
-    </row>
-    <row r="905" ht="15.75" customHeight="1">
-      <c r="B905" s="5"/>
-    </row>
-    <row r="906" ht="15.75" customHeight="1">
-      <c r="B906" s="5"/>
-    </row>
-    <row r="907" ht="15.75" customHeight="1">
-      <c r="B907" s="5"/>
-    </row>
-    <row r="908" ht="15.75" customHeight="1">
-      <c r="B908" s="5"/>
-    </row>
-    <row r="909" ht="15.75" customHeight="1">
-      <c r="B909" s="5"/>
-    </row>
-    <row r="910" ht="15.75" customHeight="1">
-      <c r="B910" s="5"/>
-    </row>
-    <row r="911" ht="15.75" customHeight="1">
-      <c r="B911" s="5"/>
-    </row>
-    <row r="912" ht="15.75" customHeight="1">
-      <c r="B912" s="5"/>
-    </row>
-    <row r="913" ht="15.75" customHeight="1">
-      <c r="B913" s="5"/>
-    </row>
-    <row r="914" ht="15.75" customHeight="1">
-      <c r="B914" s="5"/>
-    </row>
-    <row r="915" ht="15.75" customHeight="1">
-      <c r="B915" s="5"/>
-    </row>
-    <row r="916" ht="15.75" customHeight="1">
-      <c r="B916" s="5"/>
-    </row>
-    <row r="917" ht="15.75" customHeight="1">
-      <c r="B917" s="5"/>
-    </row>
-    <row r="918" ht="15.75" customHeight="1">
-      <c r="B918" s="5"/>
-    </row>
-    <row r="919" ht="15.75" customHeight="1">
-      <c r="B919" s="5"/>
-    </row>
-    <row r="920" ht="15.75" customHeight="1">
-      <c r="B920" s="5"/>
-    </row>
-    <row r="921" ht="15.75" customHeight="1">
-      <c r="B921" s="5"/>
-    </row>
-    <row r="922" ht="15.75" customHeight="1">
-      <c r="B922" s="5"/>
-    </row>
-    <row r="923" ht="15.75" customHeight="1">
-      <c r="B923" s="5"/>
-    </row>
-    <row r="924" ht="15.75" customHeight="1">
-      <c r="B924" s="5"/>
-    </row>
-    <row r="925" ht="15.75" customHeight="1">
-      <c r="B925" s="5"/>
-    </row>
-    <row r="926" ht="15.75" customHeight="1">
-      <c r="B926" s="5"/>
-    </row>
-    <row r="927" ht="15.75" customHeight="1">
-      <c r="B927" s="5"/>
-    </row>
-    <row r="928" ht="15.75" customHeight="1">
-      <c r="B928" s="5"/>
-    </row>
-    <row r="929" ht="15.75" customHeight="1">
-      <c r="B929" s="5"/>
-    </row>
-    <row r="930" ht="15.75" customHeight="1">
-      <c r="B930" s="5"/>
-    </row>
-    <row r="931" ht="15.75" customHeight="1">
-      <c r="B931" s="5"/>
-    </row>
-    <row r="932" ht="15.75" customHeight="1">
-      <c r="B932" s="5"/>
-    </row>
-    <row r="933" ht="15.75" customHeight="1">
-      <c r="B933" s="5"/>
-    </row>
-    <row r="934" ht="15.75" customHeight="1">
-      <c r="B934" s="5"/>
-    </row>
-    <row r="935" ht="15.75" customHeight="1">
-      <c r="B935" s="5"/>
-    </row>
-    <row r="936" ht="15.75" customHeight="1">
-      <c r="B936" s="5"/>
-    </row>
-    <row r="937" ht="15.75" customHeight="1">
-      <c r="B937" s="5"/>
-    </row>
-    <row r="938" ht="15.75" customHeight="1">
-      <c r="B938" s="5"/>
-    </row>
-    <row r="939" ht="15.75" customHeight="1">
-      <c r="B939" s="5"/>
-    </row>
-    <row r="940" ht="15.75" customHeight="1">
-      <c r="B940" s="5"/>
-    </row>
-    <row r="941" ht="15.75" customHeight="1">
-      <c r="B941" s="5"/>
-    </row>
-    <row r="942" ht="15.75" customHeight="1">
-      <c r="B942" s="5"/>
-    </row>
-    <row r="943" ht="15.75" customHeight="1">
-      <c r="B943" s="5"/>
-    </row>
-    <row r="944" ht="15.75" customHeight="1">
-      <c r="B944" s="5"/>
-    </row>
-    <row r="945" ht="15.75" customHeight="1">
-      <c r="B945" s="5"/>
-    </row>
-    <row r="946" ht="15.75" customHeight="1">
-      <c r="B946" s="5"/>
-    </row>
-    <row r="947" ht="15.75" customHeight="1">
-      <c r="B947" s="5"/>
-    </row>
-    <row r="948" ht="15.75" customHeight="1">
-      <c r="B948" s="5"/>
-    </row>
-    <row r="949" ht="15.75" customHeight="1">
-      <c r="B949" s="5"/>
-    </row>
-    <row r="950" ht="15.75" customHeight="1">
-      <c r="B950" s="5"/>
-    </row>
-    <row r="951" ht="15.75" customHeight="1">
-      <c r="B951" s="5"/>
-    </row>
-    <row r="952" ht="15.75" customHeight="1">
-      <c r="B952" s="5"/>
-    </row>
-    <row r="953" ht="15.75" customHeight="1">
-      <c r="B953" s="5"/>
-    </row>
-    <row r="954" ht="15.75" customHeight="1">
-      <c r="B954" s="5"/>
-    </row>
-    <row r="955" ht="15.75" customHeight="1">
-      <c r="B955" s="5"/>
-    </row>
-    <row r="956" ht="15.75" customHeight="1">
-      <c r="B956" s="5"/>
-    </row>
-    <row r="957" ht="15.75" customHeight="1">
-      <c r="B957" s="5"/>
-    </row>
-    <row r="958" ht="15.75" customHeight="1">
-      <c r="B958" s="5"/>
-    </row>
-    <row r="959" ht="15.75" customHeight="1">
-      <c r="B959" s="5"/>
-    </row>
-    <row r="960" ht="15.75" customHeight="1">
-      <c r="B960" s="5"/>
-    </row>
-    <row r="961" ht="15.75" customHeight="1">
-      <c r="B961" s="5"/>
-    </row>
-    <row r="962" ht="15.75" customHeight="1">
-      <c r="B962" s="5"/>
-    </row>
-    <row r="963" ht="15.75" customHeight="1">
-      <c r="B963" s="5"/>
-    </row>
-    <row r="964" ht="15.75" customHeight="1">
-      <c r="B964" s="5"/>
-    </row>
-    <row r="965" ht="15.75" customHeight="1">
-      <c r="B965" s="5"/>
-    </row>
-    <row r="966" ht="15.75" customHeight="1">
-      <c r="B966" s="5"/>
-    </row>
-    <row r="967" ht="15.75" customHeight="1">
-      <c r="B967" s="5"/>
-    </row>
-    <row r="968" ht="15.75" customHeight="1">
-      <c r="B968" s="5"/>
-    </row>
-    <row r="969" ht="15.75" customHeight="1">
-      <c r="B969" s="5"/>
-    </row>
-    <row r="970" ht="15.75" customHeight="1">
-      <c r="B970" s="5"/>
-    </row>
-    <row r="971" ht="15.75" customHeight="1">
-      <c r="B971" s="5"/>
-    </row>
-    <row r="972" ht="15.75" customHeight="1">
-      <c r="B972" s="5"/>
-    </row>
-    <row r="973" ht="15.75" customHeight="1">
-      <c r="B973" s="5"/>
-    </row>
-    <row r="974" ht="15.75" customHeight="1">
-      <c r="B974" s="5"/>
-    </row>
-    <row r="975" ht="15.75" customHeight="1">
-      <c r="B975" s="5"/>
-    </row>
-    <row r="976" ht="15.75" customHeight="1">
-      <c r="B976" s="5"/>
-    </row>
-    <row r="977" ht="15.75" customHeight="1">
-      <c r="B977" s="5"/>
-    </row>
-    <row r="978" ht="15.75" customHeight="1">
-      <c r="B978" s="5"/>
-    </row>
-    <row r="979" ht="15.75" customHeight="1">
-      <c r="B979" s="5"/>
-    </row>
-    <row r="980" ht="15.75" customHeight="1">
-      <c r="B980" s="5"/>
-    </row>
-    <row r="981" ht="15.75" customHeight="1">
-      <c r="B981" s="5"/>
-    </row>
-    <row r="982" ht="15.75" customHeight="1">
-      <c r="B982" s="5"/>
-    </row>
-    <row r="983" ht="15.75" customHeight="1">
-      <c r="B983" s="5"/>
-    </row>
-    <row r="984" ht="15.75" customHeight="1">
-      <c r="B984" s="5"/>
-    </row>
-    <row r="985" ht="15.75" customHeight="1">
-      <c r="B985" s="5"/>
-    </row>
-    <row r="986" ht="15.75" customHeight="1">
-      <c r="B986" s="5"/>
-    </row>
-    <row r="987" ht="15.75" customHeight="1">
-      <c r="B987" s="5"/>
-    </row>
-    <row r="988" ht="15.75" customHeight="1">
-      <c r="B988" s="5"/>
-    </row>
-    <row r="989" ht="15.75" customHeight="1">
-      <c r="B989" s="5"/>
-    </row>
-    <row r="990" ht="15.75" customHeight="1">
-      <c r="B990" s="5"/>
-    </row>
-    <row r="991" ht="15.75" customHeight="1">
-      <c r="B991" s="5"/>
-    </row>
-    <row r="992" ht="15.75" customHeight="1">
-      <c r="B992" s="5"/>
-    </row>
-    <row r="993" ht="15.75" customHeight="1">
-      <c r="B993" s="5"/>
-    </row>
-    <row r="994" ht="15.75" customHeight="1">
-      <c r="B994" s="5"/>
-    </row>
-    <row r="995" ht="15.75" customHeight="1">
-      <c r="B995" s="5"/>
-    </row>
-    <row r="996" ht="15.75" customHeight="1">
-      <c r="B996" s="5"/>
-    </row>
-    <row r="997" ht="15.75" customHeight="1">
-      <c r="B997" s="5"/>
-    </row>
-    <row r="998" ht="15.75" customHeight="1">
-      <c r="B998" s="5"/>
-    </row>
-    <row r="999" ht="15.75" customHeight="1">
-      <c r="B999" s="5"/>
-    </row>
-    <row r="1000" ht="15.75" customHeight="1">
-      <c r="B1000" s="5"/>
-    </row>
+      <c r="AA220" s="1"/>
+    </row>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/BlockInfo/BlockInfoTable.xlsx
+++ b/Templates/Tables/BlockInfo/BlockInfoTable.xlsx
@@ -328,7 +328,7 @@
     <col customWidth="1" min="1" max="27" width="14.38"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -377,7 +377,7 @@
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -426,7 +426,7 @@
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="2"/>
       <c r="C3" s="1"/>
@@ -455,7 +455,7 @@
       <c r="Z3" s="1"/>
       <c r="AA3" s="1"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
+    <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="2"/>
       <c r="C4" s="1"/>
@@ -484,7 +484,7 @@
       <c r="Z4" s="1"/>
       <c r="AA4" s="1"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
+    <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="2"/>
       <c r="C5" s="1"/>
@@ -513,7 +513,7 @@
       <c r="Z5" s="1"/>
       <c r="AA5" s="1"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
+    <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="1"/>
@@ -542,7 +542,7 @@
       <c r="Z6" s="1"/>
       <c r="AA6" s="1"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="2"/>
       <c r="C7" s="1"/>
@@ -571,7 +571,7 @@
       <c r="Z7" s="1"/>
       <c r="AA7" s="1"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="2"/>
       <c r="C8" s="1"/>
@@ -600,7 +600,7 @@
       <c r="Z8" s="1"/>
       <c r="AA8" s="1"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="2"/>
       <c r="C9" s="1"/>
@@ -629,7 +629,7 @@
       <c r="Z9" s="1"/>
       <c r="AA9" s="1"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="2"/>
       <c r="C10" s="1"/>
@@ -658,7 +658,7 @@
       <c r="Z10" s="1"/>
       <c r="AA10" s="1"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" ht="15.0" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="2"/>
       <c r="C11" s="1"/>
@@ -687,7 +687,7 @@
       <c r="Z11" s="1"/>
       <c r="AA11" s="1"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" ht="15.0" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="2"/>
       <c r="C12" s="1"/>
@@ -716,7 +716,7 @@
       <c r="Z12" s="1"/>
       <c r="AA12" s="1"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
+    <row r="13" ht="15.0" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="2"/>
       <c r="C13" s="1"/>
@@ -745,7 +745,7 @@
       <c r="Z13" s="1"/>
       <c r="AA13" s="1"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
+    <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="2"/>
       <c r="C14" s="1"/>
@@ -774,7 +774,7 @@
       <c r="Z14" s="1"/>
       <c r="AA14" s="1"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="2"/>
       <c r="C15" s="1"/>
@@ -803,7 +803,7 @@
       <c r="Z15" s="1"/>
       <c r="AA15" s="1"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="2"/>
       <c r="C16" s="1"/>
@@ -832,7 +832,7 @@
       <c r="Z16" s="1"/>
       <c r="AA16" s="1"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="2"/>
       <c r="C17" s="1"/>
@@ -861,7 +861,7 @@
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="2"/>
       <c r="C18" s="1"/>
@@ -890,7 +890,7 @@
       <c r="Z18" s="1"/>
       <c r="AA18" s="1"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="2"/>
       <c r="C19" s="1"/>
@@ -919,7 +919,7 @@
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="2"/>
       <c r="C20" s="1"/>
@@ -948,7 +948,7 @@
       <c r="Z20" s="1"/>
       <c r="AA20" s="1"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="2"/>
       <c r="C21" s="1"/>
@@ -977,7 +977,7 @@
       <c r="Z21" s="1"/>
       <c r="AA21" s="1"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="2"/>
       <c r="C22" s="1"/>
@@ -1006,7 +1006,7 @@
       <c r="Z22" s="1"/>
       <c r="AA22" s="1"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="2"/>
       <c r="C23" s="1"/>
@@ -1035,7 +1035,7 @@
       <c r="Z23" s="1"/>
       <c r="AA23" s="1"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="2"/>
       <c r="C24" s="1"/>
@@ -1064,7 +1064,7 @@
       <c r="Z24" s="1"/>
       <c r="AA24" s="1"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="2"/>
       <c r="C25" s="1"/>
@@ -1093,7 +1093,7 @@
       <c r="Z25" s="1"/>
       <c r="AA25" s="1"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="2"/>
       <c r="C26" s="1"/>
@@ -1122,7 +1122,7 @@
       <c r="Z26" s="1"/>
       <c r="AA26" s="1"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="2"/>
       <c r="C27" s="1"/>
@@ -1151,7 +1151,7 @@
       <c r="Z27" s="1"/>
       <c r="AA27" s="1"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="2"/>
       <c r="C28" s="1"/>
@@ -1180,7 +1180,7 @@
       <c r="Z28" s="1"/>
       <c r="AA28" s="1"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="2"/>
       <c r="C29" s="1"/>
@@ -1209,7 +1209,7 @@
       <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="2"/>
       <c r="C30" s="1"/>
@@ -1238,7 +1238,7 @@
       <c r="Z30" s="1"/>
       <c r="AA30" s="1"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="2"/>
       <c r="C31" s="1"/>
@@ -1267,7 +1267,7 @@
       <c r="Z31" s="1"/>
       <c r="AA31" s="1"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="2"/>
       <c r="C32" s="1"/>
@@ -1296,7 +1296,7 @@
       <c r="Z32" s="1"/>
       <c r="AA32" s="1"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="2"/>
       <c r="C33" s="1"/>
@@ -1325,7 +1325,7 @@
       <c r="Z33" s="1"/>
       <c r="AA33" s="1"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="2"/>
       <c r="C34" s="1"/>
@@ -1354,7 +1354,7 @@
       <c r="Z34" s="1"/>
       <c r="AA34" s="1"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="2"/>
       <c r="C35" s="1"/>
@@ -1383,7 +1383,7 @@
       <c r="Z35" s="1"/>
       <c r="AA35" s="1"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="2"/>
       <c r="C36" s="1"/>
@@ -1412,7 +1412,7 @@
       <c r="Z36" s="1"/>
       <c r="AA36" s="1"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="2"/>
       <c r="C37" s="1"/>
@@ -1441,7 +1441,7 @@
       <c r="Z37" s="1"/>
       <c r="AA37" s="1"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="2"/>
       <c r="C38" s="1"/>
@@ -1470,7 +1470,7 @@
       <c r="Z38" s="1"/>
       <c r="AA38" s="1"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="2"/>
       <c r="C39" s="1"/>
@@ -1499,7 +1499,7 @@
       <c r="Z39" s="1"/>
       <c r="AA39" s="1"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="2"/>
       <c r="C40" s="1"/>
@@ -1528,7 +1528,7 @@
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="2"/>
       <c r="C41" s="1"/>
@@ -1557,7 +1557,7 @@
       <c r="Z41" s="1"/>
       <c r="AA41" s="1"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="1"/>
       <c r="B42" s="2"/>
       <c r="C42" s="1"/>
@@ -1586,7 +1586,7 @@
       <c r="Z42" s="1"/>
       <c r="AA42" s="1"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="1"/>
       <c r="B43" s="2"/>
       <c r="C43" s="1"/>
@@ -1615,7 +1615,7 @@
       <c r="Z43" s="1"/>
       <c r="AA43" s="1"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="1"/>
       <c r="B44" s="2"/>
       <c r="C44" s="1"/>
@@ -1644,7 +1644,7 @@
       <c r="Z44" s="1"/>
       <c r="AA44" s="1"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="1"/>
       <c r="B45" s="2"/>
       <c r="C45" s="1"/>
@@ -1673,7 +1673,7 @@
       <c r="Z45" s="1"/>
       <c r="AA45" s="1"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="1"/>
       <c r="B46" s="2"/>
       <c r="C46" s="1"/>
@@ -1702,7 +1702,7 @@
       <c r="Z46" s="1"/>
       <c r="AA46" s="1"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="1"/>
       <c r="B47" s="2"/>
       <c r="C47" s="1"/>
@@ -1731,7 +1731,7 @@
       <c r="Z47" s="1"/>
       <c r="AA47" s="1"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="1"/>
       <c r="B48" s="2"/>
       <c r="C48" s="1"/>
@@ -1760,7 +1760,7 @@
       <c r="Z48" s="1"/>
       <c r="AA48" s="1"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="1"/>
       <c r="B49" s="2"/>
       <c r="C49" s="1"/>
@@ -1789,7 +1789,7 @@
       <c r="Z49" s="1"/>
       <c r="AA49" s="1"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="1"/>
       <c r="B50" s="2"/>
       <c r="C50" s="1"/>
@@ -1818,7 +1818,7 @@
       <c r="Z50" s="1"/>
       <c r="AA50" s="1"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="1"/>
       <c r="B51" s="2"/>
       <c r="C51" s="1"/>
@@ -1847,7 +1847,7 @@
       <c r="Z51" s="1"/>
       <c r="AA51" s="1"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="1"/>
       <c r="B52" s="2"/>
       <c r="C52" s="1"/>
@@ -1876,7 +1876,7 @@
       <c r="Z52" s="1"/>
       <c r="AA52" s="1"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="1"/>
       <c r="B53" s="2"/>
       <c r="C53" s="1"/>
@@ -1905,7 +1905,7 @@
       <c r="Z53" s="1"/>
       <c r="AA53" s="1"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="1"/>
       <c r="B54" s="2"/>
       <c r="C54" s="1"/>
@@ -1934,7 +1934,7 @@
       <c r="Z54" s="1"/>
       <c r="AA54" s="1"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="1"/>
       <c r="B55" s="2"/>
       <c r="C55" s="1"/>
@@ -1963,7 +1963,7 @@
       <c r="Z55" s="1"/>
       <c r="AA55" s="1"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="1"/>
       <c r="B56" s="2"/>
       <c r="C56" s="1"/>
@@ -1992,7 +1992,7 @@
       <c r="Z56" s="1"/>
       <c r="AA56" s="1"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="1"/>
       <c r="B57" s="2"/>
       <c r="C57" s="1"/>
@@ -2021,7 +2021,7 @@
       <c r="Z57" s="1"/>
       <c r="AA57" s="1"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="1"/>
       <c r="B58" s="2"/>
       <c r="C58" s="1"/>
@@ -2050,7 +2050,7 @@
       <c r="Z58" s="1"/>
       <c r="AA58" s="1"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="1"/>
       <c r="B59" s="2"/>
       <c r="C59" s="1"/>
@@ -2079,7 +2079,7 @@
       <c r="Z59" s="1"/>
       <c r="AA59" s="1"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="1"/>
       <c r="B60" s="2"/>
       <c r="C60" s="1"/>
@@ -2108,7 +2108,7 @@
       <c r="Z60" s="1"/>
       <c r="AA60" s="1"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="1"/>
       <c r="B61" s="2"/>
       <c r="C61" s="1"/>
@@ -2137,7 +2137,7 @@
       <c r="Z61" s="1"/>
       <c r="AA61" s="1"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="1"/>
       <c r="B62" s="2"/>
       <c r="C62" s="1"/>
@@ -2166,7 +2166,7 @@
       <c r="Z62" s="1"/>
       <c r="AA62" s="1"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="1"/>
       <c r="B63" s="2"/>
       <c r="C63" s="1"/>
@@ -2195,7 +2195,7 @@
       <c r="Z63" s="1"/>
       <c r="AA63" s="1"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="1"/>
       <c r="B64" s="2"/>
       <c r="C64" s="1"/>
@@ -2224,7 +2224,7 @@
       <c r="Z64" s="1"/>
       <c r="AA64" s="1"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="1"/>
       <c r="B65" s="2"/>
       <c r="C65" s="1"/>
@@ -2253,7 +2253,7 @@
       <c r="Z65" s="1"/>
       <c r="AA65" s="1"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="1"/>
       <c r="B66" s="2"/>
       <c r="C66" s="1"/>
@@ -2282,7 +2282,7 @@
       <c r="Z66" s="1"/>
       <c r="AA66" s="1"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="1"/>
       <c r="B67" s="2"/>
       <c r="C67" s="1"/>
@@ -2311,7 +2311,7 @@
       <c r="Z67" s="1"/>
       <c r="AA67" s="1"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="1"/>
       <c r="B68" s="2"/>
       <c r="C68" s="1"/>
@@ -2340,7 +2340,7 @@
       <c r="Z68" s="1"/>
       <c r="AA68" s="1"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="1"/>
       <c r="B69" s="2"/>
       <c r="C69" s="1"/>
@@ -2369,7 +2369,7 @@
       <c r="Z69" s="1"/>
       <c r="AA69" s="1"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="1"/>
       <c r="B70" s="2"/>
       <c r="C70" s="1"/>
@@ -2398,7 +2398,7 @@
       <c r="Z70" s="1"/>
       <c r="AA70" s="1"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="1"/>
       <c r="B71" s="2"/>
       <c r="C71" s="1"/>
@@ -2427,7 +2427,7 @@
       <c r="Z71" s="1"/>
       <c r="AA71" s="1"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="1"/>
       <c r="B72" s="2"/>
       <c r="C72" s="1"/>
@@ -2456,7 +2456,7 @@
       <c r="Z72" s="1"/>
       <c r="AA72" s="1"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="1"/>
       <c r="B73" s="2"/>
       <c r="C73" s="1"/>
@@ -2485,7 +2485,7 @@
       <c r="Z73" s="1"/>
       <c r="AA73" s="1"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="1"/>
       <c r="B74" s="2"/>
       <c r="C74" s="1"/>
@@ -2514,7 +2514,7 @@
       <c r="Z74" s="1"/>
       <c r="AA74" s="1"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="1"/>
       <c r="B75" s="2"/>
       <c r="C75" s="1"/>
@@ -2543,7 +2543,7 @@
       <c r="Z75" s="1"/>
       <c r="AA75" s="1"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="1"/>
       <c r="B76" s="2"/>
       <c r="C76" s="1"/>
@@ -2572,7 +2572,7 @@
       <c r="Z76" s="1"/>
       <c r="AA76" s="1"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="1"/>
       <c r="B77" s="2"/>
       <c r="C77" s="1"/>
@@ -2601,7 +2601,7 @@
       <c r="Z77" s="1"/>
       <c r="AA77" s="1"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="1"/>
       <c r="B78" s="2"/>
       <c r="C78" s="1"/>
@@ -2630,7 +2630,7 @@
       <c r="Z78" s="1"/>
       <c r="AA78" s="1"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="1"/>
       <c r="B79" s="2"/>
       <c r="C79" s="1"/>
@@ -2659,7 +2659,7 @@
       <c r="Z79" s="1"/>
       <c r="AA79" s="1"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="1"/>
       <c r="B80" s="2"/>
       <c r="C80" s="1"/>
@@ -2688,7 +2688,7 @@
       <c r="Z80" s="1"/>
       <c r="AA80" s="1"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="1"/>
       <c r="B81" s="2"/>
       <c r="C81" s="1"/>
@@ -2717,7 +2717,7 @@
       <c r="Z81" s="1"/>
       <c r="AA81" s="1"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="1"/>
       <c r="B82" s="2"/>
       <c r="C82" s="1"/>
@@ -2746,7 +2746,7 @@
       <c r="Z82" s="1"/>
       <c r="AA82" s="1"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="1"/>
       <c r="B83" s="2"/>
       <c r="C83" s="1"/>
@@ -2775,7 +2775,7 @@
       <c r="Z83" s="1"/>
       <c r="AA83" s="1"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="1"/>
       <c r="B84" s="2"/>
       <c r="C84" s="1"/>
@@ -2804,7 +2804,7 @@
       <c r="Z84" s="1"/>
       <c r="AA84" s="1"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="1"/>
       <c r="B85" s="2"/>
       <c r="C85" s="1"/>
@@ -2833,7 +2833,7 @@
       <c r="Z85" s="1"/>
       <c r="AA85" s="1"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="1"/>
       <c r="B86" s="2"/>
       <c r="C86" s="1"/>
@@ -2862,7 +2862,7 @@
       <c r="Z86" s="1"/>
       <c r="AA86" s="1"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="1"/>
       <c r="B87" s="2"/>
       <c r="C87" s="1"/>
@@ -2891,7 +2891,7 @@
       <c r="Z87" s="1"/>
       <c r="AA87" s="1"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="1"/>
       <c r="B88" s="2"/>
       <c r="C88" s="1"/>
@@ -2920,7 +2920,7 @@
       <c r="Z88" s="1"/>
       <c r="AA88" s="1"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="1"/>
       <c r="B89" s="2"/>
       <c r="C89" s="1"/>
@@ -2949,7 +2949,7 @@
       <c r="Z89" s="1"/>
       <c r="AA89" s="1"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="1"/>
       <c r="B90" s="2"/>
       <c r="C90" s="1"/>
@@ -2978,7 +2978,7 @@
       <c r="Z90" s="1"/>
       <c r="AA90" s="1"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="1"/>
       <c r="B91" s="2"/>
       <c r="C91" s="1"/>
@@ -3007,7 +3007,7 @@
       <c r="Z91" s="1"/>
       <c r="AA91" s="1"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="1"/>
       <c r="B92" s="2"/>
       <c r="C92" s="1"/>
@@ -3036,7 +3036,7 @@
       <c r="Z92" s="1"/>
       <c r="AA92" s="1"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="1"/>
       <c r="B93" s="2"/>
       <c r="C93" s="1"/>
@@ -3065,7 +3065,7 @@
       <c r="Z93" s="1"/>
       <c r="AA93" s="1"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="1"/>
       <c r="B94" s="2"/>
       <c r="C94" s="1"/>
@@ -3094,7 +3094,7 @@
       <c r="Z94" s="1"/>
       <c r="AA94" s="1"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="1"/>
       <c r="B95" s="2"/>
       <c r="C95" s="1"/>
@@ -3123,7 +3123,7 @@
       <c r="Z95" s="1"/>
       <c r="AA95" s="1"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="1"/>
       <c r="B96" s="2"/>
       <c r="C96" s="1"/>
@@ -3152,7 +3152,7 @@
       <c r="Z96" s="1"/>
       <c r="AA96" s="1"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="1"/>
       <c r="B97" s="2"/>
       <c r="C97" s="1"/>
@@ -3181,7 +3181,7 @@
       <c r="Z97" s="1"/>
       <c r="AA97" s="1"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="1"/>
       <c r="B98" s="2"/>
       <c r="C98" s="1"/>
@@ -3210,7 +3210,7 @@
       <c r="Z98" s="1"/>
       <c r="AA98" s="1"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="1"/>
       <c r="B99" s="2"/>
       <c r="C99" s="1"/>
@@ -3239,7 +3239,7 @@
       <c r="Z99" s="1"/>
       <c r="AA99" s="1"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="1"/>
       <c r="B100" s="2"/>
       <c r="C100" s="1"/>
@@ -3268,7 +3268,7 @@
       <c r="Z100" s="1"/>
       <c r="AA100" s="1"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="1"/>
       <c r="B101" s="2"/>
       <c r="C101" s="1"/>
@@ -3297,7 +3297,7 @@
       <c r="Z101" s="1"/>
       <c r="AA101" s="1"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="1"/>
       <c r="B102" s="2"/>
       <c r="C102" s="1"/>
@@ -3326,7 +3326,7 @@
       <c r="Z102" s="1"/>
       <c r="AA102" s="1"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="1"/>
       <c r="B103" s="2"/>
       <c r="C103" s="1"/>
@@ -3355,7 +3355,7 @@
       <c r="Z103" s="1"/>
       <c r="AA103" s="1"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="1"/>
       <c r="B104" s="2"/>
       <c r="C104" s="1"/>
@@ -3384,7 +3384,7 @@
       <c r="Z104" s="1"/>
       <c r="AA104" s="1"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="1"/>
       <c r="B105" s="2"/>
       <c r="C105" s="1"/>
@@ -3413,7 +3413,7 @@
       <c r="Z105" s="1"/>
       <c r="AA105" s="1"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="1"/>
       <c r="B106" s="2"/>
       <c r="C106" s="1"/>
@@ -3442,7 +3442,7 @@
       <c r="Z106" s="1"/>
       <c r="AA106" s="1"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="1"/>
       <c r="B107" s="2"/>
       <c r="C107" s="1"/>
@@ -3471,7 +3471,7 @@
       <c r="Z107" s="1"/>
       <c r="AA107" s="1"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="1"/>
       <c r="B108" s="2"/>
       <c r="C108" s="1"/>
@@ -3500,7 +3500,7 @@
       <c r="Z108" s="1"/>
       <c r="AA108" s="1"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="1"/>
       <c r="B109" s="2"/>
       <c r="C109" s="1"/>
@@ -3529,7 +3529,7 @@
       <c r="Z109" s="1"/>
       <c r="AA109" s="1"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="1"/>
       <c r="B110" s="2"/>
       <c r="C110" s="1"/>
@@ -3558,7 +3558,7 @@
       <c r="Z110" s="1"/>
       <c r="AA110" s="1"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="1"/>
       <c r="B111" s="2"/>
       <c r="C111" s="1"/>
@@ -3587,7 +3587,7 @@
       <c r="Z111" s="1"/>
       <c r="AA111" s="1"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="1"/>
       <c r="B112" s="2"/>
       <c r="C112" s="1"/>
@@ -3616,7 +3616,7 @@
       <c r="Z112" s="1"/>
       <c r="AA112" s="1"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="1"/>
       <c r="B113" s="2"/>
       <c r="C113" s="1"/>
@@ -3645,7 +3645,7 @@
       <c r="Z113" s="1"/>
       <c r="AA113" s="1"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="1"/>
       <c r="B114" s="2"/>
       <c r="C114" s="1"/>
@@ -3674,7 +3674,7 @@
       <c r="Z114" s="1"/>
       <c r="AA114" s="1"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="1"/>
       <c r="B115" s="2"/>
       <c r="C115" s="1"/>
@@ -3703,7 +3703,7 @@
       <c r="Z115" s="1"/>
       <c r="AA115" s="1"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="1"/>
       <c r="B116" s="2"/>
       <c r="C116" s="1"/>
@@ -3732,7 +3732,7 @@
       <c r="Z116" s="1"/>
       <c r="AA116" s="1"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="1"/>
       <c r="B117" s="2"/>
       <c r="C117" s="1"/>
@@ -3761,7 +3761,7 @@
       <c r="Z117" s="1"/>
       <c r="AA117" s="1"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="1"/>
       <c r="B118" s="2"/>
       <c r="C118" s="1"/>
@@ -3790,7 +3790,7 @@
       <c r="Z118" s="1"/>
       <c r="AA118" s="1"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="1"/>
       <c r="B119" s="2"/>
       <c r="C119" s="1"/>
@@ -3819,7 +3819,7 @@
       <c r="Z119" s="1"/>
       <c r="AA119" s="1"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="1"/>
       <c r="B120" s="2"/>
       <c r="C120" s="1"/>
@@ -3848,7 +3848,7 @@
       <c r="Z120" s="1"/>
       <c r="AA120" s="1"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="1"/>
       <c r="B121" s="2"/>
       <c r="C121" s="1"/>
@@ -3877,7 +3877,7 @@
       <c r="Z121" s="1"/>
       <c r="AA121" s="1"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="1"/>
       <c r="B122" s="2"/>
       <c r="C122" s="1"/>
@@ -3906,7 +3906,7 @@
       <c r="Z122" s="1"/>
       <c r="AA122" s="1"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="1"/>
       <c r="B123" s="2"/>
       <c r="C123" s="1"/>
@@ -3935,7 +3935,7 @@
       <c r="Z123" s="1"/>
       <c r="AA123" s="1"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="1"/>
       <c r="B124" s="2"/>
       <c r="C124" s="1"/>
@@ -3964,7 +3964,7 @@
       <c r="Z124" s="1"/>
       <c r="AA124" s="1"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="1"/>
       <c r="B125" s="2"/>
       <c r="C125" s="1"/>
@@ -3993,7 +3993,7 @@
       <c r="Z125" s="1"/>
       <c r="AA125" s="1"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="1"/>
       <c r="B126" s="2"/>
       <c r="C126" s="1"/>
@@ -4022,7 +4022,7 @@
       <c r="Z126" s="1"/>
       <c r="AA126" s="1"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
+    <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="1"/>
       <c r="B127" s="2"/>
       <c r="C127" s="1"/>
@@ -4051,7 +4051,7 @@
       <c r="Z127" s="1"/>
       <c r="AA127" s="1"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1">
+    <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="1"/>
       <c r="B128" s="2"/>
       <c r="C128" s="1"/>
@@ -4080,7 +4080,7 @@
       <c r="Z128" s="1"/>
       <c r="AA128" s="1"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1">
+    <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="1"/>
       <c r="B129" s="2"/>
       <c r="C129" s="1"/>
@@ -4109,7 +4109,7 @@
       <c r="Z129" s="1"/>
       <c r="AA129" s="1"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1">
+    <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="1"/>
       <c r="B130" s="2"/>
       <c r="C130" s="1"/>
@@ -4138,7 +4138,7 @@
       <c r="Z130" s="1"/>
       <c r="AA130" s="1"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1">
+    <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="1"/>
       <c r="B131" s="2"/>
       <c r="C131" s="1"/>
@@ -4167,7 +4167,7 @@
       <c r="Z131" s="1"/>
       <c r="AA131" s="1"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1">
+    <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="1"/>
       <c r="B132" s="2"/>
       <c r="C132" s="1"/>
@@ -4196,7 +4196,7 @@
       <c r="Z132" s="1"/>
       <c r="AA132" s="1"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1">
+    <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="1"/>
       <c r="B133" s="2"/>
       <c r="C133" s="1"/>
@@ -4225,7 +4225,7 @@
       <c r="Z133" s="1"/>
       <c r="AA133" s="1"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1">
+    <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="1"/>
       <c r="B134" s="2"/>
       <c r="C134" s="1"/>
@@ -4254,7 +4254,7 @@
       <c r="Z134" s="1"/>
       <c r="AA134" s="1"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1">
+    <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="1"/>
       <c r="B135" s="2"/>
       <c r="C135" s="1"/>
@@ -4283,7 +4283,7 @@
       <c r="Z135" s="1"/>
       <c r="AA135" s="1"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1">
+    <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="1"/>
       <c r="B136" s="2"/>
       <c r="C136" s="1"/>
@@ -4312,7 +4312,7 @@
       <c r="Z136" s="1"/>
       <c r="AA136" s="1"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
+    <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="1"/>
       <c r="B137" s="2"/>
       <c r="C137" s="1"/>
@@ -4341,7 +4341,7 @@
       <c r="Z137" s="1"/>
       <c r="AA137" s="1"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1">
+    <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="1"/>
       <c r="B138" s="2"/>
       <c r="C138" s="1"/>
@@ -4370,7 +4370,7 @@
       <c r="Z138" s="1"/>
       <c r="AA138" s="1"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1">
+    <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="1"/>
       <c r="B139" s="2"/>
       <c r="C139" s="1"/>
@@ -4399,7 +4399,7 @@
       <c r="Z139" s="1"/>
       <c r="AA139" s="1"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
+    <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="1"/>
       <c r="B140" s="2"/>
       <c r="C140" s="1"/>
@@ -4428,7 +4428,7 @@
       <c r="Z140" s="1"/>
       <c r="AA140" s="1"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1">
+    <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="1"/>
       <c r="B141" s="2"/>
       <c r="C141" s="1"/>
@@ -4457,7 +4457,7 @@
       <c r="Z141" s="1"/>
       <c r="AA141" s="1"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
+    <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="1"/>
       <c r="B142" s="2"/>
       <c r="C142" s="1"/>
@@ -4486,7 +4486,7 @@
       <c r="Z142" s="1"/>
       <c r="AA142" s="1"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1">
+    <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="1"/>
       <c r="B143" s="2"/>
       <c r="C143" s="1"/>
@@ -4515,7 +4515,7 @@
       <c r="Z143" s="1"/>
       <c r="AA143" s="1"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1">
+    <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="1"/>
       <c r="B144" s="2"/>
       <c r="C144" s="1"/>
@@ -4544,7 +4544,7 @@
       <c r="Z144" s="1"/>
       <c r="AA144" s="1"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1">
+    <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="1"/>
       <c r="B145" s="2"/>
       <c r="C145" s="1"/>
@@ -4573,7 +4573,7 @@
       <c r="Z145" s="1"/>
       <c r="AA145" s="1"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1">
+    <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="1"/>
       <c r="B146" s="2"/>
       <c r="C146" s="1"/>
@@ -4602,7 +4602,7 @@
       <c r="Z146" s="1"/>
       <c r="AA146" s="1"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1">
+    <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="1"/>
       <c r="B147" s="2"/>
       <c r="C147" s="1"/>
@@ -4631,7 +4631,7 @@
       <c r="Z147" s="1"/>
       <c r="AA147" s="1"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1">
+    <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="1"/>
       <c r="B148" s="2"/>
       <c r="C148" s="1"/>
@@ -4660,7 +4660,7 @@
       <c r="Z148" s="1"/>
       <c r="AA148" s="1"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1">
+    <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="1"/>
       <c r="B149" s="2"/>
       <c r="C149" s="1"/>
@@ -4689,7 +4689,7 @@
       <c r="Z149" s="1"/>
       <c r="AA149" s="1"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
+    <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="1"/>
       <c r="B150" s="2"/>
       <c r="C150" s="1"/>
@@ -4718,7 +4718,7 @@
       <c r="Z150" s="1"/>
       <c r="AA150" s="1"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1">
+    <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="1"/>
       <c r="B151" s="2"/>
       <c r="C151" s="1"/>
@@ -4747,7 +4747,7 @@
       <c r="Z151" s="1"/>
       <c r="AA151" s="1"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1">
+    <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="1"/>
       <c r="B152" s="2"/>
       <c r="C152" s="1"/>
@@ -4776,7 +4776,7 @@
       <c r="Z152" s="1"/>
       <c r="AA152" s="1"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
+    <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="1"/>
       <c r="B153" s="2"/>
       <c r="C153" s="1"/>
@@ -4805,7 +4805,7 @@
       <c r="Z153" s="1"/>
       <c r="AA153" s="1"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1">
+    <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="1"/>
       <c r="B154" s="2"/>
       <c r="C154" s="1"/>
@@ -4834,7 +4834,7 @@
       <c r="Z154" s="1"/>
       <c r="AA154" s="1"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1">
+    <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="1"/>
       <c r="B155" s="2"/>
       <c r="C155" s="1"/>
@@ -4863,7 +4863,7 @@
       <c r="Z155" s="1"/>
       <c r="AA155" s="1"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1">
+    <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="1"/>
       <c r="B156" s="2"/>
       <c r="C156" s="1"/>
@@ -4892,7 +4892,7 @@
       <c r="Z156" s="1"/>
       <c r="AA156" s="1"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1">
+    <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="1"/>
       <c r="B157" s="2"/>
       <c r="C157" s="1"/>
@@ -4921,7 +4921,7 @@
       <c r="Z157" s="1"/>
       <c r="AA157" s="1"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1">
+    <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="1"/>
       <c r="B158" s="2"/>
       <c r="C158" s="1"/>
@@ -4950,7 +4950,7 @@
       <c r="Z158" s="1"/>
       <c r="AA158" s="1"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1">
+    <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="1"/>
       <c r="B159" s="2"/>
       <c r="C159" s="1"/>
@@ -4979,7 +4979,7 @@
       <c r="Z159" s="1"/>
       <c r="AA159" s="1"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1">
+    <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="1"/>
       <c r="B160" s="2"/>
       <c r="C160" s="1"/>
@@ -5008,7 +5008,7 @@
       <c r="Z160" s="1"/>
       <c r="AA160" s="1"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1">
+    <row r="161" ht="15.0" customHeight="1">
       <c r="A161" s="1"/>
       <c r="B161" s="2"/>
       <c r="C161" s="1"/>
@@ -5037,7 +5037,7 @@
       <c r="Z161" s="1"/>
       <c r="AA161" s="1"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1">
+    <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="1"/>
       <c r="B162" s="2"/>
       <c r="C162" s="1"/>
@@ -5066,7 +5066,7 @@
       <c r="Z162" s="1"/>
       <c r="AA162" s="1"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1">
+    <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="1"/>
       <c r="B163" s="2"/>
       <c r="C163" s="1"/>
@@ -5095,7 +5095,7 @@
       <c r="Z163" s="1"/>
       <c r="AA163" s="1"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1">
+    <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="1"/>
       <c r="B164" s="2"/>
       <c r="C164" s="1"/>
@@ -5124,7 +5124,7 @@
       <c r="Z164" s="1"/>
       <c r="AA164" s="1"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1">
+    <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="1"/>
       <c r="B165" s="2"/>
       <c r="C165" s="1"/>
@@ -5153,7 +5153,7 @@
       <c r="Z165" s="1"/>
       <c r="AA165" s="1"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1">
+    <row r="166" ht="15.0" customHeight="1">
       <c r="A166" s="1"/>
       <c r="B166" s="2"/>
       <c r="C166" s="1"/>
@@ -5182,7 +5182,7 @@
       <c r="Z166" s="1"/>
       <c r="AA166" s="1"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
+    <row r="167" ht="15.0" customHeight="1">
       <c r="A167" s="1"/>
       <c r="B167" s="2"/>
       <c r="C167" s="1"/>
@@ -5211,7 +5211,7 @@
       <c r="Z167" s="1"/>
       <c r="AA167" s="1"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
+    <row r="168" ht="15.0" customHeight="1">
       <c r="A168" s="1"/>
       <c r="B168" s="2"/>
       <c r="C168" s="1"/>
@@ -5240,7 +5240,7 @@
       <c r="Z168" s="1"/>
       <c r="AA168" s="1"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
+    <row r="169" ht="15.0" customHeight="1">
       <c r="A169" s="1"/>
       <c r="B169" s="2"/>
       <c r="C169" s="1"/>
@@ -5269,7 +5269,7 @@
       <c r="Z169" s="1"/>
       <c r="AA169" s="1"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
+    <row r="170" ht="15.0" customHeight="1">
       <c r="A170" s="1"/>
       <c r="B170" s="2"/>
       <c r="C170" s="1"/>
@@ -5298,7 +5298,7 @@
       <c r="Z170" s="1"/>
       <c r="AA170" s="1"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
+    <row r="171" ht="15.0" customHeight="1">
       <c r="A171" s="1"/>
       <c r="B171" s="2"/>
       <c r="C171" s="1"/>
@@ -5327,7 +5327,7 @@
       <c r="Z171" s="1"/>
       <c r="AA171" s="1"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
+    <row r="172" ht="15.0" customHeight="1">
       <c r="A172" s="1"/>
       <c r="B172" s="2"/>
       <c r="C172" s="1"/>
@@ -5356,7 +5356,7 @@
       <c r="Z172" s="1"/>
       <c r="AA172" s="1"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
+    <row r="173" ht="15.0" customHeight="1">
       <c r="A173" s="1"/>
       <c r="B173" s="2"/>
       <c r="C173" s="1"/>
@@ -5385,7 +5385,7 @@
       <c r="Z173" s="1"/>
       <c r="AA173" s="1"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
+    <row r="174" ht="15.0" customHeight="1">
       <c r="A174" s="1"/>
       <c r="B174" s="2"/>
       <c r="C174" s="1"/>
@@ -5414,7 +5414,7 @@
       <c r="Z174" s="1"/>
       <c r="AA174" s="1"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
+    <row r="175" ht="15.0" customHeight="1">
       <c r="A175" s="1"/>
       <c r="B175" s="2"/>
       <c r="C175" s="1"/>
@@ -5443,7 +5443,7 @@
       <c r="Z175" s="1"/>
       <c r="AA175" s="1"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
+    <row r="176" ht="15.0" customHeight="1">
       <c r="A176" s="1"/>
       <c r="B176" s="2"/>
       <c r="C176" s="1"/>
@@ -5472,7 +5472,7 @@
       <c r="Z176" s="1"/>
       <c r="AA176" s="1"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
+    <row r="177" ht="15.0" customHeight="1">
       <c r="A177" s="1"/>
       <c r="B177" s="2"/>
       <c r="C177" s="1"/>
@@ -5501,7 +5501,7 @@
       <c r="Z177" s="1"/>
       <c r="AA177" s="1"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
+    <row r="178" ht="15.0" customHeight="1">
       <c r="A178" s="1"/>
       <c r="B178" s="2"/>
       <c r="C178" s="1"/>
@@ -5530,7 +5530,7 @@
       <c r="Z178" s="1"/>
       <c r="AA178" s="1"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1">
+    <row r="179" ht="15.0" customHeight="1">
       <c r="A179" s="1"/>
       <c r="B179" s="2"/>
       <c r="C179" s="1"/>
@@ -5559,7 +5559,7 @@
       <c r="Z179" s="1"/>
       <c r="AA179" s="1"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1">
+    <row r="180" ht="15.0" customHeight="1">
       <c r="A180" s="1"/>
       <c r="B180" s="2"/>
       <c r="C180" s="1"/>
@@ -5588,7 +5588,7 @@
       <c r="Z180" s="1"/>
       <c r="AA180" s="1"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1">
+    <row r="181" ht="15.0" customHeight="1">
       <c r="A181" s="1"/>
       <c r="B181" s="2"/>
       <c r="C181" s="1"/>
@@ -5617,7 +5617,7 @@
       <c r="Z181" s="1"/>
       <c r="AA181" s="1"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
+    <row r="182" ht="15.0" customHeight="1">
       <c r="A182" s="1"/>
       <c r="B182" s="2"/>
       <c r="C182" s="1"/>
@@ -5646,7 +5646,7 @@
       <c r="Z182" s="1"/>
       <c r="AA182" s="1"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1">
+    <row r="183" ht="15.0" customHeight="1">
       <c r="A183" s="1"/>
       <c r="B183" s="2"/>
       <c r="C183" s="1"/>
@@ -5675,7 +5675,7 @@
       <c r="Z183" s="1"/>
       <c r="AA183" s="1"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1">
+    <row r="184" ht="15.0" customHeight="1">
       <c r="A184" s="1"/>
       <c r="B184" s="2"/>
       <c r="C184" s="1"/>
@@ -5704,7 +5704,7 @@
       <c r="Z184" s="1"/>
       <c r="AA184" s="1"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1">
+    <row r="185" ht="15.0" customHeight="1">
       <c r="A185" s="1"/>
       <c r="B185" s="2"/>
       <c r="C185" s="1"/>
@@ -5733,7 +5733,7 @@
       <c r="Z185" s="1"/>
       <c r="AA185" s="1"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1">
+    <row r="186" ht="15.0" customHeight="1">
       <c r="A186" s="1"/>
       <c r="B186" s="2"/>
       <c r="C186" s="1"/>
@@ -5762,7 +5762,7 @@
       <c r="Z186" s="1"/>
       <c r="AA186" s="1"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1">
+    <row r="187" ht="15.0" customHeight="1">
       <c r="A187" s="1"/>
       <c r="B187" s="2"/>
       <c r="C187" s="1"/>
@@ -5791,7 +5791,7 @@
       <c r="Z187" s="1"/>
       <c r="AA187" s="1"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1">
+    <row r="188" ht="15.0" customHeight="1">
       <c r="A188" s="1"/>
       <c r="B188" s="2"/>
       <c r="C188" s="1"/>
@@ -5820,7 +5820,7 @@
       <c r="Z188" s="1"/>
       <c r="AA188" s="1"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1">
+    <row r="189" ht="15.0" customHeight="1">
       <c r="A189" s="1"/>
       <c r="B189" s="2"/>
       <c r="C189" s="1"/>
@@ -5849,7 +5849,7 @@
       <c r="Z189" s="1"/>
       <c r="AA189" s="1"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1">
+    <row r="190" ht="15.0" customHeight="1">
       <c r="A190" s="1"/>
       <c r="B190" s="2"/>
       <c r="C190" s="1"/>
@@ -5878,7 +5878,7 @@
       <c r="Z190" s="1"/>
       <c r="AA190" s="1"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1">
+    <row r="191" ht="15.0" customHeight="1">
       <c r="A191" s="1"/>
       <c r="B191" s="2"/>
       <c r="C191" s="1"/>
@@ -5907,7 +5907,7 @@
       <c r="Z191" s="1"/>
       <c r="AA191" s="1"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1">
+    <row r="192" ht="15.0" customHeight="1">
       <c r="A192" s="1"/>
       <c r="B192" s="2"/>
       <c r="C192" s="1"/>
@@ -5936,7 +5936,7 @@
       <c r="Z192" s="1"/>
       <c r="AA192" s="1"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1">
+    <row r="193" ht="15.0" customHeight="1">
       <c r="A193" s="1"/>
       <c r="B193" s="2"/>
       <c r="C193" s="1"/>
@@ -5965,7 +5965,7 @@
       <c r="Z193" s="1"/>
       <c r="AA193" s="1"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1">
+    <row r="194" ht="15.0" customHeight="1">
       <c r="A194" s="1"/>
       <c r="B194" s="2"/>
       <c r="C194" s="1"/>
@@ -5994,7 +5994,7 @@
       <c r="Z194" s="1"/>
       <c r="AA194" s="1"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1">
+    <row r="195" ht="15.0" customHeight="1">
       <c r="A195" s="1"/>
       <c r="B195" s="2"/>
       <c r="C195" s="1"/>
@@ -6023,7 +6023,7 @@
       <c r="Z195" s="1"/>
       <c r="AA195" s="1"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1">
+    <row r="196" ht="15.0" customHeight="1">
       <c r="A196" s="1"/>
       <c r="B196" s="2"/>
       <c r="C196" s="1"/>
@@ -6052,7 +6052,7 @@
       <c r="Z196" s="1"/>
       <c r="AA196" s="1"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1">
+    <row r="197" ht="15.0" customHeight="1">
       <c r="A197" s="1"/>
       <c r="B197" s="2"/>
       <c r="C197" s="1"/>
@@ -6081,7 +6081,7 @@
       <c r="Z197" s="1"/>
       <c r="AA197" s="1"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1">
+    <row r="198" ht="15.0" customHeight="1">
       <c r="A198" s="1"/>
       <c r="B198" s="2"/>
       <c r="C198" s="1"/>
@@ -6110,7 +6110,7 @@
       <c r="Z198" s="1"/>
       <c r="AA198" s="1"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1">
+    <row r="199" ht="15.0" customHeight="1">
       <c r="A199" s="1"/>
       <c r="B199" s="2"/>
       <c r="C199" s="1"/>
@@ -6139,7 +6139,7 @@
       <c r="Z199" s="1"/>
       <c r="AA199" s="1"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1">
+    <row r="200" ht="15.0" customHeight="1">
       <c r="A200" s="1"/>
       <c r="B200" s="2"/>
       <c r="C200" s="1"/>
@@ -6168,7 +6168,7 @@
       <c r="Z200" s="1"/>
       <c r="AA200" s="1"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1">
+    <row r="201" ht="15.0" customHeight="1">
       <c r="A201" s="1"/>
       <c r="B201" s="2"/>
       <c r="C201" s="1"/>
@@ -6197,7 +6197,7 @@
       <c r="Z201" s="1"/>
       <c r="AA201" s="1"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1">
+    <row r="202" ht="15.0" customHeight="1">
       <c r="A202" s="1"/>
       <c r="B202" s="2"/>
       <c r="C202" s="1"/>
@@ -6226,7 +6226,7 @@
       <c r="Z202" s="1"/>
       <c r="AA202" s="1"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1">
+    <row r="203" ht="15.0" customHeight="1">
       <c r="A203" s="1"/>
       <c r="B203" s="2"/>
       <c r="C203" s="1"/>
@@ -6255,7 +6255,7 @@
       <c r="Z203" s="1"/>
       <c r="AA203" s="1"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1">
+    <row r="204" ht="15.0" customHeight="1">
       <c r="A204" s="1"/>
       <c r="B204" s="2"/>
       <c r="C204" s="1"/>
@@ -6284,7 +6284,7 @@
       <c r="Z204" s="1"/>
       <c r="AA204" s="1"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1">
+    <row r="205" ht="15.0" customHeight="1">
       <c r="A205" s="1"/>
       <c r="B205" s="2"/>
       <c r="C205" s="1"/>
@@ -6313,7 +6313,7 @@
       <c r="Z205" s="1"/>
       <c r="AA205" s="1"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1">
+    <row r="206" ht="15.0" customHeight="1">
       <c r="A206" s="1"/>
       <c r="B206" s="2"/>
       <c r="C206" s="1"/>
@@ -6342,7 +6342,7 @@
       <c r="Z206" s="1"/>
       <c r="AA206" s="1"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1">
+    <row r="207" ht="15.0" customHeight="1">
       <c r="A207" s="1"/>
       <c r="B207" s="2"/>
       <c r="C207" s="1"/>
@@ -6371,7 +6371,7 @@
       <c r="Z207" s="1"/>
       <c r="AA207" s="1"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1">
+    <row r="208" ht="15.0" customHeight="1">
       <c r="A208" s="1"/>
       <c r="B208" s="2"/>
       <c r="C208" s="1"/>
@@ -6400,7 +6400,7 @@
       <c r="Z208" s="1"/>
       <c r="AA208" s="1"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1">
+    <row r="209" ht="15.0" customHeight="1">
       <c r="A209" s="1"/>
       <c r="B209" s="2"/>
       <c r="C209" s="1"/>
@@ -6429,7 +6429,7 @@
       <c r="Z209" s="1"/>
       <c r="AA209" s="1"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1">
+    <row r="210" ht="15.0" customHeight="1">
       <c r="A210" s="1"/>
       <c r="B210" s="2"/>
       <c r="C210" s="1"/>
@@ -6458,7 +6458,7 @@
       <c r="Z210" s="1"/>
       <c r="AA210" s="1"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1">
+    <row r="211" ht="15.0" customHeight="1">
       <c r="A211" s="1"/>
       <c r="B211" s="2"/>
       <c r="C211" s="1"/>
@@ -6487,7 +6487,7 @@
       <c r="Z211" s="1"/>
       <c r="AA211" s="1"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1">
+    <row r="212" ht="15.0" customHeight="1">
       <c r="A212" s="1"/>
       <c r="B212" s="2"/>
       <c r="C212" s="1"/>
@@ -6516,7 +6516,7 @@
       <c r="Z212" s="1"/>
       <c r="AA212" s="1"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1">
+    <row r="213" ht="15.0" customHeight="1">
       <c r="A213" s="1"/>
       <c r="B213" s="2"/>
       <c r="C213" s="1"/>
@@ -6545,7 +6545,7 @@
       <c r="Z213" s="1"/>
       <c r="AA213" s="1"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1">
+    <row r="214" ht="15.0" customHeight="1">
       <c r="A214" s="1"/>
       <c r="B214" s="2"/>
       <c r="C214" s="1"/>
@@ -6574,7 +6574,7 @@
       <c r="Z214" s="1"/>
       <c r="AA214" s="1"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1">
+    <row r="215" ht="15.0" customHeight="1">
       <c r="A215" s="1"/>
       <c r="B215" s="2"/>
       <c r="C215" s="1"/>
@@ -6603,7 +6603,7 @@
       <c r="Z215" s="1"/>
       <c r="AA215" s="1"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1">
+    <row r="216" ht="15.0" customHeight="1">
       <c r="A216" s="1"/>
       <c r="B216" s="2"/>
       <c r="C216" s="1"/>
@@ -6632,7 +6632,7 @@
       <c r="Z216" s="1"/>
       <c r="AA216" s="1"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1">
+    <row r="217" ht="15.0" customHeight="1">
       <c r="A217" s="1"/>
       <c r="B217" s="2"/>
       <c r="C217" s="1"/>
@@ -6661,7 +6661,7 @@
       <c r="Z217" s="1"/>
       <c r="AA217" s="1"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1">
+    <row r="218" ht="15.0" customHeight="1">
       <c r="A218" s="1"/>
       <c r="B218" s="2"/>
       <c r="C218" s="1"/>
@@ -6690,7 +6690,7 @@
       <c r="Z218" s="1"/>
       <c r="AA218" s="1"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1">
+    <row r="219" ht="15.0" customHeight="1">
       <c r="A219" s="1"/>
       <c r="B219" s="2"/>
       <c r="C219" s="1"/>
@@ -6719,7 +6719,7 @@
       <c r="Z219" s="1"/>
       <c r="AA219" s="1"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1">
+    <row r="220" ht="15.0" customHeight="1">
       <c r="A220" s="1"/>
       <c r="B220" s="2"/>
       <c r="C220" s="1"/>
@@ -6748,786 +6748,786 @@
       <c r="Z220" s="1"/>
       <c r="AA220" s="1"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.0" customHeight="1"/>
+    <row r="222" ht="15.0" customHeight="1"/>
+    <row r="223" ht="15.0" customHeight="1"/>
+    <row r="224" ht="15.0" customHeight="1"/>
+    <row r="225" ht="15.0" customHeight="1"/>
+    <row r="226" ht="15.0" customHeight="1"/>
+    <row r="227" ht="15.0" customHeight="1"/>
+    <row r="228" ht="15.0" customHeight="1"/>
+    <row r="229" ht="15.0" customHeight="1"/>
+    <row r="230" ht="15.0" customHeight="1"/>
+    <row r="231" ht="15.0" customHeight="1"/>
+    <row r="232" ht="15.0" customHeight="1"/>
+    <row r="233" ht="15.0" customHeight="1"/>
+    <row r="234" ht="15.0" customHeight="1"/>
+    <row r="235" ht="15.0" customHeight="1"/>
+    <row r="236" ht="15.0" customHeight="1"/>
+    <row r="237" ht="15.0" customHeight="1"/>
+    <row r="238" ht="15.0" customHeight="1"/>
+    <row r="239" ht="15.0" customHeight="1"/>
+    <row r="240" ht="15.0" customHeight="1"/>
+    <row r="241" ht="15.0" customHeight="1"/>
+    <row r="242" ht="15.0" customHeight="1"/>
+    <row r="243" ht="15.0" customHeight="1"/>
+    <row r="244" ht="15.0" customHeight="1"/>
+    <row r="245" ht="15.0" customHeight="1"/>
+    <row r="246" ht="15.0" customHeight="1"/>
+    <row r="247" ht="15.0" customHeight="1"/>
+    <row r="248" ht="15.0" customHeight="1"/>
+    <row r="249" ht="15.0" customHeight="1"/>
+    <row r="250" ht="15.0" customHeight="1"/>
+    <row r="251" ht="15.0" customHeight="1"/>
+    <row r="252" ht="15.0" customHeight="1"/>
+    <row r="253" ht="15.0" customHeight="1"/>
+    <row r="254" ht="15.0" customHeight="1"/>
+    <row r="255" ht="15.0" customHeight="1"/>
+    <row r="256" ht="15.0" customHeight="1"/>
+    <row r="257" ht="15.0" customHeight="1"/>
+    <row r="258" ht="15.0" customHeight="1"/>
+    <row r="259" ht="15.0" customHeight="1"/>
+    <row r="260" ht="15.0" customHeight="1"/>
+    <row r="261" ht="15.0" customHeight="1"/>
+    <row r="262" ht="15.0" customHeight="1"/>
+    <row r="263" ht="15.0" customHeight="1"/>
+    <row r="264" ht="15.0" customHeight="1"/>
+    <row r="265" ht="15.0" customHeight="1"/>
+    <row r="266" ht="15.0" customHeight="1"/>
+    <row r="267" ht="15.0" customHeight="1"/>
+    <row r="268" ht="15.0" customHeight="1"/>
+    <row r="269" ht="15.0" customHeight="1"/>
+    <row r="270" ht="15.0" customHeight="1"/>
+    <row r="271" ht="15.0" customHeight="1"/>
+    <row r="272" ht="15.0" customHeight="1"/>
+    <row r="273" ht="15.0" customHeight="1"/>
+    <row r="274" ht="15.0" customHeight="1"/>
+    <row r="275" ht="15.0" customHeight="1"/>
+    <row r="276" ht="15.0" customHeight="1"/>
+    <row r="277" ht="15.0" customHeight="1"/>
+    <row r="278" ht="15.0" customHeight="1"/>
+    <row r="279" ht="15.0" customHeight="1"/>
+    <row r="280" ht="15.0" customHeight="1"/>
+    <row r="281" ht="15.0" customHeight="1"/>
+    <row r="282" ht="15.0" customHeight="1"/>
+    <row r="283" ht="15.0" customHeight="1"/>
+    <row r="284" ht="15.0" customHeight="1"/>
+    <row r="285" ht="15.0" customHeight="1"/>
+    <row r="286" ht="15.0" customHeight="1"/>
+    <row r="287" ht="15.0" customHeight="1"/>
+    <row r="288" ht="15.0" customHeight="1"/>
+    <row r="289" ht="15.0" customHeight="1"/>
+    <row r="290" ht="15.0" customHeight="1"/>
+    <row r="291" ht="15.0" customHeight="1"/>
+    <row r="292" ht="15.0" customHeight="1"/>
+    <row r="293" ht="15.0" customHeight="1"/>
+    <row r="294" ht="15.0" customHeight="1"/>
+    <row r="295" ht="15.0" customHeight="1"/>
+    <row r="296" ht="15.0" customHeight="1"/>
+    <row r="297" ht="15.0" customHeight="1"/>
+    <row r="298" ht="15.0" customHeight="1"/>
+    <row r="299" ht="15.0" customHeight="1"/>
+    <row r="300" ht="15.0" customHeight="1"/>
+    <row r="301" ht="15.0" customHeight="1"/>
+    <row r="302" ht="15.0" customHeight="1"/>
+    <row r="303" ht="15.0" customHeight="1"/>
+    <row r="304" ht="15.0" customHeight="1"/>
+    <row r="305" ht="15.0" customHeight="1"/>
+    <row r="306" ht="15.0" customHeight="1"/>
+    <row r="307" ht="15.0" customHeight="1"/>
+    <row r="308" ht="15.0" customHeight="1"/>
+    <row r="309" ht="15.0" customHeight="1"/>
+    <row r="310" ht="15.0" customHeight="1"/>
+    <row r="311" ht="15.0" customHeight="1"/>
+    <row r="312" ht="15.0" customHeight="1"/>
+    <row r="313" ht="15.0" customHeight="1"/>
+    <row r="314" ht="15.0" customHeight="1"/>
+    <row r="315" ht="15.0" customHeight="1"/>
+    <row r="316" ht="15.0" customHeight="1"/>
+    <row r="317" ht="15.0" customHeight="1"/>
+    <row r="318" ht="15.0" customHeight="1"/>
+    <row r="319" ht="15.0" customHeight="1"/>
+    <row r="320" ht="15.0" customHeight="1"/>
+    <row r="321" ht="15.0" customHeight="1"/>
+    <row r="322" ht="15.0" customHeight="1"/>
+    <row r="323" ht="15.0" customHeight="1"/>
+    <row r="324" ht="15.0" customHeight="1"/>
+    <row r="325" ht="15.0" customHeight="1"/>
+    <row r="326" ht="15.0" customHeight="1"/>
+    <row r="327" ht="15.0" customHeight="1"/>
+    <row r="328" ht="15.0" customHeight="1"/>
+    <row r="329" ht="15.0" customHeight="1"/>
+    <row r="330" ht="15.0" customHeight="1"/>
+    <row r="331" ht="15.0" customHeight="1"/>
+    <row r="332" ht="15.0" customHeight="1"/>
+    <row r="333" ht="15.0" customHeight="1"/>
+    <row r="334" ht="15.0" customHeight="1"/>
+    <row r="335" ht="15.0" customHeight="1"/>
+    <row r="336" ht="15.0" customHeight="1"/>
+    <row r="337" ht="15.0" customHeight="1"/>
+    <row r="338" ht="15.0" customHeight="1"/>
+    <row r="339" ht="15.0" customHeight="1"/>
+    <row r="340" ht="15.0" customHeight="1"/>
+    <row r="341" ht="15.0" customHeight="1"/>
+    <row r="342" ht="15.0" customHeight="1"/>
+    <row r="343" ht="15.0" customHeight="1"/>
+    <row r="344" ht="15.0" customHeight="1"/>
+    <row r="345" ht="15.0" customHeight="1"/>
+    <row r="346" ht="15.0" customHeight="1"/>
+    <row r="347" ht="15.0" customHeight="1"/>
+    <row r="348" ht="15.0" customHeight="1"/>
+    <row r="349" ht="15.0" customHeight="1"/>
+    <row r="350" ht="15.0" customHeight="1"/>
+    <row r="351" ht="15.0" customHeight="1"/>
+    <row r="352" ht="15.0" customHeight="1"/>
+    <row r="353" ht="15.0" customHeight="1"/>
+    <row r="354" ht="15.0" customHeight="1"/>
+    <row r="355" ht="15.0" customHeight="1"/>
+    <row r="356" ht="15.0" customHeight="1"/>
+    <row r="357" ht="15.0" customHeight="1"/>
+    <row r="358" ht="15.0" customHeight="1"/>
+    <row r="359" ht="15.0" customHeight="1"/>
+    <row r="360" ht="15.0" customHeight="1"/>
+    <row r="361" ht="15.0" customHeight="1"/>
+    <row r="362" ht="15.0" customHeight="1"/>
+    <row r="363" ht="15.0" customHeight="1"/>
+    <row r="364" ht="15.0" customHeight="1"/>
+    <row r="365" ht="15.0" customHeight="1"/>
+    <row r="366" ht="15.0" customHeight="1"/>
+    <row r="367" ht="15.0" customHeight="1"/>
+    <row r="368" ht="15.0" customHeight="1"/>
+    <row r="369" ht="15.0" customHeight="1"/>
+    <row r="370" ht="15.0" customHeight="1"/>
+    <row r="371" ht="15.0" customHeight="1"/>
+    <row r="372" ht="15.0" customHeight="1"/>
+    <row r="373" ht="15.0" customHeight="1"/>
+    <row r="374" ht="15.0" customHeight="1"/>
+    <row r="375" ht="15.0" customHeight="1"/>
+    <row r="376" ht="15.0" customHeight="1"/>
+    <row r="377" ht="15.0" customHeight="1"/>
+    <row r="378" ht="15.0" customHeight="1"/>
+    <row r="379" ht="15.0" customHeight="1"/>
+    <row r="380" ht="15.0" customHeight="1"/>
+    <row r="381" ht="15.0" customHeight="1"/>
+    <row r="382" ht="15.0" customHeight="1"/>
+    <row r="383" ht="15.0" customHeight="1"/>
+    <row r="384" ht="15.0" customHeight="1"/>
+    <row r="385" ht="15.0" customHeight="1"/>
+    <row r="386" ht="15.0" customHeight="1"/>
+    <row r="387" ht="15.0" customHeight="1"/>
+    <row r="388" ht="15.0" customHeight="1"/>
+    <row r="389" ht="15.0" customHeight="1"/>
+    <row r="390" ht="15.0" customHeight="1"/>
+    <row r="391" ht="15.0" customHeight="1"/>
+    <row r="392" ht="15.0" customHeight="1"/>
+    <row r="393" ht="15.0" customHeight="1"/>
+    <row r="394" ht="15.0" customHeight="1"/>
+    <row r="395" ht="15.0" customHeight="1"/>
+    <row r="396" ht="15.0" customHeight="1"/>
+    <row r="397" ht="15.0" customHeight="1"/>
+    <row r="398" ht="15.0" customHeight="1"/>
+    <row r="399" ht="15.0" customHeight="1"/>
+    <row r="400" ht="15.0" customHeight="1"/>
+    <row r="401" ht="15.0" customHeight="1"/>
+    <row r="402" ht="15.0" customHeight="1"/>
+    <row r="403" ht="15.0" customHeight="1"/>
+    <row r="404" ht="15.0" customHeight="1"/>
+    <row r="405" ht="15.0" customHeight="1"/>
+    <row r="406" ht="15.0" customHeight="1"/>
+    <row r="407" ht="15.0" customHeight="1"/>
+    <row r="408" ht="15.0" customHeight="1"/>
+    <row r="409" ht="15.0" customHeight="1"/>
+    <row r="410" ht="15.0" customHeight="1"/>
+    <row r="411" ht="15.0" customHeight="1"/>
+    <row r="412" ht="15.0" customHeight="1"/>
+    <row r="413" ht="15.0" customHeight="1"/>
+    <row r="414" ht="15.0" customHeight="1"/>
+    <row r="415" ht="15.0" customHeight="1"/>
+    <row r="416" ht="15.0" customHeight="1"/>
+    <row r="417" ht="15.0" customHeight="1"/>
+    <row r="418" ht="15.0" customHeight="1"/>
+    <row r="419" ht="15.0" customHeight="1"/>
+    <row r="420" ht="15.0" customHeight="1"/>
+    <row r="421" ht="15.0" customHeight="1"/>
+    <row r="422" ht="15.0" customHeight="1"/>
+    <row r="423" ht="15.0" customHeight="1"/>
+    <row r="424" ht="15.0" customHeight="1"/>
+    <row r="425" ht="15.0" customHeight="1"/>
+    <row r="426" ht="15.0" customHeight="1"/>
+    <row r="427" ht="15.0" customHeight="1"/>
+    <row r="428" ht="15.0" customHeight="1"/>
+    <row r="429" ht="15.0" customHeight="1"/>
+    <row r="430" ht="15.0" customHeight="1"/>
+    <row r="431" ht="15.0" customHeight="1"/>
+    <row r="432" ht="15.0" customHeight="1"/>
+    <row r="433" ht="15.0" customHeight="1"/>
+    <row r="434" ht="15.0" customHeight="1"/>
+    <row r="435" ht="15.0" customHeight="1"/>
+    <row r="436" ht="15.0" customHeight="1"/>
+    <row r="437" ht="15.0" customHeight="1"/>
+    <row r="438" ht="15.0" customHeight="1"/>
+    <row r="439" ht="15.0" customHeight="1"/>
+    <row r="440" ht="15.0" customHeight="1"/>
+    <row r="441" ht="15.0" customHeight="1"/>
+    <row r="442" ht="15.0" customHeight="1"/>
+    <row r="443" ht="15.0" customHeight="1"/>
+    <row r="444" ht="15.0" customHeight="1"/>
+    <row r="445" ht="15.0" customHeight="1"/>
+    <row r="446" ht="15.0" customHeight="1"/>
+    <row r="447" ht="15.0" customHeight="1"/>
+    <row r="448" ht="15.0" customHeight="1"/>
+    <row r="449" ht="15.0" customHeight="1"/>
+    <row r="450" ht="15.0" customHeight="1"/>
+    <row r="451" ht="15.0" customHeight="1"/>
+    <row r="452" ht="15.0" customHeight="1"/>
+    <row r="453" ht="15.0" customHeight="1"/>
+    <row r="454" ht="15.0" customHeight="1"/>
+    <row r="455" ht="15.0" customHeight="1"/>
+    <row r="456" ht="15.0" customHeight="1"/>
+    <row r="457" ht="15.0" customHeight="1"/>
+    <row r="458" ht="15.0" customHeight="1"/>
+    <row r="459" ht="15.0" customHeight="1"/>
+    <row r="460" ht="15.0" customHeight="1"/>
+    <row r="461" ht="15.0" customHeight="1"/>
+    <row r="462" ht="15.0" customHeight="1"/>
+    <row r="463" ht="15.0" customHeight="1"/>
+    <row r="464" ht="15.0" customHeight="1"/>
+    <row r="465" ht="15.0" customHeight="1"/>
+    <row r="466" ht="15.0" customHeight="1"/>
+    <row r="467" ht="15.0" customHeight="1"/>
+    <row r="468" ht="15.0" customHeight="1"/>
+    <row r="469" ht="15.0" customHeight="1"/>
+    <row r="470" ht="15.0" customHeight="1"/>
+    <row r="471" ht="15.0" customHeight="1"/>
+    <row r="472" ht="15.0" customHeight="1"/>
+    <row r="473" ht="15.0" customHeight="1"/>
+    <row r="474" ht="15.0" customHeight="1"/>
+    <row r="475" ht="15.0" customHeight="1"/>
+    <row r="476" ht="15.0" customHeight="1"/>
+    <row r="477" ht="15.0" customHeight="1"/>
+    <row r="478" ht="15.0" customHeight="1"/>
+    <row r="479" ht="15.0" customHeight="1"/>
+    <row r="480" ht="15.0" customHeight="1"/>
+    <row r="481" ht="15.0" customHeight="1"/>
+    <row r="482" ht="15.0" customHeight="1"/>
+    <row r="483" ht="15.0" customHeight="1"/>
+    <row r="484" ht="15.0" customHeight="1"/>
+    <row r="485" ht="15.0" customHeight="1"/>
+    <row r="486" ht="15.0" customHeight="1"/>
+    <row r="487" ht="15.0" customHeight="1"/>
+    <row r="488" ht="15.0" customHeight="1"/>
+    <row r="489" ht="15.0" customHeight="1"/>
+    <row r="490" ht="15.0" customHeight="1"/>
+    <row r="491" ht="15.0" customHeight="1"/>
+    <row r="492" ht="15.0" customHeight="1"/>
+    <row r="493" ht="15.0" customHeight="1"/>
+    <row r="494" ht="15.0" customHeight="1"/>
+    <row r="495" ht="15.0" customHeight="1"/>
+    <row r="496" ht="15.0" customHeight="1"/>
+    <row r="497" ht="15.0" customHeight="1"/>
+    <row r="498" ht="15.0" customHeight="1"/>
+    <row r="499" ht="15.0" customHeight="1"/>
+    <row r="500" ht="15.0" customHeight="1"/>
+    <row r="501" ht="15.0" customHeight="1"/>
+    <row r="502" ht="15.0" customHeight="1"/>
+    <row r="503" ht="15.0" customHeight="1"/>
+    <row r="504" ht="15.0" customHeight="1"/>
+    <row r="505" ht="15.0" customHeight="1"/>
+    <row r="506" ht="15.0" customHeight="1"/>
+    <row r="507" ht="15.0" customHeight="1"/>
+    <row r="508" ht="15.0" customHeight="1"/>
+    <row r="509" ht="15.0" customHeight="1"/>
+    <row r="510" ht="15.0" customHeight="1"/>
+    <row r="511" ht="15.0" customHeight="1"/>
+    <row r="512" ht="15.0" customHeight="1"/>
+    <row r="513" ht="15.0" customHeight="1"/>
+    <row r="514" ht="15.0" customHeight="1"/>
+    <row r="515" ht="15.0" customHeight="1"/>
+    <row r="516" ht="15.0" customHeight="1"/>
+    <row r="517" ht="15.0" customHeight="1"/>
+    <row r="518" ht="15.0" customHeight="1"/>
+    <row r="519" ht="15.0" customHeight="1"/>
+    <row r="520" ht="15.0" customHeight="1"/>
+    <row r="521" ht="15.0" customHeight="1"/>
+    <row r="522" ht="15.0" customHeight="1"/>
+    <row r="523" ht="15.0" customHeight="1"/>
+    <row r="524" ht="15.0" customHeight="1"/>
+    <row r="525" ht="15.0" customHeight="1"/>
+    <row r="526" ht="15.0" customHeight="1"/>
+    <row r="527" ht="15.0" customHeight="1"/>
+    <row r="528" ht="15.0" customHeight="1"/>
+    <row r="529" ht="15.0" customHeight="1"/>
+    <row r="530" ht="15.0" customHeight="1"/>
+    <row r="531" ht="15.0" customHeight="1"/>
+    <row r="532" ht="15.0" customHeight="1"/>
+    <row r="533" ht="15.0" customHeight="1"/>
+    <row r="534" ht="15.0" customHeight="1"/>
+    <row r="535" ht="15.0" customHeight="1"/>
+    <row r="536" ht="15.0" customHeight="1"/>
+    <row r="537" ht="15.0" customHeight="1"/>
+    <row r="538" ht="15.0" customHeight="1"/>
+    <row r="539" ht="15.0" customHeight="1"/>
+    <row r="540" ht="15.0" customHeight="1"/>
+    <row r="541" ht="15.0" customHeight="1"/>
+    <row r="542" ht="15.0" customHeight="1"/>
+    <row r="543" ht="15.0" customHeight="1"/>
+    <row r="544" ht="15.0" customHeight="1"/>
+    <row r="545" ht="15.0" customHeight="1"/>
+    <row r="546" ht="15.0" customHeight="1"/>
+    <row r="547" ht="15.0" customHeight="1"/>
+    <row r="548" ht="15.0" customHeight="1"/>
+    <row r="549" ht="15.0" customHeight="1"/>
+    <row r="550" ht="15.0" customHeight="1"/>
+    <row r="551" ht="15.0" customHeight="1"/>
+    <row r="552" ht="15.0" customHeight="1"/>
+    <row r="553" ht="15.0" customHeight="1"/>
+    <row r="554" ht="15.0" customHeight="1"/>
+    <row r="555" ht="15.0" customHeight="1"/>
+    <row r="556" ht="15.0" customHeight="1"/>
+    <row r="557" ht="15.0" customHeight="1"/>
+    <row r="558" ht="15.0" customHeight="1"/>
+    <row r="559" ht="15.0" customHeight="1"/>
+    <row r="560" ht="15.0" customHeight="1"/>
+    <row r="561" ht="15.0" customHeight="1"/>
+    <row r="562" ht="15.0" customHeight="1"/>
+    <row r="563" ht="15.0" customHeight="1"/>
+    <row r="564" ht="15.0" customHeight="1"/>
+    <row r="565" ht="15.0" customHeight="1"/>
+    <row r="566" ht="15.0" customHeight="1"/>
+    <row r="567" ht="15.0" customHeight="1"/>
+    <row r="568" ht="15.0" customHeight="1"/>
+    <row r="569" ht="15.0" customHeight="1"/>
+    <row r="570" ht="15.0" customHeight="1"/>
+    <row r="571" ht="15.0" customHeight="1"/>
+    <row r="572" ht="15.0" customHeight="1"/>
+    <row r="573" ht="15.0" customHeight="1"/>
+    <row r="574" ht="15.0" customHeight="1"/>
+    <row r="575" ht="15.0" customHeight="1"/>
+    <row r="576" ht="15.0" customHeight="1"/>
+    <row r="577" ht="15.0" customHeight="1"/>
+    <row r="578" ht="15.0" customHeight="1"/>
+    <row r="579" ht="15.0" customHeight="1"/>
+    <row r="580" ht="15.0" customHeight="1"/>
+    <row r="581" ht="15.0" customHeight="1"/>
+    <row r="582" ht="15.0" customHeight="1"/>
+    <row r="583" ht="15.0" customHeight="1"/>
+    <row r="584" ht="15.0" customHeight="1"/>
+    <row r="585" ht="15.0" customHeight="1"/>
+    <row r="586" ht="15.0" customHeight="1"/>
+    <row r="587" ht="15.0" customHeight="1"/>
+    <row r="588" ht="15.0" customHeight="1"/>
+    <row r="589" ht="15.0" customHeight="1"/>
+    <row r="590" ht="15.0" customHeight="1"/>
+    <row r="591" ht="15.0" customHeight="1"/>
+    <row r="592" ht="15.0" customHeight="1"/>
+    <row r="593" ht="15.0" customHeight="1"/>
+    <row r="594" ht="15.0" customHeight="1"/>
+    <row r="595" ht="15.0" customHeight="1"/>
+    <row r="596" ht="15.0" customHeight="1"/>
+    <row r="597" ht="15.0" customHeight="1"/>
+    <row r="598" ht="15.0" customHeight="1"/>
+    <row r="599" ht="15.0" customHeight="1"/>
+    <row r="600" ht="15.0" customHeight="1"/>
+    <row r="601" ht="15.0" customHeight="1"/>
+    <row r="602" ht="15.0" customHeight="1"/>
+    <row r="603" ht="15.0" customHeight="1"/>
+    <row r="604" ht="15.0" customHeight="1"/>
+    <row r="605" ht="15.0" customHeight="1"/>
+    <row r="606" ht="15.0" customHeight="1"/>
+    <row r="607" ht="15.0" customHeight="1"/>
+    <row r="608" ht="15.0" customHeight="1"/>
+    <row r="609" ht="15.0" customHeight="1"/>
+    <row r="610" ht="15.0" customHeight="1"/>
+    <row r="611" ht="15.0" customHeight="1"/>
+    <row r="612" ht="15.0" customHeight="1"/>
+    <row r="613" ht="15.0" customHeight="1"/>
+    <row r="614" ht="15.0" customHeight="1"/>
+    <row r="615" ht="15.0" customHeight="1"/>
+    <row r="616" ht="15.0" customHeight="1"/>
+    <row r="617" ht="15.0" customHeight="1"/>
+    <row r="618" ht="15.0" customHeight="1"/>
+    <row r="619" ht="15.0" customHeight="1"/>
+    <row r="620" ht="15.0" customHeight="1"/>
+    <row r="621" ht="15.0" customHeight="1"/>
+    <row r="622" ht="15.0" customHeight="1"/>
+    <row r="623" ht="15.0" customHeight="1"/>
+    <row r="624" ht="15.0" customHeight="1"/>
+    <row r="625" ht="15.0" customHeight="1"/>
+    <row r="626" ht="15.0" customHeight="1"/>
+    <row r="627" ht="15.0" customHeight="1"/>
+    <row r="628" ht="15.0" customHeight="1"/>
+    <row r="629" ht="15.0" customHeight="1"/>
+    <row r="630" ht="15.0" customHeight="1"/>
+    <row r="631" ht="15.0" customHeight="1"/>
+    <row r="632" ht="15.0" customHeight="1"/>
+    <row r="633" ht="15.0" customHeight="1"/>
+    <row r="634" ht="15.0" customHeight="1"/>
+    <row r="635" ht="15.0" customHeight="1"/>
+    <row r="636" ht="15.0" customHeight="1"/>
+    <row r="637" ht="15.0" customHeight="1"/>
+    <row r="638" ht="15.0" customHeight="1"/>
+    <row r="639" ht="15.0" customHeight="1"/>
+    <row r="640" ht="15.0" customHeight="1"/>
+    <row r="641" ht="15.0" customHeight="1"/>
+    <row r="642" ht="15.0" customHeight="1"/>
+    <row r="643" ht="15.0" customHeight="1"/>
+    <row r="644" ht="15.0" customHeight="1"/>
+    <row r="645" ht="15.0" customHeight="1"/>
+    <row r="646" ht="15.0" customHeight="1"/>
+    <row r="647" ht="15.0" customHeight="1"/>
+    <row r="648" ht="15.0" customHeight="1"/>
+    <row r="649" ht="15.0" customHeight="1"/>
+    <row r="650" ht="15.0" customHeight="1"/>
+    <row r="651" ht="15.0" customHeight="1"/>
+    <row r="652" ht="15.0" customHeight="1"/>
+    <row r="653" ht="15.0" customHeight="1"/>
+    <row r="654" ht="15.0" customHeight="1"/>
+    <row r="655" ht="15.0" customHeight="1"/>
+    <row r="656" ht="15.0" customHeight="1"/>
+    <row r="657" ht="15.0" customHeight="1"/>
+    <row r="658" ht="15.0" customHeight="1"/>
+    <row r="659" ht="15.0" customHeight="1"/>
+    <row r="660" ht="15.0" customHeight="1"/>
+    <row r="661" ht="15.0" customHeight="1"/>
+    <row r="662" ht="15.0" customHeight="1"/>
+    <row r="663" ht="15.0" customHeight="1"/>
+    <row r="664" ht="15.0" customHeight="1"/>
+    <row r="665" ht="15.0" customHeight="1"/>
+    <row r="666" ht="15.0" customHeight="1"/>
+    <row r="667" ht="15.0" customHeight="1"/>
+    <row r="668" ht="15.0" customHeight="1"/>
+    <row r="669" ht="15.0" customHeight="1"/>
+    <row r="670" ht="15.0" customHeight="1"/>
+    <row r="671" ht="15.0" customHeight="1"/>
+    <row r="672" ht="15.0" customHeight="1"/>
+    <row r="673" ht="15.0" customHeight="1"/>
+    <row r="674" ht="15.0" customHeight="1"/>
+    <row r="675" ht="15.0" customHeight="1"/>
+    <row r="676" ht="15.0" customHeight="1"/>
+    <row r="677" ht="15.0" customHeight="1"/>
+    <row r="678" ht="15.0" customHeight="1"/>
+    <row r="679" ht="15.0" customHeight="1"/>
+    <row r="680" ht="15.0" customHeight="1"/>
+    <row r="681" ht="15.0" customHeight="1"/>
+    <row r="682" ht="15.0" customHeight="1"/>
+    <row r="683" ht="15.0" customHeight="1"/>
+    <row r="684" ht="15.0" customHeight="1"/>
+    <row r="685" ht="15.0" customHeight="1"/>
+    <row r="686" ht="15.0" customHeight="1"/>
+    <row r="687" ht="15.0" customHeight="1"/>
+    <row r="688" ht="15.0" customHeight="1"/>
+    <row r="689" ht="15.0" customHeight="1"/>
+    <row r="690" ht="15.0" customHeight="1"/>
+    <row r="691" ht="15.0" customHeight="1"/>
+    <row r="692" ht="15.0" customHeight="1"/>
+    <row r="693" ht="15.0" customHeight="1"/>
+    <row r="694" ht="15.0" customHeight="1"/>
+    <row r="695" ht="15.0" customHeight="1"/>
+    <row r="696" ht="15.0" customHeight="1"/>
+    <row r="697" ht="15.0" customHeight="1"/>
+    <row r="698" ht="15.0" customHeight="1"/>
+    <row r="699" ht="15.0" customHeight="1"/>
+    <row r="700" ht="15.0" customHeight="1"/>
+    <row r="701" ht="15.0" customHeight="1"/>
+    <row r="702" ht="15.0" customHeight="1"/>
+    <row r="703" ht="15.0" customHeight="1"/>
+    <row r="704" ht="15.0" customHeight="1"/>
+    <row r="705" ht="15.0" customHeight="1"/>
+    <row r="706" ht="15.0" customHeight="1"/>
+    <row r="707" ht="15.0" customHeight="1"/>
+    <row r="708" ht="15.0" customHeight="1"/>
+    <row r="709" ht="15.0" customHeight="1"/>
+    <row r="710" ht="15.0" customHeight="1"/>
+    <row r="711" ht="15.0" customHeight="1"/>
+    <row r="712" ht="15.0" customHeight="1"/>
+    <row r="713" ht="15.0" customHeight="1"/>
+    <row r="714" ht="15.0" customHeight="1"/>
+    <row r="715" ht="15.0" customHeight="1"/>
+    <row r="716" ht="15.0" customHeight="1"/>
+    <row r="717" ht="15.0" customHeight="1"/>
+    <row r="718" ht="15.0" customHeight="1"/>
+    <row r="719" ht="15.0" customHeight="1"/>
+    <row r="720" ht="15.0" customHeight="1"/>
+    <row r="721" ht="15.0" customHeight="1"/>
+    <row r="722" ht="15.0" customHeight="1"/>
+    <row r="723" ht="15.0" customHeight="1"/>
+    <row r="724" ht="15.0" customHeight="1"/>
+    <row r="725" ht="15.0" customHeight="1"/>
+    <row r="726" ht="15.0" customHeight="1"/>
+    <row r="727" ht="15.0" customHeight="1"/>
+    <row r="728" ht="15.0" customHeight="1"/>
+    <row r="729" ht="15.0" customHeight="1"/>
+    <row r="730" ht="15.0" customHeight="1"/>
+    <row r="731" ht="15.0" customHeight="1"/>
+    <row r="732" ht="15.0" customHeight="1"/>
+    <row r="733" ht="15.0" customHeight="1"/>
+    <row r="734" ht="15.0" customHeight="1"/>
+    <row r="735" ht="15.0" customHeight="1"/>
+    <row r="736" ht="15.0" customHeight="1"/>
+    <row r="737" ht="15.0" customHeight="1"/>
+    <row r="738" ht="15.0" customHeight="1"/>
+    <row r="739" ht="15.0" customHeight="1"/>
+    <row r="740" ht="15.0" customHeight="1"/>
+    <row r="741" ht="15.0" customHeight="1"/>
+    <row r="742" ht="15.0" customHeight="1"/>
+    <row r="743" ht="15.0" customHeight="1"/>
+    <row r="744" ht="15.0" customHeight="1"/>
+    <row r="745" ht="15.0" customHeight="1"/>
+    <row r="746" ht="15.0" customHeight="1"/>
+    <row r="747" ht="15.0" customHeight="1"/>
+    <row r="748" ht="15.0" customHeight="1"/>
+    <row r="749" ht="15.0" customHeight="1"/>
+    <row r="750" ht="15.0" customHeight="1"/>
+    <row r="751" ht="15.0" customHeight="1"/>
+    <row r="752" ht="15.0" customHeight="1"/>
+    <row r="753" ht="15.0" customHeight="1"/>
+    <row r="754" ht="15.0" customHeight="1"/>
+    <row r="755" ht="15.0" customHeight="1"/>
+    <row r="756" ht="15.0" customHeight="1"/>
+    <row r="757" ht="15.0" customHeight="1"/>
+    <row r="758" ht="15.0" customHeight="1"/>
+    <row r="759" ht="15.0" customHeight="1"/>
+    <row r="760" ht="15.0" customHeight="1"/>
+    <row r="761" ht="15.0" customHeight="1"/>
+    <row r="762" ht="15.0" customHeight="1"/>
+    <row r="763" ht="15.0" customHeight="1"/>
+    <row r="764" ht="15.0" customHeight="1"/>
+    <row r="765" ht="15.0" customHeight="1"/>
+    <row r="766" ht="15.0" customHeight="1"/>
+    <row r="767" ht="15.0" customHeight="1"/>
+    <row r="768" ht="15.0" customHeight="1"/>
+    <row r="769" ht="15.0" customHeight="1"/>
+    <row r="770" ht="15.0" customHeight="1"/>
+    <row r="771" ht="15.0" customHeight="1"/>
+    <row r="772" ht="15.0" customHeight="1"/>
+    <row r="773" ht="15.0" customHeight="1"/>
+    <row r="774" ht="15.0" customHeight="1"/>
+    <row r="775" ht="15.0" customHeight="1"/>
+    <row r="776" ht="15.0" customHeight="1"/>
+    <row r="777" ht="15.0" customHeight="1"/>
+    <row r="778" ht="15.0" customHeight="1"/>
+    <row r="779" ht="15.0" customHeight="1"/>
+    <row r="780" ht="15.0" customHeight="1"/>
+    <row r="781" ht="15.0" customHeight="1"/>
+    <row r="782" ht="15.0" customHeight="1"/>
+    <row r="783" ht="15.0" customHeight="1"/>
+    <row r="784" ht="15.0" customHeight="1"/>
+    <row r="785" ht="15.0" customHeight="1"/>
+    <row r="786" ht="15.0" customHeight="1"/>
+    <row r="787" ht="15.0" customHeight="1"/>
+    <row r="788" ht="15.0" customHeight="1"/>
+    <row r="789" ht="15.0" customHeight="1"/>
+    <row r="790" ht="15.0" customHeight="1"/>
+    <row r="791" ht="15.0" customHeight="1"/>
+    <row r="792" ht="15.0" customHeight="1"/>
+    <row r="793" ht="15.0" customHeight="1"/>
+    <row r="794" ht="15.0" customHeight="1"/>
+    <row r="795" ht="15.0" customHeight="1"/>
+    <row r="796" ht="15.0" customHeight="1"/>
+    <row r="797" ht="15.0" customHeight="1"/>
+    <row r="798" ht="15.0" customHeight="1"/>
+    <row r="799" ht="15.0" customHeight="1"/>
+    <row r="800" ht="15.0" customHeight="1"/>
+    <row r="801" ht="15.0" customHeight="1"/>
+    <row r="802" ht="15.0" customHeight="1"/>
+    <row r="803" ht="15.0" customHeight="1"/>
+    <row r="804" ht="15.0" customHeight="1"/>
+    <row r="805" ht="15.0" customHeight="1"/>
+    <row r="806" ht="15.0" customHeight="1"/>
+    <row r="807" ht="15.0" customHeight="1"/>
+    <row r="808" ht="15.0" customHeight="1"/>
+    <row r="809" ht="15.0" customHeight="1"/>
+    <row r="810" ht="15.0" customHeight="1"/>
+    <row r="811" ht="15.0" customHeight="1"/>
+    <row r="812" ht="15.0" customHeight="1"/>
+    <row r="813" ht="15.0" customHeight="1"/>
+    <row r="814" ht="15.0" customHeight="1"/>
+    <row r="815" ht="15.0" customHeight="1"/>
+    <row r="816" ht="15.0" customHeight="1"/>
+    <row r="817" ht="15.0" customHeight="1"/>
+    <row r="818" ht="15.0" customHeight="1"/>
+    <row r="819" ht="15.0" customHeight="1"/>
+    <row r="820" ht="15.0" customHeight="1"/>
+    <row r="821" ht="15.0" customHeight="1"/>
+    <row r="822" ht="15.0" customHeight="1"/>
+    <row r="823" ht="15.0" customHeight="1"/>
+    <row r="824" ht="15.0" customHeight="1"/>
+    <row r="825" ht="15.0" customHeight="1"/>
+    <row r="826" ht="15.0" customHeight="1"/>
+    <row r="827" ht="15.0" customHeight="1"/>
+    <row r="828" ht="15.0" customHeight="1"/>
+    <row r="829" ht="15.0" customHeight="1"/>
+    <row r="830" ht="15.0" customHeight="1"/>
+    <row r="831" ht="15.0" customHeight="1"/>
+    <row r="832" ht="15.0" customHeight="1"/>
+    <row r="833" ht="15.0" customHeight="1"/>
+    <row r="834" ht="15.0" customHeight="1"/>
+    <row r="835" ht="15.0" customHeight="1"/>
+    <row r="836" ht="15.0" customHeight="1"/>
+    <row r="837" ht="15.0" customHeight="1"/>
+    <row r="838" ht="15.0" customHeight="1"/>
+    <row r="839" ht="15.0" customHeight="1"/>
+    <row r="840" ht="15.0" customHeight="1"/>
+    <row r="841" ht="15.0" customHeight="1"/>
+    <row r="842" ht="15.0" customHeight="1"/>
+    <row r="843" ht="15.0" customHeight="1"/>
+    <row r="844" ht="15.0" customHeight="1"/>
+    <row r="845" ht="15.0" customHeight="1"/>
+    <row r="846" ht="15.0" customHeight="1"/>
+    <row r="847" ht="15.0" customHeight="1"/>
+    <row r="848" ht="15.0" customHeight="1"/>
+    <row r="849" ht="15.0" customHeight="1"/>
+    <row r="850" ht="15.0" customHeight="1"/>
+    <row r="851" ht="15.0" customHeight="1"/>
+    <row r="852" ht="15.0" customHeight="1"/>
+    <row r="853" ht="15.0" customHeight="1"/>
+    <row r="854" ht="15.0" customHeight="1"/>
+    <row r="855" ht="15.0" customHeight="1"/>
+    <row r="856" ht="15.0" customHeight="1"/>
+    <row r="857" ht="15.0" customHeight="1"/>
+    <row r="858" ht="15.0" customHeight="1"/>
+    <row r="859" ht="15.0" customHeight="1"/>
+    <row r="860" ht="15.0" customHeight="1"/>
+    <row r="861" ht="15.0" customHeight="1"/>
+    <row r="862" ht="15.0" customHeight="1"/>
+    <row r="863" ht="15.0" customHeight="1"/>
+    <row r="864" ht="15.0" customHeight="1"/>
+    <row r="865" ht="15.0" customHeight="1"/>
+    <row r="866" ht="15.0" customHeight="1"/>
+    <row r="867" ht="15.0" customHeight="1"/>
+    <row r="868" ht="15.0" customHeight="1"/>
+    <row r="869" ht="15.0" customHeight="1"/>
+    <row r="870" ht="15.0" customHeight="1"/>
+    <row r="871" ht="15.0" customHeight="1"/>
+    <row r="872" ht="15.0" customHeight="1"/>
+    <row r="873" ht="15.0" customHeight="1"/>
+    <row r="874" ht="15.0" customHeight="1"/>
+    <row r="875" ht="15.0" customHeight="1"/>
+    <row r="876" ht="15.0" customHeight="1"/>
+    <row r="877" ht="15.0" customHeight="1"/>
+    <row r="878" ht="15.0" customHeight="1"/>
+    <row r="879" ht="15.0" customHeight="1"/>
+    <row r="880" ht="15.0" customHeight="1"/>
+    <row r="881" ht="15.0" customHeight="1"/>
+    <row r="882" ht="15.0" customHeight="1"/>
+    <row r="883" ht="15.0" customHeight="1"/>
+    <row r="884" ht="15.0" customHeight="1"/>
+    <row r="885" ht="15.0" customHeight="1"/>
+    <row r="886" ht="15.0" customHeight="1"/>
+    <row r="887" ht="15.0" customHeight="1"/>
+    <row r="888" ht="15.0" customHeight="1"/>
+    <row r="889" ht="15.0" customHeight="1"/>
+    <row r="890" ht="15.0" customHeight="1"/>
+    <row r="891" ht="15.0" customHeight="1"/>
+    <row r="892" ht="15.0" customHeight="1"/>
+    <row r="893" ht="15.0" customHeight="1"/>
+    <row r="894" ht="15.0" customHeight="1"/>
+    <row r="895" ht="15.0" customHeight="1"/>
+    <row r="896" ht="15.0" customHeight="1"/>
+    <row r="897" ht="15.0" customHeight="1"/>
+    <row r="898" ht="15.0" customHeight="1"/>
+    <row r="899" ht="15.0" customHeight="1"/>
+    <row r="900" ht="15.0" customHeight="1"/>
+    <row r="901" ht="15.0" customHeight="1"/>
+    <row r="902" ht="15.0" customHeight="1"/>
+    <row r="903" ht="15.0" customHeight="1"/>
+    <row r="904" ht="15.0" customHeight="1"/>
+    <row r="905" ht="15.0" customHeight="1"/>
+    <row r="906" ht="15.0" customHeight="1"/>
+    <row r="907" ht="15.0" customHeight="1"/>
+    <row r="908" ht="15.0" customHeight="1"/>
+    <row r="909" ht="15.0" customHeight="1"/>
+    <row r="910" ht="15.0" customHeight="1"/>
+    <row r="911" ht="15.0" customHeight="1"/>
+    <row r="912" ht="15.0" customHeight="1"/>
+    <row r="913" ht="15.0" customHeight="1"/>
+    <row r="914" ht="15.0" customHeight="1"/>
+    <row r="915" ht="15.0" customHeight="1"/>
+    <row r="916" ht="15.0" customHeight="1"/>
+    <row r="917" ht="15.0" customHeight="1"/>
+    <row r="918" ht="15.0" customHeight="1"/>
+    <row r="919" ht="15.0" customHeight="1"/>
+    <row r="920" ht="15.0" customHeight="1"/>
+    <row r="921" ht="15.0" customHeight="1"/>
+    <row r="922" ht="15.0" customHeight="1"/>
+    <row r="923" ht="15.0" customHeight="1"/>
+    <row r="924" ht="15.0" customHeight="1"/>
+    <row r="925" ht="15.0" customHeight="1"/>
+    <row r="926" ht="15.0" customHeight="1"/>
+    <row r="927" ht="15.0" customHeight="1"/>
+    <row r="928" ht="15.0" customHeight="1"/>
+    <row r="929" ht="15.0" customHeight="1"/>
+    <row r="930" ht="15.0" customHeight="1"/>
+    <row r="931" ht="15.0" customHeight="1"/>
+    <row r="932" ht="15.0" customHeight="1"/>
+    <row r="933" ht="15.0" customHeight="1"/>
+    <row r="934" ht="15.0" customHeight="1"/>
+    <row r="935" ht="15.0" customHeight="1"/>
+    <row r="936" ht="15.0" customHeight="1"/>
+    <row r="937" ht="15.0" customHeight="1"/>
+    <row r="938" ht="15.0" customHeight="1"/>
+    <row r="939" ht="15.0" customHeight="1"/>
+    <row r="940" ht="15.0" customHeight="1"/>
+    <row r="941" ht="15.0" customHeight="1"/>
+    <row r="942" ht="15.0" customHeight="1"/>
+    <row r="943" ht="15.0" customHeight="1"/>
+    <row r="944" ht="15.0" customHeight="1"/>
+    <row r="945" ht="15.0" customHeight="1"/>
+    <row r="946" ht="15.0" customHeight="1"/>
+    <row r="947" ht="15.0" customHeight="1"/>
+    <row r="948" ht="15.0" customHeight="1"/>
+    <row r="949" ht="15.0" customHeight="1"/>
+    <row r="950" ht="15.0" customHeight="1"/>
+    <row r="951" ht="15.0" customHeight="1"/>
+    <row r="952" ht="15.0" customHeight="1"/>
+    <row r="953" ht="15.0" customHeight="1"/>
+    <row r="954" ht="15.0" customHeight="1"/>
+    <row r="955" ht="15.0" customHeight="1"/>
+    <row r="956" ht="15.0" customHeight="1"/>
+    <row r="957" ht="15.0" customHeight="1"/>
+    <row r="958" ht="15.0" customHeight="1"/>
+    <row r="959" ht="15.0" customHeight="1"/>
+    <row r="960" ht="15.0" customHeight="1"/>
+    <row r="961" ht="15.0" customHeight="1"/>
+    <row r="962" ht="15.0" customHeight="1"/>
+    <row r="963" ht="15.0" customHeight="1"/>
+    <row r="964" ht="15.0" customHeight="1"/>
+    <row r="965" ht="15.0" customHeight="1"/>
+    <row r="966" ht="15.0" customHeight="1"/>
+    <row r="967" ht="15.0" customHeight="1"/>
+    <row r="968" ht="15.0" customHeight="1"/>
+    <row r="969" ht="15.0" customHeight="1"/>
+    <row r="970" ht="15.0" customHeight="1"/>
+    <row r="971" ht="15.0" customHeight="1"/>
+    <row r="972" ht="15.0" customHeight="1"/>
+    <row r="973" ht="15.0" customHeight="1"/>
+    <row r="974" ht="15.0" customHeight="1"/>
+    <row r="975" ht="15.0" customHeight="1"/>
+    <row r="976" ht="15.0" customHeight="1"/>
+    <row r="977" ht="15.0" customHeight="1"/>
+    <row r="978" ht="15.0" customHeight="1"/>
+    <row r="979" ht="15.0" customHeight="1"/>
+    <row r="980" ht="15.0" customHeight="1"/>
+    <row r="981" ht="15.0" customHeight="1"/>
+    <row r="982" ht="15.0" customHeight="1"/>
+    <row r="983" ht="15.0" customHeight="1"/>
+    <row r="984" ht="15.0" customHeight="1"/>
+    <row r="985" ht="15.0" customHeight="1"/>
+    <row r="986" ht="15.0" customHeight="1"/>
+    <row r="987" ht="15.0" customHeight="1"/>
+    <row r="988" ht="15.0" customHeight="1"/>
+    <row r="989" ht="15.0" customHeight="1"/>
+    <row r="990" ht="15.0" customHeight="1"/>
+    <row r="991" ht="15.0" customHeight="1"/>
+    <row r="992" ht="15.0" customHeight="1"/>
+    <row r="993" ht="15.0" customHeight="1"/>
+    <row r="994" ht="15.0" customHeight="1"/>
+    <row r="995" ht="15.0" customHeight="1"/>
+    <row r="996" ht="15.0" customHeight="1"/>
+    <row r="997" ht="15.0" customHeight="1"/>
+    <row r="998" ht="15.0" customHeight="1"/>
+    <row r="999" ht="15.0" customHeight="1"/>
+    <row r="1000" ht="15.0" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/BlockInfo/BlockInfoTable.xlsx
+++ b/Templates/Tables/BlockInfo/BlockInfoTable.xlsx
@@ -325,7 +325,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="27" width="14.38"/>
+    <col customWidth="1" min="1" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
@@ -375,7 +375,6 @@
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -424,7 +423,6 @@
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
-      <c r="AA2" s="1"/>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1"/>
@@ -453,7 +451,6 @@
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
-      <c r="AA3" s="1"/>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1"/>
@@ -482,7 +479,6 @@
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
-      <c r="AA4" s="1"/>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1"/>
@@ -511,7 +507,6 @@
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
-      <c r="AA5" s="1"/>
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1"/>
@@ -540,7 +535,6 @@
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
-      <c r="AA6" s="1"/>
     </row>
     <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1"/>
@@ -569,7 +563,6 @@
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
-      <c r="AA7" s="1"/>
     </row>
     <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="1"/>
@@ -598,7 +591,6 @@
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
-      <c r="AA8" s="1"/>
     </row>
     <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="1"/>
@@ -627,7 +619,6 @@
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
-      <c r="AA9" s="1"/>
     </row>
     <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="1"/>
@@ -656,7 +647,6 @@
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
-      <c r="AA10" s="1"/>
     </row>
     <row r="11" ht="15.0" customHeight="1">
       <c r="A11" s="1"/>
@@ -685,7 +675,6 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
-      <c r="AA11" s="1"/>
     </row>
     <row r="12" ht="15.0" customHeight="1">
       <c r="A12" s="1"/>
@@ -714,7 +703,6 @@
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
-      <c r="AA12" s="1"/>
     </row>
     <row r="13" ht="15.0" customHeight="1">
       <c r="A13" s="1"/>
@@ -743,7 +731,6 @@
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
-      <c r="AA13" s="1"/>
     </row>
     <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="1"/>
@@ -772,7 +759,6 @@
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
-      <c r="AA14" s="1"/>
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="1"/>
@@ -801,7 +787,6 @@
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
-      <c r="AA15" s="1"/>
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="1"/>
@@ -830,7 +815,6 @@
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
-      <c r="AA16" s="1"/>
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="1"/>
@@ -859,7 +843,6 @@
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
-      <c r="AA17" s="1"/>
     </row>
     <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="1"/>
@@ -888,7 +871,6 @@
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
-      <c r="AA18" s="1"/>
     </row>
     <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="1"/>
@@ -917,7 +899,6 @@
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
-      <c r="AA19" s="1"/>
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="1"/>
@@ -946,7 +927,6 @@
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
-      <c r="AA20" s="1"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="1"/>
@@ -975,7 +955,6 @@
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
-      <c r="AA21" s="1"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1"/>
@@ -1004,7 +983,6 @@
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
-      <c r="AA22" s="1"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="1"/>
@@ -1033,7 +1011,6 @@
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
-      <c r="AA23" s="1"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="1"/>
@@ -1062,7 +1039,6 @@
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
-      <c r="AA24" s="1"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="1"/>
@@ -1091,7 +1067,6 @@
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
-      <c r="AA25" s="1"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="1"/>
@@ -1120,7 +1095,6 @@
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
-      <c r="AA26" s="1"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="1"/>
@@ -1149,7 +1123,6 @@
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
-      <c r="AA27" s="1"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="1"/>
@@ -1178,7 +1151,6 @@
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
-      <c r="AA28" s="1"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="1"/>
@@ -1207,7 +1179,6 @@
       <c r="X29" s="1"/>
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
-      <c r="AA29" s="1"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="1"/>
@@ -1236,7 +1207,6 @@
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
-      <c r="AA30" s="1"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="1"/>
@@ -1265,7 +1235,6 @@
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
-      <c r="AA31" s="1"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="1"/>
@@ -1294,7 +1263,6 @@
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
-      <c r="AA32" s="1"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="1"/>
@@ -1323,7 +1291,6 @@
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
-      <c r="AA33" s="1"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="1"/>
@@ -1352,7 +1319,6 @@
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
-      <c r="AA34" s="1"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="1"/>
@@ -1381,7 +1347,6 @@
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
-      <c r="AA35" s="1"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="1"/>
@@ -1410,7 +1375,6 @@
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
-      <c r="AA36" s="1"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="1"/>
@@ -1439,7 +1403,6 @@
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
-      <c r="AA37" s="1"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="1"/>
@@ -1468,7 +1431,6 @@
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
-      <c r="AA38" s="1"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="1"/>
@@ -1497,7 +1459,6 @@
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
-      <c r="AA39" s="1"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="1"/>
@@ -1526,7 +1487,6 @@
       <c r="X40" s="1"/>
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
-      <c r="AA40" s="1"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="1"/>
@@ -1555,7 +1515,6 @@
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
-      <c r="AA41" s="1"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="1"/>
@@ -1584,7 +1543,6 @@
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
-      <c r="AA42" s="1"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="1"/>
@@ -1613,7 +1571,6 @@
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
-      <c r="AA43" s="1"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="1"/>
@@ -1642,7 +1599,6 @@
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
-      <c r="AA44" s="1"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="1"/>
@@ -1671,7 +1627,6 @@
       <c r="X45" s="1"/>
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
-      <c r="AA45" s="1"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="1"/>
@@ -1700,7 +1655,6 @@
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
-      <c r="AA46" s="1"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="1"/>
@@ -1729,7 +1683,6 @@
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
-      <c r="AA47" s="1"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="1"/>
@@ -1758,7 +1711,6 @@
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
-      <c r="AA48" s="1"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="1"/>
@@ -1787,7 +1739,6 @@
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
-      <c r="AA49" s="1"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="1"/>
@@ -1816,7 +1767,6 @@
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
-      <c r="AA50" s="1"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="1"/>
@@ -1845,7 +1795,6 @@
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
-      <c r="AA51" s="1"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="1"/>
@@ -1874,7 +1823,6 @@
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
-      <c r="AA52" s="1"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="1"/>
@@ -1903,7 +1851,6 @@
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
-      <c r="AA53" s="1"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="1"/>
@@ -1932,7 +1879,6 @@
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
-      <c r="AA54" s="1"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="1"/>
@@ -1961,7 +1907,6 @@
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
-      <c r="AA55" s="1"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="1"/>
@@ -1990,7 +1935,6 @@
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
-      <c r="AA56" s="1"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="1"/>
@@ -2019,7 +1963,6 @@
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
-      <c r="AA57" s="1"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="1"/>
@@ -2048,7 +1991,6 @@
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
-      <c r="AA58" s="1"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="1"/>
@@ -2077,7 +2019,6 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
-      <c r="AA59" s="1"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="1"/>
@@ -2106,7 +2047,6 @@
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
-      <c r="AA60" s="1"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="1"/>
@@ -2135,7 +2075,6 @@
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
-      <c r="AA61" s="1"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="1"/>
@@ -2164,7 +2103,6 @@
       <c r="X62" s="1"/>
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
-      <c r="AA62" s="1"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="1"/>
@@ -2193,7 +2131,6 @@
       <c r="X63" s="1"/>
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
-      <c r="AA63" s="1"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="1"/>
@@ -2222,7 +2159,6 @@
       <c r="X64" s="1"/>
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
-      <c r="AA64" s="1"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="1"/>
@@ -2251,7 +2187,6 @@
       <c r="X65" s="1"/>
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
-      <c r="AA65" s="1"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="1"/>
@@ -2280,7 +2215,6 @@
       <c r="X66" s="1"/>
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
-      <c r="AA66" s="1"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="1"/>
@@ -2309,7 +2243,6 @@
       <c r="X67" s="1"/>
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
-      <c r="AA67" s="1"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="1"/>
@@ -2338,7 +2271,6 @@
       <c r="X68" s="1"/>
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
-      <c r="AA68" s="1"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="1"/>
@@ -2367,7 +2299,6 @@
       <c r="X69" s="1"/>
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
-      <c r="AA69" s="1"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="1"/>
@@ -2396,7 +2327,6 @@
       <c r="X70" s="1"/>
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
-      <c r="AA70" s="1"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="1"/>
@@ -2425,7 +2355,6 @@
       <c r="X71" s="1"/>
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
-      <c r="AA71" s="1"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="1"/>
@@ -2454,7 +2383,6 @@
       <c r="X72" s="1"/>
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
-      <c r="AA72" s="1"/>
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="1"/>
@@ -2483,7 +2411,6 @@
       <c r="X73" s="1"/>
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
-      <c r="AA73" s="1"/>
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="1"/>
@@ -2512,7 +2439,6 @@
       <c r="X74" s="1"/>
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
-      <c r="AA74" s="1"/>
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="1"/>
@@ -2541,7 +2467,6 @@
       <c r="X75" s="1"/>
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
-      <c r="AA75" s="1"/>
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="1"/>
@@ -2570,7 +2495,6 @@
       <c r="X76" s="1"/>
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
-      <c r="AA76" s="1"/>
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="1"/>
@@ -2599,7 +2523,6 @@
       <c r="X77" s="1"/>
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
-      <c r="AA77" s="1"/>
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="1"/>
@@ -2628,7 +2551,6 @@
       <c r="X78" s="1"/>
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
-      <c r="AA78" s="1"/>
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="1"/>
@@ -2657,7 +2579,6 @@
       <c r="X79" s="1"/>
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
-      <c r="AA79" s="1"/>
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="1"/>
@@ -2686,7 +2607,6 @@
       <c r="X80" s="1"/>
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
-      <c r="AA80" s="1"/>
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="1"/>
@@ -2715,7 +2635,6 @@
       <c r="X81" s="1"/>
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
-      <c r="AA81" s="1"/>
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="1"/>
@@ -2744,7 +2663,6 @@
       <c r="X82" s="1"/>
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
-      <c r="AA82" s="1"/>
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="1"/>
@@ -2773,7 +2691,6 @@
       <c r="X83" s="1"/>
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
-      <c r="AA83" s="1"/>
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="1"/>
@@ -2802,7 +2719,6 @@
       <c r="X84" s="1"/>
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
-      <c r="AA84" s="1"/>
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="1"/>
@@ -2831,7 +2747,6 @@
       <c r="X85" s="1"/>
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
-      <c r="AA85" s="1"/>
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="1"/>
@@ -2860,7 +2775,6 @@
       <c r="X86" s="1"/>
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
-      <c r="AA86" s="1"/>
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="1"/>
@@ -2889,7 +2803,6 @@
       <c r="X87" s="1"/>
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
-      <c r="AA87" s="1"/>
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="1"/>
@@ -2918,7 +2831,6 @@
       <c r="X88" s="1"/>
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
-      <c r="AA88" s="1"/>
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="1"/>
@@ -2947,7 +2859,6 @@
       <c r="X89" s="1"/>
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
-      <c r="AA89" s="1"/>
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="1"/>
@@ -2976,7 +2887,6 @@
       <c r="X90" s="1"/>
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
-      <c r="AA90" s="1"/>
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="1"/>
@@ -3005,7 +2915,6 @@
       <c r="X91" s="1"/>
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
-      <c r="AA91" s="1"/>
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="1"/>
@@ -3034,7 +2943,6 @@
       <c r="X92" s="1"/>
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
-      <c r="AA92" s="1"/>
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="1"/>
@@ -3063,7 +2971,6 @@
       <c r="X93" s="1"/>
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
-      <c r="AA93" s="1"/>
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="1"/>
@@ -3092,7 +2999,6 @@
       <c r="X94" s="1"/>
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
-      <c r="AA94" s="1"/>
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="1"/>
@@ -3121,7 +3027,6 @@
       <c r="X95" s="1"/>
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
-      <c r="AA95" s="1"/>
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="1"/>
@@ -3150,7 +3055,6 @@
       <c r="X96" s="1"/>
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
-      <c r="AA96" s="1"/>
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="1"/>
@@ -3179,7 +3083,6 @@
       <c r="X97" s="1"/>
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
-      <c r="AA97" s="1"/>
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="1"/>
@@ -3208,7 +3111,6 @@
       <c r="X98" s="1"/>
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
-      <c r="AA98" s="1"/>
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="1"/>
@@ -3237,7 +3139,6 @@
       <c r="X99" s="1"/>
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
-      <c r="AA99" s="1"/>
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="1"/>
@@ -3266,7 +3167,6 @@
       <c r="X100" s="1"/>
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
-      <c r="AA100" s="1"/>
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="1"/>
@@ -3295,7 +3195,6 @@
       <c r="X101" s="1"/>
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
-      <c r="AA101" s="1"/>
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="1"/>
@@ -3324,7 +3223,6 @@
       <c r="X102" s="1"/>
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
-      <c r="AA102" s="1"/>
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="1"/>
@@ -3353,7 +3251,6 @@
       <c r="X103" s="1"/>
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
-      <c r="AA103" s="1"/>
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="1"/>
@@ -3382,7 +3279,6 @@
       <c r="X104" s="1"/>
       <c r="Y104" s="1"/>
       <c r="Z104" s="1"/>
-      <c r="AA104" s="1"/>
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="1"/>
@@ -3411,7 +3307,6 @@
       <c r="X105" s="1"/>
       <c r="Y105" s="1"/>
       <c r="Z105" s="1"/>
-      <c r="AA105" s="1"/>
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="1"/>
@@ -3440,7 +3335,6 @@
       <c r="X106" s="1"/>
       <c r="Y106" s="1"/>
       <c r="Z106" s="1"/>
-      <c r="AA106" s="1"/>
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="1"/>
@@ -3469,7 +3363,6 @@
       <c r="X107" s="1"/>
       <c r="Y107" s="1"/>
       <c r="Z107" s="1"/>
-      <c r="AA107" s="1"/>
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="1"/>
@@ -3498,7 +3391,6 @@
       <c r="X108" s="1"/>
       <c r="Y108" s="1"/>
       <c r="Z108" s="1"/>
-      <c r="AA108" s="1"/>
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="1"/>
@@ -3527,7 +3419,6 @@
       <c r="X109" s="1"/>
       <c r="Y109" s="1"/>
       <c r="Z109" s="1"/>
-      <c r="AA109" s="1"/>
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="1"/>
@@ -3556,7 +3447,6 @@
       <c r="X110" s="1"/>
       <c r="Y110" s="1"/>
       <c r="Z110" s="1"/>
-      <c r="AA110" s="1"/>
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="1"/>
@@ -3585,7 +3475,6 @@
       <c r="X111" s="1"/>
       <c r="Y111" s="1"/>
       <c r="Z111" s="1"/>
-      <c r="AA111" s="1"/>
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="1"/>
@@ -3614,7 +3503,6 @@
       <c r="X112" s="1"/>
       <c r="Y112" s="1"/>
       <c r="Z112" s="1"/>
-      <c r="AA112" s="1"/>
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="1"/>
@@ -3643,7 +3531,6 @@
       <c r="X113" s="1"/>
       <c r="Y113" s="1"/>
       <c r="Z113" s="1"/>
-      <c r="AA113" s="1"/>
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="1"/>
@@ -3672,7 +3559,6 @@
       <c r="X114" s="1"/>
       <c r="Y114" s="1"/>
       <c r="Z114" s="1"/>
-      <c r="AA114" s="1"/>
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="1"/>
@@ -3701,7 +3587,6 @@
       <c r="X115" s="1"/>
       <c r="Y115" s="1"/>
       <c r="Z115" s="1"/>
-      <c r="AA115" s="1"/>
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="1"/>
@@ -3730,7 +3615,6 @@
       <c r="X116" s="1"/>
       <c r="Y116" s="1"/>
       <c r="Z116" s="1"/>
-      <c r="AA116" s="1"/>
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="1"/>
@@ -3759,7 +3643,6 @@
       <c r="X117" s="1"/>
       <c r="Y117" s="1"/>
       <c r="Z117" s="1"/>
-      <c r="AA117" s="1"/>
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="1"/>
@@ -3788,7 +3671,6 @@
       <c r="X118" s="1"/>
       <c r="Y118" s="1"/>
       <c r="Z118" s="1"/>
-      <c r="AA118" s="1"/>
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="1"/>
@@ -3817,7 +3699,6 @@
       <c r="X119" s="1"/>
       <c r="Y119" s="1"/>
       <c r="Z119" s="1"/>
-      <c r="AA119" s="1"/>
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="1"/>
@@ -3846,7 +3727,6 @@
       <c r="X120" s="1"/>
       <c r="Y120" s="1"/>
       <c r="Z120" s="1"/>
-      <c r="AA120" s="1"/>
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="1"/>
@@ -3875,7 +3755,6 @@
       <c r="X121" s="1"/>
       <c r="Y121" s="1"/>
       <c r="Z121" s="1"/>
-      <c r="AA121" s="1"/>
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="1"/>
@@ -3904,7 +3783,6 @@
       <c r="X122" s="1"/>
       <c r="Y122" s="1"/>
       <c r="Z122" s="1"/>
-      <c r="AA122" s="1"/>
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="1"/>
@@ -3933,7 +3811,6 @@
       <c r="X123" s="1"/>
       <c r="Y123" s="1"/>
       <c r="Z123" s="1"/>
-      <c r="AA123" s="1"/>
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="1"/>
@@ -3962,7 +3839,6 @@
       <c r="X124" s="1"/>
       <c r="Y124" s="1"/>
       <c r="Z124" s="1"/>
-      <c r="AA124" s="1"/>
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="1"/>
@@ -3991,7 +3867,6 @@
       <c r="X125" s="1"/>
       <c r="Y125" s="1"/>
       <c r="Z125" s="1"/>
-      <c r="AA125" s="1"/>
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="1"/>
@@ -4020,7 +3895,6 @@
       <c r="X126" s="1"/>
       <c r="Y126" s="1"/>
       <c r="Z126" s="1"/>
-      <c r="AA126" s="1"/>
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="1"/>
@@ -4049,7 +3923,6 @@
       <c r="X127" s="1"/>
       <c r="Y127" s="1"/>
       <c r="Z127" s="1"/>
-      <c r="AA127" s="1"/>
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="1"/>
@@ -4078,7 +3951,6 @@
       <c r="X128" s="1"/>
       <c r="Y128" s="1"/>
       <c r="Z128" s="1"/>
-      <c r="AA128" s="1"/>
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="1"/>
@@ -4107,7 +3979,6 @@
       <c r="X129" s="1"/>
       <c r="Y129" s="1"/>
       <c r="Z129" s="1"/>
-      <c r="AA129" s="1"/>
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="1"/>
@@ -4136,7 +4007,6 @@
       <c r="X130" s="1"/>
       <c r="Y130" s="1"/>
       <c r="Z130" s="1"/>
-      <c r="AA130" s="1"/>
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="1"/>
@@ -4165,7 +4035,6 @@
       <c r="X131" s="1"/>
       <c r="Y131" s="1"/>
       <c r="Z131" s="1"/>
-      <c r="AA131" s="1"/>
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="1"/>
@@ -4194,7 +4063,6 @@
       <c r="X132" s="1"/>
       <c r="Y132" s="1"/>
       <c r="Z132" s="1"/>
-      <c r="AA132" s="1"/>
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="1"/>
@@ -4223,7 +4091,6 @@
       <c r="X133" s="1"/>
       <c r="Y133" s="1"/>
       <c r="Z133" s="1"/>
-      <c r="AA133" s="1"/>
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="1"/>
@@ -4252,7 +4119,6 @@
       <c r="X134" s="1"/>
       <c r="Y134" s="1"/>
       <c r="Z134" s="1"/>
-      <c r="AA134" s="1"/>
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="1"/>
@@ -4281,7 +4147,6 @@
       <c r="X135" s="1"/>
       <c r="Y135" s="1"/>
       <c r="Z135" s="1"/>
-      <c r="AA135" s="1"/>
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="1"/>
@@ -4310,7 +4175,6 @@
       <c r="X136" s="1"/>
       <c r="Y136" s="1"/>
       <c r="Z136" s="1"/>
-      <c r="AA136" s="1"/>
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="1"/>
@@ -4339,7 +4203,6 @@
       <c r="X137" s="1"/>
       <c r="Y137" s="1"/>
       <c r="Z137" s="1"/>
-      <c r="AA137" s="1"/>
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="1"/>
@@ -4368,7 +4231,6 @@
       <c r="X138" s="1"/>
       <c r="Y138" s="1"/>
       <c r="Z138" s="1"/>
-      <c r="AA138" s="1"/>
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="1"/>
@@ -4397,7 +4259,6 @@
       <c r="X139" s="1"/>
       <c r="Y139" s="1"/>
       <c r="Z139" s="1"/>
-      <c r="AA139" s="1"/>
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="1"/>
@@ -4426,7 +4287,6 @@
       <c r="X140" s="1"/>
       <c r="Y140" s="1"/>
       <c r="Z140" s="1"/>
-      <c r="AA140" s="1"/>
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="1"/>
@@ -4455,7 +4315,6 @@
       <c r="X141" s="1"/>
       <c r="Y141" s="1"/>
       <c r="Z141" s="1"/>
-      <c r="AA141" s="1"/>
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="1"/>
@@ -4484,7 +4343,6 @@
       <c r="X142" s="1"/>
       <c r="Y142" s="1"/>
       <c r="Z142" s="1"/>
-      <c r="AA142" s="1"/>
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="1"/>
@@ -4513,7 +4371,6 @@
       <c r="X143" s="1"/>
       <c r="Y143" s="1"/>
       <c r="Z143" s="1"/>
-      <c r="AA143" s="1"/>
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="1"/>
@@ -4542,7 +4399,6 @@
       <c r="X144" s="1"/>
       <c r="Y144" s="1"/>
       <c r="Z144" s="1"/>
-      <c r="AA144" s="1"/>
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="1"/>
@@ -4571,7 +4427,6 @@
       <c r="X145" s="1"/>
       <c r="Y145" s="1"/>
       <c r="Z145" s="1"/>
-      <c r="AA145" s="1"/>
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="1"/>
@@ -4600,7 +4455,6 @@
       <c r="X146" s="1"/>
       <c r="Y146" s="1"/>
       <c r="Z146" s="1"/>
-      <c r="AA146" s="1"/>
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="1"/>
@@ -4629,7 +4483,6 @@
       <c r="X147" s="1"/>
       <c r="Y147" s="1"/>
       <c r="Z147" s="1"/>
-      <c r="AA147" s="1"/>
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="1"/>
@@ -4658,7 +4511,6 @@
       <c r="X148" s="1"/>
       <c r="Y148" s="1"/>
       <c r="Z148" s="1"/>
-      <c r="AA148" s="1"/>
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="1"/>
@@ -4687,7 +4539,6 @@
       <c r="X149" s="1"/>
       <c r="Y149" s="1"/>
       <c r="Z149" s="1"/>
-      <c r="AA149" s="1"/>
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="1"/>
@@ -4716,7 +4567,6 @@
       <c r="X150" s="1"/>
       <c r="Y150" s="1"/>
       <c r="Z150" s="1"/>
-      <c r="AA150" s="1"/>
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="1"/>
@@ -4745,7 +4595,6 @@
       <c r="X151" s="1"/>
       <c r="Y151" s="1"/>
       <c r="Z151" s="1"/>
-      <c r="AA151" s="1"/>
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="1"/>
@@ -4774,7 +4623,6 @@
       <c r="X152" s="1"/>
       <c r="Y152" s="1"/>
       <c r="Z152" s="1"/>
-      <c r="AA152" s="1"/>
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="1"/>
@@ -4803,7 +4651,6 @@
       <c r="X153" s="1"/>
       <c r="Y153" s="1"/>
       <c r="Z153" s="1"/>
-      <c r="AA153" s="1"/>
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="1"/>
@@ -4832,7 +4679,6 @@
       <c r="X154" s="1"/>
       <c r="Y154" s="1"/>
       <c r="Z154" s="1"/>
-      <c r="AA154" s="1"/>
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="1"/>
@@ -4861,7 +4707,6 @@
       <c r="X155" s="1"/>
       <c r="Y155" s="1"/>
       <c r="Z155" s="1"/>
-      <c r="AA155" s="1"/>
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="1"/>
@@ -4890,7 +4735,6 @@
       <c r="X156" s="1"/>
       <c r="Y156" s="1"/>
       <c r="Z156" s="1"/>
-      <c r="AA156" s="1"/>
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="1"/>
@@ -4919,7 +4763,6 @@
       <c r="X157" s="1"/>
       <c r="Y157" s="1"/>
       <c r="Z157" s="1"/>
-      <c r="AA157" s="1"/>
     </row>
     <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="1"/>
@@ -4948,7 +4791,6 @@
       <c r="X158" s="1"/>
       <c r="Y158" s="1"/>
       <c r="Z158" s="1"/>
-      <c r="AA158" s="1"/>
     </row>
     <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="1"/>
@@ -4977,7 +4819,6 @@
       <c r="X159" s="1"/>
       <c r="Y159" s="1"/>
       <c r="Z159" s="1"/>
-      <c r="AA159" s="1"/>
     </row>
     <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="1"/>
@@ -5006,7 +4847,6 @@
       <c r="X160" s="1"/>
       <c r="Y160" s="1"/>
       <c r="Z160" s="1"/>
-      <c r="AA160" s="1"/>
     </row>
     <row r="161" ht="15.0" customHeight="1">
       <c r="A161" s="1"/>
@@ -5035,7 +4875,6 @@
       <c r="X161" s="1"/>
       <c r="Y161" s="1"/>
       <c r="Z161" s="1"/>
-      <c r="AA161" s="1"/>
     </row>
     <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="1"/>
@@ -5064,7 +4903,6 @@
       <c r="X162" s="1"/>
       <c r="Y162" s="1"/>
       <c r="Z162" s="1"/>
-      <c r="AA162" s="1"/>
     </row>
     <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="1"/>
@@ -5093,7 +4931,6 @@
       <c r="X163" s="1"/>
       <c r="Y163" s="1"/>
       <c r="Z163" s="1"/>
-      <c r="AA163" s="1"/>
     </row>
     <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="1"/>
@@ -5122,7 +4959,6 @@
       <c r="X164" s="1"/>
       <c r="Y164" s="1"/>
       <c r="Z164" s="1"/>
-      <c r="AA164" s="1"/>
     </row>
     <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="1"/>
@@ -5151,7 +4987,6 @@
       <c r="X165" s="1"/>
       <c r="Y165" s="1"/>
       <c r="Z165" s="1"/>
-      <c r="AA165" s="1"/>
     </row>
     <row r="166" ht="15.0" customHeight="1">
       <c r="A166" s="1"/>
@@ -5180,7 +5015,6 @@
       <c r="X166" s="1"/>
       <c r="Y166" s="1"/>
       <c r="Z166" s="1"/>
-      <c r="AA166" s="1"/>
     </row>
     <row r="167" ht="15.0" customHeight="1">
       <c r="A167" s="1"/>
@@ -5209,7 +5043,6 @@
       <c r="X167" s="1"/>
       <c r="Y167" s="1"/>
       <c r="Z167" s="1"/>
-      <c r="AA167" s="1"/>
     </row>
     <row r="168" ht="15.0" customHeight="1">
       <c r="A168" s="1"/>
@@ -5238,7 +5071,6 @@
       <c r="X168" s="1"/>
       <c r="Y168" s="1"/>
       <c r="Z168" s="1"/>
-      <c r="AA168" s="1"/>
     </row>
     <row r="169" ht="15.0" customHeight="1">
       <c r="A169" s="1"/>
@@ -5267,7 +5099,6 @@
       <c r="X169" s="1"/>
       <c r="Y169" s="1"/>
       <c r="Z169" s="1"/>
-      <c r="AA169" s="1"/>
     </row>
     <row r="170" ht="15.0" customHeight="1">
       <c r="A170" s="1"/>
@@ -5296,7 +5127,6 @@
       <c r="X170" s="1"/>
       <c r="Y170" s="1"/>
       <c r="Z170" s="1"/>
-      <c r="AA170" s="1"/>
     </row>
     <row r="171" ht="15.0" customHeight="1">
       <c r="A171" s="1"/>
@@ -5325,7 +5155,6 @@
       <c r="X171" s="1"/>
       <c r="Y171" s="1"/>
       <c r="Z171" s="1"/>
-      <c r="AA171" s="1"/>
     </row>
     <row r="172" ht="15.0" customHeight="1">
       <c r="A172" s="1"/>
@@ -5354,7 +5183,6 @@
       <c r="X172" s="1"/>
       <c r="Y172" s="1"/>
       <c r="Z172" s="1"/>
-      <c r="AA172" s="1"/>
     </row>
     <row r="173" ht="15.0" customHeight="1">
       <c r="A173" s="1"/>
@@ -5383,7 +5211,6 @@
       <c r="X173" s="1"/>
       <c r="Y173" s="1"/>
       <c r="Z173" s="1"/>
-      <c r="AA173" s="1"/>
     </row>
     <row r="174" ht="15.0" customHeight="1">
       <c r="A174" s="1"/>
@@ -5412,7 +5239,6 @@
       <c r="X174" s="1"/>
       <c r="Y174" s="1"/>
       <c r="Z174" s="1"/>
-      <c r="AA174" s="1"/>
     </row>
     <row r="175" ht="15.0" customHeight="1">
       <c r="A175" s="1"/>
@@ -5441,7 +5267,6 @@
       <c r="X175" s="1"/>
       <c r="Y175" s="1"/>
       <c r="Z175" s="1"/>
-      <c r="AA175" s="1"/>
     </row>
     <row r="176" ht="15.0" customHeight="1">
       <c r="A176" s="1"/>
@@ -5470,7 +5295,6 @@
       <c r="X176" s="1"/>
       <c r="Y176" s="1"/>
       <c r="Z176" s="1"/>
-      <c r="AA176" s="1"/>
     </row>
     <row r="177" ht="15.0" customHeight="1">
       <c r="A177" s="1"/>
@@ -5499,7 +5323,6 @@
       <c r="X177" s="1"/>
       <c r="Y177" s="1"/>
       <c r="Z177" s="1"/>
-      <c r="AA177" s="1"/>
     </row>
     <row r="178" ht="15.0" customHeight="1">
       <c r="A178" s="1"/>
@@ -5528,7 +5351,6 @@
       <c r="X178" s="1"/>
       <c r="Y178" s="1"/>
       <c r="Z178" s="1"/>
-      <c r="AA178" s="1"/>
     </row>
     <row r="179" ht="15.0" customHeight="1">
       <c r="A179" s="1"/>
@@ -5557,7 +5379,6 @@
       <c r="X179" s="1"/>
       <c r="Y179" s="1"/>
       <c r="Z179" s="1"/>
-      <c r="AA179" s="1"/>
     </row>
     <row r="180" ht="15.0" customHeight="1">
       <c r="A180" s="1"/>
@@ -5586,7 +5407,6 @@
       <c r="X180" s="1"/>
       <c r="Y180" s="1"/>
       <c r="Z180" s="1"/>
-      <c r="AA180" s="1"/>
     </row>
     <row r="181" ht="15.0" customHeight="1">
       <c r="A181" s="1"/>
@@ -5615,7 +5435,6 @@
       <c r="X181" s="1"/>
       <c r="Y181" s="1"/>
       <c r="Z181" s="1"/>
-      <c r="AA181" s="1"/>
     </row>
     <row r="182" ht="15.0" customHeight="1">
       <c r="A182" s="1"/>
@@ -5644,7 +5463,6 @@
       <c r="X182" s="1"/>
       <c r="Y182" s="1"/>
       <c r="Z182" s="1"/>
-      <c r="AA182" s="1"/>
     </row>
     <row r="183" ht="15.0" customHeight="1">
       <c r="A183" s="1"/>
@@ -5673,7 +5491,6 @@
       <c r="X183" s="1"/>
       <c r="Y183" s="1"/>
       <c r="Z183" s="1"/>
-      <c r="AA183" s="1"/>
     </row>
     <row r="184" ht="15.0" customHeight="1">
       <c r="A184" s="1"/>
@@ -5702,7 +5519,6 @@
       <c r="X184" s="1"/>
       <c r="Y184" s="1"/>
       <c r="Z184" s="1"/>
-      <c r="AA184" s="1"/>
     </row>
     <row r="185" ht="15.0" customHeight="1">
       <c r="A185" s="1"/>
@@ -5731,7 +5547,6 @@
       <c r="X185" s="1"/>
       <c r="Y185" s="1"/>
       <c r="Z185" s="1"/>
-      <c r="AA185" s="1"/>
     </row>
     <row r="186" ht="15.0" customHeight="1">
       <c r="A186" s="1"/>
@@ -5760,7 +5575,6 @@
       <c r="X186" s="1"/>
       <c r="Y186" s="1"/>
       <c r="Z186" s="1"/>
-      <c r="AA186" s="1"/>
     </row>
     <row r="187" ht="15.0" customHeight="1">
       <c r="A187" s="1"/>
@@ -5789,7 +5603,6 @@
       <c r="X187" s="1"/>
       <c r="Y187" s="1"/>
       <c r="Z187" s="1"/>
-      <c r="AA187" s="1"/>
     </row>
     <row r="188" ht="15.0" customHeight="1">
       <c r="A188" s="1"/>
@@ -5818,7 +5631,6 @@
       <c r="X188" s="1"/>
       <c r="Y188" s="1"/>
       <c r="Z188" s="1"/>
-      <c r="AA188" s="1"/>
     </row>
     <row r="189" ht="15.0" customHeight="1">
       <c r="A189" s="1"/>
@@ -5847,7 +5659,6 @@
       <c r="X189" s="1"/>
       <c r="Y189" s="1"/>
       <c r="Z189" s="1"/>
-      <c r="AA189" s="1"/>
     </row>
     <row r="190" ht="15.0" customHeight="1">
       <c r="A190" s="1"/>
@@ -5876,7 +5687,6 @@
       <c r="X190" s="1"/>
       <c r="Y190" s="1"/>
       <c r="Z190" s="1"/>
-      <c r="AA190" s="1"/>
     </row>
     <row r="191" ht="15.0" customHeight="1">
       <c r="A191" s="1"/>
@@ -5905,7 +5715,6 @@
       <c r="X191" s="1"/>
       <c r="Y191" s="1"/>
       <c r="Z191" s="1"/>
-      <c r="AA191" s="1"/>
     </row>
     <row r="192" ht="15.0" customHeight="1">
       <c r="A192" s="1"/>
@@ -5934,7 +5743,6 @@
       <c r="X192" s="1"/>
       <c r="Y192" s="1"/>
       <c r="Z192" s="1"/>
-      <c r="AA192" s="1"/>
     </row>
     <row r="193" ht="15.0" customHeight="1">
       <c r="A193" s="1"/>
@@ -5963,7 +5771,6 @@
       <c r="X193" s="1"/>
       <c r="Y193" s="1"/>
       <c r="Z193" s="1"/>
-      <c r="AA193" s="1"/>
     </row>
     <row r="194" ht="15.0" customHeight="1">
       <c r="A194" s="1"/>
@@ -5992,7 +5799,6 @@
       <c r="X194" s="1"/>
       <c r="Y194" s="1"/>
       <c r="Z194" s="1"/>
-      <c r="AA194" s="1"/>
     </row>
     <row r="195" ht="15.0" customHeight="1">
       <c r="A195" s="1"/>
@@ -6021,7 +5827,6 @@
       <c r="X195" s="1"/>
       <c r="Y195" s="1"/>
       <c r="Z195" s="1"/>
-      <c r="AA195" s="1"/>
     </row>
     <row r="196" ht="15.0" customHeight="1">
       <c r="A196" s="1"/>
@@ -6050,7 +5855,6 @@
       <c r="X196" s="1"/>
       <c r="Y196" s="1"/>
       <c r="Z196" s="1"/>
-      <c r="AA196" s="1"/>
     </row>
     <row r="197" ht="15.0" customHeight="1">
       <c r="A197" s="1"/>
@@ -6079,7 +5883,6 @@
       <c r="X197" s="1"/>
       <c r="Y197" s="1"/>
       <c r="Z197" s="1"/>
-      <c r="AA197" s="1"/>
     </row>
     <row r="198" ht="15.0" customHeight="1">
       <c r="A198" s="1"/>
@@ -6108,7 +5911,6 @@
       <c r="X198" s="1"/>
       <c r="Y198" s="1"/>
       <c r="Z198" s="1"/>
-      <c r="AA198" s="1"/>
     </row>
     <row r="199" ht="15.0" customHeight="1">
       <c r="A199" s="1"/>
@@ -6137,7 +5939,6 @@
       <c r="X199" s="1"/>
       <c r="Y199" s="1"/>
       <c r="Z199" s="1"/>
-      <c r="AA199" s="1"/>
     </row>
     <row r="200" ht="15.0" customHeight="1">
       <c r="A200" s="1"/>
@@ -6166,7 +5967,6 @@
       <c r="X200" s="1"/>
       <c r="Y200" s="1"/>
       <c r="Z200" s="1"/>
-      <c r="AA200" s="1"/>
     </row>
     <row r="201" ht="15.0" customHeight="1">
       <c r="A201" s="1"/>
@@ -6195,7 +5995,6 @@
       <c r="X201" s="1"/>
       <c r="Y201" s="1"/>
       <c r="Z201" s="1"/>
-      <c r="AA201" s="1"/>
     </row>
     <row r="202" ht="15.0" customHeight="1">
       <c r="A202" s="1"/>
@@ -6224,7 +6023,6 @@
       <c r="X202" s="1"/>
       <c r="Y202" s="1"/>
       <c r="Z202" s="1"/>
-      <c r="AA202" s="1"/>
     </row>
     <row r="203" ht="15.0" customHeight="1">
       <c r="A203" s="1"/>
@@ -6253,7 +6051,6 @@
       <c r="X203" s="1"/>
       <c r="Y203" s="1"/>
       <c r="Z203" s="1"/>
-      <c r="AA203" s="1"/>
     </row>
     <row r="204" ht="15.0" customHeight="1">
       <c r="A204" s="1"/>
@@ -6282,7 +6079,6 @@
       <c r="X204" s="1"/>
       <c r="Y204" s="1"/>
       <c r="Z204" s="1"/>
-      <c r="AA204" s="1"/>
     </row>
     <row r="205" ht="15.0" customHeight="1">
       <c r="A205" s="1"/>
@@ -6311,7 +6107,6 @@
       <c r="X205" s="1"/>
       <c r="Y205" s="1"/>
       <c r="Z205" s="1"/>
-      <c r="AA205" s="1"/>
     </row>
     <row r="206" ht="15.0" customHeight="1">
       <c r="A206" s="1"/>
@@ -6340,7 +6135,6 @@
       <c r="X206" s="1"/>
       <c r="Y206" s="1"/>
       <c r="Z206" s="1"/>
-      <c r="AA206" s="1"/>
     </row>
     <row r="207" ht="15.0" customHeight="1">
       <c r="A207" s="1"/>
@@ -6369,7 +6163,6 @@
       <c r="X207" s="1"/>
       <c r="Y207" s="1"/>
       <c r="Z207" s="1"/>
-      <c r="AA207" s="1"/>
     </row>
     <row r="208" ht="15.0" customHeight="1">
       <c r="A208" s="1"/>
@@ -6398,7 +6191,6 @@
       <c r="X208" s="1"/>
       <c r="Y208" s="1"/>
       <c r="Z208" s="1"/>
-      <c r="AA208" s="1"/>
     </row>
     <row r="209" ht="15.0" customHeight="1">
       <c r="A209" s="1"/>
@@ -6427,7 +6219,6 @@
       <c r="X209" s="1"/>
       <c r="Y209" s="1"/>
       <c r="Z209" s="1"/>
-      <c r="AA209" s="1"/>
     </row>
     <row r="210" ht="15.0" customHeight="1">
       <c r="A210" s="1"/>
@@ -6456,7 +6247,6 @@
       <c r="X210" s="1"/>
       <c r="Y210" s="1"/>
       <c r="Z210" s="1"/>
-      <c r="AA210" s="1"/>
     </row>
     <row r="211" ht="15.0" customHeight="1">
       <c r="A211" s="1"/>
@@ -6485,7 +6275,6 @@
       <c r="X211" s="1"/>
       <c r="Y211" s="1"/>
       <c r="Z211" s="1"/>
-      <c r="AA211" s="1"/>
     </row>
     <row r="212" ht="15.0" customHeight="1">
       <c r="A212" s="1"/>
@@ -6514,7 +6303,6 @@
       <c r="X212" s="1"/>
       <c r="Y212" s="1"/>
       <c r="Z212" s="1"/>
-      <c r="AA212" s="1"/>
     </row>
     <row r="213" ht="15.0" customHeight="1">
       <c r="A213" s="1"/>
@@ -6543,7 +6331,6 @@
       <c r="X213" s="1"/>
       <c r="Y213" s="1"/>
       <c r="Z213" s="1"/>
-      <c r="AA213" s="1"/>
     </row>
     <row r="214" ht="15.0" customHeight="1">
       <c r="A214" s="1"/>
@@ -6572,7 +6359,6 @@
       <c r="X214" s="1"/>
       <c r="Y214" s="1"/>
       <c r="Z214" s="1"/>
-      <c r="AA214" s="1"/>
     </row>
     <row r="215" ht="15.0" customHeight="1">
       <c r="A215" s="1"/>
@@ -6601,7 +6387,6 @@
       <c r="X215" s="1"/>
       <c r="Y215" s="1"/>
       <c r="Z215" s="1"/>
-      <c r="AA215" s="1"/>
     </row>
     <row r="216" ht="15.0" customHeight="1">
       <c r="A216" s="1"/>
@@ -6630,7 +6415,6 @@
       <c r="X216" s="1"/>
       <c r="Y216" s="1"/>
       <c r="Z216" s="1"/>
-      <c r="AA216" s="1"/>
     </row>
     <row r="217" ht="15.0" customHeight="1">
       <c r="A217" s="1"/>
@@ -6659,7 +6443,6 @@
       <c r="X217" s="1"/>
       <c r="Y217" s="1"/>
       <c r="Z217" s="1"/>
-      <c r="AA217" s="1"/>
     </row>
     <row r="218" ht="15.0" customHeight="1">
       <c r="A218" s="1"/>
@@ -6688,7 +6471,6 @@
       <c r="X218" s="1"/>
       <c r="Y218" s="1"/>
       <c r="Z218" s="1"/>
-      <c r="AA218" s="1"/>
     </row>
     <row r="219" ht="15.0" customHeight="1">
       <c r="A219" s="1"/>
@@ -6717,7 +6499,6 @@
       <c r="X219" s="1"/>
       <c r="Y219" s="1"/>
       <c r="Z219" s="1"/>
-      <c r="AA219" s="1"/>
     </row>
     <row r="220" ht="15.0" customHeight="1">
       <c r="A220" s="1"/>
@@ -6746,7 +6527,6 @@
       <c r="X220" s="1"/>
       <c r="Y220" s="1"/>
       <c r="Z220" s="1"/>
-      <c r="AA220" s="1"/>
     </row>
     <row r="221" ht="15.0" customHeight="1"/>
     <row r="222" ht="15.0" customHeight="1"/>
